--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD4CC5A-B5AA-45C6-8F51-FC9C0C2DD473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17513DC6-9B5E-4AF4-B77C-9CA409FD2735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="109">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -995,64 +995,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C6" s="5">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D6" s="5">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E6" s="5">
-        <v>6254.26</v>
+        <v>7442.5599999999904</v>
       </c>
       <c r="F6" s="5">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G6" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" s="5">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="I6" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" s="5">
-        <v>260.59416666666601</v>
+        <v>206.73777777777701</v>
       </c>
       <c r="L6" s="5">
-        <v>1250.8520000000001</v>
+        <v>744.25599999999997</v>
       </c>
       <c r="M6" s="5">
-        <v>-100</v>
+        <v>175.41598589732499</v>
       </c>
       <c r="N6" s="6">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="O6" s="6">
-        <v>11884.34</v>
+        <v>14779.67</v>
       </c>
       <c r="P6" s="6">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="Q6" s="6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R6" s="6">
         <v>2</v>
       </c>
       <c r="S6" s="6">
-        <v>191.682903225806</v>
+        <v>202.46123287671199</v>
       </c>
       <c r="T6" s="6">
-        <v>1080.3945454545401</v>
+        <v>985.31133333333298</v>
       </c>
       <c r="U6" s="6">
-        <v>-25.919403180992798</v>
+        <v>-40.4317552421671</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1079,7 +1079,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1087,64 +1087,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C7" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" s="5">
+        <v>25</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1293.1099999999999</v>
+      </c>
+      <c r="F7" s="5">
         <v>20</v>
       </c>
-      <c r="E7" s="5">
-        <v>1089.06</v>
-      </c>
-      <c r="F7" s="5">
-        <v>16</v>
-      </c>
       <c r="G7" s="5">
         <v>1</v>
       </c>
       <c r="H7" s="5">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5">
+        <v>4</v>
+      </c>
+      <c r="J7" s="5">
         <v>2</v>
       </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
       <c r="K7" s="5">
-        <v>68.066249999999997</v>
+        <v>64.655499999999904</v>
       </c>
       <c r="L7" s="5">
-        <v>544.53</v>
+        <v>323.27749999999997</v>
       </c>
       <c r="M7" s="5">
-        <v>-100</v>
+        <v>880.73636426908695</v>
       </c>
       <c r="N7" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O7" s="6">
-        <v>3052.72</v>
+        <v>3803.22</v>
       </c>
       <c r="P7" s="6">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q7" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" s="6">
         <v>2</v>
       </c>
       <c r="S7" s="6">
-        <v>122.10879999999899</v>
+        <v>135.82928571428499</v>
       </c>
       <c r="T7" s="6">
-        <v>1526.36</v>
+        <v>1267.74</v>
       </c>
       <c r="U7" s="6">
-        <v>188.39821536203701</v>
+        <v>131.48779192368499</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1171,7 +1171,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1179,30 +1179,44 @@
         <v>26</v>
       </c>
       <c r="B8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="5">
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>398.53</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+        <v>501.47</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>501.47</v>
+      </c>
       <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
+      <c r="M8" s="5">
+        <v>-100</v>
+      </c>
       <c r="N8" s="6">
         <v>1</v>
       </c>
       <c r="O8" s="6">
-        <v>431.66</v>
+        <v>530.63</v>
       </c>
       <c r="P8" s="6">
         <v>2</v>
@@ -1214,10 +1228,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>215.83</v>
+        <v>265.315</v>
       </c>
       <c r="T8" s="6">
-        <v>431.66</v>
+        <v>530.63</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1247,7 +1261,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1255,49 +1269,49 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="5">
         <v>3</v>
       </c>
       <c r="D9" s="5">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1567.42</v>
+      </c>
+      <c r="F9" s="5">
+        <v>5</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>4</v>
+      </c>
+      <c r="I9" s="5">
         <v>2</v>
       </c>
-      <c r="E9" s="5">
-        <v>1415.7</v>
-      </c>
-      <c r="F9" s="5">
-        <v>4</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>3</v>
-      </c>
-      <c r="I9" s="5">
-        <v>1</v>
-      </c>
       <c r="J9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>353.92500000000001</v>
+        <v>313.48399999999998</v>
       </c>
       <c r="L9" s="5">
-        <v>1415.7</v>
+        <v>783.71</v>
       </c>
       <c r="M9" s="5">
-        <v>-100</v>
+        <v>398.65383879241</v>
       </c>
       <c r="N9" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O9" s="6">
-        <v>978.03</v>
+        <v>1296</v>
       </c>
       <c r="P9" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q9" s="6">
         <v>2</v>
@@ -1306,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="6">
-        <v>195.60599999999999</v>
+        <v>185.142857142857</v>
       </c>
       <c r="T9" s="6">
-        <v>489.01499999999999</v>
+        <v>648</v>
       </c>
       <c r="U9" s="6">
         <v>-100</v>
@@ -1333,7 +1347,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1356,14 +1370,24 @@
         <v>0</v>
       </c>
       <c r="O10" s="6">
-        <v>544.88</v>
-      </c>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
+        <v>618.35</v>
+      </c>
+      <c r="P10" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6">
+        <v>618.35</v>
+      </c>
       <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
+      <c r="U10" s="6">
+        <v>-100</v>
+      </c>
       <c r="V10" s="7">
         <v>5</v>
       </c>
@@ -1377,7 +1401,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1385,36 +1409,38 @@
         <v>106</v>
       </c>
       <c r="B11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5">
         <v>0</v>
       </c>
       <c r="D11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5">
-        <v>677.43</v>
+        <v>783.15</v>
       </c>
       <c r="F11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
       </c>
       <c r="H11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="5">
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>677.43</v>
-      </c>
-      <c r="L11" s="5"/>
+        <v>391.57499999999999</v>
+      </c>
+      <c r="L11" s="5">
+        <v>783.15</v>
+      </c>
       <c r="M11" s="5">
         <v>-100</v>
       </c>
@@ -1422,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="6">
-        <v>192.37</v>
+        <v>244.14</v>
       </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
@@ -1455,7 +1481,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1478,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6">
-        <v>68.13</v>
+        <v>84.39</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1499,7 +1525,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1507,25 +1533,25 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C13" s="5">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1687.21</v>
+      </c>
+      <c r="F13" s="5">
+        <v>4</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5">
         <v>3</v>
-      </c>
-      <c r="D13" s="5">
-        <v>2</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1378.68</v>
-      </c>
-      <c r="F13" s="5">
-        <v>2</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0</v>
-      </c>
-      <c r="H13" s="5">
-        <v>2</v>
       </c>
       <c r="I13" s="5">
         <v>2</v>
@@ -1534,22 +1560,22 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>689.34</v>
+        <v>421.80250000000001</v>
       </c>
       <c r="L13" s="5">
-        <v>689.34</v>
+        <v>843.60500000000002</v>
       </c>
       <c r="M13" s="5">
         <v>-100</v>
       </c>
       <c r="N13" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" s="6">
-        <v>479.53</v>
+        <v>669.24</v>
       </c>
       <c r="P13" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q13" s="6">
         <v>3</v>
@@ -1558,10 +1584,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="6">
-        <v>119.88249999999999</v>
+        <v>133.84800000000001</v>
       </c>
       <c r="T13" s="6">
-        <v>159.84333333333299</v>
+        <v>223.08</v>
       </c>
       <c r="U13" s="6">
         <v>-100</v>
@@ -1591,7 +1617,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1614,7 +1640,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>152.83000000000001</v>
+        <v>195.3</v>
       </c>
       <c r="P14" s="6">
         <v>1</v>
@@ -1626,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>152.83000000000001</v>
+        <v>195.3</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1651,7 +1677,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1674,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
@@ -1695,7 +1721,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1718,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="6">
-        <v>200.46</v>
+        <v>245.63</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1745,7 +1771,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1762,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>185.91</v>
+        <v>271.97000000000003</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1776,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="6">
-        <v>183.69</v>
+        <v>216.03</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
@@ -1809,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1829,10 +1855,10 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O18" s="6">
-        <v>639.84</v>
+        <v>788.46</v>
       </c>
       <c r="P18" s="6">
         <v>3</v>
@@ -1844,10 +1870,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>213.28</v>
+        <v>262.82</v>
       </c>
       <c r="T18" s="6">
-        <v>639.84</v>
+        <v>788.46</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1871,7 +1897,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1879,33 +1905,47 @@
         <v>36</v>
       </c>
       <c r="B19" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C19" s="5">
         <v>3</v>
       </c>
       <c r="D19" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="5">
-        <v>609</v>
-      </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
+        <v>736.91</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>736.91</v>
+      </c>
       <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
+      <c r="M19" s="5">
+        <v>-100</v>
+      </c>
       <c r="N19" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O19" s="6">
-        <v>641.66999999999996</v>
+        <v>810.74</v>
       </c>
       <c r="P19" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="6">
         <v>0</v>
@@ -1914,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="6">
-        <v>641.66999999999996</v>
+        <v>270.24666666666599</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6">
@@ -1945,7 +1985,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1968,22 +2008,22 @@
         <v>1</v>
       </c>
       <c r="O20" s="6">
-        <v>736.63</v>
+        <v>906.94</v>
       </c>
       <c r="P20" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q20" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" s="6">
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>245.54333333333301</v>
+        <v>226.73500000000001</v>
       </c>
       <c r="T20" s="6">
-        <v>736.63</v>
+        <v>453.47</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2007,7 +2047,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2027,25 +2067,25 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O21" s="6">
-        <v>2039.19</v>
+        <v>2465.4299999999998</v>
       </c>
       <c r="P21" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q21" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R21" s="6">
         <v>0</v>
       </c>
       <c r="S21" s="6">
-        <v>203.91900000000001</v>
+        <v>224.13</v>
       </c>
       <c r="T21" s="6">
-        <v>2039.19</v>
+        <v>821.81</v>
       </c>
       <c r="U21" s="6">
         <v>-100</v>
@@ -2069,7 +2109,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2077,36 +2117,38 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22" s="5">
         <v>1</v>
       </c>
       <c r="D22" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22" s="5">
-        <v>499.95</v>
+        <v>601.32000000000005</v>
       </c>
       <c r="F22" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="5">
         <v>0</v>
       </c>
       <c r="H22" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="5">
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>499.95</v>
-      </c>
-      <c r="L22" s="5"/>
+        <v>200.44</v>
+      </c>
+      <c r="L22" s="5">
+        <v>601.32000000000005</v>
+      </c>
       <c r="M22" s="5">
         <v>-100</v>
       </c>
@@ -2114,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="O22" s="6">
-        <v>435.72</v>
+        <v>526.28</v>
       </c>
       <c r="P22" s="6">
         <v>2</v>
@@ -2126,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>217.86</v>
+        <v>263.14</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2157,7 +2199,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2177,10 +2219,10 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O23" s="6">
-        <v>728.59</v>
+        <v>899.02</v>
       </c>
       <c r="P23" s="6">
         <v>5</v>
@@ -2192,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>145.71799999999999</v>
+        <v>179.804</v>
       </c>
       <c r="T23" s="6"/>
       <c r="U23" s="6">
@@ -2221,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2244,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="O24" s="6">
-        <v>376.68</v>
+        <v>477.52</v>
       </c>
       <c r="P24" s="6">
         <v>1</v>
@@ -2256,7 +2298,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>376.68</v>
+        <v>477.52</v>
       </c>
       <c r="T24" s="6"/>
       <c r="U24" s="6">
@@ -2281,7 +2323,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46146</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3587,41 +3629,43 @@
         <v>18</v>
       </c>
       <c r="D19" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F19" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="10">
-        <v>0</v>
+        <v>7816</v>
       </c>
       <c r="J19" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="10">
-        <v>0</v>
+        <v>7816</v>
       </c>
       <c r="L19" s="10">
         <v>16.670000000000002</v>
       </c>
-      <c r="M19" s="10"/>
+      <c r="M19" s="10">
+        <v>38.130000000000003</v>
+      </c>
       <c r="N19" s="10">
         <v>50</v>
       </c>
       <c r="O19" s="10">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="P19" s="10">
-        <v>0</v>
+        <v>16.670000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -3635,16 +3679,16 @@
         <v>18</v>
       </c>
       <c r="D20" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" s="10">
         <v>2</v>
       </c>
       <c r="G20" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="10">
         <v>0</v>
@@ -3659,11 +3703,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="10">
-        <v>8.33</v>
-      </c>
-      <c r="M20" s="10"/>
+        <v>11.11</v>
+      </c>
+      <c r="M20" s="10">
+        <v>0</v>
+      </c>
       <c r="N20" s="10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O20" s="10">
         <v>0</v>
@@ -3695,10 +3741,10 @@
         <v>2</v>
       </c>
       <c r="H21" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="10">
-        <v>0</v>
+        <v>5410</v>
       </c>
       <c r="J21" s="10">
         <v>0</v>
@@ -3707,15 +3753,17 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>8.33</v>
-      </c>
-      <c r="M21" s="10"/>
+        <v>5.56</v>
+      </c>
+      <c r="M21" s="10">
+        <v>26.39</v>
+      </c>
       <c r="N21" s="10">
         <v>0</v>
       </c>
       <c r="O21" s="10"/>
       <c r="P21" s="10">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -3753,9 +3801,11 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>4.17</v>
-      </c>
-      <c r="M22" s="10"/>
+        <v>2.78</v>
+      </c>
+      <c r="M22" s="10">
+        <v>0</v>
+      </c>
       <c r="N22" s="10">
         <v>0</v>
       </c>
@@ -3775,39 +3825,41 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E23" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F23" s="10">
         <v>0</v>
       </c>
       <c r="G23" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="10">
-        <v>0</v>
+        <v>7272</v>
       </c>
       <c r="J23" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="10">
-        <v>0</v>
+        <v>7272</v>
       </c>
       <c r="L23" s="10">
-        <v>45.83</v>
-      </c>
-      <c r="M23" s="10"/>
+        <v>36.11</v>
+      </c>
+      <c r="M23" s="10">
+        <v>35.479999999999997</v>
+      </c>
       <c r="N23" s="10">
         <v>0</v>
       </c>
       <c r="O23" s="10"/>
       <c r="P23" s="10">
-        <v>0</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -3821,13 +3873,13 @@
         <v>18</v>
       </c>
       <c r="D24" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="10">
         <v>0</v>
@@ -3845,13 +3897,17 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>4.17</v>
-      </c>
-      <c r="M24" s="10"/>
+        <v>8.33</v>
+      </c>
+      <c r="M24" s="10">
+        <v>0</v>
+      </c>
       <c r="N24" s="10">
-        <v>0</v>
-      </c>
-      <c r="O24" s="10"/>
+        <v>33.33</v>
+      </c>
+      <c r="O24" s="10">
+        <v>0</v>
+      </c>
       <c r="P24" s="10">
         <v>0</v>
       </c>
@@ -3867,13 +3923,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="10">
         <v>0</v>
@@ -3891,13 +3947,17 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>4.17</v>
-      </c>
-      <c r="M25" s="10"/>
+        <v>5.56</v>
+      </c>
+      <c r="M25" s="10">
+        <v>0</v>
+      </c>
       <c r="N25" s="10">
-        <v>0</v>
-      </c>
-      <c r="O25" s="10"/>
+        <v>50</v>
+      </c>
+      <c r="O25" s="10">
+        <v>0</v>
+      </c>
       <c r="P25" s="10">
         <v>0</v>
       </c>
@@ -3913,13 +3973,13 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
+        <v>3</v>
+      </c>
+      <c r="E26" s="10">
+        <v>3</v>
+      </c>
+      <c r="F26" s="10">
         <v>2</v>
-      </c>
-      <c r="E26" s="10">
-        <v>2</v>
-      </c>
-      <c r="F26" s="10">
-        <v>1</v>
       </c>
       <c r="G26" s="10">
         <v>1</v>
@@ -3939,9 +3999,11 @@
       <c r="L26" s="10">
         <v>8.33</v>
       </c>
-      <c r="M26" s="10"/>
+      <c r="M26" s="10">
+        <v>0</v>
+      </c>
       <c r="N26" s="10">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="O26" s="10">
         <v>0</v>
@@ -3951,38 +4013,104 @@
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
+      <c r="A27" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="19">
+        <v>2026</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="10">
+        <v>1</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1</v>
+      </c>
+      <c r="F27" s="10">
+        <v>1</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0</v>
+      </c>
+      <c r="I27" s="10">
+        <v>0</v>
+      </c>
+      <c r="J27" s="10">
+        <v>0</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0</v>
+      </c>
+      <c r="L27" s="10">
+        <v>2.78</v>
+      </c>
+      <c r="M27" s="10">
+        <v>0</v>
+      </c>
+      <c r="N27" s="10">
+        <v>100</v>
+      </c>
+      <c r="O27" s="10">
+        <v>0</v>
+      </c>
+      <c r="P27" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="19">
+        <v>2026</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="10">
+        <v>1</v>
+      </c>
+      <c r="E28" s="10">
+        <v>1</v>
+      </c>
+      <c r="F28" s="10">
+        <v>1</v>
+      </c>
+      <c r="G28" s="10">
+        <v>0</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
+        <v>0</v>
+      </c>
+      <c r="J28" s="10">
+        <v>0</v>
+      </c>
+      <c r="K28" s="10">
+        <v>0</v>
+      </c>
+      <c r="L28" s="10">
+        <v>2.78</v>
+      </c>
+      <c r="M28" s="10">
+        <v>0</v>
+      </c>
+      <c r="N28" s="10">
+        <v>100</v>
+      </c>
+      <c r="O28" s="10">
+        <v>0</v>
+      </c>
+      <c r="P28" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B29" s="19"/>
@@ -4622,19 +4750,19 @@
         <v>164</v>
       </c>
       <c r="G19" s="5">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H19" s="5">
         <v>21</v>
       </c>
       <c r="I19" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J19" s="5">
-        <v>78971.64</v>
+        <v>86665.64</v>
       </c>
       <c r="K19" s="5">
-        <v>9.9600000000000009</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -4657,10 +4785,10 @@
         <v>167</v>
       </c>
       <c r="G20" s="10">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H20" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I20" s="10">
         <v>8</v>
@@ -4683,28 +4811,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>454</v>
+        <v>538</v>
       </c>
       <c r="E21" s="10">
-        <v>1089.06</v>
+        <v>1293.1099999999999</v>
       </c>
       <c r="F21" s="10">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G21" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H21" s="10">
+        <v>4</v>
+      </c>
+      <c r="I21" s="10">
         <v>2</v>
       </c>
-      <c r="I21" s="10">
-        <v>0</v>
-      </c>
       <c r="J21" s="10">
-        <v>0</v>
+        <v>12682</v>
       </c>
       <c r="K21" s="10">
-        <v>-1</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5156,10 +5284,10 @@
         <v>2</v>
       </c>
       <c r="J34" s="10">
-        <v>15484</v>
+        <v>17864</v>
       </c>
       <c r="K34" s="10">
-        <v>4.63</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -5278,19 +5406,29 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="E38" s="10">
-        <v>398.53</v>
+        <v>501.47</v>
       </c>
       <c r="F38" s="10">
-        <v>1</v>
-      </c>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
+        <v>2</v>
+      </c>
+      <c r="G38" s="10">
+        <v>1</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0</v>
+      </c>
+      <c r="I38" s="10">
+        <v>0</v>
+      </c>
+      <c r="J38" s="10">
+        <v>0</v>
+      </c>
+      <c r="K38" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
@@ -5522,7 +5660,7 @@
         <v>23</v>
       </c>
       <c r="G45" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H45" s="10">
         <v>6</v>
@@ -5863,28 +6001,28 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="E55" s="10">
-        <v>1415.7</v>
+        <v>1567.42</v>
       </c>
       <c r="F55" s="10">
+        <v>6</v>
+      </c>
+      <c r="G55" s="10">
         <v>5</v>
       </c>
-      <c r="G55" s="10">
-        <v>4</v>
-      </c>
       <c r="H55" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I55" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="10">
-        <v>0</v>
+        <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>-1</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6142,7 +6280,7 @@
         <v>3</v>
       </c>
       <c r="G63" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H63" s="10">
         <v>5</v>
@@ -6858,19 +6996,19 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E84" s="10">
-        <v>677.43</v>
+        <v>783.15</v>
       </c>
       <c r="F84" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G84" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" s="10">
         <v>0</v>
@@ -7337,10 +7475,10 @@
         <v>17</v>
       </c>
       <c r="G98" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H98" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I98" s="10">
         <v>6</v>
@@ -7748,19 +7886,19 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="E110" s="10">
-        <v>1378.68</v>
+        <v>1687.21</v>
       </c>
       <c r="F110" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G110" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H110" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I110" s="10">
         <v>0</v>
@@ -8467,7 +8605,7 @@
         <v>6</v>
       </c>
       <c r="G132" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H132" s="10">
         <v>2</v>
@@ -9263,10 +9401,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E155" s="10">
-        <v>185.91</v>
+        <v>271.97000000000003</v>
       </c>
       <c r="F155" s="10">
         <v>0</v>
@@ -10339,19 +10477,29 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E186" s="10">
-        <v>609</v>
+        <v>736.91</v>
       </c>
       <c r="F186" s="10">
-        <v>4</v>
-      </c>
-      <c r="G186" s="10"/>
-      <c r="H186" s="10"/>
-      <c r="I186" s="10"/>
-      <c r="J186" s="10"/>
-      <c r="K186" s="10"/>
+        <v>6</v>
+      </c>
+      <c r="G186" s="10">
+        <v>1</v>
+      </c>
+      <c r="H186" s="10">
+        <v>0</v>
+      </c>
+      <c r="I186" s="10">
+        <v>0</v>
+      </c>
+      <c r="J186" s="10">
+        <v>0</v>
+      </c>
+      <c r="K186" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="10" t="s">
@@ -11904,19 +12052,19 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E231" s="10">
-        <v>499.95</v>
+        <v>601.32000000000005</v>
       </c>
       <c r="F231" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G231" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H231" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I231" s="10">
         <v>0</v>
@@ -16648,33 +16796,33 @@
         <v>107</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>7816</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B44" s="18">
         <v>2026</v>
@@ -16683,16 +16831,16 @@
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -16712,7 +16860,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B45" s="18">
         <v>2026</v>
@@ -16721,16 +16869,16 @@
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -16759,7 +16907,7 @@
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -16774,10 +16922,10 @@
         <v>1</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>5410</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -16788,7 +16936,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B47" s="18">
         <v>2026</v>
@@ -16797,19 +16945,19 @@
         <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -16826,7 +16974,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B48" s="18">
         <v>2026</v>
@@ -16838,16 +16986,16 @@
         <v>13</v>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -16873,36 +17021,36 @@
         <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>7272</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>7272</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B50" s="18">
         <v>2026</v>
@@ -16911,7 +17059,7 @@
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -16940,7 +17088,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B51" s="18">
         <v>2026</v>
@@ -16949,7 +17097,7 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -16978,7 +17126,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B52" s="18">
         <v>2026</v>
@@ -16990,16 +17138,16 @@
         <v>13</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -17016,7 +17164,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B53" s="18">
         <v>2026</v>
@@ -17053,24 +17201,194 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B54" s="18"/>
-      <c r="C54" s="19"/>
+      <c r="A54" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B55" s="18"/>
-      <c r="C55" s="19"/>
+      <c r="A55" t="s">
+        <v>100</v>
+      </c>
+      <c r="B55" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+      <c r="H55">
+        <v>1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B56" s="18"/>
-      <c r="C56" s="19"/>
+      <c r="A56" t="s">
+        <v>100</v>
+      </c>
+      <c r="B56" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B57" s="18"/>
-      <c r="C57" s="19"/>
+      <c r="A57" t="s">
+        <v>101</v>
+      </c>
+      <c r="B57" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" t="s">
+        <v>106</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B58" s="18"/>
-      <c r="C58" s="19"/>
+      <c r="A58" t="s">
+        <v>103</v>
+      </c>
+      <c r="B58" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B59" s="18"/>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17513DC6-9B5E-4AF4-B77C-9CA409FD2735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E48A2C-8512-4497-AD92-B9E01169C6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -995,64 +995,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C6" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6" s="5">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E6" s="5">
-        <v>7442.5599999999904</v>
+        <v>8814.02</v>
       </c>
       <c r="F6" s="5">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G6" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6" s="5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I6" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J6" s="5">
         <v>3</v>
       </c>
       <c r="K6" s="5">
-        <v>206.73777777777701</v>
+        <v>209.85761904761901</v>
       </c>
       <c r="L6" s="5">
-        <v>744.25599999999997</v>
+        <v>734.50166666666598</v>
       </c>
       <c r="M6" s="5">
-        <v>175.41598589732499</v>
+        <v>132.56130573790301</v>
       </c>
       <c r="N6" s="6">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="O6" s="6">
-        <v>14779.67</v>
+        <v>17932.13</v>
       </c>
       <c r="P6" s="6">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="Q6" s="6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R6" s="6">
         <v>2</v>
       </c>
       <c r="S6" s="6">
-        <v>202.46123287671199</v>
+        <v>218.68451219512099</v>
       </c>
       <c r="T6" s="6">
-        <v>985.31133333333298</v>
+        <v>996.22944444444397</v>
       </c>
       <c r="U6" s="6">
-        <v>-40.4317552421671</v>
+        <v>-50.903824587486199</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1079,7 +1079,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1087,49 +1087,49 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C7" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D7" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" s="5">
-        <v>1293.1099999999999</v>
+        <v>1525.87</v>
       </c>
       <c r="F7" s="5">
+        <v>23</v>
+      </c>
+      <c r="G7" s="5">
+        <v>3</v>
+      </c>
+      <c r="H7" s="5">
         <v>20</v>
       </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>19</v>
-      </c>
       <c r="I7" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J7" s="5">
         <v>2</v>
       </c>
       <c r="K7" s="5">
-        <v>64.655499999999904</v>
+        <v>66.342173913043396</v>
       </c>
       <c r="L7" s="5">
-        <v>323.27749999999997</v>
+        <v>254.31166666666601</v>
       </c>
       <c r="M7" s="5">
-        <v>880.73636426908695</v>
+        <v>731.13240315360997</v>
       </c>
       <c r="N7" s="6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O7" s="6">
-        <v>3803.22</v>
+        <v>4555.37</v>
       </c>
       <c r="P7" s="6">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="Q7" s="6">
         <v>3</v>
@@ -1138,13 +1138,13 @@
         <v>2</v>
       </c>
       <c r="S7" s="6">
-        <v>135.82928571428499</v>
+        <v>138.041515151515</v>
       </c>
       <c r="T7" s="6">
-        <v>1267.74</v>
+        <v>1518.4566666666601</v>
       </c>
       <c r="U7" s="6">
-        <v>131.48779192368499</v>
+        <v>93.266189135020795</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1171,7 +1171,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>501.47</v>
+        <v>573.78</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>501.47</v>
+        <v>573.78</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1216,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="6">
-        <v>530.63</v>
+        <v>631.70000000000005</v>
       </c>
       <c r="P8" s="6">
         <v>2</v>
@@ -1228,10 +1228,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>265.315</v>
+        <v>315.85000000000002</v>
       </c>
       <c r="T8" s="6">
-        <v>530.63</v>
+        <v>631.70000000000005</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1261,7 +1261,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1278,7 +1278,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="5">
-        <v>1567.42</v>
+        <v>1848.69</v>
       </c>
       <c r="F9" s="5">
         <v>5</v>
@@ -1296,19 +1296,19 @@
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>313.48399999999998</v>
+        <v>369.738</v>
       </c>
       <c r="L9" s="5">
-        <v>783.71</v>
+        <v>924.34500000000003</v>
       </c>
       <c r="M9" s="5">
-        <v>398.65383879241</v>
+        <v>322.78586458519197</v>
       </c>
       <c r="N9" s="6">
         <v>6</v>
       </c>
       <c r="O9" s="6">
-        <v>1296</v>
+        <v>1612.74</v>
       </c>
       <c r="P9" s="6">
         <v>7</v>
@@ -1320,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="6">
-        <v>185.142857142857</v>
+        <v>230.39142857142801</v>
       </c>
       <c r="T9" s="6">
-        <v>648</v>
+        <v>806.37</v>
       </c>
       <c r="U9" s="6">
         <v>-100</v>
@@ -1347,7 +1347,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1370,21 +1370,23 @@
         <v>0</v>
       </c>
       <c r="O10" s="6">
-        <v>618.35</v>
+        <v>770.81</v>
       </c>
       <c r="P10" s="6">
         <v>1</v>
       </c>
       <c r="Q10" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="6">
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>618.35</v>
-      </c>
-      <c r="T10" s="6"/>
+        <v>770.81</v>
+      </c>
+      <c r="T10" s="6">
+        <v>770.81</v>
+      </c>
       <c r="U10" s="6">
         <v>-100</v>
       </c>
@@ -1401,7 +1403,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1418,7 +1420,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="5">
-        <v>783.15</v>
+        <v>941.02</v>
       </c>
       <c r="F11" s="5">
         <v>2</v>
@@ -1436,10 +1438,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>391.57499999999999</v>
+        <v>470.51</v>
       </c>
       <c r="L11" s="5">
-        <v>783.15</v>
+        <v>941.02</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
@@ -1448,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="6">
-        <v>244.14</v>
+        <v>303.77</v>
       </c>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
@@ -1481,7 +1483,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1504,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6">
-        <v>84.39</v>
+        <v>96.27</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1525,7 +1527,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1533,26 +1535,26 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5">
         <v>6</v>
       </c>
       <c r="D13" s="5">
+        <v>5</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1980.46</v>
+      </c>
+      <c r="F13" s="5">
+        <v>6</v>
+      </c>
+      <c r="G13" s="5">
+        <v>2</v>
+      </c>
+      <c r="H13" s="5">
         <v>4</v>
       </c>
-      <c r="E13" s="5">
-        <v>1687.21</v>
-      </c>
-      <c r="F13" s="5">
-        <v>4</v>
-      </c>
-      <c r="G13" s="5">
-        <v>1</v>
-      </c>
-      <c r="H13" s="5">
-        <v>3</v>
-      </c>
       <c r="I13" s="5">
         <v>2</v>
       </c>
@@ -1560,34 +1562,34 @@
         <v>0</v>
       </c>
       <c r="K13" s="5">
-        <v>421.80250000000001</v>
+        <v>330.07666666666597</v>
       </c>
       <c r="L13" s="5">
-        <v>843.60500000000002</v>
+        <v>990.23</v>
       </c>
       <c r="M13" s="5">
         <v>-100</v>
       </c>
       <c r="N13" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" s="6">
-        <v>669.24</v>
+        <v>877.65</v>
       </c>
       <c r="P13" s="6">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="6">
         <v>5</v>
       </c>
-      <c r="Q13" s="6">
-        <v>3</v>
-      </c>
       <c r="R13" s="6">
         <v>0</v>
       </c>
       <c r="S13" s="6">
-        <v>133.84800000000001</v>
+        <v>109.70625</v>
       </c>
       <c r="T13" s="6">
-        <v>223.08</v>
+        <v>175.53</v>
       </c>
       <c r="U13" s="6">
         <v>-100</v>
@@ -1617,7 +1619,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1640,7 +1642,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>195.3</v>
+        <v>221.18</v>
       </c>
       <c r="P14" s="6">
         <v>1</v>
@@ -1652,7 +1654,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>195.3</v>
+        <v>221.18</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1677,7 +1679,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1700,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="6">
-        <v>2.35</v>
+        <v>2.74</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6"/>
@@ -1721,7 +1723,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1744,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="6">
-        <v>245.63</v>
+        <v>295.81</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1771,7 +1773,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1788,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>271.97000000000003</v>
+        <v>344.78</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1802,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="6">
-        <v>216.03</v>
+        <v>286.17</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
@@ -1835,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1858,7 +1860,7 @@
         <v>5</v>
       </c>
       <c r="O18" s="6">
-        <v>788.46</v>
+        <v>936.65</v>
       </c>
       <c r="P18" s="6">
         <v>3</v>
@@ -1870,10 +1872,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>262.82</v>
+        <v>312.21666666666601</v>
       </c>
       <c r="T18" s="6">
-        <v>788.46</v>
+        <v>936.65</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1897,7 +1899,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1914,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="5">
-        <v>736.91</v>
+        <v>856.55</v>
       </c>
       <c r="F19" s="5">
         <v>1</v>
@@ -1932,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>736.91</v>
+        <v>856.55</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5">
@@ -1942,7 +1944,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="6">
-        <v>810.74</v>
+        <v>979.77</v>
       </c>
       <c r="P19" s="6">
         <v>3</v>
@@ -1954,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="6">
-        <v>270.24666666666599</v>
+        <v>326.58999999999997</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6">
@@ -1985,7 +1987,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2008,7 +2010,7 @@
         <v>1</v>
       </c>
       <c r="O20" s="6">
-        <v>906.94</v>
+        <v>1077.56</v>
       </c>
       <c r="P20" s="6">
         <v>4</v>
@@ -2020,10 +2022,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>226.73500000000001</v>
+        <v>269.39</v>
       </c>
       <c r="T20" s="6">
-        <v>453.47</v>
+        <v>538.78</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2047,7 +2049,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2070,7 +2072,7 @@
         <v>14</v>
       </c>
       <c r="O21" s="6">
-        <v>2465.4299999999998</v>
+        <v>2890.29</v>
       </c>
       <c r="P21" s="6">
         <v>11</v>
@@ -2082,10 +2084,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="6">
-        <v>224.13</v>
+        <v>262.75363636363602</v>
       </c>
       <c r="T21" s="6">
-        <v>821.81</v>
+        <v>963.43</v>
       </c>
       <c r="U21" s="6">
         <v>-100</v>
@@ -2109,7 +2111,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2117,25 +2119,25 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22" s="5">
         <v>1</v>
       </c>
       <c r="D22" s="5">
+        <v>6</v>
+      </c>
+      <c r="E22" s="5">
+        <v>742.87</v>
+      </c>
+      <c r="F22" s="5">
         <v>4</v>
       </c>
-      <c r="E22" s="5">
-        <v>601.32000000000005</v>
-      </c>
-      <c r="F22" s="5">
-        <v>3</v>
-      </c>
       <c r="G22" s="5">
         <v>0</v>
       </c>
       <c r="H22" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="5">
         <v>1</v>
@@ -2144,19 +2146,19 @@
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>200.44</v>
+        <v>185.7175</v>
       </c>
       <c r="L22" s="5">
-        <v>601.32000000000005</v>
+        <v>742.87</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
       </c>
       <c r="N22" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" s="6">
-        <v>526.28</v>
+        <v>744</v>
       </c>
       <c r="P22" s="6">
         <v>2</v>
@@ -2168,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>263.14</v>
+        <v>372</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2199,7 +2201,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2219,10 +2221,10 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O23" s="6">
-        <v>899.02</v>
+        <v>1067.99</v>
       </c>
       <c r="P23" s="6">
         <v>5</v>
@@ -2234,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>179.804</v>
+        <v>213.59800000000001</v>
       </c>
       <c r="T23" s="6"/>
       <c r="U23" s="6">
@@ -2263,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2283,13 +2285,13 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O24" s="6">
-        <v>477.52</v>
+        <v>581.66</v>
       </c>
       <c r="P24" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="6">
         <v>0</v>
@@ -2298,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>477.52</v>
+        <v>290.83</v>
       </c>
       <c r="T24" s="6"/>
       <c r="U24" s="6">
@@ -2323,7 +2325,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46148</v>
+        <v>46149</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3638,7 +3640,7 @@
         <v>3</v>
       </c>
       <c r="G19" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" s="10">
         <v>1</v>
@@ -3653,7 +3655,7 @@
         <v>7816</v>
       </c>
       <c r="L19" s="10">
-        <v>16.670000000000002</v>
+        <v>14.29</v>
       </c>
       <c r="M19" s="10">
         <v>38.130000000000003</v>
@@ -3679,10 +3681,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F20" s="10">
         <v>2</v>
@@ -3703,13 +3705,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="10">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
       <c r="M20" s="10">
         <v>0</v>
       </c>
       <c r="N20" s="10">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="O20" s="10">
         <v>0</v>
@@ -3753,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>5.56</v>
+        <v>4.76</v>
       </c>
       <c r="M21" s="10">
         <v>26.39</v>
@@ -3801,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -3825,10 +3827,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F23" s="10">
         <v>0</v>
@@ -3849,7 +3851,7 @@
         <v>7272</v>
       </c>
       <c r="L23" s="10">
-        <v>36.11</v>
+        <v>33.33</v>
       </c>
       <c r="M23" s="10">
         <v>35.479999999999997</v>
@@ -3859,7 +3861,7 @@
       </c>
       <c r="O23" s="10"/>
       <c r="P23" s="10">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -3897,7 +3899,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>8.33</v>
+        <v>7.14</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -3923,7 +3925,7 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="10">
         <v>2</v>
@@ -3947,13 +3949,13 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>5.56</v>
+        <v>7.14</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
       </c>
       <c r="N25" s="10">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="O25" s="10">
         <v>0</v>
@@ -3973,16 +3975,16 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
+        <v>5</v>
+      </c>
+      <c r="E26" s="10">
+        <v>5</v>
+      </c>
+      <c r="F26" s="10">
         <v>3</v>
       </c>
-      <c r="E26" s="10">
-        <v>3</v>
-      </c>
-      <c r="F26" s="10">
-        <v>2</v>
-      </c>
       <c r="G26" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="10">
         <v>0</v>
@@ -3997,13 +3999,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>8.33</v>
+        <v>11.9</v>
       </c>
       <c r="M26" s="10">
         <v>0</v>
       </c>
       <c r="N26" s="10">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="O26" s="10">
         <v>0</v>
@@ -4047,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="10">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="M27" s="10">
         <v>0</v>
@@ -4097,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>2.78</v>
+        <v>2.38</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
@@ -4811,19 +4813,19 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>538</v>
+        <v>642</v>
       </c>
       <c r="E21" s="10">
-        <v>1293.1099999999999</v>
+        <v>1525.87</v>
       </c>
       <c r="F21" s="10">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G21" s="10">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H21" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I21" s="10">
         <v>2</v>
@@ -4832,7 +4834,7 @@
         <v>12682</v>
       </c>
       <c r="K21" s="10">
-        <v>8.81</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5406,10 +5408,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E38" s="10">
-        <v>501.47</v>
+        <v>573.78</v>
       </c>
       <c r="F38" s="10">
         <v>2</v>
@@ -6001,10 +6003,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="E55" s="10">
-        <v>1567.42</v>
+        <v>1848.69</v>
       </c>
       <c r="F55" s="10">
         <v>6</v>
@@ -6022,7 +6024,7 @@
         <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>3.99</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6996,10 +6998,10 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E84" s="10">
-        <v>783.15</v>
+        <v>941.02</v>
       </c>
       <c r="F84" s="10">
         <v>2</v>
@@ -7886,16 +7888,16 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="E110" s="10">
-        <v>1687.21</v>
+        <v>1980.46</v>
       </c>
       <c r="F110" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G110" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H110" s="10">
         <v>3</v>
@@ -9401,10 +9403,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E155" s="10">
-        <v>271.97000000000003</v>
+        <v>344.78</v>
       </c>
       <c r="F155" s="10">
         <v>0</v>
@@ -10477,10 +10479,10 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="E186" s="10">
-        <v>736.91</v>
+        <v>856.55</v>
       </c>
       <c r="F186" s="10">
         <v>6</v>
@@ -12052,16 +12054,16 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="E231" s="10">
-        <v>601.32000000000005</v>
+        <v>742.87</v>
       </c>
       <c r="F231" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G231" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H231" s="10">
         <v>1</v>
@@ -16805,7 +16807,7 @@
         <v>2</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43">
         <v>1</v>
@@ -16872,10 +16874,10 @@
         <v>29</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -17024,10 +17026,10 @@
         <v>13</v>
       </c>
       <c r="E49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -17214,7 +17216,7 @@
         <v>13</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54">
         <v>2</v>
@@ -17252,13 +17254,13 @@
         <v>13</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -17290,16 +17292,16 @@
         <v>39</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>0</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02E48A2C-8512-4497-AD92-B9E01169C6AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623CB0BD-40C4-4870-A413-86893359E350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="111">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -350,6 +350,12 @@
   </si>
   <si>
     <t>Austin Single Form - Updated</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>June</t>
   </si>
 </sst>
 </file>
@@ -995,64 +1001,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C6" s="5">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D6" s="5">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E6" s="5">
-        <v>8814.02</v>
+        <v>12704.21</v>
       </c>
       <c r="F6" s="5">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="G6" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6" s="5">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="I6" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J6" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" s="5">
-        <v>209.85761904761901</v>
+        <v>235.26314814814799</v>
       </c>
       <c r="L6" s="5">
-        <v>734.50166666666598</v>
+        <v>977.24692307692305</v>
       </c>
       <c r="M6" s="5">
-        <v>132.56130573790301</v>
+        <v>100.579178083485</v>
       </c>
       <c r="N6" s="6">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="O6" s="6">
-        <v>17932.13</v>
+        <v>26176.87</v>
       </c>
       <c r="P6" s="6">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="Q6" s="6">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="R6" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S6" s="6">
-        <v>218.68451219512099</v>
+        <v>212.820081300813</v>
       </c>
       <c r="T6" s="6">
-        <v>996.22944444444397</v>
+        <v>969.51370370370296</v>
       </c>
       <c r="U6" s="6">
-        <v>-50.903824587486199</v>
+        <v>72.895346158650696</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1067,7 +1073,7 @@
         <v>77</v>
       </c>
       <c r="Z6" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA6" s="8">
         <v>45500</v>
@@ -1079,7 +1085,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1087,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C7" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7" s="5">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E7" s="5">
-        <v>1525.87</v>
+        <v>2175.2600000000002</v>
       </c>
       <c r="F7" s="5">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G7" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I7" s="5">
         <v>6</v>
@@ -1114,37 +1120,37 @@
         <v>2</v>
       </c>
       <c r="K7" s="5">
-        <v>66.342173913043396</v>
+        <v>75.008965517241293</v>
       </c>
       <c r="L7" s="5">
-        <v>254.31166666666601</v>
+        <v>362.54333333333301</v>
       </c>
       <c r="M7" s="5">
-        <v>731.13240315360997</v>
+        <v>483.010766529058</v>
       </c>
       <c r="N7" s="6">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="O7" s="6">
-        <v>4555.37</v>
+        <v>6534.53</v>
       </c>
       <c r="P7" s="6">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R7" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S7" s="6">
-        <v>138.041515151515</v>
+        <v>128.12803921568599</v>
       </c>
       <c r="T7" s="6">
-        <v>1518.4566666666601</v>
+        <v>1306.9059999999999</v>
       </c>
       <c r="U7" s="6">
-        <v>93.266189135020795</v>
+        <v>402.37017811533502</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1159,7 +1165,7 @@
         <v>29</v>
       </c>
       <c r="Z7" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA7" s="8">
         <v>10000</v>
@@ -1171,7 +1177,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1188,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>573.78</v>
+        <v>776.48</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1206,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>573.78</v>
+        <v>776.48</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1216,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="6">
-        <v>631.70000000000005</v>
+        <v>911.68</v>
       </c>
       <c r="P8" s="6">
         <v>2</v>
@@ -1228,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>315.85000000000002</v>
+        <v>455.84</v>
       </c>
       <c r="T8" s="6">
-        <v>631.70000000000005</v>
+        <v>911.68</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1261,7 +1267,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1269,25 +1275,25 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5">
+        <v>2745.78</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
         <v>6</v>
-      </c>
-      <c r="C9" s="5">
-        <v>3</v>
-      </c>
-      <c r="D9" s="5">
-        <v>3</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1848.69</v>
-      </c>
-      <c r="F9" s="5">
-        <v>5</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>4</v>
       </c>
       <c r="I9" s="5">
         <v>2</v>
@@ -1296,37 +1302,37 @@
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>369.738</v>
+        <v>392.254285714285</v>
       </c>
       <c r="L9" s="5">
-        <v>924.34500000000003</v>
+        <v>1372.89</v>
       </c>
       <c r="M9" s="5">
-        <v>322.78586458519197</v>
+        <v>184.654997851248</v>
       </c>
       <c r="N9" s="6">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O9" s="6">
-        <v>1612.74</v>
+        <v>2473.67</v>
       </c>
       <c r="P9" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q9" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R9" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>230.39142857142801</v>
+        <v>309.20875000000001</v>
       </c>
       <c r="T9" s="6">
-        <v>806.37</v>
+        <v>824.55666666666605</v>
       </c>
       <c r="U9" s="6">
-        <v>-100</v>
+        <v>115.50974867302401</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1347,7 +1353,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1370,22 +1376,22 @@
         <v>0</v>
       </c>
       <c r="O10" s="6">
-        <v>770.81</v>
+        <v>966.1</v>
       </c>
       <c r="P10" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q10" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" s="6">
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>770.81</v>
+        <v>241.52500000000001</v>
       </c>
       <c r="T10" s="6">
-        <v>770.81</v>
+        <v>483.05</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1403,7 +1409,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1411,16 +1417,16 @@
         <v>106</v>
       </c>
       <c r="B11" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5">
         <v>2</v>
       </c>
       <c r="E11" s="5">
-        <v>941.02</v>
+        <v>1407.07</v>
       </c>
       <c r="F11" s="5">
         <v>2</v>
@@ -1438,10 +1444,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>470.51</v>
+        <v>703.53499999999997</v>
       </c>
       <c r="L11" s="5">
-        <v>941.02</v>
+        <v>1407.07</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
@@ -1450,14 +1456,24 @@
         <v>0</v>
       </c>
       <c r="O11" s="6">
-        <v>303.77</v>
-      </c>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
+        <v>481.25</v>
+      </c>
+      <c r="P11" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>0</v>
+      </c>
+      <c r="R11" s="6">
+        <v>0</v>
+      </c>
+      <c r="S11" s="6">
+        <v>481.25</v>
+      </c>
       <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
+      <c r="U11" s="6">
+        <v>-100</v>
+      </c>
       <c r="V11" s="7">
         <v>4</v>
       </c>
@@ -1483,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1506,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6">
-        <v>96.27</v>
+        <v>123.77</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1527,7 +1543,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1535,61 +1551,61 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
+        <v>16</v>
+      </c>
+      <c r="C13" s="5">
+        <v>7</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2733.23</v>
+      </c>
+      <c r="F13" s="5">
+        <v>9</v>
+      </c>
+      <c r="G13" s="5">
+        <v>3</v>
+      </c>
+      <c r="H13" s="5">
+        <v>6</v>
+      </c>
+      <c r="I13" s="5">
+        <v>3</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5">
+        <v>303.69222222222197</v>
+      </c>
+      <c r="L13" s="5">
+        <v>911.07666666666603</v>
+      </c>
+      <c r="M13" s="5">
+        <v>82.348357072035597</v>
+      </c>
+      <c r="N13" s="6">
+        <v>5</v>
+      </c>
+      <c r="O13" s="6">
+        <v>1460.71</v>
+      </c>
+      <c r="P13" s="6">
         <v>11</v>
       </c>
-      <c r="C13" s="5">
-        <v>6</v>
-      </c>
-      <c r="D13" s="5">
-        <v>5</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1980.46</v>
-      </c>
-      <c r="F13" s="5">
-        <v>6</v>
-      </c>
-      <c r="G13" s="5">
-        <v>2</v>
-      </c>
-      <c r="H13" s="5">
-        <v>4</v>
-      </c>
-      <c r="I13" s="5">
-        <v>2</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5">
-        <v>330.07666666666597</v>
-      </c>
-      <c r="L13" s="5">
-        <v>990.23</v>
-      </c>
-      <c r="M13" s="5">
-        <v>-100</v>
-      </c>
-      <c r="N13" s="6">
-        <v>3</v>
-      </c>
-      <c r="O13" s="6">
-        <v>877.65</v>
-      </c>
-      <c r="P13" s="6">
-        <v>8</v>
-      </c>
       <c r="Q13" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R13" s="6">
         <v>0</v>
       </c>
       <c r="S13" s="6">
-        <v>109.70625</v>
+        <v>132.791818181818</v>
       </c>
       <c r="T13" s="6">
-        <v>175.53</v>
+        <v>208.672857142857</v>
       </c>
       <c r="U13" s="6">
         <v>-100</v>
@@ -1619,7 +1635,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1642,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>221.18</v>
+        <v>299.48</v>
       </c>
       <c r="P14" s="6">
         <v>1</v>
@@ -1654,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>221.18</v>
+        <v>299.48</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1679,7 +1695,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1723,7 +1739,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1746,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="6">
-        <v>295.81</v>
+        <v>417.68</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1773,7 +1789,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1790,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>344.78</v>
+        <v>486.68</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1801,10 +1817,10 @@
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="6">
-        <v>286.17</v>
+        <v>369.87</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
@@ -1837,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1860,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="O18" s="6">
-        <v>936.65</v>
+        <v>1296.3800000000001</v>
       </c>
       <c r="P18" s="6">
         <v>3</v>
@@ -1872,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>312.21666666666601</v>
+        <v>432.12666666666598</v>
       </c>
       <c r="T18" s="6">
-        <v>936.65</v>
+        <v>1296.3800000000001</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1899,7 +1915,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1907,25 +1923,25 @@
         <v>36</v>
       </c>
       <c r="B19" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" s="5">
         <v>3</v>
       </c>
       <c r="D19" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E19" s="5">
-        <v>856.55</v>
+        <v>1238.75</v>
       </c>
       <c r="F19" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5">
         <v>0</v>
       </c>
       <c r="H19" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="5">
         <v>0</v>
@@ -1934,33 +1950,35 @@
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>856.55</v>
+        <v>619.375</v>
       </c>
       <c r="L19" s="5"/>
       <c r="M19" s="5">
         <v>-100</v>
       </c>
       <c r="N19" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O19" s="6">
-        <v>979.77</v>
+        <v>1480.92</v>
       </c>
       <c r="P19" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q19" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>326.58999999999997</v>
-      </c>
-      <c r="T19" s="6"/>
+        <v>185.11500000000001</v>
+      </c>
+      <c r="T19" s="6">
+        <v>1480.92</v>
+      </c>
       <c r="U19" s="6">
-        <v>-100</v>
+        <v>379.43575615158102</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -1975,7 +1993,7 @@
         <v>7</v>
       </c>
       <c r="Z19" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="8">
         <v>3500</v>
@@ -1987,7 +2005,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2007,13 +2025,13 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O20" s="6">
-        <v>1077.56</v>
+        <v>1568.14</v>
       </c>
       <c r="P20" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q20" s="6">
         <v>2</v>
@@ -2022,10 +2040,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>269.39</v>
+        <v>313.62799999999999</v>
       </c>
       <c r="T20" s="6">
-        <v>538.78</v>
+        <v>784.07</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2049,7 +2067,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2069,13 +2087,13 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O21" s="6">
-        <v>2890.29</v>
+        <v>4151.66</v>
       </c>
       <c r="P21" s="6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q21" s="6">
         <v>3</v>
@@ -2084,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="6">
-        <v>262.75363636363602</v>
+        <v>276.77733333333299</v>
       </c>
       <c r="T21" s="6">
-        <v>963.43</v>
+        <v>1383.8866666666599</v>
       </c>
       <c r="U21" s="6">
         <v>-100</v>
@@ -2111,7 +2129,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2128,7 +2146,7 @@
         <v>6</v>
       </c>
       <c r="E22" s="5">
-        <v>742.87</v>
+        <v>1140.96</v>
       </c>
       <c r="F22" s="5">
         <v>4</v>
@@ -2146,22 +2164,22 @@
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>185.7175</v>
+        <v>285.24</v>
       </c>
       <c r="L22" s="5">
-        <v>742.87</v>
+        <v>1140.96</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
       </c>
       <c r="N22" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" s="6">
-        <v>744</v>
+        <v>1189.6099999999999</v>
       </c>
       <c r="P22" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -2170,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>372</v>
+        <v>396.53666666666601</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2201,7 +2219,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2221,24 +2239,26 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O23" s="6">
-        <v>1067.99</v>
+        <v>1573.59</v>
       </c>
       <c r="P23" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q23" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="6">
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>213.59800000000001</v>
-      </c>
-      <c r="T23" s="6"/>
+        <v>196.69874999999999</v>
+      </c>
+      <c r="T23" s="6">
+        <v>1573.59</v>
+      </c>
       <c r="U23" s="6">
         <v>-100</v>
       </c>
@@ -2265,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2288,21 +2308,23 @@
         <v>3</v>
       </c>
       <c r="O24" s="6">
-        <v>581.66</v>
+        <v>875.09</v>
       </c>
       <c r="P24" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="6">
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>290.83</v>
-      </c>
-      <c r="T24" s="6"/>
+        <v>291.69666666666598</v>
+      </c>
+      <c r="T24" s="6">
+        <v>875.09</v>
+      </c>
       <c r="U24" s="6">
         <v>-100</v>
       </c>
@@ -2325,7 +2347,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46149</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3631,10 +3653,10 @@
         <v>18</v>
       </c>
       <c r="D19" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" s="10">
         <v>3</v>
@@ -3655,19 +3677,19 @@
         <v>7816</v>
       </c>
       <c r="L19" s="10">
-        <v>14.29</v>
+        <v>12.96</v>
       </c>
       <c r="M19" s="10">
-        <v>38.130000000000003</v>
+        <v>30.67</v>
       </c>
       <c r="N19" s="10">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="O19" s="10">
         <v>33.33</v>
       </c>
       <c r="P19" s="10">
-        <v>16.670000000000002</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -3681,10 +3703,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F20" s="10">
         <v>2</v>
@@ -3693,31 +3715,31 @@
         <v>1</v>
       </c>
       <c r="H20" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="10">
-        <v>0</v>
+        <v>4984</v>
       </c>
       <c r="J20" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="10">
-        <v>0</v>
+        <v>4984</v>
       </c>
       <c r="L20" s="10">
-        <v>14.29</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="M20" s="10">
-        <v>0</v>
+        <v>19.559999999999999</v>
       </c>
       <c r="N20" s="10">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="O20" s="10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P20" s="10">
-        <v>0</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -3755,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>4.76</v>
+        <v>3.7</v>
       </c>
       <c r="M21" s="10">
-        <v>26.39</v>
+        <v>21.23</v>
       </c>
       <c r="N21" s="10">
         <v>0</v>
@@ -3770,7 +3792,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="B22" s="19">
         <v>2026</v>
@@ -3782,7 +3804,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="10">
         <v>0</v>
@@ -3803,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -3818,7 +3840,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23" s="19">
         <v>2026</v>
@@ -3827,46 +3849,48 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E23" s="10">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F23" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H23" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="10">
-        <v>7272</v>
+        <v>0</v>
       </c>
       <c r="J23" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="10">
-        <v>7272</v>
+        <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>33.33</v>
+        <v>3.7</v>
       </c>
       <c r="M23" s="10">
-        <v>35.479999999999997</v>
+        <v>0</v>
       </c>
       <c r="N23" s="10">
-        <v>0</v>
-      </c>
-      <c r="O23" s="10"/>
+        <v>50</v>
+      </c>
+      <c r="O23" s="10">
+        <v>0</v>
+      </c>
       <c r="P23" s="10">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B24" s="19">
         <v>2026</v>
@@ -3875,48 +3899,46 @@
         <v>18</v>
       </c>
       <c r="D24" s="10">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E24" s="10">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="10">
-        <v>0</v>
+        <v>7272</v>
       </c>
       <c r="J24" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="10">
-        <v>0</v>
+        <v>7272</v>
       </c>
       <c r="L24" s="10">
-        <v>7.14</v>
+        <v>33.33</v>
       </c>
       <c r="M24" s="10">
-        <v>0</v>
+        <v>28.54</v>
       </c>
       <c r="N24" s="10">
-        <v>33.33</v>
-      </c>
-      <c r="O24" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O24" s="10"/>
       <c r="P24" s="10">
-        <v>0</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B25" s="19">
         <v>2026</v>
@@ -3928,7 +3950,7 @@
         <v>3</v>
       </c>
       <c r="E25" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="10">
         <v>1</v>
@@ -3949,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>7.14</v>
+        <v>5.56</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -3966,7 +3988,7 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B26" s="19">
         <v>2026</v>
@@ -3975,16 +3997,16 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F26" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="10">
         <v>0</v>
@@ -3999,13 +4021,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>11.9</v>
+        <v>7.41</v>
       </c>
       <c r="M26" s="10">
         <v>0</v>
       </c>
       <c r="N26" s="10">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="O26" s="10">
         <v>0</v>
@@ -4016,7 +4038,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B27" s="19">
         <v>2026</v>
@@ -4025,16 +4047,16 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E27" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F27" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" s="10">
         <v>0</v>
@@ -4049,13 +4071,13 @@
         <v>0</v>
       </c>
       <c r="L27" s="10">
-        <v>2.38</v>
+        <v>11.11</v>
       </c>
       <c r="M27" s="10">
         <v>0</v>
       </c>
       <c r="N27" s="10">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="O27" s="10">
         <v>0</v>
@@ -4066,7 +4088,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B28" s="19">
         <v>2026</v>
@@ -4099,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
@@ -4115,21 +4137,54 @@
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="19">
+        <v>2027</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="10">
+        <v>1</v>
+      </c>
+      <c r="E29" s="10">
+        <v>1</v>
+      </c>
+      <c r="F29" s="10">
+        <v>1</v>
+      </c>
+      <c r="G29" s="10">
+        <v>0</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0</v>
+      </c>
+      <c r="I29" s="10">
+        <v>0</v>
+      </c>
+      <c r="J29" s="10">
+        <v>0</v>
+      </c>
+      <c r="K29" s="10">
+        <v>0</v>
+      </c>
+      <c r="L29" s="10">
+        <v>1.85</v>
+      </c>
+      <c r="M29" s="10">
+        <v>0</v>
+      </c>
+      <c r="N29" s="10">
+        <v>100</v>
+      </c>
+      <c r="O29" s="10">
+        <v>0</v>
+      </c>
+      <c r="P29" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B30" s="19"/>
@@ -4367,7 +4422,7 @@
         <v>129</v>
       </c>
       <c r="G8" s="5">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H8" s="5">
         <v>34</v>
@@ -4793,13 +4848,13 @@
         <v>17</v>
       </c>
       <c r="I20" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J20" s="10">
-        <v>61731</v>
+        <v>54115</v>
       </c>
       <c r="K20" s="10">
-        <v>7.29</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -4813,16 +4868,16 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>642</v>
+        <v>949</v>
       </c>
       <c r="E21" s="10">
-        <v>1525.87</v>
+        <v>2175.2600000000002</v>
       </c>
       <c r="F21" s="10">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="G21" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H21" s="10">
         <v>6</v>
@@ -4834,7 +4889,7 @@
         <v>12682</v>
       </c>
       <c r="K21" s="10">
-        <v>7.31</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5408,10 +5463,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E38" s="10">
-        <v>573.78</v>
+        <v>776.48</v>
       </c>
       <c r="F38" s="10">
         <v>2</v>
@@ -6003,16 +6058,16 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>239</v>
+        <v>361</v>
       </c>
       <c r="E55" s="10">
-        <v>1848.69</v>
+        <v>2745.78</v>
       </c>
       <c r="F55" s="10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G55" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H55" s="10">
         <v>2</v>
@@ -6024,7 +6079,7 @@
         <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>3.23</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6998,13 +7053,13 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>133</v>
+        <v>199</v>
       </c>
       <c r="E84" s="10">
-        <v>941.02</v>
+        <v>1407.07</v>
       </c>
       <c r="F84" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G84" s="10">
         <v>2</v>
@@ -7147,7 +7202,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -7888,28 +7943,28 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>213</v>
+        <v>277</v>
       </c>
       <c r="E110" s="10">
-        <v>1980.46</v>
+        <v>2733.23</v>
       </c>
       <c r="F110" s="10">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G110" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H110" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I110" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="10">
-        <v>0</v>
+        <v>4984</v>
       </c>
       <c r="K110" s="10">
-        <v>-1</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9403,10 +9458,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E155" s="10">
-        <v>344.78</v>
+        <v>486.68</v>
       </c>
       <c r="F155" s="10">
         <v>0</v>
@@ -10479,16 +10534,16 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="E186" s="10">
-        <v>856.55</v>
+        <v>1238.75</v>
       </c>
       <c r="F186" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G186" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H186" s="10">
         <v>0</v>
@@ -12054,10 +12109,10 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="E231" s="10">
-        <v>742.87</v>
+        <v>1140.96</v>
       </c>
       <c r="F231" s="10">
         <v>7</v>
@@ -16798,10 +16853,10 @@
         <v>107</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -16871,19 +16926,19 @@
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E45">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -16900,7 +16955,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B46" s="18">
         <v>2026</v>
@@ -16909,16 +16964,16 @@
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -16927,13 +16982,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>5410</v>
+        <v>4984</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>4984</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -16947,7 +17002,7 @@
         <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E47">
         <v>1</v>
@@ -16962,10 +17017,10 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>5410</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -16976,7 +17031,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B48" s="18">
         <v>2026</v>
@@ -16985,19 +17040,19 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -17014,7 +17069,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B49" s="18">
         <v>2026</v>
@@ -17026,33 +17081,33 @@
         <v>13</v>
       </c>
       <c r="E49">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>7272</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>7272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B50" s="18">
         <v>2026</v>
@@ -17061,7 +17116,7 @@
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -17090,7 +17145,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" s="18">
         <v>2026</v>
@@ -17099,7 +17154,7 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -17108,7 +17163,7 @@
         <v>1</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -17128,7 +17183,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="18">
         <v>2026</v>
@@ -17140,33 +17195,33 @@
         <v>13</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>7272</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>7272</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B53" s="18">
         <v>2026</v>
@@ -17175,7 +17230,7 @@
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -17204,7 +17259,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B54" s="18">
         <v>2026</v>
@@ -17213,16 +17268,16 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -17242,7 +17297,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B55" s="18">
         <v>2026</v>
@@ -17251,19 +17306,19 @@
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -17280,7 +17335,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B56" s="18">
         <v>2026</v>
@@ -17289,19 +17344,19 @@
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -17318,7 +17373,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B57" s="18">
         <v>2026</v>
@@ -17327,7 +17382,7 @@
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -17336,7 +17391,7 @@
         <v>1</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -17356,7 +17411,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B58" s="18">
         <v>2026</v>
@@ -17368,10 +17423,10 @@
         <v>13</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -17393,24 +17448,194 @@
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B59" s="18"/>
-      <c r="C59" s="19"/>
+      <c r="A59" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59">
+        <v>2</v>
+      </c>
+      <c r="H59">
+        <v>1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B60" s="18"/>
-      <c r="C60" s="19"/>
+      <c r="A60" t="s">
+        <v>100</v>
+      </c>
+      <c r="B60" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B61" s="18"/>
-      <c r="C61" s="19"/>
+      <c r="A61" t="s">
+        <v>100</v>
+      </c>
+      <c r="B61" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" t="s">
+        <v>39</v>
+      </c>
+      <c r="E61">
+        <v>3</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+      <c r="H61">
+        <v>1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B62" s="18"/>
-      <c r="C62" s="19"/>
+      <c r="A62" t="s">
+        <v>101</v>
+      </c>
+      <c r="B62" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" t="s">
+        <v>106</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B63" s="18"/>
-      <c r="C63" s="19"/>
+      <c r="A63" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B64" s="18"/>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623CB0BD-40C4-4870-A413-86893359E350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0F7914-D900-4CC8-9B79-5B5694C6E8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47892" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="110">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -353,9 +353,6 @@
   </si>
   <si>
     <t>Corporate</t>
-  </si>
-  <si>
-    <t>June</t>
   </si>
 </sst>
 </file>
@@ -1001,64 +998,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C6" s="5">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D6" s="5">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E6" s="5">
-        <v>12704.21</v>
+        <v>14311.45</v>
       </c>
       <c r="F6" s="5">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G6" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H6" s="5">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I6" s="5">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J6" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K6" s="5">
-        <v>235.26314814814799</v>
+        <v>234.61393442622901</v>
       </c>
       <c r="L6" s="5">
-        <v>977.24692307692305</v>
+        <v>795.08055555555495</v>
       </c>
       <c r="M6" s="5">
-        <v>100.579178083485</v>
+        <v>162.90837057041699</v>
       </c>
       <c r="N6" s="6">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="O6" s="6">
-        <v>26176.87</v>
+        <v>28500.089999999898</v>
       </c>
       <c r="P6" s="6">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="Q6" s="6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R6" s="6">
         <v>6</v>
       </c>
       <c r="S6" s="6">
-        <v>212.820081300813</v>
+        <v>217.557938931297</v>
       </c>
       <c r="T6" s="6">
-        <v>969.51370370370296</v>
+        <v>1017.86035714285</v>
       </c>
       <c r="U6" s="6">
-        <v>72.895346158650696</v>
+        <v>58.801568696800601</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1085,7 +1082,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1093,49 +1090,49 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C7" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" s="5">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E7" s="5">
-        <v>2175.2600000000002</v>
+        <v>2465.73</v>
       </c>
       <c r="F7" s="5">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
       </c>
       <c r="H7" s="5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I7" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J7" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K7" s="5">
-        <v>75.008965517241293</v>
+        <v>74.719090909090895</v>
       </c>
       <c r="L7" s="5">
-        <v>362.54333333333301</v>
+        <v>352.24714285714202</v>
       </c>
       <c r="M7" s="5">
-        <v>483.010766529058</v>
+        <v>906.8417872192</v>
       </c>
       <c r="N7" s="6">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="O7" s="6">
-        <v>6534.53</v>
+        <v>7062.2</v>
       </c>
       <c r="P7" s="6">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q7" s="6">
         <v>5</v>
@@ -1144,13 +1141,13 @@
         <v>4</v>
       </c>
       <c r="S7" s="6">
-        <v>128.12803921568599</v>
+        <v>128.403636363636</v>
       </c>
       <c r="T7" s="6">
-        <v>1306.9059999999999</v>
+        <v>1412.44</v>
       </c>
       <c r="U7" s="6">
-        <v>402.37017811533502</v>
+        <v>364.834329245844</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1177,7 +1174,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1194,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>776.48</v>
+        <v>877.36</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1212,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>776.48</v>
+        <v>877.36</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1222,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="O8" s="6">
-        <v>911.68</v>
+        <v>969.16</v>
       </c>
       <c r="P8" s="6">
         <v>2</v>
@@ -1234,10 +1231,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>455.84</v>
+        <v>484.58</v>
       </c>
       <c r="T8" s="6">
-        <v>911.68</v>
+        <v>969.16</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1267,7 +1264,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1284,7 +1281,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="5">
-        <v>2745.78</v>
+        <v>3046.96</v>
       </c>
       <c r="F9" s="5">
         <v>7</v>
@@ -1302,19 +1299,19 @@
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>392.254285714285</v>
+        <v>435.28</v>
       </c>
       <c r="L9" s="5">
-        <v>1372.89</v>
+        <v>1523.48</v>
       </c>
       <c r="M9" s="5">
-        <v>184.654997851248</v>
+        <v>156.517972011447</v>
       </c>
       <c r="N9" s="6">
         <v>12</v>
       </c>
       <c r="O9" s="6">
-        <v>2473.67</v>
+        <v>2780.45</v>
       </c>
       <c r="P9" s="6">
         <v>8</v>
@@ -1326,13 +1323,13 @@
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>309.20875000000001</v>
+        <v>347.55624999999998</v>
       </c>
       <c r="T9" s="6">
-        <v>824.55666666666605</v>
+        <v>926.81666666666604</v>
       </c>
       <c r="U9" s="6">
-        <v>115.50974867302401</v>
+        <v>91.731554244816493</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1353,7 +1350,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1376,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="6">
-        <v>966.1</v>
+        <v>988.8</v>
       </c>
       <c r="P10" s="6">
         <v>4</v>
@@ -1388,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>241.52500000000001</v>
+        <v>247.2</v>
       </c>
       <c r="T10" s="6">
-        <v>483.05</v>
+        <v>494.4</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1409,7 +1406,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1426,7 +1423,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="5">
-        <v>1407.07</v>
+        <v>1574.96</v>
       </c>
       <c r="F11" s="5">
         <v>2</v>
@@ -1444,10 +1441,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>703.53499999999997</v>
+        <v>787.48</v>
       </c>
       <c r="L11" s="5">
-        <v>1407.07</v>
+        <v>1574.96</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
@@ -1456,21 +1453,23 @@
         <v>0</v>
       </c>
       <c r="O11" s="6">
-        <v>481.25</v>
+        <v>519.49</v>
       </c>
       <c r="P11" s="6">
         <v>1</v>
       </c>
       <c r="Q11" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="6">
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>481.25</v>
-      </c>
-      <c r="T11" s="6"/>
+        <v>519.49</v>
+      </c>
+      <c r="T11" s="6">
+        <v>519.49</v>
+      </c>
       <c r="U11" s="6">
         <v>-100</v>
       </c>
@@ -1499,7 +1498,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1522,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6">
-        <v>123.77</v>
+        <v>140.46</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1543,7 +1542,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1551,49 +1550,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C13" s="5">
+        <v>9</v>
+      </c>
+      <c r="D13" s="5">
+        <v>11</v>
+      </c>
+      <c r="E13" s="5">
+        <v>3131.83</v>
+      </c>
+      <c r="F13" s="5">
+        <v>11</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4</v>
+      </c>
+      <c r="H13" s="5">
         <v>7</v>
       </c>
-      <c r="D13" s="5">
-        <v>9</v>
-      </c>
-      <c r="E13" s="5">
-        <v>2733.23</v>
-      </c>
-      <c r="F13" s="5">
-        <v>9</v>
-      </c>
-      <c r="G13" s="5">
-        <v>3</v>
-      </c>
-      <c r="H13" s="5">
-        <v>6</v>
-      </c>
       <c r="I13" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" s="5">
         <v>1</v>
       </c>
       <c r="K13" s="5">
-        <v>303.69222222222197</v>
+        <v>284.71181818181799</v>
       </c>
       <c r="L13" s="5">
-        <v>911.07666666666603</v>
+        <v>782.95749999999998</v>
       </c>
       <c r="M13" s="5">
-        <v>82.348357072035597</v>
+        <v>59.140183215564001</v>
       </c>
       <c r="N13" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O13" s="6">
-        <v>1460.71</v>
+        <v>1574.04</v>
       </c>
       <c r="P13" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q13" s="6">
         <v>7</v>
@@ -1602,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="6">
-        <v>132.791818181818</v>
+        <v>131.16999999999999</v>
       </c>
       <c r="T13" s="6">
-        <v>208.672857142857</v>
+        <v>224.862857142857</v>
       </c>
       <c r="U13" s="6">
         <v>-100</v>
@@ -1635,7 +1634,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1658,7 +1657,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>299.48</v>
+        <v>305.18</v>
       </c>
       <c r="P14" s="6">
         <v>1</v>
@@ -1670,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>299.48</v>
+        <v>305.18</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1695,7 +1694,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1739,7 +1738,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1759,10 +1758,10 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" s="6">
-        <v>417.68</v>
+        <v>451.93</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1789,7 +1788,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1806,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>486.68</v>
+        <v>582.97</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1820,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="6">
-        <v>369.87</v>
+        <v>374</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
@@ -1853,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1876,10 +1875,10 @@
         <v>5</v>
       </c>
       <c r="O18" s="6">
-        <v>1296.3800000000001</v>
+        <v>1456.38</v>
       </c>
       <c r="P18" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q18" s="6">
         <v>1</v>
@@ -1888,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>432.12666666666598</v>
+        <v>291.27600000000001</v>
       </c>
       <c r="T18" s="6">
-        <v>1296.3800000000001</v>
+        <v>1456.38</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1915,7 +1914,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1932,7 +1931,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="5">
-        <v>1238.75</v>
+        <v>1365.65</v>
       </c>
       <c r="F19" s="5">
         <v>2</v>
@@ -1944,15 +1943,17 @@
         <v>2</v>
       </c>
       <c r="I19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" s="5">
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>619.375</v>
-      </c>
-      <c r="L19" s="5"/>
+        <v>682.82500000000005</v>
+      </c>
+      <c r="L19" s="5">
+        <v>1365.65</v>
+      </c>
       <c r="M19" s="5">
         <v>-100</v>
       </c>
@@ -1960,7 +1961,7 @@
         <v>13</v>
       </c>
       <c r="O19" s="6">
-        <v>1480.92</v>
+        <v>1621.6</v>
       </c>
       <c r="P19" s="6">
         <v>8</v>
@@ -1972,13 +1973,13 @@
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>185.11500000000001</v>
+        <v>202.7</v>
       </c>
       <c r="T19" s="6">
-        <v>1480.92</v>
+        <v>1621.6</v>
       </c>
       <c r="U19" s="6">
-        <v>379.43575615158102</v>
+        <v>337.84287123828301</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2005,7 +2006,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2028,7 +2029,7 @@
         <v>4</v>
       </c>
       <c r="O20" s="6">
-        <v>1568.14</v>
+        <v>1714.48</v>
       </c>
       <c r="P20" s="6">
         <v>5</v>
@@ -2040,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>313.62799999999999</v>
+        <v>342.89600000000002</v>
       </c>
       <c r="T20" s="6">
-        <v>784.07</v>
+        <v>857.24</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2067,7 +2068,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2087,13 +2088,13 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O21" s="6">
-        <v>4151.66</v>
+        <v>4582.07</v>
       </c>
       <c r="P21" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q21" s="6">
         <v>3</v>
@@ -2102,10 +2103,10 @@
         <v>0</v>
       </c>
       <c r="S21" s="6">
-        <v>276.77733333333299</v>
+        <v>286.37937499999998</v>
       </c>
       <c r="T21" s="6">
-        <v>1383.8866666666599</v>
+        <v>1527.35666666666</v>
       </c>
       <c r="U21" s="6">
         <v>-100</v>
@@ -2129,7 +2130,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2137,37 +2138,37 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="5">
         <v>6</v>
       </c>
       <c r="E22" s="5">
-        <v>1140.96</v>
+        <v>1265.99</v>
       </c>
       <c r="F22" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="5">
         <v>4</v>
       </c>
       <c r="I22" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" s="5">
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>285.24</v>
+        <v>253.19800000000001</v>
       </c>
       <c r="L22" s="5">
-        <v>1140.96</v>
+        <v>421.99666666666599</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2176,7 +2177,7 @@
         <v>3</v>
       </c>
       <c r="O22" s="6">
-        <v>1189.6099999999999</v>
+        <v>1290.69</v>
       </c>
       <c r="P22" s="6">
         <v>3</v>
@@ -2188,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>396.53666666666601</v>
+        <v>430.23</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2219,7 +2220,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2242,7 +2243,7 @@
         <v>12</v>
       </c>
       <c r="O23" s="6">
-        <v>1573.59</v>
+        <v>1711.26</v>
       </c>
       <c r="P23" s="6">
         <v>8</v>
@@ -2254,10 +2255,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>196.69874999999999</v>
+        <v>213.9075</v>
       </c>
       <c r="T23" s="6">
-        <v>1573.59</v>
+        <v>1711.26</v>
       </c>
       <c r="U23" s="6">
         <v>-100</v>
@@ -2285,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2308,7 +2309,7 @@
         <v>3</v>
       </c>
       <c r="O24" s="6">
-        <v>875.09</v>
+        <v>955.16</v>
       </c>
       <c r="P24" s="6">
         <v>3</v>
@@ -2320,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>291.69666666666598</v>
+        <v>318.38666666666597</v>
       </c>
       <c r="T24" s="6">
-        <v>875.09</v>
+        <v>955.16</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2347,7 +2348,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46152</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3662,7 +3663,7 @@
         <v>3</v>
       </c>
       <c r="G19" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="10">
         <v>1</v>
@@ -3677,10 +3678,10 @@
         <v>7816</v>
       </c>
       <c r="L19" s="10">
-        <v>12.96</v>
+        <v>11.48</v>
       </c>
       <c r="M19" s="10">
-        <v>30.67</v>
+        <v>20.77</v>
       </c>
       <c r="N19" s="10">
         <v>42.86</v>
@@ -3703,13 +3704,13 @@
         <v>18</v>
       </c>
       <c r="D20" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E20" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F20" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="10">
         <v>1</v>
@@ -3727,19 +3728,19 @@
         <v>4984</v>
       </c>
       <c r="L20" s="10">
-        <v>16.670000000000002</v>
+        <v>18.03</v>
       </c>
       <c r="M20" s="10">
-        <v>19.559999999999999</v>
+        <v>13.25</v>
       </c>
       <c r="N20" s="10">
-        <v>22.22</v>
+        <v>27.27</v>
       </c>
       <c r="O20" s="10">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="P20" s="10">
-        <v>11.11</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -3777,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="M21" s="10">
-        <v>21.23</v>
+        <v>14.38</v>
       </c>
       <c r="N21" s="10">
         <v>0</v>
@@ -3825,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -3840,7 +3841,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B23" s="19">
         <v>2026</v>
@@ -3849,10 +3850,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="10">
         <v>1</v>
@@ -3873,13 +3874,13 @@
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>3.7</v>
+        <v>1.64</v>
       </c>
       <c r="M23" s="10">
         <v>0</v>
       </c>
       <c r="N23" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O23" s="10">
         <v>0</v>
@@ -3890,7 +3891,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24" s="19">
         <v>2026</v>
@@ -3899,46 +3900,48 @@
         <v>18</v>
       </c>
       <c r="D24" s="10">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E24" s="10">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="F24" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="10">
-        <v>7272</v>
+        <v>0</v>
       </c>
       <c r="J24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" s="10">
-        <v>7272</v>
+        <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>33.33</v>
+        <v>3.28</v>
       </c>
       <c r="M24" s="10">
-        <v>28.54</v>
+        <v>0</v>
       </c>
       <c r="N24" s="10">
-        <v>0</v>
-      </c>
-      <c r="O24" s="10"/>
+        <v>50</v>
+      </c>
+      <c r="O24" s="10">
+        <v>0</v>
+      </c>
       <c r="P24" s="10">
-        <v>5.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B25" s="19">
         <v>2026</v>
@@ -3947,48 +3950,46 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
+        <v>21</v>
+      </c>
+      <c r="E25" s="10">
+        <v>21</v>
+      </c>
+      <c r="F25" s="10">
+        <v>0</v>
+      </c>
+      <c r="G25" s="10">
+        <v>6</v>
+      </c>
+      <c r="H25" s="10">
         <v>3</v>
       </c>
-      <c r="E25" s="10">
+      <c r="I25" s="10">
+        <v>19416</v>
+      </c>
+      <c r="J25" s="10">
         <v>3</v>
       </c>
-      <c r="F25" s="10">
-        <v>1</v>
-      </c>
-      <c r="G25" s="10">
-        <v>0</v>
-      </c>
-      <c r="H25" s="10">
-        <v>0</v>
-      </c>
-      <c r="I25" s="10">
-        <v>0</v>
-      </c>
-      <c r="J25" s="10">
-        <v>0</v>
-      </c>
       <c r="K25" s="10">
-        <v>0</v>
+        <v>19416</v>
       </c>
       <c r="L25" s="10">
-        <v>5.56</v>
+        <v>34.43</v>
       </c>
       <c r="M25" s="10">
-        <v>0</v>
+        <v>51.6</v>
       </c>
       <c r="N25" s="10">
-        <v>33.33</v>
-      </c>
-      <c r="O25" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O25" s="10"/>
       <c r="P25" s="10">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B26" s="19">
         <v>2026</v>
@@ -3997,7 +3998,7 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="10">
         <v>3</v>
@@ -4021,13 +4022,13 @@
         <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>7.41</v>
+        <v>4.92</v>
       </c>
       <c r="M26" s="10">
         <v>0</v>
       </c>
       <c r="N26" s="10">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="O26" s="10">
         <v>0</v>
@@ -4038,7 +4039,7 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="19">
         <v>2026</v>
@@ -4047,16 +4048,16 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E27" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F27" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G27" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" s="10">
         <v>0</v>
@@ -4071,13 +4072,13 @@
         <v>0</v>
       </c>
       <c r="L27" s="10">
-        <v>11.11</v>
+        <v>6.56</v>
       </c>
       <c r="M27" s="10">
         <v>0</v>
       </c>
       <c r="N27" s="10">
-        <v>83.33</v>
+        <v>25</v>
       </c>
       <c r="O27" s="10">
         <v>0</v>
@@ -4088,7 +4089,7 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B28" s="19">
         <v>2026</v>
@@ -4097,16 +4098,16 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E28" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F28" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G28" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" s="10">
         <v>0</v>
@@ -4121,13 +4122,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>1.85</v>
+        <v>9.84</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="O28" s="10">
         <v>0</v>
@@ -4138,13 +4139,13 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B29" s="19">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="D29" s="10">
         <v>1</v>
@@ -4171,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
@@ -4187,38 +4188,104 @@
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
+      <c r="A30" t="s">
+        <v>102</v>
+      </c>
+      <c r="B30" s="19">
+        <v>2026</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="10">
+        <v>1</v>
+      </c>
+      <c r="E30" s="10">
+        <v>1</v>
+      </c>
+      <c r="F30" s="10">
+        <v>1</v>
+      </c>
+      <c r="G30" s="10">
+        <v>0</v>
+      </c>
+      <c r="H30" s="10">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10">
+        <v>0</v>
+      </c>
+      <c r="J30" s="10">
+        <v>0</v>
+      </c>
+      <c r="K30" s="10">
+        <v>0</v>
+      </c>
+      <c r="L30" s="10">
+        <v>1.64</v>
+      </c>
+      <c r="M30" s="10">
+        <v>0</v>
+      </c>
+      <c r="N30" s="10">
+        <v>100</v>
+      </c>
+      <c r="O30" s="10">
+        <v>0</v>
+      </c>
+      <c r="P30" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
+      <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" s="19">
+        <v>2026</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="10">
+        <v>1</v>
+      </c>
+      <c r="E31" s="10">
+        <v>1</v>
+      </c>
+      <c r="F31" s="10">
+        <v>1</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0</v>
+      </c>
+      <c r="H31" s="10">
+        <v>0</v>
+      </c>
+      <c r="I31" s="10">
+        <v>0</v>
+      </c>
+      <c r="J31" s="10">
+        <v>0</v>
+      </c>
+      <c r="K31" s="10">
+        <v>0</v>
+      </c>
+      <c r="L31" s="10">
+        <v>1.64</v>
+      </c>
+      <c r="M31" s="10">
+        <v>0</v>
+      </c>
+      <c r="N31" s="10">
+        <v>100</v>
+      </c>
+      <c r="O31" s="10">
+        <v>0</v>
+      </c>
+      <c r="P31" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B32" s="19"/>
@@ -4422,7 +4489,7 @@
         <v>129</v>
       </c>
       <c r="G8" s="5">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H8" s="5">
         <v>34</v>
@@ -4807,7 +4874,7 @@
         <v>164</v>
       </c>
       <c r="G19" s="5">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" s="5">
         <v>21</v>
@@ -4868,28 +4935,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>949</v>
+        <v>1065</v>
       </c>
       <c r="E21" s="10">
-        <v>2175.2600000000002</v>
+        <v>2465.73</v>
       </c>
       <c r="F21" s="10">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G21" s="10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H21" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J21" s="10">
-        <v>12682</v>
+        <v>24826</v>
       </c>
       <c r="K21" s="10">
-        <v>4.83</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5463,10 +5530,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E38" s="10">
-        <v>776.48</v>
+        <v>877.36</v>
       </c>
       <c r="F38" s="10">
         <v>2</v>
@@ -6058,10 +6125,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>361</v>
+        <v>407</v>
       </c>
       <c r="E55" s="10">
-        <v>2745.78</v>
+        <v>3046.96</v>
       </c>
       <c r="F55" s="10">
         <v>12</v>
@@ -6079,7 +6146,7 @@
         <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -7053,10 +7120,10 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="E84" s="10">
-        <v>1407.07</v>
+        <v>1574.96</v>
       </c>
       <c r="F84" s="10">
         <v>3</v>
@@ -7202,7 +7269,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -7532,10 +7599,10 @@
         <v>17</v>
       </c>
       <c r="G98" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H98" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I98" s="10">
         <v>6</v>
@@ -7943,19 +8010,19 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>277</v>
+        <v>305</v>
       </c>
       <c r="E110" s="10">
-        <v>2733.23</v>
+        <v>3131.83</v>
       </c>
       <c r="F110" s="10">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G110" s="10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H110" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I110" s="10">
         <v>1</v>
@@ -7964,7 +8031,7 @@
         <v>4984</v>
       </c>
       <c r="K110" s="10">
-        <v>0.82</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9458,10 +9525,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E155" s="10">
-        <v>486.68</v>
+        <v>582.97</v>
       </c>
       <c r="F155" s="10">
         <v>0</v>
@@ -9492,7 +9559,7 @@
         <v>30</v>
       </c>
       <c r="G156" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H156" s="10">
         <v>2</v>
@@ -10534,10 +10601,10 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="E186" s="10">
-        <v>1238.75</v>
+        <v>1365.65</v>
       </c>
       <c r="F186" s="10">
         <v>8</v>
@@ -10546,7 +10613,7 @@
         <v>2</v>
       </c>
       <c r="H186" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I186" s="10">
         <v>0</v>
@@ -12109,19 +12176,19 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="E231" s="10">
-        <v>1140.96</v>
+        <v>1265.99</v>
       </c>
       <c r="F231" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G231" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H231" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I231" s="10">
         <v>0</v>
@@ -16824,7 +16891,7 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -16967,13 +17034,13 @@
         <v>29</v>
       </c>
       <c r="E46">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F46">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -17107,7 +17174,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B50" s="18">
         <v>2026</v>
@@ -17116,7 +17183,7 @@
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -17125,7 +17192,7 @@
         <v>1</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -17154,7 +17221,7 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -17163,7 +17230,7 @@
         <v>1</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -17183,7 +17250,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B52" s="18">
         <v>2026</v>
@@ -17192,31 +17259,31 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E52">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>7272</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52">
-        <v>7272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -17230,31 +17297,31 @@
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>19416</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>19416</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -17268,7 +17335,7 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -17306,7 +17373,7 @@
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -17335,7 +17402,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B56" s="18">
         <v>2026</v>
@@ -17344,16 +17411,16 @@
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -17382,16 +17449,16 @@
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -17411,7 +17478,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B58" s="18">
         <v>2026</v>
@@ -17420,16 +17487,16 @@
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E58">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -17449,7 +17516,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B59" s="18">
         <v>2026</v>
@@ -17461,16 +17528,16 @@
         <v>13</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -17496,19 +17563,19 @@
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -17534,19 +17601,19 @@
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -17563,7 +17630,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B62" s="18">
         <v>2026</v>
@@ -17572,19 +17639,19 @@
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -17601,7 +17668,7 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B63" s="18">
         <v>2026</v>
@@ -17610,98 +17677,166 @@
         <v>18</v>
       </c>
       <c r="D63" t="s">
+        <v>106</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>102</v>
+      </c>
+      <c r="B64" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" t="s">
         <v>13</v>
       </c>
-      <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
-      </c>
-      <c r="G63">
-        <v>1</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B64" s="18"/>
-      <c r="C64" s="19"/>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B65" s="18"/>
-      <c r="C65" s="19"/>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>103</v>
+      </c>
+      <c r="B65" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B66" s="18"/>
       <c r="C66" s="19"/>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B67" s="18"/>
       <c r="C67" s="19"/>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B68" s="18"/>
       <c r="C68" s="19"/>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B69" s="18"/>
       <c r="C69" s="19"/>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B70" s="18"/>
       <c r="C70" s="19"/>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B71" s="18"/>
       <c r="C71" s="19"/>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B72" s="18"/>
       <c r="C72" s="19"/>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B73" s="18"/>
       <c r="C73" s="19"/>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B74" s="18"/>
       <c r="C74" s="19"/>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B75" s="18"/>
       <c r="C75" s="19"/>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B76" s="18"/>
       <c r="C76" s="19"/>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B77" s="18"/>
       <c r="C77" s="19"/>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B78" s="18"/>
       <c r="C78" s="19"/>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B79" s="18"/>
       <c r="C79" s="19"/>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B80" s="18"/>
       <c r="C80" s="19"/>
     </row>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0F7914-D900-4CC8-9B79-5B5694C6E8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CB984D-2915-4566-8118-027463D179A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47892" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -998,64 +998,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C6" s="5">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D6" s="5">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E6" s="5">
-        <v>14311.45</v>
+        <v>15859.99</v>
       </c>
       <c r="F6" s="5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6" s="5">
         <v>11</v>
       </c>
       <c r="H6" s="5">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I6" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J6" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K6" s="5">
-        <v>234.61393442622901</v>
+        <v>251.745873015873</v>
       </c>
       <c r="L6" s="5">
-        <v>795.08055555555495</v>
+        <v>932.94058823529394</v>
       </c>
       <c r="M6" s="5">
-        <v>162.90837057041699</v>
+        <v>244.48394986377599</v>
       </c>
       <c r="N6" s="6">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="O6" s="6">
-        <v>28500.089999999898</v>
+        <v>31475.129999999899</v>
       </c>
       <c r="P6" s="6">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="Q6" s="6">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="R6" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S6" s="6">
-        <v>217.557938931297</v>
+        <v>205.719803921568</v>
       </c>
       <c r="T6" s="6">
-        <v>1017.86035714285</v>
+        <v>925.73911764705804</v>
       </c>
       <c r="U6" s="6">
-        <v>58.801568696800601</v>
+        <v>103.42527576534199</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1070,7 +1070,7 @@
         <v>77</v>
       </c>
       <c r="Z6" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA6" s="8">
         <v>45500</v>
@@ -1082,7 +1082,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1090,64 +1090,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C7" s="5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D7" s="5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E7" s="5">
-        <v>2465.73</v>
+        <v>2745.53</v>
       </c>
       <c r="F7" s="5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
       </c>
       <c r="H7" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I7" s="5">
         <v>7</v>
       </c>
       <c r="J7" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K7" s="5">
-        <v>74.719090909090895</v>
+        <v>78.443714285714293</v>
       </c>
       <c r="L7" s="5">
-        <v>352.24714285714202</v>
+        <v>392.21857142857101</v>
       </c>
       <c r="M7" s="5">
-        <v>906.8417872192</v>
+        <v>1138.9957494545599</v>
       </c>
       <c r="N7" s="6">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="O7" s="6">
-        <v>7062.2</v>
+        <v>7811.8</v>
       </c>
       <c r="P7" s="6">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="Q7" s="6">
+        <v>7</v>
+      </c>
+      <c r="R7" s="6">
         <v>5</v>
       </c>
-      <c r="R7" s="6">
-        <v>4</v>
-      </c>
       <c r="S7" s="6">
-        <v>128.403636363636</v>
+        <v>116.594029850746</v>
       </c>
       <c r="T7" s="6">
-        <v>1412.44</v>
+        <v>1115.9714285714199</v>
       </c>
       <c r="U7" s="6">
-        <v>364.834329245844</v>
+        <v>465.38505850124102</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1162,7 +1162,7 @@
         <v>29</v>
       </c>
       <c r="Z7" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA7" s="8">
         <v>10000</v>
@@ -1174,7 +1174,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1191,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>877.36</v>
+        <v>977.78</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1209,20 +1209,20 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>877.36</v>
+        <v>977.78</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
         <v>-100</v>
       </c>
       <c r="N8" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>969.16</v>
+        <v>1073.06</v>
       </c>
       <c r="P8" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8" s="6">
         <v>1</v>
@@ -1231,10 +1231,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>484.58</v>
+        <v>357.68666666666599</v>
       </c>
       <c r="T8" s="6">
-        <v>969.16</v>
+        <v>1073.06</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1264,7 +1264,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1281,7 +1281,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="5">
-        <v>3046.96</v>
+        <v>3346.18</v>
       </c>
       <c r="F9" s="5">
         <v>7</v>
@@ -1299,19 +1299,19 @@
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>435.28</v>
+        <v>478.025714285714</v>
       </c>
       <c r="L9" s="5">
-        <v>1523.48</v>
+        <v>1673.09</v>
       </c>
       <c r="M9" s="5">
-        <v>156.517972011447</v>
+        <v>133.57978351433499</v>
       </c>
       <c r="N9" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O9" s="6">
-        <v>2780.45</v>
+        <v>3102.56</v>
       </c>
       <c r="P9" s="6">
         <v>8</v>
@@ -1323,13 +1323,13 @@
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>347.55624999999998</v>
+        <v>387.82</v>
       </c>
       <c r="T9" s="6">
-        <v>926.81666666666604</v>
+        <v>1034.1866666666599</v>
       </c>
       <c r="U9" s="6">
-        <v>91.731554244816493</v>
+        <v>71.825847042442305</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1350,7 +1350,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1370,25 +1370,25 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" s="6">
-        <v>988.8</v>
+        <v>1065.26</v>
       </c>
       <c r="P10" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" s="6">
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>247.2</v>
+        <v>213.05199999999999</v>
       </c>
       <c r="T10" s="6">
-        <v>494.4</v>
+        <v>355.08666666666602</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1406,7 +1406,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1423,7 +1423,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="5">
-        <v>1574.96</v>
+        <v>1732.77</v>
       </c>
       <c r="F11" s="5">
         <v>2</v>
@@ -1435,17 +1435,15 @@
         <v>2</v>
       </c>
       <c r="I11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="5">
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>787.48</v>
-      </c>
-      <c r="L11" s="5">
-        <v>1574.96</v>
-      </c>
+        <v>866.38499999999999</v>
+      </c>
+      <c r="L11" s="5"/>
       <c r="M11" s="5">
         <v>-100</v>
       </c>
@@ -1453,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="6">
-        <v>519.49</v>
+        <v>583.28</v>
       </c>
       <c r="P11" s="6">
         <v>1</v>
@@ -1465,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>519.49</v>
+        <v>583.28</v>
       </c>
       <c r="T11" s="6">
-        <v>519.49</v>
+        <v>583.28</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1498,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1521,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6">
-        <v>140.46</v>
+        <v>156.75</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1542,7 +1540,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1559,7 +1557,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="5">
-        <v>3131.83</v>
+        <v>3470.16</v>
       </c>
       <c r="F13" s="5">
         <v>11</v>
@@ -1574,37 +1572,37 @@
         <v>4</v>
       </c>
       <c r="J13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" s="5">
-        <v>284.71181818181799</v>
+        <v>315.46909090909003</v>
       </c>
       <c r="L13" s="5">
-        <v>782.95749999999998</v>
+        <v>867.54</v>
       </c>
       <c r="M13" s="5">
-        <v>59.140183215564001</v>
+        <v>268.92016506443503</v>
       </c>
       <c r="N13" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O13" s="6">
-        <v>1574.04</v>
+        <v>1734.81</v>
       </c>
       <c r="P13" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q13" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R13" s="6">
         <v>0</v>
       </c>
       <c r="S13" s="6">
-        <v>131.16999999999999</v>
+        <v>115.654</v>
       </c>
       <c r="T13" s="6">
-        <v>224.862857142857</v>
+        <v>216.85124999999999</v>
       </c>
       <c r="U13" s="6">
         <v>-100</v>
@@ -1634,7 +1632,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1657,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>305.18</v>
+        <v>340.93</v>
       </c>
       <c r="P14" s="6">
         <v>1</v>
@@ -1669,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>305.18</v>
+        <v>340.93</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1694,7 +1692,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1738,7 +1736,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1761,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="6">
-        <v>451.93</v>
+        <v>504.08</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1788,7 +1786,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1805,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>582.97</v>
+        <v>733.88</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1819,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="6">
-        <v>374</v>
+        <v>380.73</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
@@ -1852,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1872,13 +1870,13 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O18" s="6">
-        <v>1456.38</v>
+        <v>1609.86</v>
       </c>
       <c r="P18" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q18" s="6">
         <v>1</v>
@@ -1887,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>291.27600000000001</v>
+        <v>268.31</v>
       </c>
       <c r="T18" s="6">
-        <v>1456.38</v>
+        <v>1609.86</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1914,7 +1912,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1931,7 +1929,7 @@
         <v>5</v>
       </c>
       <c r="E19" s="5">
-        <v>1365.65</v>
+        <v>1492.92</v>
       </c>
       <c r="F19" s="5">
         <v>2</v>
@@ -1949,37 +1947,37 @@
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>682.82500000000005</v>
+        <v>746.46</v>
       </c>
       <c r="L19" s="5">
-        <v>1365.65</v>
+        <v>1492.92</v>
       </c>
       <c r="M19" s="5">
         <v>-100</v>
       </c>
       <c r="N19" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" s="6">
-        <v>1621.6</v>
+        <v>1795.01</v>
       </c>
       <c r="P19" s="6">
         <v>8</v>
       </c>
       <c r="Q19" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R19" s="6">
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>202.7</v>
+        <v>224.37625</v>
       </c>
       <c r="T19" s="6">
-        <v>1621.6</v>
+        <v>897.505</v>
       </c>
       <c r="U19" s="6">
-        <v>337.84287123828301</v>
+        <v>295.54431451635298</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2006,7 +2004,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2026,13 +2024,13 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O20" s="6">
-        <v>1714.48</v>
+        <v>1877.32</v>
       </c>
       <c r="P20" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="6">
         <v>2</v>
@@ -2041,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>342.89600000000002</v>
+        <v>312.88666666666597</v>
       </c>
       <c r="T20" s="6">
-        <v>857.24</v>
+        <v>938.66</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2068,7 +2066,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2088,28 +2086,28 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O21" s="6">
-        <v>4582.07</v>
+        <v>5007.01</v>
       </c>
       <c r="P21" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q21" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R21" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" s="6">
-        <v>286.37937499999998</v>
+        <v>278.16722222222199</v>
       </c>
       <c r="T21" s="6">
-        <v>1527.35666666666</v>
+        <v>1251.7525000000001</v>
       </c>
       <c r="U21" s="6">
-        <v>-100</v>
+        <v>48.403138799403202</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2124,13 +2122,13 @@
         <v>5</v>
       </c>
       <c r="Z21" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21" s="8"/>
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2147,7 +2145,7 @@
         <v>6</v>
       </c>
       <c r="E22" s="5">
-        <v>1265.99</v>
+        <v>1360.77</v>
       </c>
       <c r="F22" s="5">
         <v>5</v>
@@ -2165,10 +2163,10 @@
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>253.19800000000001</v>
+        <v>272.154</v>
       </c>
       <c r="L22" s="5">
-        <v>421.99666666666599</v>
+        <v>453.59</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2177,7 +2175,7 @@
         <v>3</v>
       </c>
       <c r="O22" s="6">
-        <v>1290.69</v>
+        <v>1519.63</v>
       </c>
       <c r="P22" s="6">
         <v>3</v>
@@ -2189,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>430.23</v>
+        <v>506.54333333333301</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2220,7 +2218,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2240,13 +2238,13 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O23" s="6">
-        <v>1711.26</v>
+        <v>1884.04</v>
       </c>
       <c r="P23" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q23" s="6">
         <v>1</v>
@@ -2255,10 +2253,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>213.9075</v>
+        <v>209.33777777777701</v>
       </c>
       <c r="T23" s="6">
-        <v>1711.26</v>
+        <v>1884.04</v>
       </c>
       <c r="U23" s="6">
         <v>-100</v>
@@ -2286,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2309,7 +2307,7 @@
         <v>3</v>
       </c>
       <c r="O24" s="6">
-        <v>955.16</v>
+        <v>1026.26</v>
       </c>
       <c r="P24" s="6">
         <v>3</v>
@@ -2321,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>318.38666666666597</v>
+        <v>342.08666666666602</v>
       </c>
       <c r="T24" s="6">
-        <v>955.16</v>
+        <v>1026.26</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2348,7 +2346,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46153</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3654,10 +3652,10 @@
         <v>18</v>
       </c>
       <c r="D19" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" s="10">
         <v>3</v>
@@ -3678,19 +3676,19 @@
         <v>7816</v>
       </c>
       <c r="L19" s="10">
-        <v>11.48</v>
+        <v>12.7</v>
       </c>
       <c r="M19" s="10">
-        <v>20.77</v>
+        <v>14.31</v>
       </c>
       <c r="N19" s="10">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="O19" s="10">
         <v>33.33</v>
       </c>
       <c r="P19" s="10">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -3728,10 +3726,10 @@
         <v>4984</v>
       </c>
       <c r="L20" s="10">
-        <v>18.03</v>
+        <v>17.46</v>
       </c>
       <c r="M20" s="10">
-        <v>13.25</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="N20" s="10">
         <v>27.27</v>
@@ -3778,10 +3776,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="M21" s="10">
-        <v>14.38</v>
+        <v>9.9</v>
       </c>
       <c r="N21" s="10">
         <v>0</v>
@@ -3826,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -3874,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="M23" s="10">
         <v>0</v>
@@ -3924,7 +3922,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -3950,10 +3948,10 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E25" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F25" s="10">
         <v>0</v>
@@ -3965,26 +3963,26 @@
         <v>3</v>
       </c>
       <c r="I25" s="10">
-        <v>19416</v>
+        <v>20397</v>
       </c>
       <c r="J25" s="10">
         <v>3</v>
       </c>
       <c r="K25" s="10">
-        <v>19416</v>
+        <v>20397</v>
       </c>
       <c r="L25" s="10">
-        <v>34.43</v>
+        <v>34.92</v>
       </c>
       <c r="M25" s="10">
-        <v>51.6</v>
+        <v>37.33</v>
       </c>
       <c r="N25" s="10">
         <v>0</v>
       </c>
       <c r="O25" s="10"/>
       <c r="P25" s="10">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
@@ -4007,34 +4005,34 @@
         <v>1</v>
       </c>
       <c r="G26" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="10">
-        <v>0</v>
+        <v>7911</v>
       </c>
       <c r="J26" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" s="10">
-        <v>0</v>
+        <v>7911</v>
       </c>
       <c r="L26" s="10">
-        <v>4.92</v>
+        <v>4.76</v>
       </c>
       <c r="M26" s="10">
-        <v>0</v>
+        <v>14.48</v>
       </c>
       <c r="N26" s="10">
         <v>33.33</v>
       </c>
       <c r="O26" s="10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26" s="10">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -4072,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="10">
-        <v>6.56</v>
+        <v>6.35</v>
       </c>
       <c r="M27" s="10">
         <v>0</v>
@@ -4107,34 +4105,34 @@
         <v>5</v>
       </c>
       <c r="G28" s="10">
+        <v>3</v>
+      </c>
+      <c r="H28" s="10">
         <v>2</v>
       </c>
-      <c r="H28" s="10">
-        <v>0</v>
-      </c>
       <c r="I28" s="10">
-        <v>0</v>
+        <v>8117.12</v>
       </c>
       <c r="J28" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" s="10">
-        <v>0</v>
+        <v>8117.12</v>
       </c>
       <c r="L28" s="10">
-        <v>9.84</v>
+        <v>9.52</v>
       </c>
       <c r="M28" s="10">
-        <v>0</v>
+        <v>14.86</v>
       </c>
       <c r="N28" s="10">
         <v>83.33</v>
       </c>
       <c r="O28" s="10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="P28" s="10">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
@@ -4154,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="10">
         <v>0</v>
@@ -4172,17 +4170,15 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
       </c>
       <c r="N29" s="10">
-        <v>100</v>
-      </c>
-      <c r="O29" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O29" s="10"/>
       <c r="P29" s="10">
         <v>0</v>
       </c>
@@ -4222,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="10">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="M30" s="10">
         <v>0</v>
@@ -4272,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="M31" s="10">
         <v>0</v>
@@ -4489,7 +4485,7 @@
         <v>129</v>
       </c>
       <c r="G8" s="5">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H8" s="5">
         <v>34</v>
@@ -4935,28 +4931,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1065</v>
+        <v>1193</v>
       </c>
       <c r="E21" s="10">
-        <v>2465.73</v>
+        <v>2745.53</v>
       </c>
       <c r="F21" s="10">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G21" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H21" s="10">
         <v>7</v>
       </c>
       <c r="I21" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J21" s="10">
-        <v>24826</v>
+        <v>34017</v>
       </c>
       <c r="K21" s="10">
-        <v>9.07</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5530,10 +5526,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E38" s="10">
-        <v>877.36</v>
+        <v>977.78</v>
       </c>
       <c r="F38" s="10">
         <v>2</v>
@@ -6125,10 +6121,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="E55" s="10">
-        <v>3046.96</v>
+        <v>3346.18</v>
       </c>
       <c r="F55" s="10">
         <v>12</v>
@@ -6146,7 +6142,7 @@
         <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -7120,10 +7116,10 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="E84" s="10">
-        <v>1574.96</v>
+        <v>1732.77</v>
       </c>
       <c r="F84" s="10">
         <v>3</v>
@@ -7269,7 +7265,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -7599,10 +7595,10 @@
         <v>17</v>
       </c>
       <c r="G98" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H98" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I98" s="10">
         <v>6</v>
@@ -8010,10 +8006,10 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="E110" s="10">
-        <v>3131.83</v>
+        <v>3470.16</v>
       </c>
       <c r="F110" s="10">
         <v>20</v>
@@ -8025,13 +8021,13 @@
         <v>5</v>
       </c>
       <c r="I110" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J110" s="10">
-        <v>4984</v>
+        <v>12802.12</v>
       </c>
       <c r="K110" s="10">
-        <v>0.59</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -8729,7 +8725,7 @@
         <v>6</v>
       </c>
       <c r="G132" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H132" s="10">
         <v>2</v>
@@ -9525,10 +9521,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E155" s="10">
-        <v>582.97</v>
+        <v>733.88</v>
       </c>
       <c r="F155" s="10">
         <v>0</v>
@@ -9559,7 +9555,7 @@
         <v>30</v>
       </c>
       <c r="G156" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H156" s="10">
         <v>2</v>
@@ -10601,10 +10597,10 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="E186" s="10">
-        <v>1365.65</v>
+        <v>1492.92</v>
       </c>
       <c r="F186" s="10">
         <v>8</v>
@@ -12176,10 +12172,10 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="E231" s="10">
-        <v>1265.99</v>
+        <v>1360.77</v>
       </c>
       <c r="F231" s="10">
         <v>8</v>
@@ -16882,10 +16878,10 @@
         <v>13</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -17300,10 +17296,10 @@
         <v>13</v>
       </c>
       <c r="E53">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F53">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -17315,13 +17311,13 @@
         <v>3</v>
       </c>
       <c r="J53">
-        <v>19416</v>
+        <v>20397</v>
       </c>
       <c r="K53">
         <v>3</v>
       </c>
       <c r="L53">
-        <v>19416</v>
+        <v>20397</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -17461,19 +17457,19 @@
         <v>1</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>7911</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>7911</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -17578,16 +17574,16 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -17613,19 +17609,19 @@
         <v>1</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -17686,7 +17682,7 @@
         <v>1</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63">
         <v>0</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10CB984D-2915-4566-8118-027463D179A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5274C731-1BFD-4CF7-BE6D-32827116D026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="2124" windowWidth="29016" windowHeight="15696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="110">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -998,25 +998,25 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C6" s="5">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D6" s="5">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E6" s="5">
-        <v>15859.99</v>
+        <v>17347.2</v>
       </c>
       <c r="F6" s="5">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G6" s="5">
         <v>11</v>
       </c>
       <c r="H6" s="5">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I6" s="5">
         <v>17</v>
@@ -1025,37 +1025,37 @@
         <v>9</v>
       </c>
       <c r="K6" s="5">
-        <v>251.745873015873</v>
+        <v>255.10588235294099</v>
       </c>
       <c r="L6" s="5">
-        <v>932.94058823529394</v>
+        <v>1020.42352941176</v>
       </c>
       <c r="M6" s="5">
-        <v>244.48394986377599</v>
+        <v>214.95065486072599</v>
       </c>
       <c r="N6" s="6">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="O6" s="6">
-        <v>31475.129999999899</v>
+        <v>34408.53</v>
       </c>
       <c r="P6" s="6">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="Q6" s="6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R6" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S6" s="6">
-        <v>205.719803921568</v>
+        <v>211.095276073619</v>
       </c>
       <c r="T6" s="6">
-        <v>925.73911764705804</v>
+        <v>955.79250000000002</v>
       </c>
       <c r="U6" s="6">
-        <v>103.42527576534199</v>
+        <v>104.23531606842801</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1070,7 +1070,7 @@
         <v>77</v>
       </c>
       <c r="Z6" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA6" s="8">
         <v>45500</v>
@@ -1082,7 +1082,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1090,64 +1090,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C7" s="5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E7" s="5">
-        <v>2745.53</v>
+        <v>3010.89</v>
       </c>
       <c r="F7" s="5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G7" s="5">
         <v>4</v>
       </c>
       <c r="H7" s="5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I7" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" s="5">
         <v>6</v>
       </c>
       <c r="K7" s="5">
-        <v>78.443714285714293</v>
+        <v>81.375405405405402</v>
       </c>
       <c r="L7" s="5">
-        <v>392.21857142857101</v>
+        <v>376.36124999999998</v>
       </c>
       <c r="M7" s="5">
-        <v>1138.9957494545599</v>
+        <v>1029.7988302461999</v>
       </c>
       <c r="N7" s="6">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O7" s="6">
-        <v>7811.8</v>
+        <v>8508.8799999999992</v>
       </c>
       <c r="P7" s="6">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q7" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R7" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S7" s="6">
-        <v>116.594029850746</v>
+        <v>119.84338028169</v>
       </c>
       <c r="T7" s="6">
-        <v>1115.9714285714199</v>
+        <v>1063.6099999999999</v>
       </c>
       <c r="U7" s="6">
-        <v>465.38505850124102</v>
+        <v>492.47221726008598</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1162,7 +1162,7 @@
         <v>29</v>
       </c>
       <c r="Z7" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA7" s="8">
         <v>10000</v>
@@ -1174,7 +1174,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1182,16 +1182,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5">
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>977.78</v>
+        <v>1081.52</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>977.78</v>
+        <v>1081.52</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1219,7 +1219,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>1073.06</v>
+        <v>1176.81</v>
       </c>
       <c r="P8" s="6">
         <v>3</v>
@@ -1231,10 +1231,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>357.68666666666599</v>
+        <v>392.27</v>
       </c>
       <c r="T8" s="6">
-        <v>1073.06</v>
+        <v>1176.81</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1264,7 +1264,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1272,16 +1272,16 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="5">
         <v>8</v>
       </c>
       <c r="E9" s="5">
-        <v>3346.18</v>
+        <v>3545.1</v>
       </c>
       <c r="F9" s="5">
         <v>7</v>
@@ -1299,19 +1299,19 @@
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>478.025714285714</v>
+        <v>506.44285714285701</v>
       </c>
       <c r="L9" s="5">
-        <v>1673.09</v>
+        <v>1772.55</v>
       </c>
       <c r="M9" s="5">
-        <v>133.57978351433499</v>
+        <v>120.47332938421999</v>
       </c>
       <c r="N9" s="6">
         <v>13</v>
       </c>
       <c r="O9" s="6">
-        <v>3102.56</v>
+        <v>3416.28</v>
       </c>
       <c r="P9" s="6">
         <v>8</v>
@@ -1323,13 +1323,13 @@
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>387.82</v>
+        <v>427.03500000000003</v>
       </c>
       <c r="T9" s="6">
-        <v>1034.1866666666599</v>
+        <v>1138.76</v>
       </c>
       <c r="U9" s="6">
-        <v>71.825847042442305</v>
+        <v>56.046928237732203</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1350,7 +1350,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1373,22 +1373,22 @@
         <v>2</v>
       </c>
       <c r="O10" s="6">
-        <v>1065.26</v>
+        <v>1265.1500000000001</v>
       </c>
       <c r="P10" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R10" s="6">
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>213.05199999999999</v>
+        <v>210.85833333333301</v>
       </c>
       <c r="T10" s="6">
-        <v>355.08666666666602</v>
+        <v>316.28750000000002</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1406,7 +1406,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1423,7 +1423,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="5">
-        <v>1732.77</v>
+        <v>1891.01</v>
       </c>
       <c r="F11" s="5">
         <v>2</v>
@@ -1441,20 +1441,20 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>866.38499999999999</v>
+        <v>945.505</v>
       </c>
       <c r="L11" s="5"/>
       <c r="M11" s="5">
         <v>-100</v>
       </c>
       <c r="N11" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="6">
-        <v>583.28</v>
+        <v>648.92999999999995</v>
       </c>
       <c r="P11" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="6">
         <v>1</v>
@@ -1463,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>583.28</v>
+        <v>324.46499999999997</v>
       </c>
       <c r="T11" s="6">
-        <v>583.28</v>
+        <v>648.92999999999995</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1496,7 +1496,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6">
-        <v>156.75</v>
+        <v>174.98</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1540,7 +1540,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1557,7 +1557,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="5">
-        <v>3470.16</v>
+        <v>3801.13</v>
       </c>
       <c r="F13" s="5">
         <v>11</v>
@@ -1575,19 +1575,19 @@
         <v>2</v>
       </c>
       <c r="K13" s="5">
-        <v>315.46909090909003</v>
+        <v>345.55727272727199</v>
       </c>
       <c r="L13" s="5">
-        <v>867.54</v>
+        <v>950.28250000000003</v>
       </c>
       <c r="M13" s="5">
-        <v>268.92016506443503</v>
+        <v>236.797741724171</v>
       </c>
       <c r="N13" s="6">
         <v>12</v>
       </c>
       <c r="O13" s="6">
-        <v>1734.81</v>
+        <v>1838.2</v>
       </c>
       <c r="P13" s="6">
         <v>15</v>
@@ -1599,10 +1599,10 @@
         <v>0</v>
       </c>
       <c r="S13" s="6">
-        <v>115.654</v>
+        <v>122.546666666666</v>
       </c>
       <c r="T13" s="6">
-        <v>216.85124999999999</v>
+        <v>229.77500000000001</v>
       </c>
       <c r="U13" s="6">
         <v>-100</v>
@@ -1632,7 +1632,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1655,10 +1655,10 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>340.93</v>
+        <v>380.33</v>
       </c>
       <c r="P14" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="6">
         <v>0</v>
@@ -1667,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>340.93</v>
+        <v>190.16499999999999</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1692,7 +1692,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1736,7 +1736,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="6">
-        <v>504.08</v>
+        <v>531.53</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1786,7 +1786,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1803,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>733.88</v>
+        <v>860.18</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -1817,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="6">
-        <v>380.73</v>
+        <v>392.87</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1873,7 +1873,7 @@
         <v>6</v>
       </c>
       <c r="O18" s="6">
-        <v>1609.86</v>
+        <v>1762.49</v>
       </c>
       <c r="P18" s="6">
         <v>6</v>
@@ -1885,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>268.31</v>
+        <v>293.74833333333299</v>
       </c>
       <c r="T18" s="6">
-        <v>1609.86</v>
+        <v>1762.49</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1912,7 +1912,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1920,25 +1920,25 @@
         <v>36</v>
       </c>
       <c r="B19" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C19" s="5">
         <v>3</v>
       </c>
       <c r="D19" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="5">
-        <v>1492.92</v>
+        <v>1620.11</v>
       </c>
       <c r="F19" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="5">
         <v>0</v>
       </c>
       <c r="H19" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" s="5">
         <v>1</v>
@@ -1947,19 +1947,19 @@
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>746.46</v>
+        <v>540.03666666666595</v>
       </c>
       <c r="L19" s="5">
-        <v>1492.92</v>
+        <v>1620.11</v>
       </c>
       <c r="M19" s="5">
         <v>-100</v>
       </c>
       <c r="N19" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O19" s="6">
-        <v>1795.01</v>
+        <v>1962.34</v>
       </c>
       <c r="P19" s="6">
         <v>8</v>
@@ -1971,13 +1971,13 @@
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>224.37625</v>
+        <v>245.29249999999999</v>
       </c>
       <c r="T19" s="6">
-        <v>897.505</v>
+        <v>981.17</v>
       </c>
       <c r="U19" s="6">
-        <v>295.54431451635298</v>
+        <v>261.81599518941601</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2004,7 +2004,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2024,13 +2024,13 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O20" s="6">
-        <v>1877.32</v>
+        <v>2047.77</v>
       </c>
       <c r="P20" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q20" s="6">
         <v>2</v>
@@ -2039,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>312.88666666666597</v>
+        <v>292.538571428571</v>
       </c>
       <c r="T20" s="6">
-        <v>938.66</v>
+        <v>1023.885</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2066,7 +2066,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2089,7 +2089,7 @@
         <v>24</v>
       </c>
       <c r="O21" s="6">
-        <v>5007.01</v>
+        <v>5429.66</v>
       </c>
       <c r="P21" s="6">
         <v>18</v>
@@ -2101,13 +2101,13 @@
         <v>1</v>
       </c>
       <c r="S21" s="6">
-        <v>278.16722222222199</v>
+        <v>301.64777777777698</v>
       </c>
       <c r="T21" s="6">
-        <v>1251.7525000000001</v>
+        <v>1357.415</v>
       </c>
       <c r="U21" s="6">
-        <v>48.403138799403202</v>
+        <v>36.851294556196798</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2128,7 +2128,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2136,37 +2136,37 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C22" s="5">
         <v>2</v>
       </c>
       <c r="D22" s="5">
+        <v>8</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1537.26</v>
+      </c>
+      <c r="F22" s="5">
+        <v>7</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
         <v>6</v>
       </c>
-      <c r="E22" s="5">
-        <v>1360.77</v>
-      </c>
-      <c r="F22" s="5">
-        <v>5</v>
-      </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
-        <v>4</v>
-      </c>
       <c r="I22" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" s="5">
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>272.154</v>
+        <v>219.608571428571</v>
       </c>
       <c r="L22" s="5">
-        <v>453.59</v>
+        <v>768.63</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2175,10 +2175,10 @@
         <v>3</v>
       </c>
       <c r="O22" s="6">
-        <v>1519.63</v>
+        <v>1710.78</v>
       </c>
       <c r="P22" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -2187,7 +2187,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>506.54333333333301</v>
+        <v>427.69499999999999</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2218,7 +2218,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2238,13 +2238,13 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O23" s="6">
-        <v>1884.04</v>
+        <v>2054.44</v>
       </c>
       <c r="P23" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q23" s="6">
         <v>1</v>
@@ -2253,10 +2253,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>209.33777777777701</v>
+        <v>205.44399999999999</v>
       </c>
       <c r="T23" s="6">
-        <v>1884.04</v>
+        <v>2054.44</v>
       </c>
       <c r="U23" s="6">
         <v>-100</v>
@@ -2284,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2307,7 +2307,7 @@
         <v>3</v>
       </c>
       <c r="O24" s="6">
-        <v>1026.26</v>
+        <v>1104.3499999999999</v>
       </c>
       <c r="P24" s="6">
         <v>3</v>
@@ -2319,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>342.08666666666602</v>
+        <v>368.11666666666599</v>
       </c>
       <c r="T24" s="6">
-        <v>1026.26</v>
+        <v>1104.3499999999999</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2346,7 +2346,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3676,7 +3676,7 @@
         <v>7816</v>
       </c>
       <c r="L19" s="10">
-        <v>12.7</v>
+        <v>11.76</v>
       </c>
       <c r="M19" s="10">
         <v>14.31</v>
@@ -3726,7 +3726,7 @@
         <v>4984</v>
       </c>
       <c r="L20" s="10">
-        <v>17.46</v>
+        <v>16.18</v>
       </c>
       <c r="M20" s="10">
         <v>9.1199999999999992</v>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>3.17</v>
+        <v>2.94</v>
       </c>
       <c r="M21" s="10">
         <v>9.9</v>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="M23" s="10">
         <v>0</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B24" s="19">
         <v>2026</v>
@@ -3898,13 +3898,13 @@
         <v>18</v>
       </c>
       <c r="D24" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="10">
         <v>0</v>
@@ -3922,24 +3922,22 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>3.17</v>
+        <v>1.47</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
       </c>
       <c r="N24" s="10">
-        <v>50</v>
-      </c>
-      <c r="O24" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O24" s="10"/>
       <c r="P24" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B25" s="19">
         <v>2026</v>
@@ -3948,46 +3946,48 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E25" s="10">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F25" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H25" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I25" s="10">
-        <v>20397</v>
+        <v>0</v>
       </c>
       <c r="J25" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K25" s="10">
-        <v>20397</v>
+        <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>34.92</v>
+        <v>4.41</v>
       </c>
       <c r="M25" s="10">
-        <v>37.33</v>
+        <v>0</v>
       </c>
       <c r="N25" s="10">
-        <v>0</v>
-      </c>
-      <c r="O25" s="10"/>
+        <v>33.33</v>
+      </c>
+      <c r="O25" s="10">
+        <v>0</v>
+      </c>
       <c r="P25" s="10">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B26" s="19">
         <v>2026</v>
@@ -3996,48 +3996,46 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
+        <v>24</v>
+      </c>
+      <c r="E26" s="10">
+        <v>23</v>
+      </c>
+      <c r="F26" s="10">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10">
+        <v>6</v>
+      </c>
+      <c r="H26" s="10">
         <v>3</v>
       </c>
-      <c r="E26" s="10">
+      <c r="I26" s="10">
+        <v>20397</v>
+      </c>
+      <c r="J26" s="10">
         <v>3</v>
       </c>
-      <c r="F26" s="10">
-        <v>1</v>
-      </c>
-      <c r="G26" s="10">
-        <v>1</v>
-      </c>
-      <c r="H26" s="10">
-        <v>1</v>
-      </c>
-      <c r="I26" s="10">
-        <v>7911</v>
-      </c>
-      <c r="J26" s="10">
-        <v>1</v>
-      </c>
       <c r="K26" s="10">
-        <v>7911</v>
+        <v>20397</v>
       </c>
       <c r="L26" s="10">
-        <v>4.76</v>
+        <v>35.29</v>
       </c>
       <c r="M26" s="10">
-        <v>14.48</v>
+        <v>37.33</v>
       </c>
       <c r="N26" s="10">
-        <v>33.33</v>
-      </c>
-      <c r="O26" s="10">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O26" s="10"/>
       <c r="P26" s="10">
-        <v>33.33</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B27" s="19">
         <v>2026</v>
@@ -4046,7 +4044,7 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" s="10">
         <v>3</v>
@@ -4055,39 +4053,39 @@
         <v>1</v>
       </c>
       <c r="G27" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="10">
-        <v>0</v>
+        <v>7911</v>
       </c>
       <c r="J27" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="10">
-        <v>0</v>
+        <v>7911</v>
       </c>
       <c r="L27" s="10">
-        <v>6.35</v>
+        <v>4.41</v>
       </c>
       <c r="M27" s="10">
-        <v>0</v>
+        <v>14.48</v>
       </c>
       <c r="N27" s="10">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="O27" s="10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27" s="10">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B28" s="19">
         <v>2026</v>
@@ -4096,48 +4094,48 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E28" s="10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F28" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G28" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" s="10">
-        <v>8117.12</v>
+        <v>0</v>
       </c>
       <c r="J28" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" s="10">
-        <v>8117.12</v>
+        <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>9.52</v>
+        <v>5.88</v>
       </c>
       <c r="M28" s="10">
-        <v>14.86</v>
+        <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>83.33</v>
+        <v>50</v>
       </c>
       <c r="O28" s="10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P28" s="10">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B29" s="19">
         <v>2026</v>
@@ -4146,46 +4144,48 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E29" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F29" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G29" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29" s="10">
-        <v>0</v>
+        <v>8117.12</v>
       </c>
       <c r="J29" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" s="10">
-        <v>0</v>
+        <v>8117.12</v>
       </c>
       <c r="L29" s="10">
-        <v>1.59</v>
+        <v>10.29</v>
       </c>
       <c r="M29" s="10">
-        <v>0</v>
+        <v>14.86</v>
       </c>
       <c r="N29" s="10">
-        <v>0</v>
-      </c>
-      <c r="O29" s="10"/>
+        <v>57.14</v>
+      </c>
+      <c r="O29" s="10">
+        <v>50</v>
+      </c>
       <c r="P29" s="10">
-        <v>0</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B30" s="19">
         <v>2026</v>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="10">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="M30" s="10">
         <v>0</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" s="19">
         <v>2026</v>
@@ -4268,7 +4268,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="M31" s="10">
         <v>0</v>
@@ -4284,21 +4284,54 @@
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
+      <c r="A32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="19">
+        <v>2026</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="10">
+        <v>1</v>
+      </c>
+      <c r="E32" s="10">
+        <v>1</v>
+      </c>
+      <c r="F32" s="10">
+        <v>1</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0</v>
+      </c>
+      <c r="H32" s="10">
+        <v>0</v>
+      </c>
+      <c r="I32" s="10">
+        <v>0</v>
+      </c>
+      <c r="J32" s="10">
+        <v>0</v>
+      </c>
+      <c r="K32" s="10">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10">
+        <v>1.47</v>
+      </c>
+      <c r="M32" s="10">
+        <v>0</v>
+      </c>
+      <c r="N32" s="10">
+        <v>100</v>
+      </c>
+      <c r="O32" s="10">
+        <v>0</v>
+      </c>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -4870,7 +4903,7 @@
         <v>164</v>
       </c>
       <c r="G19" s="5">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H19" s="5">
         <v>21</v>
@@ -4931,19 +4964,19 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1193</v>
+        <v>1303</v>
       </c>
       <c r="E21" s="10">
-        <v>2745.53</v>
+        <v>3010.89</v>
       </c>
       <c r="F21" s="10">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G21" s="10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H21" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="10">
         <v>6</v>
@@ -4952,7 +4985,7 @@
         <v>34017</v>
       </c>
       <c r="K21" s="10">
-        <v>11.39</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5526,13 +5559,13 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="E38" s="10">
-        <v>977.78</v>
+        <v>1081.52</v>
       </c>
       <c r="F38" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G38" s="10">
         <v>1</v>
@@ -6121,13 +6154,13 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="E55" s="10">
-        <v>3346.18</v>
+        <v>3545.1</v>
       </c>
       <c r="F55" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G55" s="10">
         <v>7</v>
@@ -6142,7 +6175,7 @@
         <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6295,7 +6328,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H60" s="10">
         <v>4</v>
@@ -7116,10 +7149,10 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="E84" s="10">
-        <v>1732.77</v>
+        <v>1891.01</v>
       </c>
       <c r="F84" s="10">
         <v>3</v>
@@ -7595,10 +7628,10 @@
         <v>17</v>
       </c>
       <c r="G98" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H98" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I98" s="10">
         <v>6</v>
@@ -8006,10 +8039,10 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="E110" s="10">
-        <v>3470.16</v>
+        <v>3801.13</v>
       </c>
       <c r="F110" s="10">
         <v>20</v>
@@ -8027,7 +8060,7 @@
         <v>12802.12</v>
       </c>
       <c r="K110" s="10">
-        <v>2.69</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -8725,7 +8758,7 @@
         <v>6</v>
       </c>
       <c r="G132" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H132" s="10">
         <v>2</v>
@@ -9521,10 +9554,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="E155" s="10">
-        <v>733.88</v>
+        <v>860.18</v>
       </c>
       <c r="F155" s="10">
         <v>0</v>
@@ -10597,16 +10630,16 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="E186" s="10">
-        <v>1492.92</v>
+        <v>1620.11</v>
       </c>
       <c r="F186" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G186" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H186" s="10">
         <v>1</v>
@@ -12172,16 +12205,16 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="E231" s="10">
-        <v>1360.77</v>
+        <v>1537.26</v>
       </c>
       <c r="F231" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G231" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H231" s="10">
         <v>3</v>
@@ -17208,7 +17241,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B51" s="18">
         <v>2026</v>
@@ -17217,7 +17250,7 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -17255,7 +17288,7 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -17264,7 +17297,7 @@
         <v>1</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -17284,7 +17317,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B53" s="18">
         <v>2026</v>
@@ -17293,31 +17326,31 @@
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E53">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J53">
-        <v>20397</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>20397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -17331,31 +17364,31 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>20397</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -17369,7 +17402,7 @@
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -17407,7 +17440,7 @@
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -17436,7 +17469,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B57" s="18">
         <v>2026</v>
@@ -17445,31 +17478,31 @@
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57">
-        <v>7911</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57">
-        <v>7911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
@@ -17483,36 +17516,36 @@
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>7911</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>7911</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B59" s="18">
         <v>2026</v>
@@ -17521,16 +17554,16 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -17550,7 +17583,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B60" s="18">
         <v>2026</v>
@@ -17562,28 +17595,28 @@
         <v>13</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -17597,16 +17630,16 @@
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -17615,13 +17648,13 @@
         <v>1</v>
       </c>
       <c r="J61">
-        <v>7818.1200000000008</v>
+        <v>299</v>
       </c>
       <c r="K61">
         <v>1</v>
       </c>
       <c r="L61">
-        <v>7818.1200000000008</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -17635,36 +17668,36 @@
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B63" s="18">
         <v>2026</v>
@@ -17673,19 +17706,19 @@
         <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -17702,7 +17735,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B64" s="18">
         <v>2026</v>
@@ -17711,7 +17744,7 @@
         <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E64">
         <v>1</v>
@@ -17740,7 +17773,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B65" s="18">
         <v>2026</v>
@@ -17777,8 +17810,42 @@
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B66" s="18"/>
-      <c r="C66" s="19"/>
+      <c r="A66" t="s">
+        <v>103</v>
+      </c>
+      <c r="B66" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B67" s="18"/>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5274C731-1BFD-4CF7-BE6D-32827116D026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A50355-3E20-4F4D-83BE-E162E941AF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="110">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -998,64 +998,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C6" s="5">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D6" s="5">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E6" s="5">
-        <v>17347.2</v>
+        <v>18820.73</v>
       </c>
       <c r="F6" s="5">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G6" s="5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H6" s="5">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I6" s="5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J6" s="5">
         <v>9</v>
       </c>
       <c r="K6" s="5">
-        <v>255.10588235294099</v>
+        <v>241.29141025640999</v>
       </c>
       <c r="L6" s="5">
-        <v>1020.42352941176</v>
+        <v>855.48772727272706</v>
       </c>
       <c r="M6" s="5">
-        <v>214.95065486072599</v>
+        <v>190.29224690009301</v>
       </c>
       <c r="N6" s="6">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="O6" s="6">
-        <v>34408.53</v>
+        <v>37404.179999999898</v>
       </c>
       <c r="P6" s="6">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="Q6" s="6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R6" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="S6" s="6">
-        <v>211.095276073619</v>
+        <v>207.80099999999899</v>
       </c>
       <c r="T6" s="6">
-        <v>955.79250000000002</v>
+        <v>935.10449999999901</v>
       </c>
       <c r="U6" s="6">
-        <v>104.23531606842801</v>
+        <v>166.42843126089099</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1070,7 +1070,7 @@
         <v>77</v>
       </c>
       <c r="Z6" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA6" s="8">
         <v>45500</v>
@@ -1082,7 +1082,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1090,64 +1090,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C7" s="5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D7" s="5">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E7" s="5">
-        <v>3010.89</v>
+        <v>3301.56</v>
       </c>
       <c r="F7" s="5">
+        <v>43</v>
+      </c>
+      <c r="G7" s="5">
+        <v>6</v>
+      </c>
+      <c r="H7" s="5">
         <v>37</v>
       </c>
-      <c r="G7" s="5">
-        <v>4</v>
-      </c>
-      <c r="H7" s="5">
-        <v>33</v>
-      </c>
       <c r="I7" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J7" s="5">
         <v>6</v>
       </c>
       <c r="K7" s="5">
-        <v>81.375405405405402</v>
+        <v>76.780465116279004</v>
       </c>
       <c r="L7" s="5">
-        <v>376.36124999999998</v>
+        <v>330.15600000000001</v>
       </c>
       <c r="M7" s="5">
-        <v>1029.7988302461999</v>
+        <v>930.33111619961403</v>
       </c>
       <c r="N7" s="6">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="O7" s="6">
-        <v>8508.8799999999992</v>
+        <v>9261.5</v>
       </c>
       <c r="P7" s="6">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="Q7" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R7" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S7" s="6">
-        <v>119.84338028169</v>
+        <v>114.33950617283899</v>
       </c>
       <c r="T7" s="6">
-        <v>1063.6099999999999</v>
+        <v>926.15</v>
       </c>
       <c r="U7" s="6">
-        <v>492.47221726008598</v>
+        <v>677.97063110727197</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1162,7 +1162,7 @@
         <v>29</v>
       </c>
       <c r="Z7" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AA7" s="8">
         <v>10000</v>
@@ -1174,7 +1174,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1191,7 +1191,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>1081.52</v>
+        <v>1140.1099999999999</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1081.52</v>
+        <v>1140.1099999999999</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1219,22 +1219,22 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>1176.81</v>
+        <v>1281.93</v>
       </c>
       <c r="P8" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" s="6">
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>392.27</v>
+        <v>320.48250000000002</v>
       </c>
       <c r="T8" s="6">
-        <v>1176.81</v>
+        <v>640.96500000000003</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1264,7 +1264,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1281,40 +1281,40 @@
         <v>8</v>
       </c>
       <c r="E9" s="5">
-        <v>3545.1</v>
+        <v>3857.66</v>
       </c>
       <c r="F9" s="5">
+        <v>8</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
         <v>7</v>
       </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>6</v>
-      </c>
       <c r="I9" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9" s="5">
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>506.44285714285701</v>
+        <v>482.20749999999998</v>
       </c>
       <c r="L9" s="5">
-        <v>1772.55</v>
+        <v>1285.8866666666599</v>
       </c>
       <c r="M9" s="5">
-        <v>120.47332938421999</v>
+        <v>102.609872306009</v>
       </c>
       <c r="N9" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O9" s="6">
-        <v>3416.28</v>
+        <v>3738.32</v>
       </c>
       <c r="P9" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q9" s="6">
         <v>3</v>
@@ -1323,13 +1323,13 @@
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>427.03500000000003</v>
+        <v>415.36888888888802</v>
       </c>
       <c r="T9" s="6">
-        <v>1138.76</v>
+        <v>1246.10666666666</v>
       </c>
       <c r="U9" s="6">
-        <v>56.046928237732203</v>
+        <v>42.604164437501296</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1350,7 +1350,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1373,7 +1373,7 @@
         <v>2</v>
       </c>
       <c r="O10" s="6">
-        <v>1265.1500000000001</v>
+        <v>1359.29</v>
       </c>
       <c r="P10" s="6">
         <v>6</v>
@@ -1385,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>210.85833333333301</v>
+        <v>226.54833333333301</v>
       </c>
       <c r="T10" s="6">
-        <v>316.28750000000002</v>
+        <v>339.82249999999999</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1406,7 +1406,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1414,36 +1414,38 @@
         <v>106</v>
       </c>
       <c r="B11" s="5">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>5</v>
+      </c>
+      <c r="E11" s="5">
+        <v>2054.27</v>
+      </c>
+      <c r="F11" s="5">
         <v>3</v>
       </c>
-      <c r="C11" s="5">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5">
-        <v>2</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1891.01</v>
-      </c>
-      <c r="F11" s="5">
-        <v>2</v>
-      </c>
       <c r="G11" s="5">
         <v>0</v>
       </c>
       <c r="H11" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="5">
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>945.505</v>
-      </c>
-      <c r="L11" s="5"/>
+        <v>684.75666666666598</v>
+      </c>
+      <c r="L11" s="5">
+        <v>2054.27</v>
+      </c>
       <c r="M11" s="5">
         <v>-100</v>
       </c>
@@ -1451,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="O11" s="6">
-        <v>648.92999999999995</v>
+        <v>707.05</v>
       </c>
       <c r="P11" s="6">
         <v>2</v>
@@ -1463,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>324.46499999999997</v>
+        <v>353.52499999999998</v>
       </c>
       <c r="T11" s="6">
-        <v>648.92999999999995</v>
+        <v>707.05</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1496,7 +1498,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1519,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6">
-        <v>174.98</v>
+        <v>189.36</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1540,7 +1542,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1548,25 +1550,25 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="5">
         <v>9</v>
       </c>
       <c r="D13" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="5">
-        <v>3801.13</v>
+        <v>4000.43</v>
       </c>
       <c r="F13" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G13" s="5">
         <v>4</v>
       </c>
       <c r="H13" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="5">
         <v>4</v>
@@ -1575,19 +1577,19 @@
         <v>2</v>
       </c>
       <c r="K13" s="5">
-        <v>345.55727272727199</v>
+        <v>333.36916666666599</v>
       </c>
       <c r="L13" s="5">
-        <v>950.28250000000003</v>
+        <v>1000.1075</v>
       </c>
       <c r="M13" s="5">
-        <v>236.797741724171</v>
+        <v>220.01859800071401</v>
       </c>
       <c r="N13" s="6">
         <v>12</v>
       </c>
       <c r="O13" s="6">
-        <v>1838.2</v>
+        <v>1984.87</v>
       </c>
       <c r="P13" s="6">
         <v>15</v>
@@ -1596,16 +1598,16 @@
         <v>8</v>
       </c>
       <c r="R13" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="6">
-        <v>122.546666666666</v>
+        <v>132.32466666666599</v>
       </c>
       <c r="T13" s="6">
-        <v>229.77500000000001</v>
+        <v>248.10874999999999</v>
       </c>
       <c r="U13" s="6">
-        <v>-100</v>
+        <v>290.05073380120598</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1620,7 +1622,7 @@
         <v>12</v>
       </c>
       <c r="Z13" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA13" s="8">
         <v>8000</v>
@@ -1632,7 +1634,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1655,7 +1657,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>380.33</v>
+        <v>427.48</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1667,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>190.16499999999999</v>
+        <v>213.74</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1692,7 +1694,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1736,7 +1738,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1759,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="6">
-        <v>531.53</v>
+        <v>583.26</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1786,7 +1788,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1794,30 +1796,46 @@
         <v>34</v>
       </c>
       <c r="B17" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5">
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>860.18</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
+        <v>895.09</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>895.09</v>
+      </c>
+      <c r="L17" s="5">
+        <v>895.09</v>
+      </c>
+      <c r="M17" s="5">
+        <v>-100</v>
+      </c>
       <c r="N17" s="6">
         <v>1</v>
       </c>
       <c r="O17" s="6">
-        <v>392.87</v>
+        <v>460.01</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
@@ -1850,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1870,25 +1888,25 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O18" s="6">
-        <v>1762.49</v>
+        <v>1916.27</v>
       </c>
       <c r="P18" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q18" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" s="6">
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>293.74833333333299</v>
+        <v>239.53375</v>
       </c>
       <c r="T18" s="6">
-        <v>1762.49</v>
+        <v>958.13499999999999</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1912,7 +1930,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1929,7 +1947,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="5">
-        <v>1620.11</v>
+        <v>1744</v>
       </c>
       <c r="F19" s="5">
         <v>3</v>
@@ -1947,22 +1965,22 @@
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>540.03666666666595</v>
+        <v>581.33333333333303</v>
       </c>
       <c r="L19" s="5">
-        <v>1620.11</v>
+        <v>1744</v>
       </c>
       <c r="M19" s="5">
         <v>-100</v>
       </c>
       <c r="N19" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O19" s="6">
-        <v>1962.34</v>
+        <v>2130.31</v>
       </c>
       <c r="P19" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q19" s="6">
         <v>2</v>
@@ -1971,13 +1989,13 @@
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>245.29249999999999</v>
+        <v>236.701111111111</v>
       </c>
       <c r="T19" s="6">
-        <v>981.17</v>
+        <v>1065.155</v>
       </c>
       <c r="U19" s="6">
-        <v>261.81599518941601</v>
+        <v>233.28764358238899</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2004,7 +2022,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2027,7 +2045,7 @@
         <v>7</v>
       </c>
       <c r="O20" s="6">
-        <v>2047.77</v>
+        <v>2218.0100000000002</v>
       </c>
       <c r="P20" s="6">
         <v>7</v>
@@ -2039,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>292.538571428571</v>
+        <v>316.858571428571</v>
       </c>
       <c r="T20" s="6">
-        <v>1023.885</v>
+        <v>1109.0050000000001</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2066,7 +2084,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2086,13 +2104,13 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O21" s="6">
-        <v>5429.66</v>
+        <v>5852.14</v>
       </c>
       <c r="P21" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q21" s="6">
         <v>4</v>
@@ -2101,13 +2119,13 @@
         <v>1</v>
       </c>
       <c r="S21" s="6">
-        <v>301.64777777777698</v>
+        <v>308.00736842105198</v>
       </c>
       <c r="T21" s="6">
-        <v>1357.415</v>
+        <v>1463.0350000000001</v>
       </c>
       <c r="U21" s="6">
-        <v>36.851294556196798</v>
+        <v>26.971671901219</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2128,7 +2146,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2145,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="5">
-        <v>1537.26</v>
+        <v>1827.61</v>
       </c>
       <c r="F22" s="5">
         <v>7</v>
@@ -2163,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>219.608571428571</v>
+        <v>261.087142857142</v>
       </c>
       <c r="L22" s="5">
-        <v>768.63</v>
+        <v>913.80499999999995</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2175,7 +2193,7 @@
         <v>3</v>
       </c>
       <c r="O22" s="6">
-        <v>1710.78</v>
+        <v>1857.38</v>
       </c>
       <c r="P22" s="6">
         <v>4</v>
@@ -2187,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>427.69499999999999</v>
+        <v>464.34500000000003</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2218,7 +2236,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2241,10 +2259,10 @@
         <v>18</v>
       </c>
       <c r="O23" s="6">
-        <v>2054.44</v>
+        <v>2225.1999999999998</v>
       </c>
       <c r="P23" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q23" s="6">
         <v>1</v>
@@ -2253,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>205.44399999999999</v>
+        <v>202.290909090909</v>
       </c>
       <c r="T23" s="6">
-        <v>2054.44</v>
+        <v>2225.1999999999998</v>
       </c>
       <c r="U23" s="6">
         <v>-100</v>
@@ -2284,7 +2302,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2307,7 +2325,7 @@
         <v>3</v>
       </c>
       <c r="O24" s="6">
-        <v>1104.3499999999999</v>
+        <v>1209.06</v>
       </c>
       <c r="P24" s="6">
         <v>3</v>
@@ -2319,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>368.11666666666599</v>
+        <v>403.02</v>
       </c>
       <c r="T24" s="6">
-        <v>1104.3499999999999</v>
+        <v>1209.06</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2346,7 +2364,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3652,13 +3670,13 @@
         <v>18</v>
       </c>
       <c r="D19" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F19" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G19" s="10">
         <v>3</v>
@@ -3676,19 +3694,19 @@
         <v>7816</v>
       </c>
       <c r="L19" s="10">
-        <v>11.76</v>
+        <v>12.82</v>
       </c>
       <c r="M19" s="10">
         <v>14.31</v>
       </c>
       <c r="N19" s="10">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="O19" s="10">
-        <v>33.33</v>
+        <v>20</v>
       </c>
       <c r="P19" s="10">
-        <v>12.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -3702,16 +3720,16 @@
         <v>18</v>
       </c>
       <c r="D20" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F20" s="10">
         <v>3</v>
       </c>
       <c r="G20" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="10">
         <v>1</v>
@@ -3726,19 +3744,19 @@
         <v>4984</v>
       </c>
       <c r="L20" s="10">
-        <v>16.18</v>
+        <v>15.38</v>
       </c>
       <c r="M20" s="10">
         <v>9.1199999999999992</v>
       </c>
       <c r="N20" s="10">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="O20" s="10">
         <v>33.33</v>
       </c>
       <c r="P20" s="10">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -3776,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>2.94</v>
+        <v>2.56</v>
       </c>
       <c r="M21" s="10">
         <v>9.9</v>
@@ -3824,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -3872,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="M23" s="10">
         <v>0</v>
@@ -3898,13 +3916,13 @@
         <v>18</v>
       </c>
       <c r="D24" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="10">
         <v>0</v>
@@ -3922,15 +3940,17 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>1.47</v>
+        <v>2.56</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
       </c>
       <c r="N24" s="10">
-        <v>0</v>
-      </c>
-      <c r="O24" s="10"/>
+        <v>50</v>
+      </c>
+      <c r="O24" s="10">
+        <v>0</v>
+      </c>
       <c r="P24" s="10">
         <v>0</v>
       </c>
@@ -3970,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>4.41</v>
+        <v>3.85</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -3996,16 +4016,16 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E26" s="10">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F26" s="10">
         <v>0</v>
       </c>
       <c r="G26" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H26" s="10">
         <v>3</v>
@@ -4020,7 +4040,7 @@
         <v>20397</v>
       </c>
       <c r="L26" s="10">
-        <v>35.29</v>
+        <v>37.18</v>
       </c>
       <c r="M26" s="10">
         <v>37.33</v>
@@ -4030,7 +4050,7 @@
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10">
-        <v>12.5</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -4068,7 +4088,7 @@
         <v>7911</v>
       </c>
       <c r="L27" s="10">
-        <v>4.41</v>
+        <v>3.85</v>
       </c>
       <c r="M27" s="10">
         <v>14.48</v>
@@ -4094,14 +4114,14 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
+        <v>5</v>
+      </c>
+      <c r="E28" s="10">
         <v>4</v>
       </c>
-      <c r="E28" s="10">
+      <c r="F28" s="10">
         <v>3</v>
       </c>
-      <c r="F28" s="10">
-        <v>2</v>
-      </c>
       <c r="G28" s="10">
         <v>0</v>
       </c>
@@ -4118,13 +4138,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>5.88</v>
+        <v>6.41</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O28" s="10">
         <v>0</v>
@@ -4168,7 +4188,7 @@
         <v>8117.12</v>
       </c>
       <c r="L29" s="10">
-        <v>10.29</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="M29" s="10">
         <v>14.86</v>
@@ -4218,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="10">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="M30" s="10">
         <v>0</v>
@@ -4268,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="M31" s="10">
         <v>0</v>
@@ -4318,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="10">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="M32" s="10">
         <v>0</v>
@@ -4903,7 +4923,7 @@
         <v>164</v>
       </c>
       <c r="G19" s="5">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" s="5">
         <v>21</v>
@@ -4941,7 +4961,7 @@
         <v>98</v>
       </c>
       <c r="H20" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I20" s="10">
         <v>7</v>
@@ -4964,19 +4984,19 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1303</v>
+        <v>1404</v>
       </c>
       <c r="E21" s="10">
-        <v>3010.89</v>
+        <v>3301.56</v>
       </c>
       <c r="F21" s="10">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G21" s="10">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H21" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I21" s="10">
         <v>6</v>
@@ -4985,7 +5005,7 @@
         <v>34017</v>
       </c>
       <c r="K21" s="10">
-        <v>10.3</v>
+        <v>9.3000000000000007</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5559,10 +5579,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E38" s="10">
-        <v>1081.52</v>
+        <v>1140.1099999999999</v>
       </c>
       <c r="F38" s="10">
         <v>3</v>
@@ -6154,19 +6174,19 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="E55" s="10">
-        <v>3545.1</v>
+        <v>3857.66</v>
       </c>
       <c r="F55" s="10">
         <v>13</v>
       </c>
       <c r="G55" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H55" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55" s="10">
         <v>1</v>
@@ -6175,7 +6195,7 @@
         <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -7149,16 +7169,16 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="E84" s="10">
-        <v>1891.01</v>
+        <v>2054.27</v>
       </c>
       <c r="F84" s="10">
+        <v>6</v>
+      </c>
+      <c r="G84" s="10">
         <v>3</v>
-      </c>
-      <c r="G84" s="10">
-        <v>2</v>
       </c>
       <c r="H84" s="10">
         <v>1</v>
@@ -8039,16 +8059,16 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="E110" s="10">
-        <v>3801.13</v>
+        <v>4000.43</v>
       </c>
       <c r="F110" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G110" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H110" s="10">
         <v>5</v>
@@ -8060,7 +8080,7 @@
         <v>12802.12</v>
       </c>
       <c r="K110" s="10">
-        <v>2.37</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9554,19 +9574,29 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E155" s="10">
-        <v>860.18</v>
+        <v>895.09</v>
       </c>
       <c r="F155" s="10">
-        <v>0</v>
-      </c>
-      <c r="G155" s="10"/>
-      <c r="H155" s="10"/>
-      <c r="I155" s="10"/>
-      <c r="J155" s="10"/>
-      <c r="K155" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="G155" s="10">
+        <v>1</v>
+      </c>
+      <c r="H155" s="10">
+        <v>1</v>
+      </c>
+      <c r="I155" s="10">
+        <v>0</v>
+      </c>
+      <c r="J155" s="10">
+        <v>0</v>
+      </c>
+      <c r="K155" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="10" t="s">
@@ -10630,10 +10660,10 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="E186" s="10">
-        <v>1620.11</v>
+        <v>1744</v>
       </c>
       <c r="F186" s="10">
         <v>10</v>
@@ -12205,10 +12235,10 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="E231" s="10">
-        <v>1537.26</v>
+        <v>1827.61</v>
       </c>
       <c r="F231" s="10">
         <v>10</v>
@@ -16911,13 +16941,13 @@
         <v>13</v>
       </c>
       <c r="E42">
+        <v>3</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42">
         <v>2</v>
-      </c>
-      <c r="F42">
-        <v>2</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -16949,13 +16979,13 @@
         <v>107</v>
       </c>
       <c r="E43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43">
         <v>2</v>
@@ -17063,16 +17093,16 @@
         <v>29</v>
       </c>
       <c r="E46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F46">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G46">
         <v>3</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -17250,7 +17280,7 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -17259,7 +17289,7 @@
         <v>1</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -17279,7 +17309,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B52" s="18">
         <v>2026</v>
@@ -17288,7 +17318,7 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E52">
         <v>1</v>
@@ -17326,19 +17356,19 @@
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -17355,7 +17385,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B54" s="18">
         <v>2026</v>
@@ -17364,31 +17394,31 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E54">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F54">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>20397</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L54">
-        <v>20397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -17402,31 +17432,31 @@
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J55">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>20397</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -17440,7 +17470,7 @@
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -17478,7 +17508,7 @@
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -17507,7 +17537,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B58" s="18">
         <v>2026</v>
@@ -17516,7 +17546,7 @@
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E58">
         <v>2</v>
@@ -17525,22 +17555,22 @@
         <v>2</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>7911</v>
+        <v>0</v>
       </c>
       <c r="K58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58">
-        <v>7911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -17554,36 +17584,36 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>7911</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>7911</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B60" s="18">
         <v>2026</v>
@@ -17592,16 +17622,16 @@
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -17621,7 +17651,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B61" s="18">
         <v>2026</v>
@@ -17633,28 +17663,28 @@
         <v>13</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -17668,16 +17698,16 @@
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -17686,13 +17716,13 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>7818.1200000000008</v>
+        <v>299</v>
       </c>
       <c r="K62">
         <v>1</v>
       </c>
       <c r="L62">
-        <v>7818.1200000000008</v>
+        <v>299</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -17706,13 +17736,13 @@
         <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -17721,21 +17751,21 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B64" s="18">
         <v>2026</v>
@@ -17744,19 +17774,19 @@
         <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -17773,7 +17803,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B65" s="18">
         <v>2026</v>
@@ -17782,7 +17812,7 @@
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -17811,7 +17841,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B66" s="18">
         <v>2026</v>
@@ -17848,8 +17878,42 @@
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B67" s="18"/>
-      <c r="C67" s="19"/>
+      <c r="A67" t="s">
+        <v>103</v>
+      </c>
+      <c r="B67" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B68" s="18"/>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A50355-3E20-4F4D-83BE-E162E941AF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A930C2-318D-4261-8478-34B6899F5847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="111">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>Corporate</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
@@ -998,64 +1001,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="C6" s="5">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D6" s="5">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="E6" s="5">
-        <v>18820.73</v>
+        <v>23180.32</v>
       </c>
       <c r="F6" s="5">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="G6" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="5">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="I6" s="5">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J6" s="5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K6" s="5">
-        <v>241.29141025640999</v>
+        <v>244.00336842105199</v>
       </c>
       <c r="L6" s="5">
-        <v>855.48772727272706</v>
+        <v>891.55076923076899</v>
       </c>
       <c r="M6" s="5">
-        <v>190.29224690009301</v>
+        <v>212.765828944552</v>
       </c>
       <c r="N6" s="6">
-        <v>188</v>
+        <v>224</v>
       </c>
       <c r="O6" s="6">
-        <v>37404.179999999898</v>
+        <v>45183.66</v>
       </c>
       <c r="P6" s="6">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="Q6" s="6">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R6" s="6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S6" s="6">
-        <v>207.80099999999899</v>
+        <v>210.15655813953401</v>
       </c>
       <c r="T6" s="6">
-        <v>935.10449999999901</v>
+        <v>1026.90136363636</v>
       </c>
       <c r="U6" s="6">
-        <v>166.42843126089099</v>
+        <v>157.038429379116</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1070,7 +1073,7 @@
         <v>77</v>
       </c>
       <c r="Z6" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AA6" s="8">
         <v>45500</v>
@@ -1082,7 +1085,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1090,64 +1093,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C7" s="5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D7" s="5">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E7" s="5">
-        <v>3301.56</v>
+        <v>4058.79</v>
       </c>
       <c r="F7" s="5">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G7" s="5">
         <v>6</v>
       </c>
       <c r="H7" s="5">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I7" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K7" s="5">
-        <v>76.780465116279004</v>
+        <v>78.053653846153793</v>
       </c>
       <c r="L7" s="5">
-        <v>330.15600000000001</v>
+        <v>338.23250000000002</v>
       </c>
       <c r="M7" s="5">
-        <v>930.33111619961403</v>
+        <v>1178.2627334747499</v>
       </c>
       <c r="N7" s="6">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="O7" s="6">
-        <v>9261.5</v>
+        <v>11252.82</v>
       </c>
       <c r="P7" s="6">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="Q7" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R7" s="6">
         <v>9</v>
       </c>
       <c r="S7" s="6">
-        <v>114.33950617283899</v>
+        <v>109.25067961165</v>
       </c>
       <c r="T7" s="6">
-        <v>926.15</v>
+        <v>937.73500000000001</v>
       </c>
       <c r="U7" s="6">
-        <v>677.97063110727197</v>
+        <v>540.29949825910296</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1174,7 +1177,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1182,16 +1185,16 @@
         <v>26</v>
       </c>
       <c r="B8" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5">
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>1140.1099999999999</v>
+        <v>1397.16</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1209,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1140.1099999999999</v>
+        <v>1397.16</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1219,10 +1222,10 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>1281.93</v>
+        <v>1514.47</v>
       </c>
       <c r="P8" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q8" s="6">
         <v>2</v>
@@ -1231,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>320.48250000000002</v>
+        <v>302.89400000000001</v>
       </c>
       <c r="T8" s="6">
-        <v>640.96500000000003</v>
+        <v>757.23500000000001</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1264,7 +1267,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1272,25 +1275,25 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9" s="5">
         <v>5</v>
       </c>
       <c r="D9" s="5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E9" s="5">
-        <v>3857.66</v>
+        <v>4765.09</v>
       </c>
       <c r="F9" s="5">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G9" s="5">
         <v>1</v>
       </c>
       <c r="H9" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I9" s="5">
         <v>3</v>
@@ -1299,22 +1302,22 @@
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>482.20749999999998</v>
+        <v>433.19</v>
       </c>
       <c r="L9" s="5">
-        <v>1285.8866666666599</v>
+        <v>1588.36333333333</v>
       </c>
       <c r="M9" s="5">
-        <v>102.609872306009</v>
+        <v>64.026282819422093</v>
       </c>
       <c r="N9" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O9" s="6">
-        <v>3738.32</v>
+        <v>4640.96</v>
       </c>
       <c r="P9" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q9" s="6">
         <v>3</v>
@@ -1323,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>415.36888888888802</v>
+        <v>464.096</v>
       </c>
       <c r="T9" s="6">
-        <v>1246.10666666666</v>
+        <v>1546.9866666666601</v>
       </c>
       <c r="U9" s="6">
-        <v>42.604164437501296</v>
+        <v>14.8684754878301</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1350,7 +1353,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1373,7 +1376,7 @@
         <v>2</v>
       </c>
       <c r="O10" s="6">
-        <v>1359.29</v>
+        <v>1572.28</v>
       </c>
       <c r="P10" s="6">
         <v>6</v>
@@ -1385,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>226.54833333333301</v>
+        <v>262.046666666666</v>
       </c>
       <c r="T10" s="6">
-        <v>339.82249999999999</v>
+        <v>393.07</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1406,7 +1409,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1423,40 +1426,40 @@
         <v>5</v>
       </c>
       <c r="E11" s="5">
-        <v>2054.27</v>
+        <v>2480.56</v>
       </c>
       <c r="F11" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
       </c>
       <c r="H11" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="5">
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>684.75666666666598</v>
+        <v>620.14</v>
       </c>
       <c r="L11" s="5">
-        <v>2054.27</v>
+        <v>1240.28</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
       </c>
       <c r="N11" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="6">
-        <v>707.05</v>
+        <v>889.69</v>
       </c>
       <c r="P11" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="6">
         <v>1</v>
@@ -1465,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>353.52499999999998</v>
+        <v>296.56333333333299</v>
       </c>
       <c r="T11" s="6">
-        <v>707.05</v>
+        <v>889.69</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1498,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1521,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6">
-        <v>189.36</v>
+        <v>239.6</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1542,7 +1545,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1550,25 +1553,25 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="5">
         <v>9</v>
       </c>
       <c r="D13" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="5">
-        <v>4000.43</v>
+        <v>4985.33</v>
       </c>
       <c r="F13" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" s="5">
         <v>4</v>
       </c>
       <c r="H13" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="5">
         <v>4</v>
@@ -1577,19 +1580,19 @@
         <v>2</v>
       </c>
       <c r="K13" s="5">
-        <v>333.36916666666599</v>
+        <v>383.48692307692301</v>
       </c>
       <c r="L13" s="5">
-        <v>1000.1075</v>
+        <v>1246.3325</v>
       </c>
       <c r="M13" s="5">
-        <v>220.01859800071401</v>
+        <v>156.79583899160099</v>
       </c>
       <c r="N13" s="6">
         <v>12</v>
       </c>
       <c r="O13" s="6">
-        <v>1984.87</v>
+        <v>2380.54</v>
       </c>
       <c r="P13" s="6">
         <v>15</v>
@@ -1598,16 +1601,16 @@
         <v>8</v>
       </c>
       <c r="R13" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" s="6">
-        <v>132.32466666666599</v>
+        <v>158.702666666666</v>
       </c>
       <c r="T13" s="6">
-        <v>248.10874999999999</v>
+        <v>297.5675</v>
       </c>
       <c r="U13" s="6">
-        <v>290.05073380120598</v>
+        <v>571.86436690834796</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1622,7 +1625,7 @@
         <v>12</v>
       </c>
       <c r="Z13" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA13" s="8">
         <v>8000</v>
@@ -1634,7 +1637,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1657,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>427.48</v>
+        <v>517.64</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1669,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>213.74</v>
+        <v>258.82</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1694,7 +1697,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1738,7 +1741,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1761,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="6">
-        <v>583.26</v>
+        <v>706.16</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1788,7 +1791,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1805,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>895.09</v>
+        <v>1002.37</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1823,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>895.09</v>
+        <v>1002.37</v>
       </c>
       <c r="L17" s="5">
-        <v>895.09</v>
+        <v>1002.37</v>
       </c>
       <c r="M17" s="5">
         <v>-100</v>
@@ -1835,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="6">
-        <v>460.01</v>
+        <v>570.29</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
@@ -1868,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1888,25 +1891,25 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O18" s="6">
-        <v>1916.27</v>
+        <v>2369.5700000000002</v>
       </c>
       <c r="P18" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q18" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R18" s="6">
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>239.53375</v>
+        <v>263.28555555555499</v>
       </c>
       <c r="T18" s="6">
-        <v>958.13499999999999</v>
+        <v>789.856666666666</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1930,7 +1933,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1938,64 +1941,64 @@
         <v>36</v>
       </c>
       <c r="B19" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" s="5">
         <v>7</v>
       </c>
       <c r="E19" s="5">
-        <v>1744</v>
+        <v>2064.29</v>
       </c>
       <c r="F19" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="5">
         <v>3</v>
       </c>
       <c r="I19" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="5">
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>581.33333333333303</v>
+        <v>516.07249999999999</v>
       </c>
       <c r="L19" s="5">
-        <v>1744</v>
+        <v>1032.145</v>
       </c>
       <c r="M19" s="5">
         <v>-100</v>
       </c>
       <c r="N19" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O19" s="6">
-        <v>2130.31</v>
+        <v>2628.98</v>
       </c>
       <c r="P19" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q19" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" s="6">
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>236.701111111111</v>
+        <v>238.998181818181</v>
       </c>
       <c r="T19" s="6">
-        <v>1065.155</v>
+        <v>876.32666666666603</v>
       </c>
       <c r="U19" s="6">
-        <v>233.28764358238899</v>
+        <v>170.069000144542</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2022,7 +2025,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2042,13 +2045,13 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O20" s="6">
-        <v>2218.0100000000002</v>
+        <v>2636.99</v>
       </c>
       <c r="P20" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q20" s="6">
         <v>2</v>
@@ -2057,10 +2060,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>316.858571428571</v>
+        <v>329.62374999999997</v>
       </c>
       <c r="T20" s="6">
-        <v>1109.0050000000001</v>
+        <v>1318.4949999999999</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2084,7 +2087,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2104,28 +2107,28 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="O21" s="6">
-        <v>5852.14</v>
+        <v>6924.45</v>
       </c>
       <c r="P21" s="6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q21" s="6">
         <v>4</v>
       </c>
       <c r="R21" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S21" s="6">
-        <v>308.00736842105198</v>
+        <v>301.06304347826</v>
       </c>
       <c r="T21" s="6">
-        <v>1463.0350000000001</v>
+        <v>1731.1125</v>
       </c>
       <c r="U21" s="6">
-        <v>26.971671901219</v>
+        <v>126.19211634137</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2140,13 +2143,13 @@
         <v>5</v>
       </c>
       <c r="Z21" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA21" s="8"/>
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2154,26 +2157,26 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
+        <v>12</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2</v>
+      </c>
+      <c r="D22" s="5">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>2</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="E22" s="5">
+        <v>2426.73</v>
+      </c>
+      <c r="F22" s="5">
+        <v>9</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
         <v>8</v>
       </c>
-      <c r="E22" s="5">
-        <v>1827.61</v>
-      </c>
-      <c r="F22" s="5">
-        <v>7</v>
-      </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
-        <v>6</v>
-      </c>
       <c r="I22" s="5">
         <v>2</v>
       </c>
@@ -2181,22 +2184,22 @@
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>261.087142857142</v>
+        <v>269.63666666666597</v>
       </c>
       <c r="L22" s="5">
-        <v>913.80499999999995</v>
+        <v>1213.365</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
       </c>
       <c r="N22" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O22" s="6">
-        <v>1857.38</v>
+        <v>2234.48</v>
       </c>
       <c r="P22" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -2205,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>464.34500000000003</v>
+        <v>446.89600000000002</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2236,7 +2239,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2256,10 +2259,10 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O23" s="6">
-        <v>2225.1999999999998</v>
+        <v>2753.83</v>
       </c>
       <c r="P23" s="6">
         <v>11</v>
@@ -2271,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>202.290909090909</v>
+        <v>250.34818181818099</v>
       </c>
       <c r="T23" s="6">
-        <v>2225.1999999999998</v>
+        <v>2753.83</v>
       </c>
       <c r="U23" s="6">
         <v>-100</v>
@@ -2302,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2322,13 +2325,13 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O24" s="6">
-        <v>1209.06</v>
+        <v>1348.17</v>
       </c>
       <c r="P24" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q24" s="6">
         <v>1</v>
@@ -2337,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>403.02</v>
+        <v>337.04250000000002</v>
       </c>
       <c r="T24" s="6">
-        <v>1209.06</v>
+        <v>1348.17</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2364,7 +2367,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46156</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2899,7 +2902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3670,13 +3673,13 @@
         <v>18</v>
       </c>
       <c r="D19" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F19" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" s="10">
         <v>3</v>
@@ -3694,19 +3697,19 @@
         <v>7816</v>
       </c>
       <c r="L19" s="10">
-        <v>12.82</v>
+        <v>12.9</v>
       </c>
       <c r="M19" s="10">
-        <v>14.31</v>
+        <v>10.78</v>
       </c>
       <c r="N19" s="10">
         <v>50</v>
       </c>
       <c r="O19" s="10">
-        <v>20</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="P19" s="10">
-        <v>10</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -3729,7 +3732,7 @@
         <v>3</v>
       </c>
       <c r="G20" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="10">
         <v>1</v>
@@ -3744,10 +3747,10 @@
         <v>4984</v>
       </c>
       <c r="L20" s="10">
-        <v>15.38</v>
+        <v>12.9</v>
       </c>
       <c r="M20" s="10">
-        <v>9.1199999999999992</v>
+        <v>6.87</v>
       </c>
       <c r="N20" s="10">
         <v>25</v>
@@ -3794,10 +3797,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="M21" s="10">
-        <v>9.9</v>
+        <v>7.46</v>
       </c>
       <c r="N21" s="10">
         <v>0</v>
@@ -3842,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -3890,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="M23" s="10">
         <v>0</v>
@@ -3925,7 +3928,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="10">
         <v>0</v>
@@ -3940,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -3966,13 +3969,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E25" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F25" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="10">
         <v>1</v>
@@ -3990,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>3.85</v>
+        <v>6.45</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -4016,10 +4019,10 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E26" s="10">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F26" s="10">
         <v>0</v>
@@ -4040,17 +4043,17 @@
         <v>20397</v>
       </c>
       <c r="L26" s="10">
-        <v>37.18</v>
+        <v>34.409999999999997</v>
       </c>
       <c r="M26" s="10">
-        <v>37.33</v>
+        <v>28.13</v>
       </c>
       <c r="N26" s="10">
         <v>0</v>
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10">
-        <v>10.34</v>
+        <v>9.3800000000000008</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -4064,16 +4067,16 @@
         <v>18</v>
       </c>
       <c r="D27" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E27" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F27" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="10">
         <v>1</v>
@@ -4088,24 +4091,24 @@
         <v>7911</v>
       </c>
       <c r="L27" s="10">
-        <v>3.85</v>
+        <v>7.53</v>
       </c>
       <c r="M27" s="10">
-        <v>14.48</v>
+        <v>10.91</v>
       </c>
       <c r="N27" s="10">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="O27" s="10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P27" s="10">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B28" s="19">
         <v>2026</v>
@@ -4114,13 +4117,13 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F28" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" s="10">
         <v>0</v>
@@ -4138,24 +4141,22 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>6.41</v>
+        <v>1.08</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
       </c>
       <c r="N28" s="10">
-        <v>60</v>
-      </c>
-      <c r="O28" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O28" s="10"/>
       <c r="P28" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B29" s="19">
         <v>2026</v>
@@ -4164,48 +4165,48 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" s="10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F29" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H29" s="10">
         <v>2</v>
       </c>
       <c r="I29" s="10">
-        <v>8117.12</v>
+        <v>17865</v>
       </c>
       <c r="J29" s="10">
         <v>2</v>
       </c>
       <c r="K29" s="10">
-        <v>8117.12</v>
+        <v>17865</v>
       </c>
       <c r="L29" s="10">
-        <v>8.9700000000000006</v>
+        <v>6.45</v>
       </c>
       <c r="M29" s="10">
-        <v>14.86</v>
+        <v>24.64</v>
       </c>
       <c r="N29" s="10">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="O29" s="10">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="P29" s="10">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B30" s="19">
         <v>2026</v>
@@ -4214,48 +4215,48 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E30" s="10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F30" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G30" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30" s="10">
-        <v>0</v>
+        <v>8117.12</v>
       </c>
       <c r="J30" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" s="10">
-        <v>0</v>
+        <v>8117.12</v>
       </c>
       <c r="L30" s="10">
-        <v>1.28</v>
+        <v>7.53</v>
       </c>
       <c r="M30" s="10">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="N30" s="10">
-        <v>100</v>
+        <v>57.14</v>
       </c>
       <c r="O30" s="10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P30" s="10">
-        <v>0</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B31" s="19">
         <v>2026</v>
@@ -4264,13 +4265,13 @@
         <v>18</v>
       </c>
       <c r="D31" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="10">
         <v>0</v>
@@ -4288,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>1.28</v>
+        <v>2.15</v>
       </c>
       <c r="M31" s="10">
         <v>0</v>
@@ -4305,7 +4306,7 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B32" s="19">
         <v>2026</v>
@@ -4338,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="10">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="M32" s="10">
         <v>0</v>
@@ -4350,6 +4351,56 @@
         <v>0</v>
       </c>
       <c r="P32" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="19">
+        <v>2026</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="10">
+        <v>1</v>
+      </c>
+      <c r="E33" s="10">
+        <v>1</v>
+      </c>
+      <c r="F33" s="10">
+        <v>1</v>
+      </c>
+      <c r="G33" s="10">
+        <v>0</v>
+      </c>
+      <c r="H33" s="10">
+        <v>0</v>
+      </c>
+      <c r="I33" s="10">
+        <v>0</v>
+      </c>
+      <c r="J33" s="10">
+        <v>0</v>
+      </c>
+      <c r="K33" s="10">
+        <v>0</v>
+      </c>
+      <c r="L33" s="10">
+        <v>1.08</v>
+      </c>
+      <c r="M33" s="10">
+        <v>0</v>
+      </c>
+      <c r="N33" s="10">
+        <v>100</v>
+      </c>
+      <c r="O33" s="10">
+        <v>0</v>
+      </c>
+      <c r="P33" s="10">
         <v>0</v>
       </c>
     </row>
@@ -4958,10 +5009,10 @@
         <v>167</v>
       </c>
       <c r="G20" s="10">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H20" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I20" s="10">
         <v>7</v>
@@ -4984,28 +5035,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1404</v>
+        <v>1674</v>
       </c>
       <c r="E21" s="10">
-        <v>3301.56</v>
+        <v>4058.79</v>
       </c>
       <c r="F21" s="10">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="G21" s="10">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H21" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I21" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J21" s="10">
-        <v>34017</v>
+        <v>51882</v>
       </c>
       <c r="K21" s="10">
-        <v>9.3000000000000007</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5579,13 +5630,13 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="E38" s="10">
-        <v>1140.1099999999999</v>
+        <v>1397.16</v>
       </c>
       <c r="F38" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G38" s="10">
         <v>1</v>
@@ -6174,16 +6225,16 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>503</v>
+        <v>608</v>
       </c>
       <c r="E55" s="10">
-        <v>3857.66</v>
+        <v>4765.09</v>
       </c>
       <c r="F55" s="10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G55" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H55" s="10">
         <v>3</v>
@@ -6195,7 +6246,7 @@
         <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>1.03</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -7169,19 +7220,19 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>271</v>
+        <v>325</v>
       </c>
       <c r="E84" s="10">
-        <v>2054.27</v>
+        <v>2480.56</v>
       </c>
       <c r="F84" s="10">
         <v>6</v>
       </c>
       <c r="G84" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H84" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" s="10">
         <v>0</v>
@@ -8059,16 +8110,16 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>398</v>
+        <v>481</v>
       </c>
       <c r="E110" s="10">
-        <v>4000.43</v>
+        <v>4985.33</v>
       </c>
       <c r="F110" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G110" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H110" s="10">
         <v>5</v>
@@ -8080,7 +8131,7 @@
         <v>12802.12</v>
       </c>
       <c r="K110" s="10">
-        <v>2.2000000000000002</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9574,10 +9625,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="E155" s="10">
-        <v>895.09</v>
+        <v>1002.37</v>
       </c>
       <c r="F155" s="10">
         <v>1</v>
@@ -10660,19 +10711,19 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>244</v>
+        <v>288</v>
       </c>
       <c r="E186" s="10">
-        <v>1744</v>
+        <v>2064.29</v>
       </c>
       <c r="F186" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G186" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H186" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I186" s="10">
         <v>0</v>
@@ -12235,16 +12286,16 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>260</v>
+        <v>323</v>
       </c>
       <c r="E231" s="10">
-        <v>1827.61</v>
+        <v>2426.73</v>
       </c>
       <c r="F231" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G231" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H231" s="10">
         <v>3</v>
@@ -16941,7 +16992,7 @@
         <v>13</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42">
         <v>3</v>
@@ -16979,10 +17030,10 @@
         <v>107</v>
       </c>
       <c r="E43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G43">
         <v>3</v>
@@ -17023,7 +17074,7 @@
         <v>1</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -17102,7 +17153,7 @@
         <v>3</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -17292,7 +17343,7 @@
         <v>1</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -17359,13 +17410,13 @@
         <v>13</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -17394,19 +17445,19 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -17423,7 +17474,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B55" s="18">
         <v>2026</v>
@@ -17432,31 +17483,31 @@
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E55">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F55">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J55">
-        <v>20397</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L55">
-        <v>20397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
@@ -17470,31 +17521,31 @@
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>20397</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -17508,7 +17559,7 @@
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -17546,13 +17597,13 @@
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -17575,7 +17626,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B59" s="18">
         <v>2026</v>
@@ -17584,7 +17635,7 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E59">
         <v>2</v>
@@ -17593,22 +17644,22 @@
         <v>2</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>7911</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59">
-        <v>7911</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
@@ -17622,36 +17673,36 @@
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F60">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>7911</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>7911</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B61" s="18">
         <v>2026</v>
@@ -17660,16 +17711,16 @@
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E61">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -17689,7 +17740,7 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B62" s="18">
         <v>2026</v>
@@ -17698,36 +17749,36 @@
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="K62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B63" s="18">
         <v>2026</v>
@@ -17736,36 +17787,36 @@
         <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63">
-        <v>7818.1200000000008</v>
+        <v>17865</v>
       </c>
       <c r="K63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63">
-        <v>7818.1200000000008</v>
+        <v>17865</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B64" s="18">
         <v>2026</v>
@@ -17777,16 +17828,16 @@
         <v>39</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -17803,7 +17854,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B65" s="18">
         <v>2026</v>
@@ -17812,36 +17863,36 @@
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B66" s="18">
         <v>2026</v>
@@ -17850,7 +17901,7 @@
         <v>18</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -17862,24 +17913,24 @@
         <v>1</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B67" s="18">
         <v>2026</v>
@@ -17888,44 +17939,146 @@
         <v>18</v>
       </c>
       <c r="D67" t="s">
+        <v>39</v>
+      </c>
+      <c r="E67">
+        <v>4</v>
+      </c>
+      <c r="F67">
+        <v>4</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>101</v>
+      </c>
+      <c r="B68" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" t="s">
+        <v>106</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" t="s">
         <v>13</v>
       </c>
-      <c r="E67">
-        <v>1</v>
-      </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-      <c r="G67">
-        <v>1</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B68" s="18"/>
-      <c r="C68" s="19"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B69" s="18"/>
-      <c r="C69" s="19"/>
+      <c r="E69">
+        <v>1</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B70" s="18"/>
-      <c r="C70" s="19"/>
+      <c r="A70" t="s">
+        <v>103</v>
+      </c>
+      <c r="B70" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B71" s="18"/>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A930C2-318D-4261-8478-34B6899F5847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA9812A-E93C-420F-9186-73755C20B433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47892" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -1001,64 +1001,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C6" s="5">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D6" s="5">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E6" s="5">
-        <v>23180.32</v>
+        <v>24777.65</v>
       </c>
       <c r="F6" s="5">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G6" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H6" s="5">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I6" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J6" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K6" s="5">
-        <v>244.00336842105199</v>
+        <v>250.27929292929201</v>
       </c>
       <c r="L6" s="5">
-        <v>891.55076923076899</v>
+        <v>884.91607142857094</v>
       </c>
       <c r="M6" s="5">
-        <v>212.765828944552</v>
+        <v>229.55554703533201</v>
       </c>
       <c r="N6" s="6">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="O6" s="6">
-        <v>45183.66</v>
+        <v>47448.15</v>
       </c>
       <c r="P6" s="6">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="Q6" s="6">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="R6" s="6">
         <v>15</v>
       </c>
       <c r="S6" s="6">
-        <v>210.15655813953401</v>
+        <v>208.105921052631</v>
       </c>
       <c r="T6" s="6">
-        <v>1026.90136363636</v>
+        <v>1031.4815217391299</v>
       </c>
       <c r="U6" s="6">
-        <v>157.038429379116</v>
+        <v>144.771123847821</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1085,7 +1085,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1093,49 +1093,49 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C7" s="5">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D7" s="5">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E7" s="5">
-        <v>4058.79</v>
+        <v>4326.1899999999996</v>
       </c>
       <c r="F7" s="5">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H7" s="5">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I7" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K7" s="5">
-        <v>78.053653846153793</v>
+        <v>80.114629629629604</v>
       </c>
       <c r="L7" s="5">
-        <v>338.23250000000002</v>
+        <v>332.78384615384601</v>
       </c>
       <c r="M7" s="5">
-        <v>1178.2627334747499</v>
+        <v>1268.2940416394099</v>
       </c>
       <c r="N7" s="6">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O7" s="6">
-        <v>11252.82</v>
+        <v>11754.37</v>
       </c>
       <c r="P7" s="6">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="Q7" s="6">
         <v>12</v>
@@ -1144,13 +1144,13 @@
         <v>9</v>
       </c>
       <c r="S7" s="6">
-        <v>109.25067961165</v>
+        <v>108.836759259259</v>
       </c>
       <c r="T7" s="6">
-        <v>937.73500000000001</v>
+        <v>979.53083333333302</v>
       </c>
       <c r="U7" s="6">
-        <v>540.29949825910296</v>
+        <v>512.97840717962697</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1177,7 +1177,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>1397.16</v>
+        <v>1498.03</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1397.16</v>
+        <v>1498.03</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1222,7 +1222,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>1514.47</v>
+        <v>1618.24</v>
       </c>
       <c r="P8" s="6">
         <v>5</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>302.89400000000001</v>
+        <v>323.64800000000002</v>
       </c>
       <c r="T8" s="6">
-        <v>757.23500000000001</v>
+        <v>809.12</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1267,7 +1267,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1275,16 +1275,16 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" s="5">
         <v>5</v>
       </c>
       <c r="D9" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E9" s="5">
-        <v>4765.09</v>
+        <v>5013.74</v>
       </c>
       <c r="F9" s="5">
         <v>11</v>
@@ -1296,28 +1296,28 @@
         <v>10</v>
       </c>
       <c r="I9" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="5">
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>433.19</v>
+        <v>455.79454545454502</v>
       </c>
       <c r="L9" s="5">
-        <v>1588.36333333333</v>
+        <v>1253.4349999999999</v>
       </c>
       <c r="M9" s="5">
-        <v>64.026282819422093</v>
+        <v>55.891609856115402</v>
       </c>
       <c r="N9" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O9" s="6">
-        <v>4640.96</v>
+        <v>4859.38</v>
       </c>
       <c r="P9" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q9" s="6">
         <v>3</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>464.096</v>
+        <v>404.94833333333298</v>
       </c>
       <c r="T9" s="6">
-        <v>1546.9866666666601</v>
+        <v>1619.7933333333301</v>
       </c>
       <c r="U9" s="6">
-        <v>14.8684754878301</v>
+        <v>9.7053533578357705</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1353,7 +1353,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1376,7 +1376,7 @@
         <v>2</v>
       </c>
       <c r="O10" s="6">
-        <v>1572.28</v>
+        <v>1738.94</v>
       </c>
       <c r="P10" s="6">
         <v>6</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>262.046666666666</v>
+        <v>289.82333333333298</v>
       </c>
       <c r="T10" s="6">
-        <v>393.07</v>
+        <v>434.73500000000001</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1409,7 +1409,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1426,7 +1426,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="5">
-        <v>2480.56</v>
+        <v>2641.3</v>
       </c>
       <c r="F11" s="5">
         <v>4</v>
@@ -1444,10 +1444,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>620.14</v>
+        <v>660.32500000000005</v>
       </c>
       <c r="L11" s="5">
-        <v>1240.28</v>
+        <v>1320.65</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
@@ -1456,7 +1456,7 @@
         <v>2</v>
       </c>
       <c r="O11" s="6">
-        <v>889.69</v>
+        <v>919.41</v>
       </c>
       <c r="P11" s="6">
         <v>3</v>
@@ -1468,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>296.56333333333299</v>
+        <v>306.469999999999</v>
       </c>
       <c r="T11" s="6">
-        <v>889.69</v>
+        <v>919.41</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1501,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1524,7 +1524,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6">
-        <v>239.6</v>
+        <v>241.74</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1545,7 +1545,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1553,22 +1553,22 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="5">
         <v>13</v>
       </c>
       <c r="E13" s="5">
-        <v>4985.33</v>
+        <v>5335.15</v>
       </c>
       <c r="F13" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" s="5">
         <v>9</v>
@@ -1580,19 +1580,19 @@
         <v>2</v>
       </c>
       <c r="K13" s="5">
-        <v>383.48692307692301</v>
+        <v>381.082142857142</v>
       </c>
       <c r="L13" s="5">
-        <v>1246.3325</v>
+        <v>1333.7874999999999</v>
       </c>
       <c r="M13" s="5">
-        <v>156.79583899160099</v>
+        <v>174.50249758675901</v>
       </c>
       <c r="N13" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O13" s="6">
-        <v>2380.54</v>
+        <v>2559.2199999999998</v>
       </c>
       <c r="P13" s="6">
         <v>15</v>
@@ -1604,13 +1604,13 @@
         <v>2</v>
       </c>
       <c r="S13" s="6">
-        <v>158.702666666666</v>
+        <v>170.61466666666601</v>
       </c>
       <c r="T13" s="6">
-        <v>297.5675</v>
+        <v>319.90249999999997</v>
       </c>
       <c r="U13" s="6">
-        <v>571.86436690834796</v>
+        <v>524.95604129383105</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1637,7 +1637,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1660,7 +1660,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>517.64</v>
+        <v>528.97</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>258.82</v>
+        <v>264.48500000000001</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1697,7 +1697,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1741,7 +1741,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1764,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="O16" s="6">
-        <v>706.16</v>
+        <v>765.28</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1791,7 +1791,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1799,16 +1799,16 @@
         <v>34</v>
       </c>
       <c r="B17" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="5">
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>1002.37</v>
+        <v>1062.97</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1826,10 +1826,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1002.37</v>
+        <v>1062.97</v>
       </c>
       <c r="L17" s="5">
-        <v>1002.37</v>
+        <v>1062.97</v>
       </c>
       <c r="M17" s="5">
         <v>-100</v>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="6">
-        <v>570.29</v>
+        <v>621.11</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6"/>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1894,7 +1894,7 @@
         <v>9</v>
       </c>
       <c r="O18" s="6">
-        <v>2369.5700000000002</v>
+        <v>2467.84</v>
       </c>
       <c r="P18" s="6">
         <v>9</v>
@@ -1906,10 +1906,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>263.28555555555499</v>
+        <v>274.20444444444399</v>
       </c>
       <c r="T18" s="6">
-        <v>789.856666666666</v>
+        <v>822.613333333333</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1933,7 +1933,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1950,7 +1950,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="5">
-        <v>2064.29</v>
+        <v>2192.15</v>
       </c>
       <c r="F19" s="5">
         <v>4</v>
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>516.07249999999999</v>
+        <v>548.03750000000002</v>
       </c>
       <c r="L19" s="5">
-        <v>1032.145</v>
+        <v>1096.075</v>
       </c>
       <c r="M19" s="5">
         <v>-100</v>
@@ -1980,25 +1980,25 @@
         <v>18</v>
       </c>
       <c r="O19" s="6">
-        <v>2628.98</v>
+        <v>2743.83</v>
       </c>
       <c r="P19" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q19" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R19" s="6">
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>238.998181818181</v>
+        <v>228.6525</v>
       </c>
       <c r="T19" s="6">
-        <v>876.32666666666603</v>
+        <v>685.95749999999998</v>
       </c>
       <c r="U19" s="6">
-        <v>170.069000144542</v>
+        <v>158.764573606965</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2025,7 +2025,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2045,25 +2045,25 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O20" s="6">
-        <v>2636.99</v>
+        <v>2803.16</v>
       </c>
       <c r="P20" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q20" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20" s="6">
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>329.62374999999997</v>
+        <v>311.46222222222201</v>
       </c>
       <c r="T20" s="6">
-        <v>1318.4949999999999</v>
+        <v>934.38666666666597</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2087,7 +2087,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2110,10 +2110,10 @@
         <v>32</v>
       </c>
       <c r="O21" s="6">
-        <v>6924.45</v>
+        <v>7224.04</v>
       </c>
       <c r="P21" s="6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q21" s="6">
         <v>4</v>
@@ -2122,13 +2122,13 @@
         <v>2</v>
       </c>
       <c r="S21" s="6">
-        <v>301.06304347826</v>
+        <v>288.96159999999998</v>
       </c>
       <c r="T21" s="6">
-        <v>1731.1125</v>
+        <v>1806.01</v>
       </c>
       <c r="U21" s="6">
-        <v>126.19211634137</v>
+        <v>116.811645561209</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2149,7 +2149,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2166,17 +2166,17 @@
         <v>10</v>
       </c>
       <c r="E22" s="5">
-        <v>2426.73</v>
+        <v>2708.12</v>
       </c>
       <c r="F22" s="5">
+        <v>10</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
         <v>9</v>
       </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
-        <v>8</v>
-      </c>
       <c r="I22" s="5">
         <v>2</v>
       </c>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>269.63666666666597</v>
+        <v>270.81200000000001</v>
       </c>
       <c r="L22" s="5">
-        <v>1213.365</v>
+        <v>1354.06</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2196,7 +2196,7 @@
         <v>4</v>
       </c>
       <c r="O22" s="6">
-        <v>2234.48</v>
+        <v>2289.11</v>
       </c>
       <c r="P22" s="6">
         <v>5</v>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>446.89600000000002</v>
+        <v>457.822</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2239,7 +2239,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2259,13 +2259,13 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O23" s="6">
-        <v>2753.83</v>
+        <v>2895.75</v>
       </c>
       <c r="P23" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q23" s="6">
         <v>1</v>
@@ -2274,10 +2274,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>250.34818181818099</v>
+        <v>222.75</v>
       </c>
       <c r="T23" s="6">
-        <v>2753.83</v>
+        <v>2895.75</v>
       </c>
       <c r="U23" s="6">
         <v>-100</v>
@@ -2305,7 +2305,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2328,7 +2328,7 @@
         <v>5</v>
       </c>
       <c r="O24" s="6">
-        <v>1348.17</v>
+        <v>1415.02</v>
       </c>
       <c r="P24" s="6">
         <v>4</v>
@@ -2340,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>337.04250000000002</v>
+        <v>353.755</v>
       </c>
       <c r="T24" s="6">
-        <v>1348.17</v>
+        <v>1415.02</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2367,7 +2367,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46159</v>
+        <v>46160</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3697,10 +3697,10 @@
         <v>7816</v>
       </c>
       <c r="L19" s="10">
-        <v>12.9</v>
+        <v>12.12</v>
       </c>
       <c r="M19" s="10">
-        <v>10.78</v>
+        <v>9.57</v>
       </c>
       <c r="N19" s="10">
         <v>50</v>
@@ -3723,10 +3723,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" s="10">
         <v>3</v>
@@ -3738,28 +3738,28 @@
         <v>1</v>
       </c>
       <c r="I20" s="10">
-        <v>4984</v>
+        <v>6827</v>
       </c>
       <c r="J20" s="10">
         <v>1</v>
       </c>
       <c r="K20" s="10">
-        <v>4984</v>
+        <v>6827</v>
       </c>
       <c r="L20" s="10">
-        <v>12.9</v>
+        <v>13.13</v>
       </c>
       <c r="M20" s="10">
-        <v>6.87</v>
+        <v>8.36</v>
       </c>
       <c r="N20" s="10">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="O20" s="10">
         <v>33.33</v>
       </c>
       <c r="P20" s="10">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -3797,10 +3797,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="10">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="M21" s="10">
-        <v>7.46</v>
+        <v>6.63</v>
       </c>
       <c r="N21" s="10">
         <v>0</v>
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="10">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="M22" s="10">
         <v>0</v>
@@ -3893,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="M23" s="10">
         <v>0</v>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -3975,10 +3975,10 @@
         <v>6</v>
       </c>
       <c r="F25" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="10">
         <v>0</v>
@@ -3993,13 +3993,13 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>6.45</v>
+        <v>6.06</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
       </c>
       <c r="N25" s="10">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="O25" s="10">
         <v>0</v>
@@ -4019,16 +4019,16 @@
         <v>18</v>
       </c>
       <c r="D26" s="10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E26" s="10">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F26" s="10">
         <v>0</v>
       </c>
       <c r="G26" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H26" s="10">
         <v>3</v>
@@ -4043,17 +4043,17 @@
         <v>20397</v>
       </c>
       <c r="L26" s="10">
-        <v>34.409999999999997</v>
+        <v>34.340000000000003</v>
       </c>
       <c r="M26" s="10">
-        <v>28.13</v>
+        <v>24.98</v>
       </c>
       <c r="N26" s="10">
         <v>0</v>
       </c>
       <c r="O26" s="10"/>
       <c r="P26" s="10">
-        <v>9.3800000000000008</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -4079,31 +4079,31 @@
         <v>2</v>
       </c>
       <c r="H27" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" s="10">
-        <v>7911</v>
+        <v>15224</v>
       </c>
       <c r="J27" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="10">
-        <v>7911</v>
+        <v>15224</v>
       </c>
       <c r="L27" s="10">
-        <v>7.53</v>
+        <v>7.07</v>
       </c>
       <c r="M27" s="10">
-        <v>10.91</v>
+        <v>18.64</v>
       </c>
       <c r="N27" s="10">
         <v>28.57</v>
       </c>
       <c r="O27" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P27" s="10">
-        <v>14.29</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>17865</v>
       </c>
       <c r="L29" s="10">
-        <v>6.45</v>
+        <v>6.06</v>
       </c>
       <c r="M29" s="10">
-        <v>24.64</v>
+        <v>21.88</v>
       </c>
       <c r="N29" s="10">
         <v>50</v>
@@ -4215,10 +4215,10 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E30" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F30" s="10">
         <v>4</v>
@@ -4239,19 +4239,19 @@
         <v>8117.12</v>
       </c>
       <c r="L30" s="10">
-        <v>7.53</v>
+        <v>9.09</v>
       </c>
       <c r="M30" s="10">
-        <v>11.2</v>
+        <v>9.94</v>
       </c>
       <c r="N30" s="10">
-        <v>57.14</v>
+        <v>44.44</v>
       </c>
       <c r="O30" s="10">
         <v>50</v>
       </c>
       <c r="P30" s="10">
-        <v>28.57</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -4289,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="M31" s="10">
         <v>0</v>
@@ -4339,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="10">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="M32" s="10">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>18</v>
       </c>
       <c r="D33" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="10">
         <v>0</v>
@@ -4389,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>1.08</v>
+        <v>2.02</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
@@ -4974,10 +4974,10 @@
         <v>164</v>
       </c>
       <c r="G19" s="5">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H19" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I19" s="5">
         <v>11</v>
@@ -5009,19 +5009,19 @@
         <v>167</v>
       </c>
       <c r="G20" s="10">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H20" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I20" s="10">
+        <v>8</v>
+      </c>
+      <c r="J20" s="10">
+        <v>59614</v>
+      </c>
+      <c r="K20" s="10">
         <v>7</v>
-      </c>
-      <c r="J20" s="10">
-        <v>54115</v>
-      </c>
-      <c r="K20" s="10">
-        <v>6.26</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -5035,28 +5035,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1674</v>
+        <v>1774</v>
       </c>
       <c r="E21" s="10">
-        <v>4058.79</v>
+        <v>4326.1899999999996</v>
       </c>
       <c r="F21" s="10">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="G21" s="10">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H21" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I21" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J21" s="10">
-        <v>51882</v>
+        <v>59195</v>
       </c>
       <c r="K21" s="10">
-        <v>11.78</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5630,10 +5630,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="E38" s="10">
-        <v>1397.16</v>
+        <v>1498.03</v>
       </c>
       <c r="F38" s="10">
         <v>5</v>
@@ -6225,19 +6225,19 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>608</v>
+        <v>647</v>
       </c>
       <c r="E55" s="10">
-        <v>4765.09</v>
+        <v>5013.74</v>
       </c>
       <c r="F55" s="10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G55" s="10">
         <v>10</v>
       </c>
       <c r="H55" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I55" s="10">
         <v>1</v>
@@ -6246,7 +6246,7 @@
         <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>0.64</v>
+        <v>0.56000000000000005</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -7220,10 +7220,10 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="E84" s="10">
-        <v>2480.56</v>
+        <v>2641.3</v>
       </c>
       <c r="F84" s="10">
         <v>6</v>
@@ -8110,16 +8110,16 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>481</v>
+        <v>509</v>
       </c>
       <c r="E110" s="10">
-        <v>4985.33</v>
+        <v>5335.15</v>
       </c>
       <c r="F110" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G110" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H110" s="10">
         <v>5</v>
@@ -8128,10 +8128,10 @@
         <v>2</v>
       </c>
       <c r="J110" s="10">
-        <v>12802.12</v>
+        <v>14645.12</v>
       </c>
       <c r="K110" s="10">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9625,13 +9625,13 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E155" s="10">
-        <v>1002.37</v>
+        <v>1062.97</v>
       </c>
       <c r="F155" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G155" s="10">
         <v>1</v>
@@ -10711,10 +10711,10 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="E186" s="10">
-        <v>2064.29</v>
+        <v>2192.15</v>
       </c>
       <c r="F186" s="10">
         <v>11</v>
@@ -12286,16 +12286,16 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>323</v>
+        <v>348</v>
       </c>
       <c r="E231" s="10">
-        <v>2426.73</v>
+        <v>2708.12</v>
       </c>
       <c r="F231" s="10">
         <v>12</v>
       </c>
       <c r="G231" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H231" s="10">
         <v>3</v>
@@ -17144,10 +17144,10 @@
         <v>29</v>
       </c>
       <c r="E46">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F46">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G46">
         <v>3</v>
@@ -17159,13 +17159,13 @@
         <v>1</v>
       </c>
       <c r="J46">
-        <v>4984</v>
+        <v>6827</v>
       </c>
       <c r="K46">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>4984</v>
+        <v>6827</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
@@ -17419,7 +17419,7 @@
         <v>1</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -17454,7 +17454,7 @@
         <v>1</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -17524,16 +17524,16 @@
         <v>13</v>
       </c>
       <c r="E56">
+        <v>29</v>
+      </c>
+      <c r="F56">
         <v>28</v>
       </c>
-      <c r="F56">
-        <v>27</v>
-      </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I56">
         <v>3</v>
@@ -17600,10 +17600,10 @@
         <v>107</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -17688,16 +17688,16 @@
         <v>2</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60">
-        <v>7911</v>
+        <v>15224</v>
       </c>
       <c r="K60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60">
-        <v>7911</v>
+        <v>15224</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -17942,10 +17942,10 @@
         <v>39</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F67">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -18056,13 +18056,13 @@
         <v>13</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70">
         <v>0</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA9812A-E93C-420F-9186-73755C20B433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5D3E20-6BED-4F23-88D4-807FEAA488A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47892" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="113">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -357,6 +357,12 @@
   <si>
     <t>Other</t>
   </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
 </sst>
 </file>
 
@@ -505,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -553,6 +559,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1001,64 +1013,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C6" s="5">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D6" s="5">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E6" s="5">
-        <v>24777.65</v>
+        <v>26269.25</v>
       </c>
       <c r="F6" s="5">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G6" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6" s="5">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I6" s="5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J6" s="5">
         <v>12</v>
       </c>
       <c r="K6" s="5">
-        <v>250.27929292929201</v>
+        <v>252.58894230769201</v>
       </c>
       <c r="L6" s="5">
-        <v>884.91607142857094</v>
+        <v>875.64166666666597</v>
       </c>
       <c r="M6" s="5">
-        <v>229.55554703533201</v>
+        <v>211.41399164422199</v>
       </c>
       <c r="N6" s="6">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="O6" s="6">
-        <v>47448.15</v>
+        <v>50579.62</v>
       </c>
       <c r="P6" s="6">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="Q6" s="6">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R6" s="6">
         <v>15</v>
       </c>
       <c r="S6" s="6">
-        <v>208.105921052631</v>
+        <v>206.44742857142799</v>
       </c>
       <c r="T6" s="6">
-        <v>1031.4815217391299</v>
+        <v>972.68499999999995</v>
       </c>
       <c r="U6" s="6">
-        <v>144.771123847821</v>
+        <v>129.61692871555701</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1085,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1093,25 +1105,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C7" s="5">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D7" s="5">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E7" s="5">
-        <v>4326.1899999999996</v>
+        <v>4580.99</v>
       </c>
       <c r="F7" s="5">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G7" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I7" s="5">
         <v>13</v>
@@ -1120,37 +1132,37 @@
         <v>9</v>
       </c>
       <c r="K7" s="5">
-        <v>80.114629629629604</v>
+        <v>78.982586206896499</v>
       </c>
       <c r="L7" s="5">
-        <v>332.78384615384601</v>
+        <v>352.38384615384598</v>
       </c>
       <c r="M7" s="5">
-        <v>1268.2940416394099</v>
+        <v>1195.46233456087</v>
       </c>
       <c r="N7" s="6">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="O7" s="6">
-        <v>11754.37</v>
+        <v>12530.92</v>
       </c>
       <c r="P7" s="6">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="Q7" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R7" s="6">
         <v>9</v>
       </c>
       <c r="S7" s="6">
-        <v>108.836759259259</v>
+        <v>105.301848739495</v>
       </c>
       <c r="T7" s="6">
-        <v>979.53083333333302</v>
+        <v>895.06571428571397</v>
       </c>
       <c r="U7" s="6">
-        <v>512.97840717962697</v>
+        <v>474.99170052956998</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1177,7 +1189,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1194,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>1498.03</v>
+        <v>1554.02</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1212,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1498.03</v>
+        <v>1554.02</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1222,7 +1234,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>1618.24</v>
+        <v>1730.21</v>
       </c>
       <c r="P8" s="6">
         <v>5</v>
@@ -1234,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>323.64800000000002</v>
+        <v>346.04199999999997</v>
       </c>
       <c r="T8" s="6">
-        <v>809.12</v>
+        <v>865.10500000000002</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1267,7 +1279,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1275,64 +1287,64 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>16</v>
+      </c>
+      <c r="E9" s="5">
+        <v>5305.17</v>
+      </c>
+      <c r="F9" s="5">
+        <v>12</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
+        <v>11</v>
+      </c>
+      <c r="I9" s="5">
         <v>5</v>
       </c>
-      <c r="D9" s="5">
-        <v>14</v>
-      </c>
-      <c r="E9" s="5">
-        <v>5013.74</v>
-      </c>
-      <c r="F9" s="5">
-        <v>11</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>10</v>
-      </c>
-      <c r="I9" s="5">
-        <v>4</v>
-      </c>
       <c r="J9" s="5">
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>455.79454545454502</v>
+        <v>442.09750000000003</v>
       </c>
       <c r="L9" s="5">
-        <v>1253.4349999999999</v>
+        <v>1061.0340000000001</v>
       </c>
       <c r="M9" s="5">
-        <v>55.891609856115402</v>
+        <v>47.327983834636697</v>
       </c>
       <c r="N9" s="6">
         <v>19</v>
       </c>
       <c r="O9" s="6">
-        <v>4859.38</v>
+        <v>5182.01</v>
       </c>
       <c r="P9" s="6">
         <v>12</v>
       </c>
       <c r="Q9" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R9" s="6">
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>404.94833333333298</v>
+        <v>431.83416666666602</v>
       </c>
       <c r="T9" s="6">
-        <v>1619.7933333333301</v>
+        <v>1295.5025000000001</v>
       </c>
       <c r="U9" s="6">
-        <v>9.7053533578357705</v>
+        <v>2.8751391834442499</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1353,7 +1365,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1376,7 +1388,7 @@
         <v>2</v>
       </c>
       <c r="O10" s="6">
-        <v>1738.94</v>
+        <v>1906.28</v>
       </c>
       <c r="P10" s="6">
         <v>6</v>
@@ -1388,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>289.82333333333298</v>
+        <v>317.71333333333303</v>
       </c>
       <c r="T10" s="6">
-        <v>434.73500000000001</v>
+        <v>476.57</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1409,7 +1421,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1426,7 +1438,7 @@
         <v>5</v>
       </c>
       <c r="E11" s="5">
-        <v>2641.3</v>
+        <v>2804.08</v>
       </c>
       <c r="F11" s="5">
         <v>4</v>
@@ -1444,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>660.32500000000005</v>
+        <v>701.02</v>
       </c>
       <c r="L11" s="5">
-        <v>1320.65</v>
+        <v>1402.04</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
@@ -1456,7 +1468,7 @@
         <v>2</v>
       </c>
       <c r="O11" s="6">
-        <v>919.41</v>
+        <v>982.51</v>
       </c>
       <c r="P11" s="6">
         <v>3</v>
@@ -1468,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>306.469999999999</v>
+        <v>327.50333333333299</v>
       </c>
       <c r="T11" s="6">
-        <v>919.41</v>
+        <v>982.51</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1501,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1524,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="6">
-        <v>241.74</v>
+        <v>246.85</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1545,7 +1557,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1562,7 +1574,7 @@
         <v>13</v>
       </c>
       <c r="E13" s="5">
-        <v>5335.15</v>
+        <v>5702.42</v>
       </c>
       <c r="F13" s="5">
         <v>14</v>
@@ -1580,19 +1592,19 @@
         <v>2</v>
       </c>
       <c r="K13" s="5">
-        <v>381.082142857142</v>
+        <v>407.31571428571402</v>
       </c>
       <c r="L13" s="5">
-        <v>1333.7874999999999</v>
+        <v>1425.605</v>
       </c>
       <c r="M13" s="5">
-        <v>174.50249758675901</v>
+        <v>156.82289273676699</v>
       </c>
       <c r="N13" s="6">
         <v>13</v>
       </c>
       <c r="O13" s="6">
-        <v>2559.2199999999998</v>
+        <v>2723.14</v>
       </c>
       <c r="P13" s="6">
         <v>15</v>
@@ -1604,13 +1616,13 @@
         <v>2</v>
       </c>
       <c r="S13" s="6">
-        <v>170.61466666666601</v>
+        <v>181.54266666666601</v>
       </c>
       <c r="T13" s="6">
-        <v>319.90249999999997</v>
+        <v>340.39249999999998</v>
       </c>
       <c r="U13" s="6">
-        <v>524.95604129383105</v>
+        <v>487.33667751198902</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1637,7 +1649,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1660,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>528.97</v>
+        <v>533.46</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1672,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>264.48500000000001</v>
+        <v>266.73</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1697,7 +1709,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1741,7 +1753,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1761,10 +1773,10 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" s="6">
-        <v>765.28</v>
+        <v>822.31</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1791,7 +1803,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1808,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>1062.97</v>
+        <v>1086.8499999999999</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1826,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1062.97</v>
+        <v>1086.8499999999999</v>
       </c>
       <c r="L17" s="5">
-        <v>1062.97</v>
+        <v>1086.8499999999999</v>
       </c>
       <c r="M17" s="5">
         <v>-100</v>
@@ -1838,14 +1850,24 @@
         <v>1</v>
       </c>
       <c r="O17" s="6">
-        <v>621.11</v>
-      </c>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
+        <v>686.09</v>
+      </c>
+      <c r="P17" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6">
+        <v>0</v>
+      </c>
+      <c r="S17" s="6">
+        <v>686.09</v>
+      </c>
       <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
+      <c r="U17" s="6">
+        <v>-100</v>
+      </c>
       <c r="V17" s="7">
         <v>2</v>
       </c>
@@ -1871,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1891,10 +1913,10 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O18" s="6">
-        <v>2467.84</v>
+        <v>2613.64</v>
       </c>
       <c r="P18" s="6">
         <v>9</v>
@@ -1906,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>274.20444444444399</v>
+        <v>290.40444444444398</v>
       </c>
       <c r="T18" s="6">
-        <v>822.613333333333</v>
+        <v>871.21333333333303</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1933,7 +1955,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1941,16 +1963,16 @@
         <v>36</v>
       </c>
       <c r="B19" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C19" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="5">
         <v>7</v>
       </c>
       <c r="E19" s="5">
-        <v>2192.15</v>
+        <v>2317.7800000000002</v>
       </c>
       <c r="F19" s="5">
         <v>4</v>
@@ -1968,22 +1990,22 @@
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>548.03750000000002</v>
+        <v>579.44500000000005</v>
       </c>
       <c r="L19" s="5">
-        <v>1096.075</v>
+        <v>1158.8900000000001</v>
       </c>
       <c r="M19" s="5">
         <v>-100</v>
       </c>
       <c r="N19" s="6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O19" s="6">
-        <v>2743.83</v>
+        <v>2900.74</v>
       </c>
       <c r="P19" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q19" s="6">
         <v>4</v>
@@ -1992,13 +2014,13 @@
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>228.6525</v>
+        <v>223.13384615384601</v>
       </c>
       <c r="T19" s="6">
-        <v>685.95749999999998</v>
+        <v>725.18499999999995</v>
       </c>
       <c r="U19" s="6">
-        <v>158.764573606965</v>
+        <v>144.76719733585199</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2025,7 +2047,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2045,25 +2067,25 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O20" s="6">
-        <v>2803.16</v>
+        <v>2977.19</v>
       </c>
       <c r="P20" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q20" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R20" s="6">
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>311.46222222222201</v>
+        <v>270.653636363636</v>
       </c>
       <c r="T20" s="6">
-        <v>934.38666666666597</v>
+        <v>595.43799999999999</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2087,7 +2109,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2107,13 +2129,13 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O21" s="6">
-        <v>7224.04</v>
+        <v>7654.85</v>
       </c>
       <c r="P21" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q21" s="6">
         <v>4</v>
@@ -2122,13 +2144,13 @@
         <v>2</v>
       </c>
       <c r="S21" s="6">
-        <v>288.96159999999998</v>
+        <v>294.41730769230702</v>
       </c>
       <c r="T21" s="6">
-        <v>1806.01</v>
+        <v>1913.7125000000001</v>
       </c>
       <c r="U21" s="6">
-        <v>116.811645561209</v>
+        <v>104.609626576614</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2149,7 +2171,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2157,16 +2179,16 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C22" s="5">
         <v>2</v>
       </c>
       <c r="D22" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" s="5">
-        <v>2708.12</v>
+        <v>2917.94</v>
       </c>
       <c r="F22" s="5">
         <v>10</v>
@@ -2178,16 +2200,16 @@
         <v>9</v>
       </c>
       <c r="I22" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="5">
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>270.81200000000001</v>
+        <v>291.79399999999998</v>
       </c>
       <c r="L22" s="5">
-        <v>1354.06</v>
+        <v>972.64666666666596</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2196,7 +2218,7 @@
         <v>4</v>
       </c>
       <c r="O22" s="6">
-        <v>2289.11</v>
+        <v>2489.9699999999998</v>
       </c>
       <c r="P22" s="6">
         <v>5</v>
@@ -2208,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>457.822</v>
+        <v>497.99399999999901</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2239,7 +2261,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2262,22 +2284,22 @@
         <v>23</v>
       </c>
       <c r="O23" s="6">
-        <v>2895.75</v>
+        <v>3063.14</v>
       </c>
       <c r="P23" s="6">
         <v>13</v>
       </c>
       <c r="Q23" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R23" s="6">
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>222.75</v>
+        <v>235.62615384615299</v>
       </c>
       <c r="T23" s="6">
-        <v>2895.75</v>
+        <v>1531.57</v>
       </c>
       <c r="U23" s="6">
         <v>-100</v>
@@ -2305,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2325,14 +2347,14 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="6">
+        <v>6</v>
+      </c>
+      <c r="O24" s="6">
+        <v>1533.57</v>
+      </c>
+      <c r="P24" s="6">
         <v>5</v>
       </c>
-      <c r="O24" s="6">
-        <v>1415.02</v>
-      </c>
-      <c r="P24" s="6">
-        <v>4</v>
-      </c>
       <c r="Q24" s="6">
         <v>1</v>
       </c>
@@ -2340,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>353.755</v>
+        <v>306.714</v>
       </c>
       <c r="T24" s="6">
-        <v>1415.02</v>
+        <v>1533.57</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2367,7 +2389,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46160</v>
+        <v>46161</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2902,7 +2924,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -2971,14 +2993,14 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="18">
         <v>2026</v>
       </c>
-      <c r="C5" s="19" t="s">
-        <v>17</v>
+      <c r="C5" s="18" t="s">
+        <v>111</v>
       </c>
       <c r="D5" s="18">
         <v>34</v>
@@ -3005,10 +3027,10 @@
         <v>45253.33</v>
       </c>
       <c r="L5" s="18">
-        <v>19.32</v>
+        <v>12.06</v>
       </c>
       <c r="M5" s="18">
-        <v>35.119999999999997</v>
+        <v>21.7</v>
       </c>
       <c r="N5" s="18">
         <v>44.12</v>
@@ -3021,67 +3043,67 @@
       </c>
     </row>
     <row r="6" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6" s="19">
+      <c r="A6" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="18">
         <v>2026</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>17</v>
+      <c r="C6" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="D6" s="18">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H6" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="18">
-        <v>17649</v>
+        <v>7816</v>
       </c>
       <c r="J6" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="18">
-        <v>17649</v>
+        <v>7816</v>
       </c>
       <c r="L6" s="18">
-        <v>8.52</v>
+        <v>4.96</v>
       </c>
       <c r="M6" s="18">
-        <v>13.7</v>
+        <v>3.75</v>
       </c>
       <c r="N6" s="18">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O6" s="18">
-        <v>33.33</v>
+        <v>14.29</v>
       </c>
       <c r="P6" s="18">
-        <v>13.33</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="19">
+      <c r="A7" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="18">
         <v>2026</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>17</v>
+      <c r="C7" s="18" t="s">
+        <v>111</v>
       </c>
       <c r="D7" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" s="18">
         <v>1</v>
@@ -3090,13 +3112,13 @@
         <v>0</v>
       </c>
       <c r="G7" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="18">
-        <v>2286</v>
+        <v>0</v>
       </c>
       <c r="J7" s="18">
         <v>0</v>
@@ -3105,522 +3127,518 @@
         <v>0</v>
       </c>
       <c r="L7" s="18">
-        <v>1.7</v>
+        <v>0.35</v>
       </c>
       <c r="M7" s="18">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="N7" s="18">
         <v>0</v>
       </c>
       <c r="O7" s="18"/>
       <c r="P7" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="18">
+        <v>14</v>
+      </c>
+      <c r="E8" s="18">
+        <v>13</v>
+      </c>
+      <c r="F8" s="18">
+        <v>6</v>
+      </c>
+      <c r="G8" s="18">
+        <v>6</v>
+      </c>
+      <c r="H8" s="18">
+        <v>2</v>
+      </c>
+      <c r="I8" s="18">
+        <v>17649</v>
+      </c>
+      <c r="J8" s="18">
+        <v>2</v>
+      </c>
+      <c r="K8" s="18">
+        <v>17649</v>
+      </c>
+      <c r="L8" s="18">
+        <v>4.96</v>
+      </c>
+      <c r="M8" s="18">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="N8" s="18">
+        <v>42.86</v>
+      </c>
+      <c r="O8" s="18">
         <v>33.33</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="P8" s="18">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="18">
+        <v>14</v>
+      </c>
+      <c r="E9" s="18">
+        <v>14</v>
+      </c>
+      <c r="F9" s="18">
+        <v>4</v>
+      </c>
+      <c r="G9" s="18">
+        <v>3</v>
+      </c>
+      <c r="H9" s="18">
+        <v>1</v>
+      </c>
+      <c r="I9" s="18">
+        <v>6827</v>
+      </c>
+      <c r="J9" s="18">
+        <v>1</v>
+      </c>
+      <c r="K9" s="18">
+        <v>6827</v>
+      </c>
+      <c r="L9" s="18">
+        <v>4.96</v>
+      </c>
+      <c r="M9" s="18">
+        <v>3.27</v>
+      </c>
+      <c r="N9" s="18">
+        <v>28.57</v>
+      </c>
+      <c r="O9" s="18">
+        <v>25</v>
+      </c>
+      <c r="P9" s="18">
+        <v>7.14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="18">
+        <v>3</v>
+      </c>
+      <c r="E10" s="18">
+        <v>1</v>
+      </c>
+      <c r="F10" s="18">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18">
+        <v>2</v>
+      </c>
+      <c r="H10" s="18">
+        <v>1</v>
+      </c>
+      <c r="I10" s="18">
+        <v>2286</v>
+      </c>
+      <c r="J10" s="18">
+        <v>0</v>
+      </c>
+      <c r="K10" s="18">
+        <v>0</v>
+      </c>
+      <c r="L10" s="18">
+        <v>1.06</v>
+      </c>
+      <c r="M10" s="18">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N10" s="18">
+        <v>0</v>
+      </c>
+      <c r="O10" s="18"/>
+      <c r="P10" s="18">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="18">
+        <v>2</v>
+      </c>
+      <c r="E11" s="18">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
+        <v>2</v>
+      </c>
+      <c r="H11" s="18">
+        <v>1</v>
+      </c>
+      <c r="I11" s="18">
+        <v>5410</v>
+      </c>
+      <c r="J11" s="18">
+        <v>0</v>
+      </c>
+      <c r="K11" s="18">
+        <v>0</v>
+      </c>
+      <c r="L11" s="18">
+        <v>0.71</v>
+      </c>
+      <c r="M11" s="18">
+        <v>2.59</v>
+      </c>
+      <c r="N11" s="18">
+        <v>0</v>
+      </c>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B12" s="18">
         <v>2026</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="18">
-        <v>1</v>
-      </c>
-      <c r="E8" s="18">
-        <v>1</v>
-      </c>
-      <c r="F8" s="18">
-        <v>0</v>
-      </c>
-      <c r="G8" s="18">
-        <v>0</v>
-      </c>
-      <c r="H8" s="18">
-        <v>0</v>
-      </c>
-      <c r="I8" s="18">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="M8" s="18">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="C12" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="18">
+        <v>1</v>
+      </c>
+      <c r="E12" s="18">
+        <v>1</v>
+      </c>
+      <c r="F12" s="18">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18">
+        <v>0</v>
+      </c>
+      <c r="I12" s="18">
+        <v>0</v>
+      </c>
+      <c r="J12" s="18">
+        <v>0</v>
+      </c>
+      <c r="K12" s="18">
+        <v>0</v>
+      </c>
+      <c r="L12" s="18">
+        <v>0.35</v>
+      </c>
+      <c r="M12" s="18">
+        <v>0</v>
+      </c>
+      <c r="N12" s="18">
+        <v>0</v>
+      </c>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B13" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="18">
+        <v>1</v>
+      </c>
+      <c r="E13" s="18">
+        <v>0</v>
+      </c>
+      <c r="F13" s="18">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18">
+        <v>0</v>
+      </c>
+      <c r="H13" s="18">
+        <v>1</v>
+      </c>
+      <c r="I13" s="18">
+        <v>160.31</v>
+      </c>
+      <c r="J13" s="18">
+        <v>0</v>
+      </c>
+      <c r="K13" s="18">
+        <v>0</v>
+      </c>
+      <c r="L13" s="18">
+        <v>0.35</v>
+      </c>
+      <c r="M13" s="18">
+        <v>0.08</v>
+      </c>
+      <c r="N13" s="18">
+        <v>100</v>
+      </c>
+      <c r="O13" s="18">
+        <v>100</v>
+      </c>
+      <c r="P13" s="18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="18">
+        <v>1</v>
+      </c>
+      <c r="E14" s="18">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18">
+        <v>0</v>
+      </c>
+      <c r="I14" s="18">
+        <v>0</v>
+      </c>
+      <c r="J14" s="18">
+        <v>0</v>
+      </c>
+      <c r="K14" s="18">
+        <v>0</v>
+      </c>
+      <c r="L14" s="18">
+        <v>0.35</v>
+      </c>
+      <c r="M14" s="18">
+        <v>0</v>
+      </c>
+      <c r="N14" s="18">
+        <v>0</v>
+      </c>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B15" s="18">
         <v>2026</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="18">
-        <v>1</v>
-      </c>
-      <c r="E9" s="18">
-        <v>1</v>
-      </c>
-      <c r="F9" s="18">
-        <v>0</v>
-      </c>
-      <c r="G9" s="18">
-        <v>0</v>
-      </c>
-      <c r="H9" s="18">
-        <v>0</v>
-      </c>
-      <c r="I9" s="18">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18">
-        <v>0</v>
-      </c>
-      <c r="K9" s="18">
-        <v>0</v>
-      </c>
-      <c r="L9" s="18">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="M9" s="18">
-        <v>0</v>
-      </c>
-      <c r="N9" s="18">
-        <v>0</v>
-      </c>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="C15" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="18">
+        <v>1</v>
+      </c>
+      <c r="E15" s="18">
+        <v>1</v>
+      </c>
+      <c r="F15" s="18">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18">
+        <v>0</v>
+      </c>
+      <c r="I15" s="18">
+        <v>0</v>
+      </c>
+      <c r="J15" s="18">
+        <v>0</v>
+      </c>
+      <c r="K15" s="18">
+        <v>0</v>
+      </c>
+      <c r="L15" s="18">
+        <v>0.35</v>
+      </c>
+      <c r="M15" s="18">
+        <v>0</v>
+      </c>
+      <c r="N15" s="18">
+        <v>0</v>
+      </c>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="18">
+        <v>1</v>
+      </c>
+      <c r="E16" s="18">
+        <v>1</v>
+      </c>
+      <c r="F16" s="18">
+        <v>1</v>
+      </c>
+      <c r="G16" s="18">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <v>0</v>
+      </c>
+      <c r="I16" s="18">
+        <v>0</v>
+      </c>
+      <c r="J16" s="18">
+        <v>0</v>
+      </c>
+      <c r="K16" s="18">
+        <v>0</v>
+      </c>
+      <c r="L16" s="18">
+        <v>0.35</v>
+      </c>
+      <c r="M16" s="18">
+        <v>0</v>
+      </c>
+      <c r="N16" s="18">
+        <v>100</v>
+      </c>
+      <c r="O16" s="18">
+        <v>0</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B17" s="18">
         <v>2026</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="18">
+      <c r="C17" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="18">
         <v>7</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E17" s="18">
         <v>7</v>
       </c>
-      <c r="F10" s="18">
-        <v>1</v>
-      </c>
-      <c r="G10" s="18">
-        <v>2</v>
-      </c>
-      <c r="H10" s="18">
-        <v>0</v>
-      </c>
-      <c r="I10" s="18">
-        <v>0</v>
-      </c>
-      <c r="J10" s="18">
-        <v>0</v>
-      </c>
-      <c r="K10" s="18">
-        <v>0</v>
-      </c>
-      <c r="L10" s="18">
-        <v>3.98</v>
-      </c>
-      <c r="M10" s="18">
-        <v>0</v>
-      </c>
-      <c r="N10" s="18">
+      <c r="F17" s="18">
+        <v>1</v>
+      </c>
+      <c r="G17" s="18">
+        <v>2</v>
+      </c>
+      <c r="H17" s="18">
+        <v>0</v>
+      </c>
+      <c r="I17" s="18">
+        <v>0</v>
+      </c>
+      <c r="J17" s="18">
+        <v>0</v>
+      </c>
+      <c r="K17" s="18">
+        <v>0</v>
+      </c>
+      <c r="L17" s="18">
+        <v>2.48</v>
+      </c>
+      <c r="M17" s="18">
+        <v>0</v>
+      </c>
+      <c r="N17" s="18">
         <v>14.29</v>
       </c>
-      <c r="O10" s="18">
-        <v>0</v>
-      </c>
-      <c r="P10" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="19">
+      <c r="O17" s="18">
+        <v>0</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="18">
         <v>2026</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="18">
-        <v>10</v>
-      </c>
-      <c r="E11" s="18">
-        <v>8</v>
-      </c>
-      <c r="F11" s="18">
-        <v>6</v>
-      </c>
-      <c r="G11" s="18">
-        <v>4</v>
-      </c>
-      <c r="H11" s="18">
-        <v>3</v>
-      </c>
-      <c r="I11" s="18">
-        <v>18084</v>
-      </c>
-      <c r="J11" s="18">
-        <v>2</v>
-      </c>
-      <c r="K11" s="18">
-        <v>12850</v>
-      </c>
-      <c r="L11" s="18">
-        <v>5.68</v>
-      </c>
-      <c r="M11" s="18">
-        <v>14.03</v>
-      </c>
-      <c r="N11" s="18">
-        <v>60</v>
-      </c>
-      <c r="O11" s="18">
-        <v>50</v>
-      </c>
-      <c r="P11" s="18">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="18">
-        <v>71</v>
-      </c>
-      <c r="E12" s="18">
-        <v>63</v>
-      </c>
-      <c r="F12" s="18">
-        <v>1</v>
-      </c>
-      <c r="G12" s="18">
-        <v>21</v>
-      </c>
-      <c r="H12" s="18">
-        <v>4</v>
-      </c>
-      <c r="I12" s="18">
-        <v>30692.31</v>
-      </c>
-      <c r="J12" s="18">
-        <v>3</v>
-      </c>
-      <c r="K12" s="18">
-        <v>30532</v>
-      </c>
-      <c r="L12" s="18">
-        <v>40.340000000000003</v>
-      </c>
-      <c r="M12" s="18">
-        <v>23.82</v>
-      </c>
-      <c r="N12" s="18">
-        <v>1.41</v>
-      </c>
-      <c r="O12" s="18">
-        <v>400</v>
-      </c>
-      <c r="P12" s="18">
-        <v>5.63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="18">
-        <v>8</v>
-      </c>
-      <c r="E13" s="18">
-        <v>6</v>
-      </c>
-      <c r="F13" s="18">
-        <v>4</v>
-      </c>
-      <c r="G13" s="18">
-        <v>2</v>
-      </c>
-      <c r="H13" s="18">
-        <v>0</v>
-      </c>
-      <c r="I13" s="18">
-        <v>0</v>
-      </c>
-      <c r="J13" s="18">
-        <v>0</v>
-      </c>
-      <c r="K13" s="18">
-        <v>0</v>
-      </c>
-      <c r="L13" s="18">
-        <v>4.55</v>
-      </c>
-      <c r="M13" s="18">
-        <v>0</v>
-      </c>
-      <c r="N13" s="18">
-        <v>50</v>
-      </c>
-      <c r="O13" s="18">
-        <v>0</v>
-      </c>
-      <c r="P13" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="18">
-        <v>9</v>
-      </c>
-      <c r="E14" s="18">
-        <v>7</v>
-      </c>
-      <c r="F14" s="18">
-        <v>3</v>
-      </c>
-      <c r="G14" s="18">
-        <v>2</v>
-      </c>
-      <c r="H14" s="18">
-        <v>1</v>
-      </c>
-      <c r="I14" s="18">
-        <v>7816</v>
-      </c>
-      <c r="J14" s="18">
-        <v>1</v>
-      </c>
-      <c r="K14" s="18">
-        <v>7816</v>
-      </c>
-      <c r="L14" s="18">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="M14" s="18">
-        <v>6.07</v>
-      </c>
-      <c r="N14" s="18">
-        <v>33.33</v>
-      </c>
-      <c r="O14" s="18">
-        <v>33.33</v>
-      </c>
-      <c r="P14" s="18">
-        <v>11.11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="18">
-        <v>3</v>
-      </c>
-      <c r="E15" s="18">
-        <v>3</v>
-      </c>
-      <c r="F15" s="18">
-        <v>2</v>
-      </c>
-      <c r="G15" s="18">
-        <v>1</v>
-      </c>
-      <c r="H15" s="18">
-        <v>0</v>
-      </c>
-      <c r="I15" s="18">
-        <v>0</v>
-      </c>
-      <c r="J15" s="18">
-        <v>0</v>
-      </c>
-      <c r="K15" s="18">
-        <v>0</v>
-      </c>
-      <c r="L15" s="18">
-        <v>1.7</v>
-      </c>
-      <c r="M15" s="18">
-        <v>0</v>
-      </c>
-      <c r="N15" s="18">
-        <v>66.67</v>
-      </c>
-      <c r="O15" s="18">
-        <v>0</v>
-      </c>
-      <c r="P15" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="18">
-        <v>10</v>
-      </c>
-      <c r="E16" s="18">
-        <v>8</v>
-      </c>
-      <c r="F16" s="18">
-        <v>1</v>
-      </c>
-      <c r="G16" s="18">
-        <v>1</v>
-      </c>
-      <c r="H16" s="18">
-        <v>1</v>
-      </c>
-      <c r="I16" s="18">
-        <v>7072</v>
-      </c>
-      <c r="J16" s="18">
-        <v>0</v>
-      </c>
-      <c r="K16" s="18">
-        <v>0</v>
-      </c>
-      <c r="L16" s="18">
-        <v>5.68</v>
-      </c>
-      <c r="M16" s="18">
-        <v>5.49</v>
-      </c>
-      <c r="N16" s="18">
-        <v>10</v>
-      </c>
-      <c r="O16" s="18">
-        <v>100</v>
-      </c>
-      <c r="P16" s="18">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="18">
-        <v>2</v>
-      </c>
-      <c r="E17" s="18">
-        <v>2</v>
-      </c>
-      <c r="F17" s="18">
-        <v>0</v>
-      </c>
-      <c r="G17" s="18">
-        <v>0</v>
-      </c>
-      <c r="H17" s="18">
-        <v>0</v>
-      </c>
-      <c r="I17" s="18">
-        <v>0</v>
-      </c>
-      <c r="J17" s="18">
-        <v>0</v>
-      </c>
-      <c r="K17" s="18">
-        <v>0</v>
-      </c>
-      <c r="L17" s="18">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="M17" s="18">
-        <v>0</v>
-      </c>
-      <c r="N17" s="18">
-        <v>0</v>
-      </c>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>17</v>
+      <c r="C18" s="18" t="s">
+        <v>18</v>
       </c>
       <c r="D18" s="18">
         <v>2</v>
@@ -3647,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="18">
-        <v>1.1399999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="M18" s="18">
         <v>0</v>
@@ -3663,70 +3681,70 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>90</v>
-      </c>
-      <c r="B19" s="19">
+      <c r="A19" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="18">
         <v>2026</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>18</v>
+      <c r="C19" s="18" t="s">
+        <v>111</v>
       </c>
       <c r="D19" s="10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" s="10">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F19" s="10">
         <v>6</v>
       </c>
       <c r="G19" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="10">
-        <v>7816</v>
+        <v>10468</v>
       </c>
       <c r="J19" s="10">
         <v>1</v>
       </c>
       <c r="K19" s="10">
-        <v>7816</v>
+        <v>5234</v>
       </c>
       <c r="L19" s="10">
-        <v>12.12</v>
+        <v>3.55</v>
       </c>
       <c r="M19" s="10">
-        <v>9.57</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="N19" s="10">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="O19" s="10">
-        <v>16.670000000000002</v>
+        <v>33.33</v>
       </c>
       <c r="P19" s="10">
-        <v>8.33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="19">
+      <c r="A20" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="18">
         <v>2026</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="10">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E20" s="10">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F20" s="10">
         <v>3</v>
@@ -3735,533 +3753,535 @@
         <v>3</v>
       </c>
       <c r="H20" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="10">
-        <v>6827</v>
+        <v>0</v>
       </c>
       <c r="J20" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="10">
-        <v>6827</v>
+        <v>0</v>
       </c>
       <c r="L20" s="10">
-        <v>13.13</v>
+        <v>2.48</v>
       </c>
       <c r="M20" s="10">
-        <v>8.36</v>
+        <v>0</v>
       </c>
       <c r="N20" s="10">
-        <v>23.08</v>
+        <v>42.86</v>
       </c>
       <c r="O20" s="10">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="P20" s="10">
-        <v>7.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" s="19">
+      <c r="A21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="18">
         <v>2026</v>
       </c>
-      <c r="C21" s="19" t="s">
-        <v>18</v>
+      <c r="C21" s="18" t="s">
+        <v>111</v>
       </c>
       <c r="D21" s="10">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="E21" s="10">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F21" s="10">
         <v>0</v>
       </c>
       <c r="G21" s="10">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H21" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I21" s="10">
-        <v>5410</v>
+        <v>36031</v>
       </c>
       <c r="J21" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K21" s="10">
-        <v>0</v>
+        <v>36031</v>
       </c>
       <c r="L21" s="10">
-        <v>2.02</v>
+        <v>24.82</v>
       </c>
       <c r="M21" s="10">
-        <v>6.63</v>
+        <v>17.28</v>
       </c>
       <c r="N21" s="10">
         <v>0</v>
       </c>
       <c r="O21" s="10"/>
       <c r="P21" s="10">
-        <v>50</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>109</v>
-      </c>
-      <c r="B22" s="19">
+      <c r="A22" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" s="18">
         <v>2026</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D22" s="10">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E22" s="10">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F22" s="10">
         <v>0</v>
       </c>
       <c r="G22" s="10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H22" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I22" s="10">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="J22" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K22" s="10">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="L22" s="10">
-        <v>1.01</v>
+        <v>12.77</v>
       </c>
       <c r="M22" s="10">
-        <v>0</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="N22" s="10">
         <v>0</v>
       </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10">
-        <v>0</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="19">
+      <c r="A23" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="18">
         <v>2026</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="10">
+        <v>8</v>
+      </c>
+      <c r="E23" s="10">
+        <v>6</v>
+      </c>
+      <c r="F23" s="10">
+        <v>4</v>
+      </c>
+      <c r="G23" s="10">
+        <v>2</v>
+      </c>
+      <c r="H23" s="10">
+        <v>0</v>
+      </c>
+      <c r="I23" s="10">
+        <v>0</v>
+      </c>
+      <c r="J23" s="10">
+        <v>0</v>
+      </c>
+      <c r="K23" s="10">
+        <v>0</v>
+      </c>
+      <c r="L23" s="10">
+        <v>2.84</v>
+      </c>
+      <c r="M23" s="10">
+        <v>0</v>
+      </c>
+      <c r="N23" s="10">
+        <v>50</v>
+      </c>
+      <c r="O23" s="10">
+        <v>0</v>
+      </c>
+      <c r="P23" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C24" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="10">
-        <v>1</v>
-      </c>
-      <c r="E23" s="10">
-        <v>1</v>
-      </c>
-      <c r="F23" s="10">
-        <v>1</v>
-      </c>
-      <c r="G23" s="10">
-        <v>0</v>
-      </c>
-      <c r="H23" s="10">
-        <v>0</v>
-      </c>
-      <c r="I23" s="10">
-        <v>0</v>
-      </c>
-      <c r="J23" s="10">
-        <v>0</v>
-      </c>
-      <c r="K23" s="10">
-        <v>0</v>
-      </c>
-      <c r="L23" s="10">
-        <v>1.01</v>
-      </c>
-      <c r="M23" s="10">
-        <v>0</v>
-      </c>
-      <c r="N23" s="10">
+      <c r="D24" s="10">
+        <v>8</v>
+      </c>
+      <c r="E24" s="10">
+        <v>8</v>
+      </c>
+      <c r="F24" s="10">
+        <v>2</v>
+      </c>
+      <c r="G24" s="10">
+        <v>2</v>
+      </c>
+      <c r="H24" s="10">
+        <v>2</v>
+      </c>
+      <c r="I24" s="10">
+        <v>15374</v>
+      </c>
+      <c r="J24" s="10">
+        <v>2</v>
+      </c>
+      <c r="K24" s="10">
+        <v>15374</v>
+      </c>
+      <c r="L24" s="10">
+        <v>2.84</v>
+      </c>
+      <c r="M24" s="10">
+        <v>7.37</v>
+      </c>
+      <c r="N24" s="10">
+        <v>25</v>
+      </c>
+      <c r="O24" s="10">
         <v>100</v>
       </c>
-      <c r="O23" s="10">
-        <v>0</v>
-      </c>
-      <c r="P23" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="19">
+      <c r="P24" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="18">
         <v>2026</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C25" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="10">
-        <v>2</v>
-      </c>
-      <c r="E24" s="10">
-        <v>2</v>
-      </c>
-      <c r="F24" s="10">
-        <v>1</v>
-      </c>
-      <c r="G24" s="10">
-        <v>1</v>
-      </c>
-      <c r="H24" s="10">
-        <v>0</v>
-      </c>
-      <c r="I24" s="10">
-        <v>0</v>
-      </c>
-      <c r="J24" s="10">
-        <v>0</v>
-      </c>
-      <c r="K24" s="10">
-        <v>0</v>
-      </c>
-      <c r="L24" s="10">
-        <v>2.02</v>
-      </c>
-      <c r="M24" s="10">
-        <v>0</v>
-      </c>
-      <c r="N24" s="10">
+      <c r="D25" s="10">
+        <v>1</v>
+      </c>
+      <c r="E25" s="10">
+        <v>1</v>
+      </c>
+      <c r="F25" s="10">
+        <v>0</v>
+      </c>
+      <c r="G25" s="10">
+        <v>0</v>
+      </c>
+      <c r="H25" s="10">
+        <v>0</v>
+      </c>
+      <c r="I25" s="10">
+        <v>0</v>
+      </c>
+      <c r="J25" s="10">
+        <v>0</v>
+      </c>
+      <c r="K25" s="10">
+        <v>0</v>
+      </c>
+      <c r="L25" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="M25" s="10">
+        <v>0</v>
+      </c>
+      <c r="N25" s="10">
+        <v>0</v>
+      </c>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="10">
+        <v>10</v>
+      </c>
+      <c r="E26" s="10">
+        <v>8</v>
+      </c>
+      <c r="F26" s="10">
+        <v>3</v>
+      </c>
+      <c r="G26" s="10">
+        <v>2</v>
+      </c>
+      <c r="H26" s="10">
+        <v>1</v>
+      </c>
+      <c r="I26" s="10">
+        <v>7816</v>
+      </c>
+      <c r="J26" s="10">
+        <v>1</v>
+      </c>
+      <c r="K26" s="10">
+        <v>7816</v>
+      </c>
+      <c r="L26" s="10">
+        <v>3.55</v>
+      </c>
+      <c r="M26" s="10">
+        <v>3.75</v>
+      </c>
+      <c r="N26" s="10">
+        <v>30</v>
+      </c>
+      <c r="O26" s="10">
+        <v>33.33</v>
+      </c>
+      <c r="P26" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B27" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="10">
+        <v>6</v>
+      </c>
+      <c r="E27" s="10">
+        <v>5</v>
+      </c>
+      <c r="F27" s="10">
+        <v>3</v>
+      </c>
+      <c r="G27" s="10">
+        <v>0</v>
+      </c>
+      <c r="H27" s="10">
+        <v>2</v>
+      </c>
+      <c r="I27" s="10">
+        <v>17865</v>
+      </c>
+      <c r="J27" s="10">
+        <v>2</v>
+      </c>
+      <c r="K27" s="10">
+        <v>17865</v>
+      </c>
+      <c r="L27" s="10">
+        <v>2.13</v>
+      </c>
+      <c r="M27" s="10">
+        <v>8.57</v>
+      </c>
+      <c r="N27" s="10">
         <v>50</v>
       </c>
-      <c r="O24" s="10">
-        <v>0</v>
-      </c>
-      <c r="P24" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="19">
+      <c r="O27" s="10">
+        <v>66.67</v>
+      </c>
+      <c r="P27" s="10">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B28" s="18">
         <v>2026</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C28" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="10">
+        <v>3</v>
+      </c>
+      <c r="E28" s="10">
+        <v>3</v>
+      </c>
+      <c r="F28" s="10">
+        <v>3</v>
+      </c>
+      <c r="G28" s="10">
+        <v>1</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10">
+        <v>0</v>
+      </c>
+      <c r="J28" s="10">
+        <v>0</v>
+      </c>
+      <c r="K28" s="10">
+        <v>0</v>
+      </c>
+      <c r="L28" s="10">
+        <v>1.06</v>
+      </c>
+      <c r="M28" s="10">
+        <v>0</v>
+      </c>
+      <c r="N28" s="10">
+        <v>100</v>
+      </c>
+      <c r="O28" s="10">
+        <v>0</v>
+      </c>
+      <c r="P28" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C29" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="10">
-        <v>6</v>
-      </c>
-      <c r="E25" s="10">
-        <v>6</v>
-      </c>
-      <c r="F25" s="10">
+      <c r="D29" s="10">
+        <v>9</v>
+      </c>
+      <c r="E29" s="10">
+        <v>9</v>
+      </c>
+      <c r="F29" s="10">
+        <v>5</v>
+      </c>
+      <c r="G29" s="10">
         <v>3</v>
       </c>
-      <c r="G25" s="10">
-        <v>2</v>
-      </c>
-      <c r="H25" s="10">
-        <v>0</v>
-      </c>
-      <c r="I25" s="10">
-        <v>0</v>
-      </c>
-      <c r="J25" s="10">
-        <v>0</v>
-      </c>
-      <c r="K25" s="10">
-        <v>0</v>
-      </c>
-      <c r="L25" s="10">
-        <v>6.06</v>
-      </c>
-      <c r="M25" s="10">
-        <v>0</v>
-      </c>
-      <c r="N25" s="10">
-        <v>50</v>
-      </c>
-      <c r="O25" s="10">
-        <v>0</v>
-      </c>
-      <c r="P25" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="19">
+      <c r="H29" s="10">
+        <v>2</v>
+      </c>
+      <c r="I29" s="10">
+        <v>8117.12</v>
+      </c>
+      <c r="J29" s="10">
+        <v>2</v>
+      </c>
+      <c r="K29" s="10">
+        <v>8117.12</v>
+      </c>
+      <c r="L29" s="10">
+        <v>3.19</v>
+      </c>
+      <c r="M29" s="10">
+        <v>3.89</v>
+      </c>
+      <c r="N29" s="10">
+        <v>55.56</v>
+      </c>
+      <c r="O29" s="10">
+        <v>40</v>
+      </c>
+      <c r="P29" s="10">
+        <v>22.22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="18">
         <v>2026</v>
       </c>
-      <c r="C26" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="10">
-        <v>34</v>
-      </c>
-      <c r="E26" s="10">
-        <v>33</v>
-      </c>
-      <c r="F26" s="10">
-        <v>0</v>
-      </c>
-      <c r="G26" s="10">
-        <v>9</v>
-      </c>
-      <c r="H26" s="10">
-        <v>3</v>
-      </c>
-      <c r="I26" s="10">
-        <v>20397</v>
-      </c>
-      <c r="J26" s="10">
-        <v>3</v>
-      </c>
-      <c r="K26" s="10">
-        <v>20397</v>
-      </c>
-      <c r="L26" s="10">
-        <v>34.340000000000003</v>
-      </c>
-      <c r="M26" s="10">
-        <v>24.98</v>
-      </c>
-      <c r="N26" s="10">
-        <v>0</v>
-      </c>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10">
-        <v>8.82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="10">
-        <v>7</v>
-      </c>
-      <c r="E27" s="10">
-        <v>7</v>
-      </c>
-      <c r="F27" s="10">
-        <v>2</v>
-      </c>
-      <c r="G27" s="10">
-        <v>2</v>
-      </c>
-      <c r="H27" s="10">
-        <v>2</v>
-      </c>
-      <c r="I27" s="10">
-        <v>15224</v>
-      </c>
-      <c r="J27" s="10">
-        <v>2</v>
-      </c>
-      <c r="K27" s="10">
-        <v>15224</v>
-      </c>
-      <c r="L27" s="10">
-        <v>7.07</v>
-      </c>
-      <c r="M27" s="10">
-        <v>18.64</v>
-      </c>
-      <c r="N27" s="10">
-        <v>28.57</v>
-      </c>
-      <c r="O27" s="10">
-        <v>100</v>
-      </c>
-      <c r="P27" s="10">
-        <v>28.57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>110</v>
-      </c>
-      <c r="B28" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="10">
-        <v>1</v>
-      </c>
-      <c r="E28" s="10">
-        <v>1</v>
-      </c>
-      <c r="F28" s="10">
-        <v>0</v>
-      </c>
-      <c r="G28" s="10">
-        <v>0</v>
-      </c>
-      <c r="H28" s="10">
-        <v>0</v>
-      </c>
-      <c r="I28" s="10">
-        <v>0</v>
-      </c>
-      <c r="J28" s="10">
-        <v>0</v>
-      </c>
-      <c r="K28" s="10">
-        <v>0</v>
-      </c>
-      <c r="L28" s="10">
-        <v>1.01</v>
-      </c>
-      <c r="M28" s="10">
-        <v>0</v>
-      </c>
-      <c r="N28" s="10">
-        <v>0</v>
-      </c>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>99</v>
-      </c>
-      <c r="B29" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="10">
-        <v>6</v>
-      </c>
-      <c r="E29" s="10">
-        <v>5</v>
-      </c>
-      <c r="F29" s="10">
-        <v>3</v>
-      </c>
-      <c r="G29" s="10">
-        <v>0</v>
-      </c>
-      <c r="H29" s="10">
-        <v>2</v>
-      </c>
-      <c r="I29" s="10">
-        <v>17865</v>
-      </c>
-      <c r="J29" s="10">
-        <v>2</v>
-      </c>
-      <c r="K29" s="10">
-        <v>17865</v>
-      </c>
-      <c r="L29" s="10">
-        <v>6.06</v>
-      </c>
-      <c r="M29" s="10">
-        <v>21.88</v>
-      </c>
-      <c r="N29" s="10">
-        <v>50</v>
-      </c>
-      <c r="O29" s="10">
-        <v>66.67</v>
-      </c>
-      <c r="P29" s="10">
-        <v>33.33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>18</v>
+      <c r="C30" s="18" t="s">
+        <v>111</v>
       </c>
       <c r="D30" s="10">
         <v>9</v>
       </c>
       <c r="E30" s="10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F30" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G30" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="10">
-        <v>8117.12</v>
+        <v>7072</v>
       </c>
       <c r="J30" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" s="10">
-        <v>8117.12</v>
+        <v>0</v>
       </c>
       <c r="L30" s="10">
-        <v>9.09</v>
+        <v>3.19</v>
       </c>
       <c r="M30" s="10">
-        <v>9.94</v>
+        <v>3.39</v>
       </c>
       <c r="N30" s="10">
-        <v>44.44</v>
+        <v>11.11</v>
       </c>
       <c r="O30" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="P30" s="10">
-        <v>22.22</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+      <c r="A31" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="18">
         <v>2026</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="18" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="10">
@@ -4289,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>2.02</v>
+        <v>0.71</v>
       </c>
       <c r="M31" s="10">
         <v>0</v>
@@ -4305,73 +4325,71 @@
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="A32" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="18">
         <v>2026</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="10">
+        <v>2</v>
+      </c>
+      <c r="E32" s="10">
+        <v>2</v>
+      </c>
+      <c r="F32" s="10">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10">
+        <v>0</v>
+      </c>
+      <c r="H32" s="10">
+        <v>0</v>
+      </c>
+      <c r="I32" s="10">
+        <v>0</v>
+      </c>
+      <c r="J32" s="10">
+        <v>0</v>
+      </c>
+      <c r="K32" s="10">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10">
+        <v>0.71</v>
+      </c>
+      <c r="M32" s="10">
+        <v>0</v>
+      </c>
+      <c r="N32" s="10">
+        <v>0</v>
+      </c>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B33" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C33" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="10">
-        <v>1</v>
-      </c>
-      <c r="E32" s="10">
-        <v>1</v>
-      </c>
-      <c r="F32" s="10">
-        <v>1</v>
-      </c>
-      <c r="G32" s="10">
-        <v>0</v>
-      </c>
-      <c r="H32" s="10">
-        <v>0</v>
-      </c>
-      <c r="I32" s="10">
-        <v>0</v>
-      </c>
-      <c r="J32" s="10">
-        <v>0</v>
-      </c>
-      <c r="K32" s="10">
-        <v>0</v>
-      </c>
-      <c r="L32" s="10">
-        <v>1.01</v>
-      </c>
-      <c r="M32" s="10">
-        <v>0</v>
-      </c>
-      <c r="N32" s="10">
-        <v>100</v>
-      </c>
-      <c r="O32" s="10">
-        <v>0</v>
-      </c>
-      <c r="P32" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" s="19">
-        <v>2026</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>18</v>
-      </c>
       <c r="D33" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="10">
         <v>0</v>
@@ -4389,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>2.02</v>
+        <v>0.35</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
@@ -4401,6 +4419,106 @@
         <v>0</v>
       </c>
       <c r="P33" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="10">
+        <v>2026</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" s="10">
+        <v>2</v>
+      </c>
+      <c r="E34" s="10">
+        <v>2</v>
+      </c>
+      <c r="F34" s="10">
+        <v>1</v>
+      </c>
+      <c r="G34" s="10">
+        <v>1</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10">
+        <v>0</v>
+      </c>
+      <c r="J34" s="10">
+        <v>0</v>
+      </c>
+      <c r="K34" s="10">
+        <v>0</v>
+      </c>
+      <c r="L34" s="10">
+        <v>0.71</v>
+      </c>
+      <c r="M34" s="10">
+        <v>0</v>
+      </c>
+      <c r="N34" s="10">
+        <v>50</v>
+      </c>
+      <c r="O34" s="10">
+        <v>0</v>
+      </c>
+      <c r="P34" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="10">
+        <v>2026</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="10">
+        <v>2</v>
+      </c>
+      <c r="E35" s="10">
+        <v>2</v>
+      </c>
+      <c r="F35" s="10">
+        <v>2</v>
+      </c>
+      <c r="G35" s="10">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10">
+        <v>0</v>
+      </c>
+      <c r="J35" s="10">
+        <v>0</v>
+      </c>
+      <c r="K35" s="10">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10">
+        <v>0.71</v>
+      </c>
+      <c r="M35" s="10">
+        <v>0</v>
+      </c>
+      <c r="N35" s="10">
+        <v>100</v>
+      </c>
+      <c r="O35" s="10">
+        <v>0</v>
+      </c>
+      <c r="P35" s="10">
         <v>0</v>
       </c>
     </row>
@@ -4913,10 +5031,10 @@
         <v>12</v>
       </c>
       <c r="J17" s="5">
-        <v>68761.23</v>
+        <v>73257.23</v>
       </c>
       <c r="K17" s="5">
-        <v>8.2200000000000006</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5035,28 +5153,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1774</v>
+        <v>1877</v>
       </c>
       <c r="E21" s="10">
-        <v>4326.1899999999996</v>
+        <v>4580.99</v>
       </c>
       <c r="F21" s="10">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="G21" s="10">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H21" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="10">
         <v>9</v>
       </c>
       <c r="J21" s="10">
-        <v>59195</v>
+        <v>59345</v>
       </c>
       <c r="K21" s="10">
-        <v>12.68</v>
+        <v>11.95</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5630,10 +5748,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="E38" s="10">
-        <v>1498.03</v>
+        <v>1554.02</v>
       </c>
       <c r="F38" s="10">
         <v>5</v>
@@ -5884,7 +6002,7 @@
         <v>23</v>
       </c>
       <c r="G45" s="10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H45" s="10">
         <v>6</v>
@@ -6059,7 +6177,7 @@
         <v>35</v>
       </c>
       <c r="G50" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="10">
         <v>12</v>
@@ -6225,19 +6343,19 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>647</v>
+        <v>686</v>
       </c>
       <c r="E55" s="10">
-        <v>5013.74</v>
+        <v>5305.17</v>
       </c>
       <c r="F55" s="10">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G55" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H55" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I55" s="10">
         <v>1</v>
@@ -6246,7 +6364,7 @@
         <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>0.56000000000000005</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6504,7 +6622,7 @@
         <v>3</v>
       </c>
       <c r="G63" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H63" s="10">
         <v>5</v>
@@ -7220,10 +7338,10 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="E84" s="10">
-        <v>2641.3</v>
+        <v>2804.08</v>
       </c>
       <c r="F84" s="10">
         <v>6</v>
@@ -8110,10 +8228,10 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>509</v>
+        <v>537</v>
       </c>
       <c r="E110" s="10">
-        <v>5335.15</v>
+        <v>5702.42</v>
       </c>
       <c r="F110" s="10">
         <v>23</v>
@@ -8131,7 +8249,7 @@
         <v>14645.12</v>
       </c>
       <c r="K110" s="10">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9625,10 +9743,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E155" s="10">
-        <v>1062.97</v>
+        <v>1086.8499999999999</v>
       </c>
       <c r="F155" s="10">
         <v>2</v>
@@ -10711,13 +10829,13 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="E186" s="10">
-        <v>2192.15</v>
+        <v>2317.7800000000002</v>
       </c>
       <c r="F186" s="10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G186" s="10">
         <v>4</v>
@@ -12286,19 +12404,19 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="E231" s="10">
-        <v>2708.12</v>
+        <v>2917.94</v>
       </c>
       <c r="F231" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G231" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H231" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I231" s="10">
         <v>0</v>
@@ -15580,7 +15698,7 @@
         <v>2026</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>13</v>
@@ -15618,16 +15736,16 @@
         <v>2026</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E6" s="18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G6" s="18">
         <v>2</v>
@@ -15656,34 +15774,34 @@
         <v>2026</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E7" s="18">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F7" s="18">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G7" s="18">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H7" s="18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I7" s="18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J7" s="18">
-        <v>45253.33</v>
+        <v>0</v>
       </c>
       <c r="K7" s="18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L7" s="18">
-        <v>45253.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -15694,98 +15812,98 @@
         <v>2026</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E8" s="18">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="F8" s="18">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G8" s="18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H8" s="18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I8" s="18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J8" s="18">
-        <v>0</v>
+        <v>45253.33</v>
       </c>
       <c r="K8" s="18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L8" s="18">
-        <v>0</v>
+        <v>45253.33</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B9" s="18">
         <v>2026</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="E9" s="18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" s="18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G9" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="18">
         <v>1</v>
       </c>
       <c r="J9" s="18">
-        <v>8991</v>
+        <v>7816</v>
       </c>
       <c r="K9" s="18">
         <v>1</v>
       </c>
       <c r="L9" s="18">
-        <v>8991</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B10" s="18">
         <v>2026</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E10" s="18">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F10" s="18">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G10" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" s="18">
         <v>0</v>
@@ -15802,16 +15920,16 @@
     </row>
     <row r="11" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B11" s="18">
         <v>2026</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E11" s="18">
         <v>1</v>
@@ -15823,51 +15941,51 @@
         <v>1</v>
       </c>
       <c r="H11" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="18">
-        <v>8658</v>
+        <v>0</v>
       </c>
       <c r="K11" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="18">
-        <v>8658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="B12" s="18">
         <v>2026</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E12" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="18">
         <v>0</v>
       </c>
       <c r="H12" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="18">
-        <v>2286</v>
+        <v>0</v>
       </c>
       <c r="K12" s="18">
         <v>0</v>
@@ -15878,51 +15996,51 @@
     </row>
     <row r="13" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B13" s="18">
         <v>2026</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E13" s="18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F13" s="18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G13" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="18">
-        <v>0</v>
+        <v>8991</v>
       </c>
       <c r="K13" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="18">
-        <v>0</v>
+        <v>8991</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B14" s="18">
         <v>2026</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>13</v>
@@ -15954,28 +16072,28 @@
     </row>
     <row r="15" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B15" s="18">
         <v>2026</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E15" s="18">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F15" s="18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G15" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" s="18">
         <v>0</v>
@@ -15992,92 +16110,92 @@
     </row>
     <row r="16" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B16" s="18">
         <v>2026</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E16" s="18">
+        <v>12</v>
+      </c>
+      <c r="F16" s="18">
+        <v>12</v>
+      </c>
+      <c r="G16" s="18">
         <v>3</v>
       </c>
-      <c r="F16" s="18">
+      <c r="H16" s="18">
         <v>3</v>
       </c>
-      <c r="G16" s="18">
-        <v>1</v>
-      </c>
-      <c r="H16" s="18">
-        <v>1</v>
-      </c>
       <c r="I16" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="18">
-        <v>0</v>
+        <v>6827</v>
       </c>
       <c r="K16" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="18">
-        <v>0</v>
+        <v>6827</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B17" s="18">
         <v>2026</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E17" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="18">
         <v>1</v>
       </c>
       <c r="I17" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="18">
-        <v>0</v>
+        <v>8658</v>
       </c>
       <c r="K17" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="18">
-        <v>0</v>
+        <v>8658</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B18" s="18">
         <v>2026</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="18">
         <v>1</v>
@@ -16086,7 +16204,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="18">
         <v>0</v>
@@ -16106,72 +16224,72 @@
     </row>
     <row r="19" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B19" s="18">
         <v>2026</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D19" s="17" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" s="18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" s="18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H19" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="18">
-        <v>12850</v>
+        <v>2286</v>
       </c>
       <c r="K19" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" s="18">
-        <v>12850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B20" s="18">
         <v>2026</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E20" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="18">
-        <v>0</v>
+        <v>5410</v>
       </c>
       <c r="K20" s="18">
         <v>0</v>
@@ -16182,34 +16300,34 @@
     </row>
     <row r="21" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B21" s="18">
         <v>2026</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E21" s="18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F21" s="18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G21" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" s="18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="18">
-        <v>5234</v>
+        <v>0</v>
       </c>
       <c r="K21" s="18">
         <v>0</v>
@@ -16220,54 +16338,54 @@
     </row>
     <row r="22" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B22" s="18">
         <v>2026</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E22" s="18">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="F22" s="18">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="G22" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="18">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I22" s="18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J22" s="18">
-        <v>30692.31</v>
+        <v>0</v>
       </c>
       <c r="K22" s="18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="18">
-        <v>30532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B23" s="18">
         <v>2026</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E23" s="18">
         <v>1</v>
@@ -16296,34 +16414,34 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B24" s="18">
         <v>2026</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>160.31</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -16334,28 +16452,28 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B25" s="18">
         <v>2026</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -16372,19 +16490,19 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B26" s="18">
         <v>2026</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -16393,7 +16511,7 @@
         <v>0</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -16410,28 +16528,28 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B27" s="18">
         <v>2026</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E27">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -16448,25 +16566,25 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B28" s="18">
         <v>2026</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -16486,28 +16604,28 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B29" s="18">
         <v>2026</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -16524,16 +16642,16 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B30" s="18">
         <v>2026</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -16562,16 +16680,16 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B31" s="18">
         <v>2026</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -16600,16 +16718,16 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B32" s="18">
         <v>2026</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -16638,51 +16756,51 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B33" s="18">
         <v>2026</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
       <c r="J33">
-        <v>7816</v>
+        <v>5234</v>
       </c>
       <c r="K33">
         <v>1</v>
       </c>
       <c r="L33">
-        <v>7816</v>
+        <v>5234</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B34" s="18">
         <v>2026</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D34" t="s">
         <v>13</v>
@@ -16714,22 +16832,22 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B35" s="18">
         <v>2026</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -16752,34 +16870,34 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B36" s="18">
         <v>2026</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>7072</v>
+        <v>0</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -16790,34 +16908,34 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B37" s="18">
         <v>2026</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>5234</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -16828,28 +16946,28 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B38" s="18">
         <v>2026</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -16866,92 +16984,92 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B39" s="18">
         <v>2026</v>
       </c>
       <c r="C39" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39">
+        <v>62</v>
+      </c>
+      <c r="F39">
+        <v>57</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
         <v>17</v>
       </c>
-      <c r="D39" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
       <c r="I39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>36031</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>36031</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B40" s="18">
         <v>2026</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F40">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>20397</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B41" s="18">
         <v>2026</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -16980,7 +17098,7 @@
     </row>
     <row r="42" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B42" s="18">
         <v>2026</v>
@@ -16989,19 +17107,19 @@
         <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -17018,45 +17136,45 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B43" s="18">
         <v>2026</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D43" t="s">
         <v>107</v>
       </c>
       <c r="E43">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43">
-        <v>7816</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43">
-        <v>7816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B44" s="18">
         <v>2026</v>
@@ -17065,16 +17183,16 @@
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -17094,28 +17212,28 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B45" s="18">
         <v>2026</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D45" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -17132,7 +17250,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B46" s="18">
         <v>2026</v>
@@ -17141,63 +17259,63 @@
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E46">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F46">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>6827</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46">
-        <v>6827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B47" s="18">
         <v>2026</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D47" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>5410</v>
+        <v>0</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -17208,28 +17326,28 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B48" s="18">
         <v>2026</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D48" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -17246,7 +17364,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B49" s="18">
         <v>2026</v>
@@ -17258,33 +17376,33 @@
         <v>13</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>15374</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>15374</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B50" s="18">
         <v>2026</v>
@@ -17302,7 +17420,7 @@
         <v>1</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -17322,7 +17440,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="B51" s="18">
         <v>2026</v>
@@ -17331,7 +17449,7 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -17340,10 +17458,10 @@
         <v>1</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -17360,28 +17478,28 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B52" s="18">
         <v>2026</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D52" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -17398,7 +17516,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B53" s="18">
         <v>2026</v>
@@ -17410,42 +17528,42 @@
         <v>13</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53">
-        <v>0</v>
+        <v>17865</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>17865</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B54" s="18">
         <v>2026</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -17474,22 +17592,22 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B55" s="18">
         <v>2026</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -17512,54 +17630,54 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B56" s="18">
         <v>2026</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D56" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E56">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>20397</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56">
-        <v>20397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B57" s="18">
         <v>2026</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D57" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -17588,7 +17706,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B58" s="18">
         <v>2026</v>
@@ -17597,13 +17715,13 @@
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -17626,83 +17744,83 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B59" s="18">
         <v>2026</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D59" t="s">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>7816</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B60" s="18">
         <v>2026</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D60" t="s">
         <v>13</v>
       </c>
       <c r="E60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F60">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>15224</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>15224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B61" s="18">
         <v>2026</v>
@@ -17711,36 +17829,36 @@
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B62" s="18">
         <v>2026</v>
@@ -17758,65 +17876,65 @@
         <v>1</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B63" s="18">
         <v>2026</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E63">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H63">
         <v>0</v>
       </c>
       <c r="I63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63">
-        <v>17865</v>
+        <v>0</v>
       </c>
       <c r="K63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L63">
-        <v>17865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B64" s="18">
         <v>2026</v>
@@ -17828,16 +17946,16 @@
         <v>39</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -17854,13 +17972,13 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B65" s="18">
         <v>2026</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D65" t="s">
         <v>13</v>
@@ -17869,45 +17987,45 @@
         <v>2</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65">
         <v>1</v>
       </c>
       <c r="J65">
-        <v>299</v>
+        <v>7072</v>
       </c>
       <c r="K65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B66" s="18">
         <v>2026</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D66" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F66">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -17916,21 +18034,21 @@
         <v>1</v>
       </c>
       <c r="I66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66">
-        <v>7818.1200000000008</v>
+        <v>0</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66">
-        <v>7818.1200000000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B67" s="18">
         <v>2026</v>
@@ -17939,19 +18057,19 @@
         <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="E67">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -17968,25 +18086,25 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B68" s="18">
         <v>2026</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D68" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -18044,53 +18162,155 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B70" s="18">
         <v>2026</v>
       </c>
       <c r="C70" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D70" t="s">
+        <v>40</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>103</v>
+      </c>
+      <c r="B71" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C72" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D72" t="s">
         <v>13</v>
       </c>
-      <c r="E70">
-        <v>2</v>
-      </c>
-      <c r="F70">
-        <v>2</v>
-      </c>
-      <c r="G70">
-        <v>2</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B71" s="18"/>
-      <c r="C71" s="19"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B72" s="18"/>
-      <c r="C72" s="19"/>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B73" s="18"/>
-      <c r="C73" s="19"/>
+      <c r="A73" t="s">
+        <v>103</v>
+      </c>
+      <c r="B73" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D73" t="s">
+        <v>39</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73">
+        <v>1</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B74" s="18"/>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5D3E20-6BED-4F23-88D4-807FEAA488A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7FF630-79C4-4DB7-8D5A-DD6909D9BFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1013,46 +1013,46 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C6" s="5">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D6" s="5">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E6" s="5">
-        <v>26269.25</v>
+        <v>27579.59</v>
       </c>
       <c r="F6" s="5">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G6" s="5">
         <v>18</v>
       </c>
       <c r="H6" s="5">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I6" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J6" s="5">
         <v>12</v>
       </c>
       <c r="K6" s="5">
-        <v>252.58894230769201</v>
+        <v>260.18481132075402</v>
       </c>
       <c r="L6" s="5">
-        <v>875.64166666666597</v>
+        <v>889.66419354838695</v>
       </c>
       <c r="M6" s="5">
-        <v>211.41399164422199</v>
+        <v>196.61833261480601</v>
       </c>
       <c r="N6" s="6">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="O6" s="6">
-        <v>50579.62</v>
+        <v>53667.38</v>
       </c>
       <c r="P6" s="6">
         <v>245</v>
@@ -1064,13 +1064,13 @@
         <v>15</v>
       </c>
       <c r="S6" s="6">
-        <v>206.44742857142799</v>
+        <v>219.05053061224399</v>
       </c>
       <c r="T6" s="6">
-        <v>972.68499999999995</v>
+        <v>1032.0650000000001</v>
       </c>
       <c r="U6" s="6">
-        <v>129.61692871555701</v>
+        <v>116.405887524227</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1105,16 +1105,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C7" s="5">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7" s="5">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E7" s="5">
-        <v>4580.99</v>
+        <v>4814.12</v>
       </c>
       <c r="F7" s="5">
         <v>58</v>
@@ -1132,19 +1132,19 @@
         <v>9</v>
       </c>
       <c r="K7" s="5">
-        <v>78.982586206896499</v>
+        <v>83.002068965517196</v>
       </c>
       <c r="L7" s="5">
-        <v>352.38384615384598</v>
+        <v>370.31692307692299</v>
       </c>
       <c r="M7" s="5">
-        <v>1195.46233456087</v>
+        <v>1132.7278921173499</v>
       </c>
       <c r="N7" s="6">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O7" s="6">
-        <v>12530.92</v>
+        <v>13318.47</v>
       </c>
       <c r="P7" s="6">
         <v>119</v>
@@ -1156,13 +1156,13 @@
         <v>9</v>
       </c>
       <c r="S7" s="6">
-        <v>105.301848739495</v>
+        <v>111.919915966386</v>
       </c>
       <c r="T7" s="6">
-        <v>895.06571428571397</v>
+        <v>951.319285714285</v>
       </c>
       <c r="U7" s="6">
-        <v>474.99170052956998</v>
+        <v>440.99119493455299</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1189,7 +1189,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>1554.02</v>
+        <v>1676.15</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1554.02</v>
+        <v>1676.15</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1234,7 +1234,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>1730.21</v>
+        <v>1832.21</v>
       </c>
       <c r="P8" s="6">
         <v>5</v>
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>346.04199999999997</v>
+        <v>366.44200000000001</v>
       </c>
       <c r="T8" s="6">
-        <v>865.10500000000002</v>
+        <v>916.10500000000002</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1279,7 +1279,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1287,25 +1287,25 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="5">
         <v>6</v>
       </c>
       <c r="D9" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="5">
-        <v>5305.17</v>
+        <v>5516.4</v>
       </c>
       <c r="F9" s="5">
+        <v>13</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5">
         <v>12</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5">
-        <v>11</v>
       </c>
       <c r="I9" s="5">
         <v>5</v>
@@ -1314,19 +1314,19 @@
         <v>1</v>
       </c>
       <c r="K9" s="5">
-        <v>442.09750000000003</v>
+        <v>424.33846153846099</v>
       </c>
       <c r="L9" s="5">
-        <v>1061.0340000000001</v>
+        <v>1103.28</v>
       </c>
       <c r="M9" s="5">
-        <v>47.327983834636697</v>
+        <v>41.686607207599103</v>
       </c>
       <c r="N9" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O9" s="6">
-        <v>5182.01</v>
+        <v>5452.81</v>
       </c>
       <c r="P9" s="6">
         <v>12</v>
@@ -1338,13 +1338,13 @@
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>431.83416666666602</v>
+        <v>454.40083333333303</v>
       </c>
       <c r="T9" s="6">
-        <v>1295.5025000000001</v>
+        <v>1363.2025000000001</v>
       </c>
       <c r="U9" s="6">
-        <v>2.8751391834442499</v>
+        <v>-2.2338940839677202</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1365,7 +1365,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1388,7 +1388,7 @@
         <v>2</v>
       </c>
       <c r="O10" s="6">
-        <v>1906.28</v>
+        <v>2026.25</v>
       </c>
       <c r="P10" s="6">
         <v>6</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>317.71333333333303</v>
+        <v>337.70833333333297</v>
       </c>
       <c r="T10" s="6">
-        <v>476.57</v>
+        <v>506.5625</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1421,7 +1421,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1429,16 +1429,16 @@
         <v>106</v>
       </c>
       <c r="B11" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" s="5">
-        <v>2804.08</v>
+        <v>2911.18</v>
       </c>
       <c r="F11" s="5">
         <v>4</v>
@@ -1456,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>701.02</v>
+        <v>727.79499999999996</v>
       </c>
       <c r="L11" s="5">
-        <v>1402.04</v>
+        <v>1455.59</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
@@ -1468,7 +1468,7 @@
         <v>2</v>
       </c>
       <c r="O11" s="6">
-        <v>982.51</v>
+        <v>1051.3499999999999</v>
       </c>
       <c r="P11" s="6">
         <v>3</v>
@@ -1480,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>327.50333333333299</v>
+        <v>350.45</v>
       </c>
       <c r="T11" s="6">
-        <v>982.51</v>
+        <v>1051.3499999999999</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1513,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1533,10 +1533,10 @@
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="6">
-        <v>246.85</v>
+        <v>262.63</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1557,7 +1557,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1565,16 +1565,16 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5">
         <v>10</v>
       </c>
       <c r="D13" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" s="5">
-        <v>5702.42</v>
+        <v>6040.9</v>
       </c>
       <c r="F13" s="5">
         <v>14</v>
@@ -1592,19 +1592,19 @@
         <v>2</v>
       </c>
       <c r="K13" s="5">
-        <v>407.31571428571402</v>
+        <v>431.49285714285702</v>
       </c>
       <c r="L13" s="5">
-        <v>1425.605</v>
+        <v>1510.2249999999999</v>
       </c>
       <c r="M13" s="5">
-        <v>156.82289273676699</v>
+        <v>142.43275008690699</v>
       </c>
       <c r="N13" s="6">
         <v>13</v>
       </c>
       <c r="O13" s="6">
-        <v>2723.14</v>
+        <v>2949.08</v>
       </c>
       <c r="P13" s="6">
         <v>15</v>
@@ -1616,13 +1616,13 @@
         <v>2</v>
       </c>
       <c r="S13" s="6">
-        <v>181.54266666666601</v>
+        <v>196.60533333333299</v>
       </c>
       <c r="T13" s="6">
-        <v>340.39249999999998</v>
+        <v>368.63499999999999</v>
       </c>
       <c r="U13" s="6">
-        <v>487.33667751198902</v>
+        <v>442.33862763980602</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1649,7 +1649,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1672,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>533.46</v>
+        <v>587.78</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1684,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>266.73</v>
+        <v>293.89</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1709,7 +1709,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1753,7 +1753,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1773,10 +1773,10 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O16" s="6">
-        <v>822.31</v>
+        <v>878.1</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
@@ -1803,7 +1803,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>1086.8499999999999</v>
+        <v>1179.94</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1838,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1086.8499999999999</v>
+        <v>1179.94</v>
       </c>
       <c r="L17" s="5">
-        <v>1086.8499999999999</v>
+        <v>1179.94</v>
       </c>
       <c r="M17" s="5">
         <v>-100</v>
@@ -1850,7 +1850,7 @@
         <v>1</v>
       </c>
       <c r="O17" s="6">
-        <v>686.09</v>
+        <v>748.01</v>
       </c>
       <c r="P17" s="6">
         <v>1</v>
@@ -1862,7 +1862,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>686.09</v>
+        <v>748.01</v>
       </c>
       <c r="T17" s="6"/>
       <c r="U17" s="6">
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1913,10 +1913,10 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O18" s="6">
-        <v>2613.64</v>
+        <v>2767.24</v>
       </c>
       <c r="P18" s="6">
         <v>9</v>
@@ -1928,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>290.40444444444398</v>
+        <v>307.47111111111099</v>
       </c>
       <c r="T18" s="6">
-        <v>871.21333333333303</v>
+        <v>922.41333333333296</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1955,7 +1955,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1972,7 +1972,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="5">
-        <v>2317.7800000000002</v>
+        <v>2445.35</v>
       </c>
       <c r="F19" s="5">
         <v>4</v>
@@ -1990,19 +1990,19 @@
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>579.44500000000005</v>
+        <v>611.33749999999998</v>
       </c>
       <c r="L19" s="5">
-        <v>1158.8900000000001</v>
+        <v>1222.675</v>
       </c>
       <c r="M19" s="5">
         <v>-100</v>
       </c>
       <c r="N19" s="6">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O19" s="6">
-        <v>2900.74</v>
+        <v>3070.96</v>
       </c>
       <c r="P19" s="6">
         <v>13</v>
@@ -2014,13 +2014,13 @@
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>223.13384615384601</v>
+        <v>236.227692307692</v>
       </c>
       <c r="T19" s="6">
-        <v>725.18499999999995</v>
+        <v>767.74</v>
       </c>
       <c r="U19" s="6">
-        <v>144.76719733585199</v>
+        <v>131.20001563029101</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2047,7 +2047,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2070,7 +2070,7 @@
         <v>13</v>
       </c>
       <c r="O20" s="6">
-        <v>2977.19</v>
+        <v>3115.88</v>
       </c>
       <c r="P20" s="6">
         <v>11</v>
@@ -2082,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>270.653636363636</v>
+        <v>283.261818181818</v>
       </c>
       <c r="T20" s="6">
-        <v>595.43799999999999</v>
+        <v>623.17600000000004</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2109,7 +2109,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2129,10 +2129,10 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O21" s="6">
-        <v>7654.85</v>
+        <v>8094.25</v>
       </c>
       <c r="P21" s="6">
         <v>26</v>
@@ -2144,13 +2144,13 @@
         <v>2</v>
       </c>
       <c r="S21" s="6">
-        <v>294.41730769230702</v>
+        <v>311.317307692307</v>
       </c>
       <c r="T21" s="6">
-        <v>1913.7125000000001</v>
+        <v>2023.5625</v>
       </c>
       <c r="U21" s="6">
-        <v>104.609626576614</v>
+        <v>93.502301016153396</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2171,7 +2171,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2188,28 +2188,28 @@
         <v>11</v>
       </c>
       <c r="E22" s="5">
-        <v>2917.94</v>
+        <v>2995.55</v>
       </c>
       <c r="F22" s="5">
+        <v>11</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
         <v>10</v>
       </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
-        <v>9</v>
-      </c>
       <c r="I22" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="5">
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>291.79399999999998</v>
+        <v>272.32272727272698</v>
       </c>
       <c r="L22" s="5">
-        <v>972.64666666666596</v>
+        <v>748.88750000000005</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2218,7 +2218,7 @@
         <v>4</v>
       </c>
       <c r="O22" s="6">
-        <v>2489.9699999999998</v>
+        <v>2622.02</v>
       </c>
       <c r="P22" s="6">
         <v>5</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>497.99399999999901</v>
+        <v>524.404</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2261,7 +2261,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2281,10 +2281,10 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O23" s="6">
-        <v>3063.14</v>
+        <v>3232.2</v>
       </c>
       <c r="P23" s="6">
         <v>13</v>
@@ -2296,10 +2296,10 @@
         <v>0</v>
       </c>
       <c r="S23" s="6">
-        <v>235.62615384615299</v>
+        <v>248.630769230769</v>
       </c>
       <c r="T23" s="6">
-        <v>1531.57</v>
+        <v>1616.1</v>
       </c>
       <c r="U23" s="6">
         <v>-100</v>
@@ -2327,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2350,7 +2350,7 @@
         <v>6</v>
       </c>
       <c r="O24" s="6">
-        <v>1533.57</v>
+        <v>1655.4</v>
       </c>
       <c r="P24" s="6">
         <v>5</v>
@@ -2362,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>306.714</v>
+        <v>331.08</v>
       </c>
       <c r="T24" s="6">
-        <v>1533.57</v>
+        <v>1655.4</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2389,7 +2389,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46161</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3009,7 +3009,7 @@
         <v>32</v>
       </c>
       <c r="F5" s="18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" s="18">
         <v>9</v>
@@ -3027,16 +3027,16 @@
         <v>45253.33</v>
       </c>
       <c r="L5" s="18">
-        <v>12.06</v>
+        <v>12.1</v>
       </c>
       <c r="M5" s="18">
         <v>21.7</v>
       </c>
       <c r="N5" s="18">
-        <v>44.12</v>
+        <v>47.06</v>
       </c>
       <c r="O5" s="18">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="P5" s="18">
         <v>20.59</v>
@@ -3062,7 +3062,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="18">
         <v>1</v>
@@ -3077,7 +3077,7 @@
         <v>7816</v>
       </c>
       <c r="L6" s="18">
-        <v>4.96</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="M6" s="18">
         <v>3.75</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="18">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="M7" s="18">
         <v>0</v>
@@ -3175,7 +3175,7 @@
         <v>17649</v>
       </c>
       <c r="L8" s="18">
-        <v>4.96</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="M8" s="18">
         <v>8.4600000000000009</v>
@@ -3225,7 +3225,7 @@
         <v>6827</v>
       </c>
       <c r="L9" s="18">
-        <v>4.96</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="M9" s="18">
         <v>3.27</v>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="L10" s="18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="M10" s="18">
         <v>1.1000000000000001</v>
@@ -3371,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="18">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="M12" s="18">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="18">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="M13" s="18">
         <v>0.08</v>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="18">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="M14" s="18">
         <v>0</v>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="18">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="M15" s="18">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="18">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="M16" s="18">
         <v>0</v>
@@ -3615,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="18">
-        <v>2.48</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="M17" s="18">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>5234</v>
       </c>
       <c r="L19" s="10">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="M19" s="10">
         <v>5.0199999999999996</v>
@@ -3765,7 +3765,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="10">
-        <v>2.48</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="M20" s="10">
         <v>0</v>
@@ -3815,7 +3815,7 @@
         <v>36031</v>
       </c>
       <c r="L21" s="10">
-        <v>24.82</v>
+        <v>24.91</v>
       </c>
       <c r="M21" s="10">
         <v>17.28</v>
@@ -3839,10 +3839,10 @@
         <v>18</v>
       </c>
       <c r="D22" s="10">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" s="10">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F22" s="10">
         <v>0</v>
@@ -3863,7 +3863,7 @@
         <v>20397</v>
       </c>
       <c r="L22" s="10">
-        <v>12.77</v>
+        <v>12.46</v>
       </c>
       <c r="M22" s="10">
         <v>9.7799999999999994</v>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10">
-        <v>8.33</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="M23" s="10">
         <v>0</v>
@@ -3961,7 +3961,7 @@
         <v>15374</v>
       </c>
       <c r="L24" s="10">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="M24" s="10">
         <v>7.37</v>
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>7816</v>
       </c>
       <c r="L26" s="10">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="M26" s="10">
         <v>3.75</v>
@@ -4109,7 +4109,7 @@
         <v>17865</v>
       </c>
       <c r="L27" s="10">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="M27" s="10">
         <v>8.57</v>
@@ -4159,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         <v>8117.12</v>
       </c>
       <c r="L29" s="10">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="M29" s="10">
         <v>3.89</v>
@@ -4259,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="10">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="M30" s="10">
         <v>3.39</v>
@@ -4407,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
@@ -5153,13 +5153,13 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1877</v>
+        <v>1990</v>
       </c>
       <c r="E21" s="10">
-        <v>4580.99</v>
+        <v>4814.12</v>
       </c>
       <c r="F21" s="10">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G21" s="10">
         <v>57</v>
@@ -5174,7 +5174,7 @@
         <v>59345</v>
       </c>
       <c r="K21" s="10">
-        <v>11.95</v>
+        <v>11.33</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5748,10 +5748,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E38" s="10">
-        <v>1554.02</v>
+        <v>1676.15</v>
       </c>
       <c r="F38" s="10">
         <v>5</v>
@@ -6002,7 +6002,7 @@
         <v>23</v>
       </c>
       <c r="G45" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H45" s="10">
         <v>6</v>
@@ -6177,7 +6177,7 @@
         <v>35</v>
       </c>
       <c r="G50" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H50" s="10">
         <v>12</v>
@@ -6343,16 +6343,16 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>686</v>
+        <v>724</v>
       </c>
       <c r="E55" s="10">
-        <v>5305.17</v>
+        <v>5516.4</v>
       </c>
       <c r="F55" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G55" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H55" s="10">
         <v>5</v>
@@ -6364,7 +6364,7 @@
         <v>7816</v>
       </c>
       <c r="K55" s="10">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6517,7 +6517,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H60" s="10">
         <v>4</v>
@@ -6622,7 +6622,7 @@
         <v>3</v>
       </c>
       <c r="G63" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H63" s="10">
         <v>5</v>
@@ -7338,13 +7338,13 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="E84" s="10">
-        <v>2804.08</v>
+        <v>2911.18</v>
       </c>
       <c r="F84" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G84" s="10">
         <v>4</v>
@@ -7817,10 +7817,10 @@
         <v>17</v>
       </c>
       <c r="G98" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H98" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I98" s="10">
         <v>6</v>
@@ -8228,13 +8228,13 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="E110" s="10">
-        <v>5702.42</v>
+        <v>6040.9</v>
       </c>
       <c r="F110" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G110" s="10">
         <v>14</v>
@@ -8249,7 +8249,7 @@
         <v>14645.12</v>
       </c>
       <c r="K110" s="10">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -8947,7 +8947,7 @@
         <v>6</v>
       </c>
       <c r="G132" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H132" s="10">
         <v>2</v>
@@ -9743,10 +9743,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E155" s="10">
-        <v>1086.8499999999999</v>
+        <v>1179.94</v>
       </c>
       <c r="F155" s="10">
         <v>2</v>
@@ -10829,10 +10829,10 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="E186" s="10">
-        <v>2317.7800000000002</v>
+        <v>2445.35</v>
       </c>
       <c r="F186" s="10">
         <v>13</v>
@@ -12404,10 +12404,10 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="E231" s="10">
-        <v>2917.94</v>
+        <v>2995.55</v>
       </c>
       <c r="F231" s="10">
         <v>13</v>
@@ -15694,14 +15694,14 @@
       <c r="A5" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="19">
         <v>2026</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="18">
         <v>3</v>
@@ -15732,14 +15732,14 @@
       <c r="A6" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="19">
         <v>2026</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="D6" s="17" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="E6" s="18">
         <v>5</v>
@@ -15770,14 +15770,14 @@
       <c r="A7" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="19">
         <v>2026</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>26</v>
       </c>
       <c r="E7" s="18">
         <v>6</v>
@@ -15808,14 +15808,14 @@
       <c r="A8" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="19">
         <v>2026</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="D8" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>107</v>
       </c>
       <c r="E8" s="18">
         <v>23</v>
@@ -15824,7 +15824,7 @@
         <v>21</v>
       </c>
       <c r="G8" s="18">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="18">
         <v>7</v>
@@ -15846,14 +15846,14 @@
       <c r="A9" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="19">
         <v>2026</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="D9" s="17" t="s">
         <v>18</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>107</v>
       </c>
       <c r="E9" s="18">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" s="18">
         <v>1</v>
@@ -15884,14 +15884,14 @@
       <c r="A10" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="19">
         <v>2026</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="D10" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>36</v>
       </c>
       <c r="E10" s="18">
         <v>2</v>
@@ -15922,14 +15922,14 @@
       <c r="A11" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="19">
         <v>2026</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="D11" s="17" t="s">
         <v>18</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>36</v>
       </c>
       <c r="E11" s="18">
         <v>1</v>
@@ -15960,14 +15960,14 @@
       <c r="A12" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="19">
         <v>2026</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="D12" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>106</v>
       </c>
       <c r="E12" s="18">
         <v>1</v>
@@ -15998,14 +15998,14 @@
       <c r="A13" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="19">
         <v>2026</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="D13" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="E13" s="18">
         <v>5</v>
@@ -16036,14 +16036,14 @@
       <c r="A14" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="19">
         <v>2026</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="D14" s="17" t="s">
         <v>18</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="E14" s="18">
         <v>1</v>
@@ -16074,14 +16074,14 @@
       <c r="A15" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="19">
         <v>2026</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="D15" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>29</v>
       </c>
       <c r="E15" s="18">
         <v>8</v>
@@ -16112,14 +16112,14 @@
       <c r="A16" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="19">
         <v>2026</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="D16" s="17" t="s">
         <v>18</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>29</v>
       </c>
       <c r="E16" s="18">
         <v>12</v>
@@ -16150,14 +16150,14 @@
       <c r="A17" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="19">
         <v>2026</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="D17" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>39</v>
       </c>
       <c r="E17" s="18">
         <v>1</v>
@@ -16188,14 +16188,14 @@
       <c r="A18" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="19">
         <v>2026</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="D18" s="17" t="s">
         <v>18</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>39</v>
       </c>
       <c r="E18" s="18">
         <v>1</v>
@@ -16226,14 +16226,14 @@
       <c r="A19" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="19">
         <v>2026</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="D19" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="E19" s="18">
         <v>2</v>
@@ -16264,14 +16264,14 @@
       <c r="A20" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="19">
         <v>2026</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="D20" s="17" t="s">
         <v>18</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="E20" s="18">
         <v>1</v>
@@ -16302,14 +16302,14 @@
       <c r="A21" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="19">
         <v>2026</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="D21" s="17" t="s">
         <v>18</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>107</v>
       </c>
       <c r="E21" s="18">
         <v>1</v>
@@ -16340,14 +16340,14 @@
       <c r="A22" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="19">
         <v>2026</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="D22" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>40</v>
       </c>
       <c r="E22" s="18">
         <v>1</v>
@@ -16378,14 +16378,14 @@
       <c r="A23" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="19">
         <v>2026</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="D23" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="E23" s="18">
         <v>1</v>
@@ -16416,14 +16416,14 @@
       <c r="A24" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="19">
         <v>2026</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="D24" t="s">
         <v>111</v>
-      </c>
-      <c r="D24" t="s">
-        <v>13</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -16454,14 +16454,14 @@
       <c r="A25" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="19">
         <v>2026</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="D25" t="s">
         <v>18</v>
-      </c>
-      <c r="D25" t="s">
-        <v>13</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -16492,14 +16492,14 @@
       <c r="A26" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="18">
+      <c r="B26" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="19">
         <v>2026</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="D26" t="s">
         <v>111</v>
-      </c>
-      <c r="D26" t="s">
-        <v>13</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -16530,14 +16530,14 @@
       <c r="A27" t="s">
         <v>94</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="19">
         <v>2026</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="D27" t="s">
         <v>18</v>
-      </c>
-      <c r="D27" t="s">
-        <v>39</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -16568,14 +16568,14 @@
       <c r="A28" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="19">
         <v>2026</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="D28" t="s">
         <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>13</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -16606,14 +16606,14 @@
       <c r="A29" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="18">
+      <c r="B29" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="19">
         <v>2026</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="D29" t="s">
         <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>34</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -16644,14 +16644,14 @@
       <c r="A30" t="s">
         <v>95</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="19">
         <v>2026</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="D30" t="s">
         <v>18</v>
-      </c>
-      <c r="D30" t="s">
-        <v>34</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -16682,14 +16682,14 @@
       <c r="A31" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="18">
+      <c r="B31" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="19">
         <v>2026</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="D31" t="s">
         <v>18</v>
-      </c>
-      <c r="D31" t="s">
-        <v>39</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -16720,14 +16720,14 @@
       <c r="A32" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="18">
+      <c r="B32" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="19">
         <v>2026</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="D32" t="s">
         <v>111</v>
-      </c>
-      <c r="D32" t="s">
-        <v>40</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -16758,14 +16758,14 @@
       <c r="A33" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="19">
         <v>2026</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="D33" t="s">
         <v>111</v>
-      </c>
-      <c r="D33" t="s">
-        <v>13</v>
       </c>
       <c r="E33">
         <v>4</v>
@@ -16796,14 +16796,14 @@
       <c r="A34" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="19">
         <v>2026</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="D34" t="s">
         <v>18</v>
-      </c>
-      <c r="D34" t="s">
-        <v>13</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -16834,14 +16834,14 @@
       <c r="A35" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="19">
         <v>2026</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="D35" t="s">
         <v>111</v>
-      </c>
-      <c r="D35" t="s">
-        <v>107</v>
       </c>
       <c r="E35">
         <v>2</v>
@@ -16872,14 +16872,14 @@
       <c r="A36" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="18">
+      <c r="B36" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="19">
         <v>2026</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="D36" t="s">
         <v>18</v>
-      </c>
-      <c r="D36" t="s">
-        <v>107</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -16910,14 +16910,14 @@
       <c r="A37" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="19">
         <v>2026</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="D37" t="s">
         <v>111</v>
-      </c>
-      <c r="D37" t="s">
-        <v>36</v>
       </c>
       <c r="E37">
         <v>4</v>
@@ -16948,14 +16948,14 @@
       <c r="A38" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="18">
+      <c r="B38" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="19">
         <v>2026</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="D38" t="s">
         <v>18</v>
-      </c>
-      <c r="D38" t="s">
-        <v>36</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -16986,14 +16986,14 @@
       <c r="A39" t="s">
         <v>97</v>
       </c>
-      <c r="B39" s="18">
+      <c r="B39" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="19">
         <v>2026</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="D39" t="s">
         <v>111</v>
-      </c>
-      <c r="D39" t="s">
-        <v>13</v>
       </c>
       <c r="E39">
         <v>62</v>
@@ -17024,14 +17024,14 @@
       <c r="A40" t="s">
         <v>97</v>
       </c>
-      <c r="B40" s="18">
+      <c r="B40" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="19">
         <v>2026</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="D40" t="s">
         <v>18</v>
-      </c>
-      <c r="D40" t="s">
-        <v>13</v>
       </c>
       <c r="E40">
         <v>31</v>
@@ -17062,14 +17062,14 @@
       <c r="A41" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="18">
+      <c r="B41" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="19">
         <v>2026</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="D41" t="s">
         <v>111</v>
-      </c>
-      <c r="D41" t="s">
-        <v>26</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -17100,14 +17100,14 @@
       <c r="A42" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" s="19">
         <v>2026</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="D42" t="s">
         <v>18</v>
-      </c>
-      <c r="D42" t="s">
-        <v>26</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -17138,14 +17138,14 @@
       <c r="A43" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="18">
+      <c r="B43" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="19">
         <v>2026</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="D43" t="s">
         <v>111</v>
-      </c>
-      <c r="D43" t="s">
-        <v>107</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -17176,20 +17176,20 @@
       <c r="A44" t="s">
         <v>97</v>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="19">
         <v>2026</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="D44" t="s">
         <v>18</v>
       </c>
-      <c r="D44" t="s">
-        <v>107</v>
-      </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -17214,14 +17214,14 @@
       <c r="A45" t="s">
         <v>97</v>
       </c>
-      <c r="B45" s="18">
+      <c r="B45" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="19">
         <v>2026</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="D45" t="s">
         <v>111</v>
-      </c>
-      <c r="D45" t="s">
-        <v>106</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -17252,14 +17252,14 @@
       <c r="A46" t="s">
         <v>97</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="19">
         <v>2026</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="D46" t="s">
         <v>18</v>
-      </c>
-      <c r="D46" t="s">
-        <v>106</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -17290,14 +17290,14 @@
       <c r="A47" t="s">
         <v>97</v>
       </c>
-      <c r="B47" s="18">
+      <c r="B47" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="19">
         <v>2026</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="D47" t="s">
         <v>111</v>
-      </c>
-      <c r="D47" t="s">
-        <v>29</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -17328,14 +17328,14 @@
       <c r="A48" t="s">
         <v>98</v>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="19">
         <v>2026</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="D48" t="s">
         <v>111</v>
-      </c>
-      <c r="D48" t="s">
-        <v>13</v>
       </c>
       <c r="E48">
         <v>8</v>
@@ -17366,14 +17366,14 @@
       <c r="A49" t="s">
         <v>98</v>
       </c>
-      <c r="B49" s="18">
+      <c r="B49" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="19">
         <v>2026</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="D49" t="s">
         <v>18</v>
-      </c>
-      <c r="D49" t="s">
-        <v>13</v>
       </c>
       <c r="E49">
         <v>7</v>
@@ -17404,14 +17404,14 @@
       <c r="A50" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="18">
+      <c r="B50" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="19">
         <v>2026</v>
       </c>
-      <c r="C50" s="19" t="s">
+      <c r="D50" t="s">
         <v>18</v>
-      </c>
-      <c r="D50" t="s">
-        <v>39</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -17442,14 +17442,14 @@
       <c r="A51" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="18">
+      <c r="B51" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="19">
         <v>2026</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="D51" t="s">
         <v>18</v>
-      </c>
-      <c r="D51" t="s">
-        <v>29</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -17480,14 +17480,14 @@
       <c r="A52" t="s">
         <v>99</v>
       </c>
-      <c r="B52" s="18">
+      <c r="B52" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="19">
         <v>2026</v>
       </c>
-      <c r="C52" s="19" t="s">
+      <c r="D52" t="s">
         <v>111</v>
-      </c>
-      <c r="D52" t="s">
-        <v>13</v>
       </c>
       <c r="E52">
         <v>4</v>
@@ -17518,14 +17518,14 @@
       <c r="A53" t="s">
         <v>99</v>
       </c>
-      <c r="B53" s="18">
+      <c r="B53" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="19">
         <v>2026</v>
       </c>
-      <c r="C53" s="19" t="s">
+      <c r="D53" t="s">
         <v>18</v>
-      </c>
-      <c r="D53" t="s">
-        <v>13</v>
       </c>
       <c r="E53">
         <v>5</v>
@@ -17556,14 +17556,14 @@
       <c r="A54" t="s">
         <v>99</v>
       </c>
-      <c r="B54" s="18">
+      <c r="B54" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" s="19">
         <v>2026</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="D54" t="s">
         <v>111</v>
-      </c>
-      <c r="D54" t="s">
-        <v>26</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -17594,14 +17594,14 @@
       <c r="A55" t="s">
         <v>99</v>
       </c>
-      <c r="B55" s="18">
+      <c r="B55" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="19">
         <v>2026</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="D55" t="s">
         <v>111</v>
-      </c>
-      <c r="D55" t="s">
-        <v>107</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -17632,14 +17632,14 @@
       <c r="A56" t="s">
         <v>99</v>
       </c>
-      <c r="B56" s="18">
+      <c r="B56" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" s="19">
         <v>2026</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="D56" t="s">
         <v>111</v>
-      </c>
-      <c r="D56" t="s">
-        <v>29</v>
       </c>
       <c r="E56">
         <v>2</v>
@@ -17670,14 +17670,14 @@
       <c r="A57" t="s">
         <v>99</v>
       </c>
-      <c r="B57" s="18">
+      <c r="B57" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" s="19">
         <v>2026</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="D57" t="s">
         <v>111</v>
-      </c>
-      <c r="D57" t="s">
-        <v>39</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -17708,14 +17708,14 @@
       <c r="A58" t="s">
         <v>99</v>
       </c>
-      <c r="B58" s="18">
+      <c r="B58" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" s="19">
         <v>2026</v>
       </c>
-      <c r="C58" s="19" t="s">
+      <c r="D58" t="s">
         <v>18</v>
-      </c>
-      <c r="D58" t="s">
-        <v>39</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -17746,14 +17746,14 @@
       <c r="A59" t="s">
         <v>99</v>
       </c>
-      <c r="B59" s="18">
+      <c r="B59" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C59" s="19">
         <v>2026</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="D59" t="s">
         <v>111</v>
-      </c>
-      <c r="D59" t="s">
-        <v>40</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -17784,14 +17784,14 @@
       <c r="A60" t="s">
         <v>100</v>
       </c>
-      <c r="B60" s="18">
+      <c r="B60" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="19">
         <v>2026</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="D60" t="s">
         <v>111</v>
-      </c>
-      <c r="D60" t="s">
-        <v>13</v>
       </c>
       <c r="E60">
         <v>2</v>
@@ -17822,14 +17822,14 @@
       <c r="A61" t="s">
         <v>100</v>
       </c>
-      <c r="B61" s="18">
+      <c r="B61" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="19">
         <v>2026</v>
       </c>
-      <c r="C61" s="19" t="s">
+      <c r="D61" t="s">
         <v>18</v>
-      </c>
-      <c r="D61" t="s">
-        <v>13</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -17860,14 +17860,14 @@
       <c r="A62" t="s">
         <v>100</v>
       </c>
-      <c r="B62" s="18">
+      <c r="B62" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" s="19">
         <v>2026</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="D62" t="s">
         <v>18</v>
-      </c>
-      <c r="D62" t="s">
-        <v>29</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -17898,14 +17898,14 @@
       <c r="A63" t="s">
         <v>100</v>
       </c>
-      <c r="B63" s="18">
+      <c r="B63" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" s="19">
         <v>2026</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="D63" t="s">
         <v>111</v>
-      </c>
-      <c r="D63" t="s">
-        <v>39</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -17936,14 +17936,14 @@
       <c r="A64" t="s">
         <v>100</v>
       </c>
-      <c r="B64" s="18">
+      <c r="B64" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="19">
         <v>2026</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="D64" t="s">
         <v>18</v>
-      </c>
-      <c r="D64" t="s">
-        <v>39</v>
       </c>
       <c r="E64">
         <v>6</v>
@@ -17974,14 +17974,14 @@
       <c r="A65" t="s">
         <v>101</v>
       </c>
-      <c r="B65" s="18">
+      <c r="B65" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="19">
         <v>2026</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="D65" t="s">
         <v>111</v>
-      </c>
-      <c r="D65" t="s">
-        <v>13</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -18012,14 +18012,14 @@
       <c r="A66" t="s">
         <v>101</v>
       </c>
-      <c r="B66" s="18">
+      <c r="B66" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C66" s="19">
         <v>2026</v>
       </c>
-      <c r="C66" s="19" t="s">
+      <c r="D66" t="s">
         <v>111</v>
-      </c>
-      <c r="D66" t="s">
-        <v>106</v>
       </c>
       <c r="E66">
         <v>7</v>
@@ -18050,14 +18050,14 @@
       <c r="A67" t="s">
         <v>101</v>
       </c>
-      <c r="B67" s="18">
+      <c r="B67" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" s="19">
         <v>2026</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="D67" t="s">
         <v>18</v>
-      </c>
-      <c r="D67" t="s">
-        <v>106</v>
       </c>
       <c r="E67">
         <v>2</v>
@@ -18088,14 +18088,14 @@
       <c r="A68" t="s">
         <v>102</v>
       </c>
-      <c r="B68" s="18">
+      <c r="B68" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="19">
         <v>2026</v>
       </c>
-      <c r="C68" s="19" t="s">
+      <c r="D68" t="s">
         <v>111</v>
-      </c>
-      <c r="D68" t="s">
-        <v>13</v>
       </c>
       <c r="E68">
         <v>1</v>
@@ -18126,14 +18126,14 @@
       <c r="A69" t="s">
         <v>102</v>
       </c>
-      <c r="B69" s="18">
+      <c r="B69" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="19">
         <v>2026</v>
       </c>
-      <c r="C69" s="19" t="s">
+      <c r="D69" t="s">
         <v>18</v>
-      </c>
-      <c r="D69" t="s">
-        <v>13</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -18164,14 +18164,14 @@
       <c r="A70" t="s">
         <v>102</v>
       </c>
-      <c r="B70" s="18">
+      <c r="B70" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C70" s="19">
         <v>2026</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="D70" t="s">
         <v>111</v>
-      </c>
-      <c r="D70" t="s">
-        <v>40</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -18202,14 +18202,14 @@
       <c r="A71" t="s">
         <v>103</v>
       </c>
-      <c r="B71" s="18">
+      <c r="B71" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="19">
         <v>2026</v>
       </c>
-      <c r="C71" s="19" t="s">
+      <c r="D71" t="s">
         <v>111</v>
-      </c>
-      <c r="D71" t="s">
-        <v>13</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -18240,14 +18240,14 @@
       <c r="A72" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="18">
+      <c r="B72" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="19">
         <v>2026</v>
       </c>
-      <c r="C72" s="19" t="s">
+      <c r="D72" t="s">
         <v>18</v>
-      </c>
-      <c r="D72" t="s">
-        <v>13</v>
       </c>
       <c r="E72">
         <v>2</v>
@@ -18278,14 +18278,14 @@
       <c r="A73" t="s">
         <v>103</v>
       </c>
-      <c r="B73" s="18">
+      <c r="B73" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" s="19">
         <v>2026</v>
       </c>
-      <c r="C73" s="19" t="s">
+      <c r="D73" t="s">
         <v>111</v>
-      </c>
-      <c r="D73" t="s">
-        <v>39</v>
       </c>
       <c r="E73">
         <v>1</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C7FF630-79C4-4DB7-8D5A-DD6909D9BFE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B606D5E6-478A-4798-88EC-3FFA7D11A6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -15694,14 +15694,14 @@
       <c r="A5" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E5" s="18">
         <v>3</v>
@@ -15732,14 +15732,14 @@
       <c r="A6" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="E6" s="18">
         <v>5</v>
@@ -15770,14 +15770,14 @@
       <c r="A7" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>26</v>
-      </c>
-      <c r="C7" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E7" s="18">
         <v>6</v>
@@ -15808,14 +15808,14 @@
       <c r="A8" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>107</v>
-      </c>
-      <c r="C8" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E8" s="18">
         <v>23</v>
@@ -15846,14 +15846,14 @@
       <c r="A9" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>107</v>
-      </c>
-      <c r="C9" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="E9" s="18">
         <v>8</v>
@@ -15884,14 +15884,14 @@
       <c r="A10" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>36</v>
-      </c>
-      <c r="C10" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E10" s="18">
         <v>2</v>
@@ -15922,14 +15922,14 @@
       <c r="A11" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="17" t="s">
         <v>36</v>
-      </c>
-      <c r="C11" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="E11" s="18">
         <v>1</v>
@@ -15960,14 +15960,14 @@
       <c r="A12" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>106</v>
-      </c>
-      <c r="C12" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E12" s="18">
         <v>1</v>
@@ -15998,14 +15998,14 @@
       <c r="A13" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>13</v>
-      </c>
-      <c r="C13" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E13" s="18">
         <v>5</v>
@@ -16036,14 +16036,14 @@
       <c r="A14" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>13</v>
-      </c>
-      <c r="C14" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="E14" s="18">
         <v>1</v>
@@ -16074,14 +16074,14 @@
       <c r="A15" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>29</v>
-      </c>
-      <c r="C15" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E15" s="18">
         <v>8</v>
@@ -16112,14 +16112,14 @@
       <c r="A16" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>29</v>
-      </c>
-      <c r="C16" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="E16" s="18">
         <v>12</v>
@@ -16150,14 +16150,14 @@
       <c r="A17" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>39</v>
-      </c>
-      <c r="C17" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E17" s="18">
         <v>1</v>
@@ -16188,14 +16188,14 @@
       <c r="A18" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>39</v>
-      </c>
-      <c r="C18" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="E18" s="18">
         <v>1</v>
@@ -16226,14 +16226,14 @@
       <c r="A19" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>13</v>
-      </c>
-      <c r="C19" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E19" s="18">
         <v>2</v>
@@ -16264,14 +16264,14 @@
       <c r="A20" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="17" t="s">
         <v>13</v>
-      </c>
-      <c r="C20" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="E20" s="18">
         <v>1</v>
@@ -16302,14 +16302,14 @@
       <c r="A21" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>107</v>
-      </c>
-      <c r="C21" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="E21" s="18">
         <v>1</v>
@@ -16340,14 +16340,14 @@
       <c r="A22" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" s="17" t="s">
         <v>40</v>
-      </c>
-      <c r="C22" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E22" s="18">
         <v>1</v>
@@ -16378,14 +16378,14 @@
       <c r="A23" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>13</v>
-      </c>
-      <c r="C23" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>111</v>
       </c>
       <c r="E23" s="18">
         <v>1</v>
@@ -16416,14 +16416,14 @@
       <c r="A24" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" t="s">
         <v>13</v>
-      </c>
-      <c r="C24" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D24" t="s">
-        <v>111</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -16454,14 +16454,14 @@
       <c r="A25" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" t="s">
         <v>13</v>
-      </c>
-      <c r="C25" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D25" t="s">
-        <v>18</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -16492,14 +16492,14 @@
       <c r="A26" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" t="s">
         <v>13</v>
-      </c>
-      <c r="C26" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D26" t="s">
-        <v>111</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -16530,14 +16530,14 @@
       <c r="A27" t="s">
         <v>94</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" t="s">
         <v>39</v>
-      </c>
-      <c r="C27" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D27" t="s">
-        <v>18</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -16568,14 +16568,14 @@
       <c r="A28" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" t="s">
         <v>13</v>
-      </c>
-      <c r="C28" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D28" t="s">
-        <v>111</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -16606,14 +16606,14 @@
       <c r="A29" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D29" t="s">
         <v>34</v>
-      </c>
-      <c r="C29" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D29" t="s">
-        <v>111</v>
       </c>
       <c r="E29">
         <v>3</v>
@@ -16644,14 +16644,14 @@
       <c r="A30" t="s">
         <v>95</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" t="s">
         <v>34</v>
-      </c>
-      <c r="C30" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D30" t="s">
-        <v>18</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -16682,14 +16682,14 @@
       <c r="A31" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" t="s">
         <v>39</v>
-      </c>
-      <c r="C31" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D31" t="s">
-        <v>18</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -16720,14 +16720,14 @@
       <c r="A32" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" t="s">
         <v>40</v>
-      </c>
-      <c r="C32" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D32" t="s">
-        <v>111</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -16758,14 +16758,14 @@
       <c r="A33" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" t="s">
         <v>13</v>
-      </c>
-      <c r="C33" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D33" t="s">
-        <v>111</v>
       </c>
       <c r="E33">
         <v>4</v>
@@ -16796,14 +16796,14 @@
       <c r="A34" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" t="s">
         <v>13</v>
-      </c>
-      <c r="C34" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D34" t="s">
-        <v>18</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -16834,14 +16834,14 @@
       <c r="A35" t="s">
         <v>96</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" t="s">
         <v>107</v>
-      </c>
-      <c r="C35" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D35" t="s">
-        <v>111</v>
       </c>
       <c r="E35">
         <v>2</v>
@@ -16872,14 +16872,14 @@
       <c r="A36" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
         <v>107</v>
-      </c>
-      <c r="C36" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D36" t="s">
-        <v>18</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -16910,14 +16910,14 @@
       <c r="A37" t="s">
         <v>96</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" t="s">
         <v>36</v>
-      </c>
-      <c r="C37" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D37" t="s">
-        <v>111</v>
       </c>
       <c r="E37">
         <v>4</v>
@@ -16948,14 +16948,14 @@
       <c r="A38" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" t="s">
         <v>36</v>
-      </c>
-      <c r="C38" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D38" t="s">
-        <v>18</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -16986,14 +16986,14 @@
       <c r="A39" t="s">
         <v>97</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" t="s">
         <v>13</v>
-      </c>
-      <c r="C39" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D39" t="s">
-        <v>111</v>
       </c>
       <c r="E39">
         <v>62</v>
@@ -17024,14 +17024,14 @@
       <c r="A40" t="s">
         <v>97</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" t="s">
         <v>13</v>
-      </c>
-      <c r="C40" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D40" t="s">
-        <v>18</v>
       </c>
       <c r="E40">
         <v>31</v>
@@ -17062,14 +17062,14 @@
       <c r="A41" t="s">
         <v>97</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" t="s">
         <v>26</v>
-      </c>
-      <c r="C41" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D41" t="s">
-        <v>111</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -17100,14 +17100,14 @@
       <c r="A42" t="s">
         <v>97</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" t="s">
         <v>26</v>
-      </c>
-      <c r="C42" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D42" t="s">
-        <v>18</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -17138,14 +17138,14 @@
       <c r="A43" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D43" t="s">
         <v>107</v>
-      </c>
-      <c r="C43" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D43" t="s">
-        <v>111</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -17176,14 +17176,14 @@
       <c r="A44" t="s">
         <v>97</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" t="s">
         <v>107</v>
-      </c>
-      <c r="C44" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D44" t="s">
-        <v>18</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -17214,14 +17214,14 @@
       <c r="A45" t="s">
         <v>97</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" t="s">
         <v>106</v>
-      </c>
-      <c r="C45" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D45" t="s">
-        <v>111</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -17252,14 +17252,14 @@
       <c r="A46" t="s">
         <v>97</v>
       </c>
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" t="s">
         <v>106</v>
-      </c>
-      <c r="C46" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D46" t="s">
-        <v>18</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -17290,14 +17290,14 @@
       <c r="A47" t="s">
         <v>97</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" t="s">
         <v>29</v>
-      </c>
-      <c r="C47" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D47" t="s">
-        <v>111</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -17328,14 +17328,14 @@
       <c r="A48" t="s">
         <v>98</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D48" t="s">
         <v>13</v>
-      </c>
-      <c r="C48" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D48" t="s">
-        <v>111</v>
       </c>
       <c r="E48">
         <v>8</v>
@@ -17366,14 +17366,14 @@
       <c r="A49" t="s">
         <v>98</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" t="s">
         <v>13</v>
-      </c>
-      <c r="C49" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D49" t="s">
-        <v>18</v>
       </c>
       <c r="E49">
         <v>7</v>
@@ -17404,14 +17404,14 @@
       <c r="A50" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" t="s">
         <v>39</v>
-      </c>
-      <c r="C50" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D50" t="s">
-        <v>18</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -17442,14 +17442,14 @@
       <c r="A51" t="s">
         <v>110</v>
       </c>
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" t="s">
         <v>29</v>
-      </c>
-      <c r="C51" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D51" t="s">
-        <v>18</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -17480,14 +17480,14 @@
       <c r="A52" t="s">
         <v>99</v>
       </c>
-      <c r="B52" s="18" t="s">
+      <c r="B52" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" t="s">
         <v>13</v>
-      </c>
-      <c r="C52" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D52" t="s">
-        <v>111</v>
       </c>
       <c r="E52">
         <v>4</v>
@@ -17518,14 +17518,14 @@
       <c r="A53" t="s">
         <v>99</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" t="s">
         <v>13</v>
-      </c>
-      <c r="C53" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D53" t="s">
-        <v>18</v>
       </c>
       <c r="E53">
         <v>5</v>
@@ -17556,14 +17556,14 @@
       <c r="A54" t="s">
         <v>99</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" t="s">
         <v>26</v>
-      </c>
-      <c r="C54" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D54" t="s">
-        <v>111</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -17594,14 +17594,14 @@
       <c r="A55" t="s">
         <v>99</v>
       </c>
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" t="s">
         <v>107</v>
-      </c>
-      <c r="C55" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D55" t="s">
-        <v>111</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -17632,14 +17632,14 @@
       <c r="A56" t="s">
         <v>99</v>
       </c>
-      <c r="B56" s="18" t="s">
+      <c r="B56" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D56" t="s">
         <v>29</v>
-      </c>
-      <c r="C56" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D56" t="s">
-        <v>111</v>
       </c>
       <c r="E56">
         <v>2</v>
@@ -17670,14 +17670,14 @@
       <c r="A57" t="s">
         <v>99</v>
       </c>
-      <c r="B57" s="18" t="s">
+      <c r="B57" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" t="s">
         <v>39</v>
-      </c>
-      <c r="C57" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D57" t="s">
-        <v>111</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -17708,14 +17708,14 @@
       <c r="A58" t="s">
         <v>99</v>
       </c>
-      <c r="B58" s="18" t="s">
+      <c r="B58" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" t="s">
         <v>39</v>
-      </c>
-      <c r="C58" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D58" t="s">
-        <v>18</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -17746,14 +17746,14 @@
       <c r="A59" t="s">
         <v>99</v>
       </c>
-      <c r="B59" s="18" t="s">
+      <c r="B59" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D59" t="s">
         <v>40</v>
-      </c>
-      <c r="C59" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D59" t="s">
-        <v>111</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -17784,14 +17784,14 @@
       <c r="A60" t="s">
         <v>100</v>
       </c>
-      <c r="B60" s="18" t="s">
+      <c r="B60" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D60" t="s">
         <v>13</v>
-      </c>
-      <c r="C60" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D60" t="s">
-        <v>111</v>
       </c>
       <c r="E60">
         <v>2</v>
@@ -17822,14 +17822,14 @@
       <c r="A61" t="s">
         <v>100</v>
       </c>
-      <c r="B61" s="18" t="s">
+      <c r="B61" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" t="s">
         <v>13</v>
-      </c>
-      <c r="C61" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D61" t="s">
-        <v>18</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -17860,14 +17860,14 @@
       <c r="A62" t="s">
         <v>100</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" t="s">
         <v>29</v>
-      </c>
-      <c r="C62" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D62" t="s">
-        <v>18</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -17898,14 +17898,14 @@
       <c r="A63" t="s">
         <v>100</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D63" t="s">
         <v>39</v>
-      </c>
-      <c r="C63" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D63" t="s">
-        <v>111</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -17936,14 +17936,14 @@
       <c r="A64" t="s">
         <v>100</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" t="s">
         <v>39</v>
-      </c>
-      <c r="C64" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D64" t="s">
-        <v>18</v>
       </c>
       <c r="E64">
         <v>6</v>
@@ -17974,14 +17974,14 @@
       <c r="A65" t="s">
         <v>101</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D65" t="s">
         <v>13</v>
-      </c>
-      <c r="C65" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D65" t="s">
-        <v>111</v>
       </c>
       <c r="E65">
         <v>2</v>
@@ -18012,14 +18012,14 @@
       <c r="A66" t="s">
         <v>101</v>
       </c>
-      <c r="B66" s="18" t="s">
+      <c r="B66" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" t="s">
         <v>106</v>
-      </c>
-      <c r="C66" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D66" t="s">
-        <v>111</v>
       </c>
       <c r="E66">
         <v>7</v>
@@ -18050,14 +18050,14 @@
       <c r="A67" t="s">
         <v>101</v>
       </c>
-      <c r="B67" s="18" t="s">
+      <c r="B67" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" t="s">
         <v>106</v>
-      </c>
-      <c r="C67" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D67" t="s">
-        <v>18</v>
       </c>
       <c r="E67">
         <v>2</v>
@@ -18088,14 +18088,14 @@
       <c r="A68" t="s">
         <v>102</v>
       </c>
-      <c r="B68" s="18" t="s">
+      <c r="B68" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" t="s">
         <v>13</v>
-      </c>
-      <c r="C68" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D68" t="s">
-        <v>111</v>
       </c>
       <c r="E68">
         <v>1</v>
@@ -18126,14 +18126,14 @@
       <c r="A69" t="s">
         <v>102</v>
       </c>
-      <c r="B69" s="18" t="s">
+      <c r="B69" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" t="s">
         <v>13</v>
-      </c>
-      <c r="C69" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D69" t="s">
-        <v>18</v>
       </c>
       <c r="E69">
         <v>1</v>
@@ -18164,14 +18164,14 @@
       <c r="A70" t="s">
         <v>102</v>
       </c>
-      <c r="B70" s="18" t="s">
+      <c r="B70" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D70" t="s">
         <v>40</v>
-      </c>
-      <c r="C70" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D70" t="s">
-        <v>111</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -18202,14 +18202,14 @@
       <c r="A71" t="s">
         <v>103</v>
       </c>
-      <c r="B71" s="18" t="s">
+      <c r="B71" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D71" t="s">
         <v>13</v>
-      </c>
-      <c r="C71" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D71" t="s">
-        <v>111</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -18240,14 +18240,14 @@
       <c r="A72" t="s">
         <v>103</v>
       </c>
-      <c r="B72" s="18" t="s">
+      <c r="B72" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" t="s">
         <v>13</v>
-      </c>
-      <c r="C72" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D72" t="s">
-        <v>18</v>
       </c>
       <c r="E72">
         <v>2</v>
@@ -18278,14 +18278,14 @@
       <c r="A73" t="s">
         <v>103</v>
       </c>
-      <c r="B73" s="18" t="s">
+      <c r="B73" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D73" t="s">
         <v>39</v>
-      </c>
-      <c r="C73" s="19">
-        <v>2026</v>
-      </c>
-      <c r="D73" t="s">
-        <v>111</v>
       </c>
       <c r="E73">
         <v>1</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B606D5E6-478A-4798-88EC-3FFA7D11A6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67F1A7F-C98E-4A90-BB5E-948F344B6371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="113">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -1013,64 +1013,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C6" s="5">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D6" s="5">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E6" s="5">
-        <v>27579.59</v>
+        <v>28992.18</v>
       </c>
       <c r="F6" s="5">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G6" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6" s="5">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="I6" s="5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J6" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6" s="5">
-        <v>260.18481132075402</v>
+        <v>256.56796460176901</v>
       </c>
       <c r="L6" s="5">
-        <v>889.66419354838695</v>
+        <v>878.55090909090904</v>
       </c>
       <c r="M6" s="5">
-        <v>196.61833261480601</v>
+        <v>209.26201479157399</v>
       </c>
       <c r="N6" s="6">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="O6" s="6">
-        <v>53667.38</v>
+        <v>56793.15</v>
       </c>
       <c r="P6" s="6">
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="Q6" s="6">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="R6" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S6" s="6">
-        <v>219.05053061224399</v>
+        <v>198.57744755244701</v>
       </c>
       <c r="T6" s="6">
-        <v>1032.0650000000001</v>
+        <v>931.03524590163897</v>
       </c>
       <c r="U6" s="6">
-        <v>116.405887524227</v>
+        <v>124.12083147351299</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1085,7 +1085,7 @@
         <v>77</v>
       </c>
       <c r="Z6" s="7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA6" s="8">
         <v>45500</v>
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1105,25 +1105,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C7" s="5">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" s="5">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E7" s="5">
-        <v>4814.12</v>
+        <v>5026.1499999999996</v>
       </c>
       <c r="F7" s="5">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G7" s="5">
         <v>8</v>
       </c>
       <c r="H7" s="5">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I7" s="5">
         <v>13</v>
@@ -1132,37 +1132,37 @@
         <v>9</v>
       </c>
       <c r="K7" s="5">
-        <v>83.002068965517196</v>
+        <v>83.769166666666607</v>
       </c>
       <c r="L7" s="5">
-        <v>370.31692307692299</v>
+        <v>386.62692307692299</v>
       </c>
       <c r="M7" s="5">
-        <v>1132.7278921173499</v>
+        <v>1080.72480924763</v>
       </c>
       <c r="N7" s="6">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="O7" s="6">
-        <v>13318.47</v>
+        <v>14103.87</v>
       </c>
       <c r="P7" s="6">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="Q7" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R7" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S7" s="6">
-        <v>111.919915966386</v>
+        <v>101.466690647482</v>
       </c>
       <c r="T7" s="6">
-        <v>951.319285714285</v>
+        <v>829.63941176470598</v>
       </c>
       <c r="U7" s="6">
-        <v>440.99119493455299</v>
+        <v>454.06601166913703</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1177,7 +1177,7 @@
         <v>29</v>
       </c>
       <c r="Z7" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7" s="8">
         <v>10000</v>
@@ -1189,7 +1189,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="5">
-        <v>1676.15</v>
+        <v>1791.14</v>
       </c>
       <c r="F8" s="5">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1676.15</v>
+        <v>1791.14</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5">
@@ -1234,7 +1234,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>1832.21</v>
+        <v>1936.03</v>
       </c>
       <c r="P8" s="6">
         <v>5</v>
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>366.44200000000001</v>
+        <v>387.20600000000002</v>
       </c>
       <c r="T8" s="6">
-        <v>916.10500000000002</v>
+        <v>968.01499999999999</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1279,7 +1279,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1287,64 +1287,64 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5">
         <v>6</v>
       </c>
       <c r="D9" s="5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E9" s="5">
-        <v>5516.4</v>
+        <v>5837.84</v>
       </c>
       <c r="F9" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9" s="5">
         <v>1</v>
       </c>
       <c r="H9" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I9" s="5">
         <v>5</v>
       </c>
       <c r="J9" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>424.33846153846099</v>
+        <v>486.486666666666</v>
       </c>
       <c r="L9" s="5">
-        <v>1103.28</v>
+        <v>1167.568</v>
       </c>
       <c r="M9" s="5">
-        <v>41.686607207599103</v>
+        <v>168.449974648157</v>
       </c>
       <c r="N9" s="6">
         <v>22</v>
       </c>
       <c r="O9" s="6">
-        <v>5452.81</v>
+        <v>5776.12</v>
       </c>
       <c r="P9" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q9" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R9" s="6">
         <v>1</v>
       </c>
       <c r="S9" s="6">
-        <v>454.40083333333303</v>
+        <v>412.58</v>
       </c>
       <c r="T9" s="6">
-        <v>1363.2025000000001</v>
+        <v>962.68666666666604</v>
       </c>
       <c r="U9" s="6">
-        <v>-2.2338940839677202</v>
+        <v>-7.7062110897973</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1365,7 +1365,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1388,7 +1388,7 @@
         <v>2</v>
       </c>
       <c r="O10" s="6">
-        <v>2026.25</v>
+        <v>2081.4299999999998</v>
       </c>
       <c r="P10" s="6">
         <v>6</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>337.70833333333297</v>
+        <v>346.90499999999997</v>
       </c>
       <c r="T10" s="6">
-        <v>506.5625</v>
+        <v>520.35749999999996</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1421,7 +1421,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1429,22 +1429,22 @@
         <v>106</v>
       </c>
       <c r="B11" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="5">
         <v>2</v>
       </c>
       <c r="D11" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="5">
-        <v>2911.18</v>
+        <v>2966.27</v>
       </c>
       <c r="F11" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="5">
         <v>4</v>
@@ -1456,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>727.79499999999996</v>
+        <v>593.25400000000002</v>
       </c>
       <c r="L11" s="5">
-        <v>1455.59</v>
+        <v>1483.135</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
@@ -1468,10 +1468,10 @@
         <v>2</v>
       </c>
       <c r="O11" s="6">
-        <v>1051.3499999999999</v>
+        <v>1120.32</v>
       </c>
       <c r="P11" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q11" s="6">
         <v>1</v>
@@ -1480,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>350.45</v>
+        <v>280.08</v>
       </c>
       <c r="T11" s="6">
-        <v>1051.3499999999999</v>
+        <v>1120.32</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1513,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1536,7 +1536,7 @@
         <v>1</v>
       </c>
       <c r="O12" s="6">
-        <v>262.63</v>
+        <v>282.88</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1557,7 +1557,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1574,16 +1574,16 @@
         <v>14</v>
       </c>
       <c r="E13" s="5">
-        <v>6040.9</v>
+        <v>6357.19</v>
       </c>
       <c r="F13" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" s="5">
         <v>5</v>
       </c>
       <c r="H13" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I13" s="5">
         <v>4</v>
@@ -1592,22 +1592,22 @@
         <v>2</v>
       </c>
       <c r="K13" s="5">
-        <v>431.49285714285702</v>
+        <v>423.81266666666602</v>
       </c>
       <c r="L13" s="5">
-        <v>1510.2249999999999</v>
+        <v>1589.2974999999999</v>
       </c>
       <c r="M13" s="5">
-        <v>142.43275008690699</v>
+        <v>130.370965788343</v>
       </c>
       <c r="N13" s="6">
         <v>13</v>
       </c>
       <c r="O13" s="6">
-        <v>2949.08</v>
+        <v>3223.68</v>
       </c>
       <c r="P13" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q13" s="6">
         <v>8</v>
@@ -1616,13 +1616,13 @@
         <v>2</v>
       </c>
       <c r="S13" s="6">
-        <v>196.60533333333299</v>
+        <v>189.62823529411699</v>
       </c>
       <c r="T13" s="6">
-        <v>368.63499999999999</v>
+        <v>402.96</v>
       </c>
       <c r="U13" s="6">
-        <v>442.33862763980602</v>
+        <v>396.14105618423599</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1649,7 +1649,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1672,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>587.78</v>
+        <v>628.20000000000005</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1684,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>293.89</v>
+        <v>314.10000000000002</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1709,7 +1709,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1753,7 +1753,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1773,17 +1773,27 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O16" s="6">
-        <v>878.1</v>
-      </c>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
+        <v>930.37</v>
+      </c>
+      <c r="P16" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6">
+        <v>0</v>
+      </c>
+      <c r="S16" s="6">
+        <v>930.37</v>
+      </c>
       <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
+      <c r="U16" s="6">
+        <v>-100</v>
+      </c>
       <c r="V16" s="7">
         <v>7</v>
       </c>
@@ -1803,7 +1813,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1820,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>1179.94</v>
+        <v>1213.92</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1838,22 +1848,22 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1179.94</v>
+        <v>1213.92</v>
       </c>
       <c r="L17" s="5">
-        <v>1179.94</v>
+        <v>1213.92</v>
       </c>
       <c r="M17" s="5">
         <v>-100</v>
       </c>
       <c r="N17" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="6">
-        <v>748.01</v>
+        <v>814.95</v>
       </c>
       <c r="P17" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="6">
         <v>0</v>
@@ -1862,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>748.01</v>
+        <v>407.47500000000002</v>
       </c>
       <c r="T17" s="6"/>
       <c r="U17" s="6">
@@ -1893,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1916,10 +1926,10 @@
         <v>15</v>
       </c>
       <c r="O18" s="6">
-        <v>2767.24</v>
+        <v>2922.53</v>
       </c>
       <c r="P18" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q18" s="6">
         <v>3</v>
@@ -1928,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>307.47111111111099</v>
+        <v>243.544166666666</v>
       </c>
       <c r="T18" s="6">
-        <v>922.41333333333296</v>
+        <v>974.17666666666605</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1955,7 +1965,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1972,7 +1982,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="5">
-        <v>2445.35</v>
+        <v>2556.0700000000002</v>
       </c>
       <c r="F19" s="5">
         <v>4</v>
@@ -1990,10 +2000,10 @@
         <v>0</v>
       </c>
       <c r="K19" s="5">
-        <v>611.33749999999998</v>
+        <v>639.01750000000004</v>
       </c>
       <c r="L19" s="5">
-        <v>1222.675</v>
+        <v>1278.0350000000001</v>
       </c>
       <c r="M19" s="5">
         <v>-100</v>
@@ -2002,25 +2012,25 @@
         <v>23</v>
       </c>
       <c r="O19" s="6">
-        <v>3070.96</v>
+        <v>3227.9</v>
       </c>
       <c r="P19" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q19" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R19" s="6">
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>236.227692307692</v>
+        <v>230.56428571428501</v>
       </c>
       <c r="T19" s="6">
-        <v>767.74</v>
+        <v>645.58000000000004</v>
       </c>
       <c r="U19" s="6">
-        <v>131.20001563029101</v>
+        <v>119.959106539855</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2047,7 +2057,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2070,22 +2080,22 @@
         <v>13</v>
       </c>
       <c r="O20" s="6">
-        <v>3115.88</v>
+        <v>3289.91</v>
       </c>
       <c r="P20" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q20" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R20" s="6">
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>283.261818181818</v>
+        <v>253.07</v>
       </c>
       <c r="T20" s="6">
-        <v>623.17600000000004</v>
+        <v>469.98714285714198</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2109,7 +2119,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2129,28 +2139,28 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="O21" s="6">
-        <v>8094.25</v>
+        <v>8550.75</v>
       </c>
       <c r="P21" s="6">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="Q21" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R21" s="6">
         <v>2</v>
       </c>
       <c r="S21" s="6">
-        <v>311.317307692307</v>
+        <v>259.11363636363598</v>
       </c>
       <c r="T21" s="6">
-        <v>2023.5625</v>
+        <v>1710.15</v>
       </c>
       <c r="U21" s="6">
-        <v>93.502301016153396</v>
+        <v>83.171768558313502</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2171,7 +2181,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2179,37 +2189,37 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C22" s="5">
         <v>2</v>
       </c>
       <c r="D22" s="5">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E22" s="5">
-        <v>2995.55</v>
+        <v>3243.6</v>
       </c>
       <c r="F22" s="5">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G22" s="5">
         <v>1</v>
       </c>
       <c r="H22" s="5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I22" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J22" s="5">
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>272.32272727272698</v>
+        <v>216.24</v>
       </c>
       <c r="L22" s="5">
-        <v>748.88750000000005</v>
+        <v>540.6</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2218,10 +2228,10 @@
         <v>4</v>
       </c>
       <c r="O22" s="6">
-        <v>2622.02</v>
+        <v>2722.8</v>
       </c>
       <c r="P22" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -2230,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>524.404</v>
+        <v>453.8</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2261,7 +2271,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2284,7 +2294,7 @@
         <v>27</v>
       </c>
       <c r="O23" s="6">
-        <v>3232.2</v>
+        <v>3400.25</v>
       </c>
       <c r="P23" s="6">
         <v>13</v>
@@ -2293,16 +2303,16 @@
         <v>2</v>
       </c>
       <c r="R23" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="6">
-        <v>248.630769230769</v>
+        <v>261.55769230769198</v>
       </c>
       <c r="T23" s="6">
-        <v>1616.1</v>
+        <v>1700.125</v>
       </c>
       <c r="U23" s="6">
-        <v>-100</v>
+        <v>48.604073229909503</v>
       </c>
       <c r="V23" s="7">
         <v>37</v>
@@ -2317,7 +2327,7 @@
         <v>4</v>
       </c>
       <c r="Z23" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" s="8"/>
       <c r="AB23" s="9">
@@ -2327,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2347,10 +2357,10 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O24" s="6">
-        <v>1655.4</v>
+        <v>1778.42</v>
       </c>
       <c r="P24" s="6">
         <v>5</v>
@@ -2362,10 +2372,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>331.08</v>
+        <v>355.68400000000003</v>
       </c>
       <c r="T24" s="6">
-        <v>1655.4</v>
+        <v>1778.42</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2389,7 +2399,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46162</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3027,10 +3037,10 @@
         <v>45253.33</v>
       </c>
       <c r="L5" s="18">
-        <v>12.1</v>
+        <v>11.81</v>
       </c>
       <c r="M5" s="18">
-        <v>21.7</v>
+        <v>20.91</v>
       </c>
       <c r="N5" s="18">
         <v>47.06</v>
@@ -3062,7 +3072,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="18">
         <v>1</v>
@@ -3077,10 +3087,10 @@
         <v>7816</v>
       </c>
       <c r="L6" s="18">
-        <v>4.9800000000000004</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="M6" s="18">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="N6" s="18">
         <v>50</v>
@@ -3127,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="18">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M7" s="18">
         <v>0</v>
@@ -3175,10 +3185,10 @@
         <v>17649</v>
       </c>
       <c r="L8" s="18">
-        <v>4.9800000000000004</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="M8" s="18">
-        <v>8.4600000000000009</v>
+        <v>8.16</v>
       </c>
       <c r="N8" s="18">
         <v>42.86</v>
@@ -3225,10 +3235,10 @@
         <v>6827</v>
       </c>
       <c r="L9" s="18">
-        <v>4.9800000000000004</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="M9" s="18">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="N9" s="18">
         <v>28.57</v>
@@ -3275,10 +3285,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="18">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="M10" s="18">
-        <v>1.1000000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="N10" s="18">
         <v>0</v>
@@ -3323,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="L11" s="18">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="M11" s="18">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="N11" s="18">
         <v>0</v>
@@ -3371,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="18">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M12" s="18">
         <v>0</v>
@@ -3419,10 +3429,10 @@
         <v>0</v>
       </c>
       <c r="L13" s="18">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M13" s="18">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="N13" s="18">
         <v>100</v>
@@ -3469,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="18">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M14" s="18">
         <v>0</v>
@@ -3517,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="18">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M15" s="18">
         <v>0</v>
@@ -3565,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="18">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M16" s="18">
         <v>0</v>
@@ -3615,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="18">
-        <v>2.4900000000000002</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="M17" s="18">
         <v>0</v>
@@ -3665,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="18">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="M18" s="18">
         <v>0</v>
@@ -3691,13 +3701,13 @@
         <v>111</v>
       </c>
       <c r="D19" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G19" s="10">
         <v>4</v>
@@ -3715,19 +3725,19 @@
         <v>5234</v>
       </c>
       <c r="L19" s="10">
-        <v>3.56</v>
+        <v>3.12</v>
       </c>
       <c r="M19" s="10">
-        <v>5.0199999999999996</v>
+        <v>4.84</v>
       </c>
       <c r="N19" s="10">
-        <v>60</v>
+        <v>55.56</v>
       </c>
       <c r="O19" s="10">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="P19" s="10">
-        <v>20</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -3753,31 +3763,31 @@
         <v>3</v>
       </c>
       <c r="H20" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="10">
-        <v>0</v>
+        <v>7855.68</v>
       </c>
       <c r="J20" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="10">
-        <v>0</v>
+        <v>7855.68</v>
       </c>
       <c r="L20" s="10">
-        <v>2.4900000000000002</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="M20" s="10">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N20" s="10">
         <v>42.86</v>
       </c>
       <c r="O20" s="10">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="P20" s="10">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -3815,10 +3825,10 @@
         <v>36031</v>
       </c>
       <c r="L21" s="10">
-        <v>24.91</v>
+        <v>24.31</v>
       </c>
       <c r="M21" s="10">
-        <v>17.28</v>
+        <v>16.649999999999999</v>
       </c>
       <c r="N21" s="10">
         <v>0</v>
@@ -3839,16 +3849,16 @@
         <v>18</v>
       </c>
       <c r="D22" s="10">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E22" s="10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F22" s="10">
         <v>0</v>
       </c>
       <c r="G22" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H22" s="10">
         <v>3</v>
@@ -3863,17 +3873,17 @@
         <v>20397</v>
       </c>
       <c r="L22" s="10">
-        <v>12.46</v>
+        <v>12.85</v>
       </c>
       <c r="M22" s="10">
-        <v>9.7799999999999994</v>
+        <v>9.43</v>
       </c>
       <c r="N22" s="10">
         <v>0</v>
       </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10">
-        <v>8.57</v>
+        <v>8.11</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
@@ -3911,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="10">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="M23" s="10">
         <v>0</v>
@@ -3937,10 +3947,10 @@
         <v>18</v>
       </c>
       <c r="D24" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" s="10">
         <v>2</v>
@@ -3961,19 +3971,19 @@
         <v>15374</v>
       </c>
       <c r="L24" s="10">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="M24" s="10">
-        <v>7.37</v>
+        <v>7.1</v>
       </c>
       <c r="N24" s="10">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="O24" s="10">
         <v>100</v>
       </c>
       <c r="P24" s="10">
-        <v>25</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
@@ -4011,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="10">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M25" s="10">
         <v>0</v>
@@ -4059,10 +4069,10 @@
         <v>7816</v>
       </c>
       <c r="L26" s="10">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="M26" s="10">
-        <v>3.75</v>
+        <v>3.61</v>
       </c>
       <c r="N26" s="10">
         <v>30</v>
@@ -4109,10 +4119,10 @@
         <v>17865</v>
       </c>
       <c r="L27" s="10">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="M27" s="10">
-        <v>8.57</v>
+        <v>8.26</v>
       </c>
       <c r="N27" s="10">
         <v>50</v>
@@ -4159,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="10">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="M28" s="10">
         <v>0</v>
@@ -4185,16 +4195,16 @@
         <v>18</v>
       </c>
       <c r="D29" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E29" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F29" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G29" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="10">
         <v>2</v>
@@ -4209,19 +4219,19 @@
         <v>8117.12</v>
       </c>
       <c r="L29" s="10">
-        <v>3.2</v>
+        <v>4.51</v>
       </c>
       <c r="M29" s="10">
-        <v>3.89</v>
+        <v>3.75</v>
       </c>
       <c r="N29" s="10">
-        <v>55.56</v>
+        <v>53.85</v>
       </c>
       <c r="O29" s="10">
-        <v>40</v>
+        <v>28.57</v>
       </c>
       <c r="P29" s="10">
-        <v>22.22</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
@@ -4259,10 +4269,10 @@
         <v>0</v>
       </c>
       <c r="L30" s="10">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="M30" s="10">
-        <v>3.39</v>
+        <v>3.27</v>
       </c>
       <c r="N30" s="10">
         <v>11.11</v>
@@ -4285,13 +4295,13 @@
         <v>18</v>
       </c>
       <c r="D31" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="10">
         <v>0</v>
@@ -4309,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>0.71</v>
+        <v>1.04</v>
       </c>
       <c r="M31" s="10">
         <v>0</v>
@@ -4359,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="10">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="M32" s="10">
         <v>0</v>
@@ -4407,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
@@ -4457,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="10">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="M34" s="10">
         <v>0</v>
@@ -4507,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="10">
-        <v>0.71</v>
+        <v>0.69</v>
       </c>
       <c r="M35" s="10">
         <v>0</v>
@@ -5095,7 +5105,7 @@
         <v>86</v>
       </c>
       <c r="H19" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="5">
         <v>11</v>
@@ -5153,16 +5163,16 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>1990</v>
+        <v>2099</v>
       </c>
       <c r="E21" s="10">
-        <v>4814.12</v>
+        <v>5026.1499999999996</v>
       </c>
       <c r="F21" s="10">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G21" s="10">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H21" s="10">
         <v>14</v>
@@ -5174,7 +5184,7 @@
         <v>59345</v>
       </c>
       <c r="K21" s="10">
-        <v>11.33</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5748,10 +5758,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="E38" s="10">
-        <v>1676.15</v>
+        <v>1791.14</v>
       </c>
       <c r="F38" s="10">
         <v>5</v>
@@ -5900,7 +5910,7 @@
         <v>23</v>
       </c>
       <c r="H42" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I42" s="10">
         <v>5</v>
@@ -6343,13 +6353,13 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>724</v>
+        <v>756</v>
       </c>
       <c r="E55" s="10">
-        <v>5516.4</v>
+        <v>5837.84</v>
       </c>
       <c r="F55" s="10">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G55" s="10">
         <v>12</v>
@@ -6358,13 +6368,13 @@
         <v>5</v>
       </c>
       <c r="I55" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55" s="10">
-        <v>7816</v>
+        <v>15671.68</v>
       </c>
       <c r="K55" s="10">
-        <v>0.42</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6517,7 +6527,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H60" s="10">
         <v>4</v>
@@ -7338,19 +7348,19 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="E84" s="10">
-        <v>2911.18</v>
+        <v>2966.27</v>
       </c>
       <c r="F84" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G84" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H84" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I84" s="10">
         <v>0</v>
@@ -7817,10 +7827,10 @@
         <v>17</v>
       </c>
       <c r="G98" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H98" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I98" s="10">
         <v>6</v>
@@ -8228,16 +8238,16 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>564</v>
+        <v>599</v>
       </c>
       <c r="E110" s="10">
-        <v>6040.9</v>
+        <v>6357.19</v>
       </c>
       <c r="F110" s="10">
         <v>24</v>
       </c>
       <c r="G110" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H110" s="10">
         <v>5</v>
@@ -8249,7 +8259,7 @@
         <v>14645.12</v>
       </c>
       <c r="K110" s="10">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -8947,7 +8957,7 @@
         <v>6</v>
       </c>
       <c r="G132" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H132" s="10">
         <v>2</v>
@@ -9743,10 +9753,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E155" s="10">
-        <v>1179.94</v>
+        <v>1213.92</v>
       </c>
       <c r="F155" s="10">
         <v>2</v>
@@ -10829,10 +10839,10 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="E186" s="10">
-        <v>2445.35</v>
+        <v>2556.0700000000002</v>
       </c>
       <c r="F186" s="10">
         <v>13</v>
@@ -12404,19 +12414,19 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="E231" s="10">
-        <v>2995.55</v>
+        <v>3243.6</v>
       </c>
       <c r="F231" s="10">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G231" s="10">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H231" s="10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I231" s="10">
         <v>0</v>
@@ -15941,7 +15951,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="18">
         <v>0</v>
@@ -16768,13 +16778,13 @@
         <v>13</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -16894,16 +16904,16 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>7855.68</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>7855.68</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -17034,10 +17044,10 @@
         <v>13</v>
       </c>
       <c r="E40">
+        <v>32</v>
+      </c>
+      <c r="F40">
         <v>31</v>
-      </c>
-      <c r="F40">
-        <v>30</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -17326,28 +17336,28 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B48" s="18">
         <v>2026</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E48">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -17370,34 +17380,34 @@
         <v>2026</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
       </c>
       <c r="E49">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F49">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H49">
         <v>2</v>
       </c>
       <c r="I49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>15374</v>
+        <v>0</v>
       </c>
       <c r="K49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>15374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
@@ -17411,36 +17421,36 @@
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>15374</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>15374</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B51" s="18">
         <v>2026</v>
@@ -17449,7 +17459,7 @@
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -17478,28 +17488,28 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B52" s="18">
         <v>2026</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -17522,34 +17532,34 @@
         <v>2026</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
       </c>
       <c r="E53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J53">
-        <v>17865</v>
+        <v>0</v>
       </c>
       <c r="K53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>17865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
@@ -17560,34 +17570,34 @@
         <v>2026</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>17865</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>17865</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -17601,7 +17611,7 @@
         <v>111</v>
       </c>
       <c r="D55" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -17613,7 +17623,7 @@
         <v>1</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -17639,19 +17649,19 @@
         <v>111</v>
       </c>
       <c r="D56" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -17677,13 +17687,13 @@
         <v>111</v>
       </c>
       <c r="D57" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -17712,7 +17722,7 @@
         <v>2026</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D58" t="s">
         <v>39</v>
@@ -17750,10 +17760,10 @@
         <v>2026</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -17762,27 +17772,27 @@
         <v>1</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>7816</v>
+        <v>0</v>
       </c>
       <c r="K59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59">
-        <v>7816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B60" s="18">
         <v>2026</v>
@@ -17791,31 +17801,31 @@
         <v>111</v>
       </c>
       <c r="D60" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>7816</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
@@ -17826,7 +17836,7 @@
         <v>2026</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
@@ -17844,16 +17854,16 @@
         <v>1</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
@@ -17867,16 +17877,16 @@
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -17885,13 +17895,13 @@
         <v>1</v>
       </c>
       <c r="J62">
-        <v>7818.1200000000008</v>
+        <v>299</v>
       </c>
       <c r="K62">
         <v>1</v>
       </c>
       <c r="L62">
-        <v>7818.1200000000008</v>
+        <v>299</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -17902,34 +17912,34 @@
         <v>2026</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63">
         <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
@@ -17940,22 +17950,22 @@
         <v>2026</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D64" t="s">
         <v>39</v>
       </c>
       <c r="E64">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -17972,34 +17982,34 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B65" s="18">
         <v>2026</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65">
-        <v>7072</v>
+        <v>0</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -18019,25 +18029,25 @@
         <v>111</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="E66">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F66">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>7072</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -18054,22 +18064,22 @@
         <v>2026</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D67" t="s">
         <v>106</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -18086,25 +18096,25 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B68" s="18">
         <v>2026</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -18130,7 +18140,7 @@
         <v>2026</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -18142,7 +18152,7 @@
         <v>1</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -18168,10 +18178,10 @@
         <v>2026</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E70">
         <v>1</v>
@@ -18180,7 +18190,7 @@
         <v>1</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -18200,7 +18210,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B71" s="18">
         <v>2026</v>
@@ -18209,7 +18219,7 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -18218,10 +18228,10 @@
         <v>1</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -18244,22 +18254,22 @@
         <v>2026</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -18282,39 +18292,73 @@
         <v>2026</v>
       </c>
       <c r="C73" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>103</v>
+      </c>
+      <c r="B74" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C74" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D74" t="s">
         <v>39</v>
       </c>
-      <c r="E73">
-        <v>1</v>
-      </c>
-      <c r="F73">
-        <v>1</v>
-      </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73">
-        <v>0</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B74" s="18"/>
-      <c r="C74" s="19"/>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B75" s="18"/>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67F1A7F-C98E-4A90-BB5E-948F344B6371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A66798D-E716-4BCE-9095-9289D772F083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="113">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -1013,64 +1013,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C6" s="5">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D6" s="5">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E6" s="5">
-        <v>28992.18</v>
+        <v>34231.550000000003</v>
       </c>
       <c r="F6" s="5">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="G6" s="5">
         <v>19</v>
       </c>
       <c r="H6" s="5">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="I6" s="5">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J6" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K6" s="5">
-        <v>256.56796460176901</v>
+        <v>267.43398437500002</v>
       </c>
       <c r="L6" s="5">
-        <v>878.55090909090904</v>
+        <v>855.78875000000005</v>
       </c>
       <c r="M6" s="5">
-        <v>209.26201479157399</v>
+        <v>189.31193591876399</v>
       </c>
       <c r="N6" s="6">
-        <v>287</v>
+        <v>335</v>
       </c>
       <c r="O6" s="6">
-        <v>56793.15</v>
+        <v>67122.909999999902</v>
       </c>
       <c r="P6" s="6">
-        <v>286</v>
+        <v>334</v>
       </c>
       <c r="Q6" s="6">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="R6" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="S6" s="6">
-        <v>198.57744755244701</v>
+        <v>200.966796407185</v>
       </c>
       <c r="T6" s="6">
-        <v>931.03524590163897</v>
+        <v>972.79579710144901</v>
       </c>
       <c r="U6" s="6">
-        <v>124.12083147351299</v>
+        <v>110.990971636956</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1085,7 +1085,7 @@
         <v>77</v>
       </c>
       <c r="Z6" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA6" s="8">
         <v>45500</v>
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1105,25 +1105,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C7" s="5">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D7" s="5">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E7" s="5">
-        <v>5026.1499999999996</v>
+        <v>5957.33</v>
       </c>
       <c r="F7" s="5">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G7" s="5">
         <v>8</v>
       </c>
       <c r="H7" s="5">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I7" s="5">
         <v>13</v>
@@ -1132,37 +1132,37 @@
         <v>9</v>
       </c>
       <c r="K7" s="5">
-        <v>83.769166666666607</v>
+        <v>93.083281249999999</v>
       </c>
       <c r="L7" s="5">
-        <v>386.62692307692299</v>
+        <v>458.25615384615298</v>
       </c>
       <c r="M7" s="5">
-        <v>1080.72480924763</v>
+        <v>896.16774628902499</v>
       </c>
       <c r="N7" s="6">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="O7" s="6">
-        <v>14103.87</v>
+        <v>16311.04</v>
       </c>
       <c r="P7" s="6">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="Q7" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R7" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S7" s="6">
-        <v>101.466690647482</v>
+        <v>100.067730061349</v>
       </c>
       <c r="T7" s="6">
-        <v>829.63941176470598</v>
+        <v>858.47578947368402</v>
       </c>
       <c r="U7" s="6">
-        <v>454.06601166913703</v>
+        <v>427.47556256375998</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1177,7 +1177,7 @@
         <v>29</v>
       </c>
       <c r="Z7" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA7" s="8">
         <v>10000</v>
@@ -1189,7 +1189,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1197,36 +1197,38 @@
         <v>26</v>
       </c>
       <c r="B8" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5">
-        <v>1791.14</v>
+        <v>2023.85</v>
       </c>
       <c r="F8" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
       </c>
       <c r="H8" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="5">
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>1791.14</v>
-      </c>
-      <c r="L8" s="5"/>
+        <v>505.96249999999998</v>
+      </c>
+      <c r="L8" s="5">
+        <v>2023.85</v>
+      </c>
       <c r="M8" s="5">
         <v>-100</v>
       </c>
@@ -1234,7 +1236,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>1936.03</v>
+        <v>2336.71</v>
       </c>
       <c r="P8" s="6">
         <v>5</v>
@@ -1246,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>387.20600000000002</v>
+        <v>467.34199999999998</v>
       </c>
       <c r="T8" s="6">
-        <v>968.01499999999999</v>
+        <v>1168.355</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1279,7 +1281,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1287,25 +1289,25 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" s="5">
         <v>22</v>
       </c>
       <c r="E9" s="5">
-        <v>5837.84</v>
+        <v>6871.47</v>
       </c>
       <c r="F9" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G9" s="5">
         <v>1</v>
       </c>
       <c r="H9" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I9" s="5">
         <v>5</v>
@@ -1314,37 +1316,37 @@
         <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>486.486666666666</v>
+        <v>490.819285714285</v>
       </c>
       <c r="L9" s="5">
-        <v>1167.568</v>
+        <v>1374.2940000000001</v>
       </c>
       <c r="M9" s="5">
-        <v>168.449974648157</v>
+        <v>128.068812059137</v>
       </c>
       <c r="N9" s="6">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="O9" s="6">
-        <v>5776.12</v>
+        <v>7029.13</v>
       </c>
       <c r="P9" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="Q9" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R9" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" s="6">
-        <v>412.58</v>
+        <v>369.95421052631502</v>
       </c>
       <c r="T9" s="6">
-        <v>962.68666666666604</v>
+        <v>1004.1614285714199</v>
       </c>
       <c r="U9" s="6">
-        <v>-7.7062110897973</v>
+        <v>67.545627979564998</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1365,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1385,25 +1387,25 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O10" s="6">
-        <v>2081.4299999999998</v>
+        <v>2291.2399999999998</v>
       </c>
       <c r="P10" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q10" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R10" s="6">
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>346.90499999999997</v>
+        <v>254.58222222222199</v>
       </c>
       <c r="T10" s="6">
-        <v>520.35749999999996</v>
+        <v>458.24799999999902</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1421,7 +1423,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1429,49 +1431,49 @@
         <v>106</v>
       </c>
       <c r="B11" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="5">
         <v>2</v>
       </c>
       <c r="D11" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="5">
-        <v>2966.27</v>
+        <v>3606.08</v>
       </c>
       <c r="F11" s="5">
+        <v>6</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5">
         <v>5</v>
       </c>
-      <c r="G11" s="5">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5">
+      <c r="I11" s="5">
         <v>4</v>
       </c>
-      <c r="I11" s="5">
-        <v>2</v>
-      </c>
       <c r="J11" s="5">
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>593.25400000000002</v>
+        <v>601.01333333333298</v>
       </c>
       <c r="L11" s="5">
-        <v>1483.135</v>
+        <v>901.52</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
       </c>
       <c r="N11" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O11" s="6">
-        <v>1120.32</v>
+        <v>1393.6</v>
       </c>
       <c r="P11" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="6">
         <v>1</v>
@@ -1480,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>280.08</v>
+        <v>278.719999999999</v>
       </c>
       <c r="T11" s="6">
-        <v>1120.32</v>
+        <v>1393.6</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1513,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1533,10 +1535,10 @@
       <c r="L12" s="5"/>
       <c r="M12" s="5"/>
       <c r="N12" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" s="6">
-        <v>282.88</v>
+        <v>349.61</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1557,7 +1559,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1565,64 +1567,64 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C13" s="5">
         <v>10</v>
       </c>
       <c r="D13" s="5">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E13" s="5">
-        <v>6357.19</v>
+        <v>7504.9</v>
       </c>
       <c r="F13" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G13" s="5">
         <v>5</v>
       </c>
       <c r="H13" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I13" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J13" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="5">
-        <v>423.81266666666602</v>
+        <v>441.46470588235201</v>
       </c>
       <c r="L13" s="5">
-        <v>1589.2974999999999</v>
+        <v>1250.81666666666</v>
       </c>
       <c r="M13" s="5">
-        <v>130.370965788343</v>
+        <v>178.04660954842799</v>
       </c>
       <c r="N13" s="6">
         <v>13</v>
       </c>
       <c r="O13" s="6">
-        <v>3223.68</v>
+        <v>4001.61</v>
       </c>
       <c r="P13" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q13" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R13" s="6">
         <v>2</v>
       </c>
       <c r="S13" s="6">
-        <v>189.62823529411699</v>
+        <v>210.61105263157799</v>
       </c>
       <c r="T13" s="6">
-        <v>402.96</v>
+        <v>444.62333333333299</v>
       </c>
       <c r="U13" s="6">
-        <v>396.14105618423599</v>
+        <v>299.68912512713598</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1649,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1672,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>628.20000000000005</v>
+        <v>709.73</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1684,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>314.10000000000002</v>
+        <v>354.86500000000001</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1709,7 +1711,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1753,7 +1755,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1776,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="O16" s="6">
-        <v>930.37</v>
+        <v>1106.19</v>
       </c>
       <c r="P16" s="6">
         <v>1</v>
@@ -1788,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>930.37</v>
+        <v>1106.19</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="6">
@@ -1813,7 +1815,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1830,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>1213.92</v>
+        <v>1345.21</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1848,10 +1850,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1213.92</v>
+        <v>1345.21</v>
       </c>
       <c r="L17" s="5">
-        <v>1213.92</v>
+        <v>1345.21</v>
       </c>
       <c r="M17" s="5">
         <v>-100</v>
@@ -1860,21 +1862,23 @@
         <v>2</v>
       </c>
       <c r="O17" s="6">
-        <v>814.95</v>
+        <v>919.93</v>
       </c>
       <c r="P17" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R17" s="6">
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>407.47500000000002</v>
-      </c>
-      <c r="T17" s="6"/>
+        <v>306.64333333333298</v>
+      </c>
+      <c r="T17" s="6">
+        <v>459.96499999999997</v>
+      </c>
       <c r="U17" s="6">
         <v>-100</v>
       </c>
@@ -1903,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1923,13 +1927,13 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O18" s="6">
-        <v>2922.53</v>
+        <v>3384.39</v>
       </c>
       <c r="P18" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q18" s="6">
         <v>3</v>
@@ -1938,10 +1942,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>243.544166666666</v>
+        <v>260.33769230769201</v>
       </c>
       <c r="T18" s="6">
-        <v>974.17666666666605</v>
+        <v>1128.1299999999901</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1965,7 +1969,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1973,49 +1977,49 @@
         <v>36</v>
       </c>
       <c r="B19" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C19" s="5">
         <v>6</v>
       </c>
       <c r="D19" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="5">
-        <v>2556.0700000000002</v>
+        <v>3003.67</v>
       </c>
       <c r="F19" s="5">
+        <v>5</v>
+      </c>
+      <c r="G19" s="5">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5">
         <v>4</v>
       </c>
-      <c r="G19" s="5">
-        <v>1</v>
-      </c>
-      <c r="H19" s="5">
+      <c r="I19" s="5">
         <v>3</v>
       </c>
-      <c r="I19" s="5">
-        <v>2</v>
-      </c>
       <c r="J19" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="5">
-        <v>639.01750000000004</v>
+        <v>600.73400000000004</v>
       </c>
       <c r="L19" s="5">
-        <v>1278.0350000000001</v>
+        <v>1001.2233333333299</v>
       </c>
       <c r="M19" s="5">
-        <v>-100</v>
+        <v>4.94361897278994</v>
       </c>
       <c r="N19" s="6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O19" s="6">
-        <v>3227.9</v>
+        <v>3907.52</v>
       </c>
       <c r="P19" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q19" s="6">
         <v>5</v>
@@ -2024,13 +2028,13 @@
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>230.56428571428501</v>
+        <v>260.50133333333298</v>
       </c>
       <c r="T19" s="6">
-        <v>645.58000000000004</v>
+        <v>781.50400000000002</v>
       </c>
       <c r="U19" s="6">
-        <v>119.959106539855</v>
+        <v>81.702460895913504</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2057,7 +2061,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2077,25 +2081,25 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="O20" s="6">
-        <v>3289.91</v>
+        <v>3896.05</v>
       </c>
       <c r="P20" s="6">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R20" s="6">
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>253.07</v>
+        <v>216.447222222222</v>
       </c>
       <c r="T20" s="6">
-        <v>469.98714285714198</v>
+        <v>487.00625000000002</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2119,7 +2123,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2139,13 +2143,13 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O21" s="6">
-        <v>8550.75</v>
+        <v>9970.2199999999993</v>
       </c>
       <c r="P21" s="6">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q21" s="6">
         <v>5</v>
@@ -2154,13 +2158,13 @@
         <v>2</v>
       </c>
       <c r="S21" s="6">
-        <v>259.11363636363598</v>
+        <v>293.24176470588202</v>
       </c>
       <c r="T21" s="6">
-        <v>1710.15</v>
+        <v>1994.0439999999901</v>
       </c>
       <c r="U21" s="6">
-        <v>83.171768558313502</v>
+        <v>57.093424217319097</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2181,7 +2185,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2189,49 +2193,49 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
+        <v>22</v>
+      </c>
+      <c r="C22" s="5">
+        <v>3</v>
+      </c>
+      <c r="D22" s="5">
+        <v>19</v>
+      </c>
+      <c r="E22" s="5">
+        <v>3919.04</v>
+      </c>
+      <c r="F22" s="5">
         <v>17</v>
       </c>
-      <c r="C22" s="5">
-        <v>2</v>
-      </c>
-      <c r="D22" s="5">
-        <v>15</v>
-      </c>
-      <c r="E22" s="5">
-        <v>3243.6</v>
-      </c>
-      <c r="F22" s="5">
-        <v>15</v>
-      </c>
       <c r="G22" s="5">
         <v>1</v>
       </c>
       <c r="H22" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I22" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="5">
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>216.24</v>
+        <v>230.53176470588201</v>
       </c>
       <c r="L22" s="5">
-        <v>540.6</v>
+        <v>559.86285714285702</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
       </c>
       <c r="N22" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O22" s="6">
-        <v>2722.8</v>
+        <v>3273.44</v>
       </c>
       <c r="P22" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -2240,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>453.8</v>
+        <v>409.18</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2271,7 +2275,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2291,13 +2295,13 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="O23" s="6">
-        <v>3400.25</v>
+        <v>3975.32</v>
       </c>
       <c r="P23" s="6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q23" s="6">
         <v>2</v>
@@ -2306,13 +2310,13 @@
         <v>1</v>
       </c>
       <c r="S23" s="6">
-        <v>261.55769230769198</v>
+        <v>265.02133333333302</v>
       </c>
       <c r="T23" s="6">
-        <v>1700.125</v>
+        <v>1987.66</v>
       </c>
       <c r="U23" s="6">
-        <v>48.604073229909503</v>
+        <v>27.107000191179502</v>
       </c>
       <c r="V23" s="7">
         <v>37</v>
@@ -2337,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2360,7 +2364,7 @@
         <v>7</v>
       </c>
       <c r="O24" s="6">
-        <v>1778.42</v>
+        <v>2264.44</v>
       </c>
       <c r="P24" s="6">
         <v>5</v>
@@ -2372,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>355.68400000000003</v>
+        <v>452.88799999999998</v>
       </c>
       <c r="T24" s="6">
-        <v>1778.42</v>
+        <v>2264.44</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2399,7 +2403,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2934,7 +2938,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -3037,10 +3041,10 @@
         <v>45253.33</v>
       </c>
       <c r="L5" s="18">
-        <v>11.81</v>
+        <v>11.18</v>
       </c>
       <c r="M5" s="18">
-        <v>20.91</v>
+        <v>20.04</v>
       </c>
       <c r="N5" s="18">
         <v>47.06</v>
@@ -3063,13 +3067,13 @@
         <v>18</v>
       </c>
       <c r="D6" s="18">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E6" s="18">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F6" s="18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" s="18">
         <v>6</v>
@@ -3087,19 +3091,19 @@
         <v>7816</v>
       </c>
       <c r="L6" s="18">
-        <v>4.8600000000000003</v>
+        <v>5.59</v>
       </c>
       <c r="M6" s="18">
-        <v>3.61</v>
+        <v>3.46</v>
       </c>
       <c r="N6" s="18">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="O6" s="18">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="P6" s="18">
-        <v>7.14</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3137,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="18">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="M7" s="18">
         <v>0</v>
@@ -3152,52 +3156,52 @@
     </row>
     <row r="8" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="B8" s="18">
         <v>2026</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D8" s="18">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E8" s="18">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F8" s="18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G8" s="18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H8" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="18">
-        <v>17649</v>
+        <v>0</v>
       </c>
       <c r="J8" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="18">
-        <v>17649</v>
+        <v>0</v>
       </c>
       <c r="L8" s="18">
-        <v>4.8600000000000003</v>
+        <v>0.33</v>
       </c>
       <c r="M8" s="18">
-        <v>8.16</v>
+        <v>0</v>
       </c>
       <c r="N8" s="18">
-        <v>42.86</v>
+        <v>100</v>
       </c>
       <c r="O8" s="18">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="P8" s="18">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3208,94 +3212,96 @@
         <v>2026</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D9" s="18">
         <v>14</v>
       </c>
       <c r="E9" s="18">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H9" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="18">
-        <v>6827</v>
+        <v>17649</v>
       </c>
       <c r="J9" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="18">
-        <v>6827</v>
+        <v>17649</v>
       </c>
       <c r="L9" s="18">
-        <v>4.8600000000000003</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="M9" s="18">
-        <v>3.15</v>
+        <v>7.82</v>
       </c>
       <c r="N9" s="18">
-        <v>28.57</v>
+        <v>42.86</v>
       </c>
       <c r="O9" s="18">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="P9" s="18">
-        <v>7.14</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B10" s="18">
         <v>2026</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D10" s="18">
+        <v>17</v>
+      </c>
+      <c r="E10" s="18">
+        <v>17</v>
+      </c>
+      <c r="F10" s="18">
+        <v>6</v>
+      </c>
+      <c r="G10" s="18">
         <v>3</v>
       </c>
-      <c r="E10" s="18">
-        <v>1</v>
-      </c>
-      <c r="F10" s="18">
-        <v>0</v>
-      </c>
-      <c r="G10" s="18">
-        <v>2</v>
-      </c>
       <c r="H10" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="18">
-        <v>2286</v>
+        <v>13049</v>
       </c>
       <c r="J10" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" s="18">
-        <v>0</v>
+        <v>13049</v>
       </c>
       <c r="L10" s="18">
-        <v>1.04</v>
+        <v>5.59</v>
       </c>
       <c r="M10" s="18">
-        <v>1.06</v>
+        <v>5.78</v>
       </c>
       <c r="N10" s="18">
-        <v>0</v>
-      </c>
-      <c r="O10" s="18"/>
+        <v>35.29</v>
+      </c>
+      <c r="O10" s="18">
+        <v>33.33</v>
+      </c>
       <c r="P10" s="18">
-        <v>33.33</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3306,13 +3312,13 @@
         <v>2026</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D11" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="18">
         <v>0</v>
@@ -3324,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="18">
-        <v>5410</v>
+        <v>2286</v>
       </c>
       <c r="J11" s="18">
         <v>0</v>
@@ -3333,46 +3339,46 @@
         <v>0</v>
       </c>
       <c r="L11" s="18">
-        <v>0.69</v>
+        <v>0.99</v>
       </c>
       <c r="M11" s="18">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="N11" s="18">
         <v>0</v>
       </c>
       <c r="O11" s="18"/>
       <c r="P11" s="18">
-        <v>50</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="18">
         <v>2026</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D12" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="18">
         <v>0</v>
       </c>
       <c r="G12" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="18">
-        <v>0</v>
+        <v>5410</v>
       </c>
       <c r="J12" s="18">
         <v>0</v>
@@ -3381,22 +3387,22 @@
         <v>0</v>
       </c>
       <c r="L12" s="18">
-        <v>0.35</v>
+        <v>0.66</v>
       </c>
       <c r="M12" s="18">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="N12" s="18">
         <v>0</v>
       </c>
       <c r="O12" s="18"/>
       <c r="P12" s="18">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B13" s="18">
         <v>2026</v>
@@ -3408,19 +3414,19 @@
         <v>1</v>
       </c>
       <c r="E13" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="18">
         <v>0</v>
       </c>
       <c r="H13" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="18">
-        <v>160.31</v>
+        <v>0</v>
       </c>
       <c r="J13" s="18">
         <v>0</v>
@@ -3429,19 +3435,17 @@
         <v>0</v>
       </c>
       <c r="L13" s="18">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="M13" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="N13" s="18">
-        <v>100</v>
-      </c>
-      <c r="O13" s="18">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O13" s="18"/>
       <c r="P13" s="18">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3452,7 +3456,7 @@
         <v>2026</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D14" s="18">
         <v>1</v>
@@ -3461,16 +3465,16 @@
         <v>0</v>
       </c>
       <c r="F14" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="18">
         <v>0</v>
       </c>
       <c r="H14" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="18">
-        <v>0</v>
+        <v>160.31</v>
       </c>
       <c r="J14" s="18">
         <v>0</v>
@@ -3479,34 +3483,36 @@
         <v>0</v>
       </c>
       <c r="L14" s="18">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="M14" s="18">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="N14" s="18">
-        <v>0</v>
-      </c>
-      <c r="O14" s="18"/>
+        <v>100</v>
+      </c>
+      <c r="O14" s="18">
+        <v>100</v>
+      </c>
       <c r="P14" s="18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B15" s="18">
         <v>2026</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D15" s="18">
         <v>1</v>
       </c>
       <c r="E15" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="18">
         <v>0</v>
@@ -3527,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="18">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="M15" s="18">
         <v>0</v>
@@ -3548,7 +3554,7 @@
         <v>2026</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D16" s="18">
         <v>1</v>
@@ -3557,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="18">
         <v>0</v>
@@ -3575,42 +3581,40 @@
         <v>0</v>
       </c>
       <c r="L16" s="18">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="M16" s="18">
         <v>0</v>
       </c>
       <c r="N16" s="18">
-        <v>100</v>
-      </c>
-      <c r="O16" s="18">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O16" s="18"/>
       <c r="P16" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B17" s="18">
         <v>2026</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D17" s="18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E17" s="18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F17" s="18">
         <v>1</v>
       </c>
       <c r="G17" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="18">
         <v>0</v>
@@ -3625,13 +3629,13 @@
         <v>0</v>
       </c>
       <c r="L17" s="18">
-        <v>2.4300000000000002</v>
+        <v>0.33</v>
       </c>
       <c r="M17" s="18">
         <v>0</v>
       </c>
       <c r="N17" s="18">
-        <v>14.29</v>
+        <v>100</v>
       </c>
       <c r="O17" s="18">
         <v>0</v>
@@ -3648,19 +3652,19 @@
         <v>2026</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D18" s="18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E18" s="18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F18" s="18">
         <v>1</v>
       </c>
       <c r="G18" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="18">
         <v>0</v>
@@ -3675,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="L18" s="18">
-        <v>0.69</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="M18" s="18">
         <v>0</v>
       </c>
       <c r="N18" s="18">
-        <v>50</v>
+        <v>14.29</v>
       </c>
       <c r="O18" s="18">
         <v>0</v>
@@ -3692,52 +3696,52 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B19" s="18">
         <v>2026</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D19" s="10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E19" s="10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F19" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G19" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" s="10">
-        <v>10468</v>
+        <v>0</v>
       </c>
       <c r="J19" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="10">
-        <v>5234</v>
+        <v>0</v>
       </c>
       <c r="L19" s="10">
-        <v>3.12</v>
+        <v>0.66</v>
       </c>
       <c r="M19" s="10">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="N19" s="10">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="O19" s="10">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P19" s="10">
-        <v>22.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
@@ -3748,94 +3752,96 @@
         <v>2026</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D20" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E20" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G20" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="10">
-        <v>7855.68</v>
+        <v>10468</v>
       </c>
       <c r="J20" s="10">
         <v>1</v>
       </c>
       <c r="K20" s="10">
-        <v>7855.68</v>
+        <v>5234</v>
       </c>
       <c r="L20" s="10">
-        <v>2.4300000000000002</v>
+        <v>3.29</v>
       </c>
       <c r="M20" s="10">
-        <v>3.63</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="N20" s="10">
-        <v>42.86</v>
+        <v>60</v>
       </c>
       <c r="O20" s="10">
         <v>33.33</v>
       </c>
       <c r="P20" s="10">
-        <v>14.29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B21" s="18">
         <v>2026</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E21" s="10">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="F21" s="10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G21" s="10">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H21" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" s="10">
-        <v>36031</v>
+        <v>11007.84</v>
       </c>
       <c r="J21" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21" s="10">
-        <v>36031</v>
+        <v>11007.84</v>
       </c>
       <c r="L21" s="10">
-        <v>24.31</v>
+        <v>2.96</v>
       </c>
       <c r="M21" s="10">
-        <v>16.649999999999999</v>
+        <v>4.88</v>
       </c>
       <c r="N21" s="10">
-        <v>0</v>
-      </c>
-      <c r="O21" s="10"/>
+        <v>44.44</v>
+      </c>
+      <c r="O21" s="10">
+        <v>50</v>
+      </c>
       <c r="P21" s="10">
-        <v>5.71</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -3846,94 +3852,92 @@
         <v>2026</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D22" s="10">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E22" s="10">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="F22" s="10">
         <v>0</v>
       </c>
       <c r="G22" s="10">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H22" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="10">
-        <v>20397</v>
+        <v>36031</v>
       </c>
       <c r="J22" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="10">
-        <v>20397</v>
+        <v>36031</v>
       </c>
       <c r="L22" s="10">
-        <v>12.85</v>
+        <v>23.03</v>
       </c>
       <c r="M22" s="10">
-        <v>9.43</v>
+        <v>15.96</v>
       </c>
       <c r="N22" s="10">
         <v>0</v>
       </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10">
-        <v>8.11</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" s="18">
         <v>2026</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="E23" s="10">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="F23" s="10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G23" s="10">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H23" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I23" s="10">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="J23" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K23" s="10">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="L23" s="10">
-        <v>2.78</v>
+        <v>13.82</v>
       </c>
       <c r="M23" s="10">
-        <v>0</v>
+        <v>9.0299999999999994</v>
       </c>
       <c r="N23" s="10">
-        <v>50</v>
-      </c>
-      <c r="O23" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O23" s="10"/>
       <c r="P23" s="10">
-        <v>0</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -3944,51 +3948,51 @@
         <v>2026</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D24" s="10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" s="10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G24" s="10">
         <v>2</v>
       </c>
       <c r="H24" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I24" s="10">
-        <v>15374</v>
+        <v>0</v>
       </c>
       <c r="J24" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" s="10">
-        <v>15374</v>
+        <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="M24" s="10">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="10">
-        <v>22.22</v>
+        <v>50</v>
       </c>
       <c r="O24" s="10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P24" s="10">
-        <v>22.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B25" s="18">
         <v>2026</v>
@@ -3997,91 +4001,91 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E25" s="10">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F25" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25" s="10">
-        <v>0</v>
+        <v>15374</v>
       </c>
       <c r="J25" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" s="10">
-        <v>0</v>
+        <v>15374</v>
       </c>
       <c r="L25" s="10">
-        <v>0.35</v>
+        <v>2.96</v>
       </c>
       <c r="M25" s="10">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="N25" s="10">
-        <v>0</v>
-      </c>
-      <c r="O25" s="10"/>
+        <v>22.22</v>
+      </c>
+      <c r="O25" s="10">
+        <v>100</v>
+      </c>
       <c r="P25" s="10">
-        <v>0</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B26" s="18">
         <v>2026</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D26" s="10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E26" s="10">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F26" s="10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G26" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="10">
-        <v>7816</v>
+        <v>0</v>
       </c>
       <c r="J26" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="10">
-        <v>7816</v>
+        <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>3.47</v>
+        <v>0.33</v>
       </c>
       <c r="M26" s="10">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N26" s="10">
-        <v>30</v>
-      </c>
-      <c r="O26" s="10">
-        <v>33.33</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O26" s="10"/>
       <c r="P26" s="10">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
@@ -4092,96 +4096,96 @@
         <v>2026</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D27" s="10">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E27" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F27" s="10">
         <v>3</v>
       </c>
       <c r="G27" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I27" s="10">
-        <v>17865</v>
+        <v>7816</v>
       </c>
       <c r="J27" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" s="10">
-        <v>17865</v>
+        <v>7816</v>
       </c>
       <c r="L27" s="10">
-        <v>2.08</v>
+        <v>3.29</v>
       </c>
       <c r="M27" s="10">
-        <v>8.26</v>
+        <v>3.46</v>
       </c>
       <c r="N27" s="10">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="O27" s="10">
-        <v>66.67</v>
+        <v>33.33</v>
       </c>
       <c r="P27" s="10">
-        <v>33.33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B28" s="18">
         <v>2026</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D28" s="10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E28" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="10">
         <v>3</v>
       </c>
       <c r="G28" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" s="10">
-        <v>0</v>
+        <v>17865</v>
       </c>
       <c r="J28" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" s="10">
-        <v>0</v>
+        <v>17865</v>
       </c>
       <c r="L28" s="10">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="M28" s="10">
-        <v>0</v>
+        <v>7.91</v>
       </c>
       <c r="N28" s="10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O28" s="10">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="P28" s="10">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
@@ -4192,96 +4196,96 @@
         <v>2026</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D29" s="10">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E29" s="10">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F29" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G29" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H29" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="10">
-        <v>8117.12</v>
+        <v>0</v>
       </c>
       <c r="J29" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" s="10">
-        <v>8117.12</v>
+        <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>4.51</v>
+        <v>0.99</v>
       </c>
       <c r="M29" s="10">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N29" s="10">
-        <v>53.85</v>
+        <v>100</v>
       </c>
       <c r="O29" s="10">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="P29" s="10">
-        <v>15.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B30" s="18">
         <v>2026</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D30" s="10">
+        <v>14</v>
+      </c>
+      <c r="E30" s="10">
+        <v>14</v>
+      </c>
+      <c r="F30" s="10">
         <v>9</v>
       </c>
-      <c r="E30" s="10">
-        <v>7</v>
-      </c>
-      <c r="F30" s="10">
-        <v>1</v>
-      </c>
       <c r="G30" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H30" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="10">
-        <v>7072</v>
+        <v>8117.12</v>
       </c>
       <c r="J30" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K30" s="10">
-        <v>0</v>
+        <v>8117.12</v>
       </c>
       <c r="L30" s="10">
-        <v>3.12</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="M30" s="10">
-        <v>3.27</v>
+        <v>3.6</v>
       </c>
       <c r="N30" s="10">
-        <v>11.11</v>
+        <v>64.290000000000006</v>
       </c>
       <c r="O30" s="10">
-        <v>100</v>
+        <v>22.22</v>
       </c>
       <c r="P30" s="10">
-        <v>11.11</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -4292,25 +4296,25 @@
         <v>2026</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D31" s="10">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E31" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F31" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="10">
-        <v>0</v>
+        <v>7072</v>
       </c>
       <c r="J31" s="10">
         <v>0</v>
@@ -4319,39 +4323,39 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="M31" s="10">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N31" s="10">
+        <v>11.11</v>
+      </c>
+      <c r="O31" s="10">
         <v>100</v>
       </c>
-      <c r="O31" s="10">
-        <v>0</v>
-      </c>
       <c r="P31" s="10">
-        <v>0</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B32" s="18">
         <v>2026</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D32" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32" s="10">
         <v>0</v>
@@ -4369,15 +4373,17 @@
         <v>0</v>
       </c>
       <c r="L32" s="10">
-        <v>0.69</v>
+        <v>0.99</v>
       </c>
       <c r="M32" s="10">
         <v>0</v>
       </c>
       <c r="N32" s="10">
-        <v>0</v>
-      </c>
-      <c r="O32" s="10"/>
+        <v>100</v>
+      </c>
+      <c r="O32" s="10">
+        <v>0</v>
+      </c>
       <c r="P32" s="10">
         <v>0</v>
       </c>
@@ -4390,16 +4396,16 @@
         <v>2026</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D33" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="10">
         <v>0</v>
@@ -4417,42 +4423,40 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>0.35</v>
+        <v>0.66</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
       </c>
       <c r="N33" s="10">
-        <v>100</v>
-      </c>
-      <c r="O33" s="10">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O33" s="10"/>
       <c r="P33" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B34" s="10">
         <v>2026</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D34" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="10">
         <v>1</v>
       </c>
       <c r="G34" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="10">
         <v>0</v>
@@ -4467,13 +4471,13 @@
         <v>0</v>
       </c>
       <c r="L34" s="10">
-        <v>0.69</v>
+        <v>0.33</v>
       </c>
       <c r="M34" s="10">
         <v>0</v>
       </c>
       <c r="N34" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="O34" s="10">
         <v>0</v>
@@ -4490,45 +4494,95 @@
         <v>2026</v>
       </c>
       <c r="C35" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" s="10">
+        <v>2</v>
+      </c>
+      <c r="E35" s="10">
+        <v>2</v>
+      </c>
+      <c r="F35" s="10">
+        <v>1</v>
+      </c>
+      <c r="G35" s="10">
+        <v>1</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10">
+        <v>0</v>
+      </c>
+      <c r="J35" s="10">
+        <v>0</v>
+      </c>
+      <c r="K35" s="10">
+        <v>0</v>
+      </c>
+      <c r="L35" s="10">
+        <v>0.66</v>
+      </c>
+      <c r="M35" s="10">
+        <v>0</v>
+      </c>
+      <c r="N35" s="10">
+        <v>50</v>
+      </c>
+      <c r="O35" s="10">
+        <v>0</v>
+      </c>
+      <c r="P35" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36">
+        <v>2026</v>
+      </c>
+      <c r="C36" t="s">
         <v>18</v>
       </c>
-      <c r="D35" s="10">
-        <v>2</v>
-      </c>
-      <c r="E35" s="10">
-        <v>2</v>
-      </c>
-      <c r="F35" s="10">
-        <v>2</v>
-      </c>
-      <c r="G35" s="10">
-        <v>0</v>
-      </c>
-      <c r="H35" s="10">
-        <v>0</v>
-      </c>
-      <c r="I35" s="10">
-        <v>0</v>
-      </c>
-      <c r="J35" s="10">
-        <v>0</v>
-      </c>
-      <c r="K35" s="10">
-        <v>0</v>
-      </c>
-      <c r="L35" s="10">
-        <v>0.69</v>
-      </c>
-      <c r="M35" s="10">
-        <v>0</v>
-      </c>
-      <c r="N35" s="10">
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0.66</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
         <v>100</v>
       </c>
-      <c r="O35" s="10">
-        <v>0</v>
-      </c>
-      <c r="P35" s="10">
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
         <v>0</v>
       </c>
     </row>
@@ -4717,7 +4771,7 @@
         <v>129</v>
       </c>
       <c r="G8" s="5">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H8" s="5">
         <v>34</v>
@@ -5163,16 +5217,16 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>2099</v>
+        <v>2453</v>
       </c>
       <c r="E21" s="10">
-        <v>5026.1499999999996</v>
+        <v>5957.33</v>
       </c>
       <c r="F21" s="10">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G21" s="10">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H21" s="10">
         <v>14</v>
@@ -5184,7 +5238,7 @@
         <v>59345</v>
       </c>
       <c r="K21" s="10">
-        <v>10.81</v>
+        <v>8.9600000000000009</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5758,19 +5812,19 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="E38" s="10">
-        <v>1791.14</v>
+        <v>2023.85</v>
       </c>
       <c r="F38" s="10">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G38" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H38" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="10">
         <v>0</v>
@@ -6187,7 +6241,7 @@
         <v>35</v>
       </c>
       <c r="G50" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="10">
         <v>12</v>
@@ -6353,16 +6407,16 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>756</v>
+        <v>887</v>
       </c>
       <c r="E55" s="10">
-        <v>5837.84</v>
+        <v>6871.47</v>
       </c>
       <c r="F55" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G55" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H55" s="10">
         <v>5</v>
@@ -6374,7 +6428,7 @@
         <v>15671.68</v>
       </c>
       <c r="K55" s="10">
-        <v>1.68</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6527,7 +6581,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H60" s="10">
         <v>4</v>
@@ -7348,19 +7402,19 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>398</v>
+        <v>486</v>
       </c>
       <c r="E84" s="10">
-        <v>2966.27</v>
+        <v>3606.08</v>
       </c>
       <c r="F84" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G84" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H84" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I84" s="10">
         <v>0</v>
@@ -7497,7 +7551,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -7900,7 +7954,7 @@
         <v>17</v>
       </c>
       <c r="H100" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I100" s="10">
         <v>5</v>
@@ -8075,7 +8129,7 @@
         <v>17</v>
       </c>
       <c r="H105" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I105" s="10">
         <v>3</v>
@@ -8238,28 +8292,28 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>599</v>
+        <v>735</v>
       </c>
       <c r="E110" s="10">
-        <v>6357.19</v>
+        <v>7504.9</v>
       </c>
       <c r="F110" s="10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G110" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H110" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I110" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J110" s="10">
-        <v>14645.12</v>
+        <v>20867.12</v>
       </c>
       <c r="K110" s="10">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9753,10 +9807,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="E155" s="10">
-        <v>1213.92</v>
+        <v>1345.21</v>
       </c>
       <c r="F155" s="10">
         <v>2</v>
@@ -9797,7 +9851,7 @@
         <v>30</v>
       </c>
       <c r="G156" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H156" s="10">
         <v>2</v>
@@ -10839,28 +10893,28 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>355</v>
+        <v>441</v>
       </c>
       <c r="E186" s="10">
-        <v>2556.0700000000002</v>
+        <v>3003.67</v>
       </c>
       <c r="F186" s="10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G186" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H186" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I186" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J186" s="10">
-        <v>0</v>
+        <v>3152.16</v>
       </c>
       <c r="K186" s="10">
-        <v>-1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
@@ -12414,19 +12468,19 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>411</v>
+        <v>500</v>
       </c>
       <c r="E231" s="10">
-        <v>3243.6</v>
+        <v>3919.04</v>
       </c>
       <c r="F231" s="10">
+        <v>22</v>
+      </c>
+      <c r="G231" s="10">
         <v>17</v>
       </c>
-      <c r="G231" s="10">
-        <v>14</v>
-      </c>
       <c r="H231" s="10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I231" s="10">
         <v>0</v>
@@ -15822,34 +15876,34 @@
         <v>2026</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E8" s="18">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F8" s="18">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G8" s="18">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H8" s="18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I8" s="18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J8" s="18">
-        <v>45253.33</v>
+        <v>0</v>
       </c>
       <c r="K8" s="18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L8" s="18">
-        <v>45253.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -15860,34 +15914,34 @@
         <v>2026</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>107</v>
       </c>
       <c r="E9" s="18">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F9" s="18">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G9" s="18">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H9" s="18">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I9" s="18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J9" s="18">
-        <v>7816</v>
+        <v>45253.33</v>
       </c>
       <c r="K9" s="18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L9" s="18">
-        <v>7816</v>
+        <v>45253.33</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -15898,34 +15952,34 @@
         <v>2026</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E10" s="18">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F10" s="18">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G10" s="18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="18">
-        <v>0</v>
+        <v>7816</v>
       </c>
       <c r="K10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="18">
-        <v>0</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -15936,22 +15990,22 @@
         <v>2026</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D11" s="17" t="s">
         <v>36</v>
       </c>
       <c r="E11" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="18">
         <v>0</v>
@@ -15968,16 +16022,16 @@
     </row>
     <row r="12" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B12" s="18">
         <v>2026</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="E12" s="18">
         <v>1</v>
@@ -15986,10 +16040,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="18">
         <v>0</v>
@@ -16006,7 +16060,7 @@
     </row>
     <row r="13" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="B13" s="18">
         <v>2026</v>
@@ -16015,36 +16069,36 @@
         <v>111</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E13" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F13" s="18">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G13" s="18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="18">
-        <v>8991</v>
+        <v>0</v>
       </c>
       <c r="K13" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="18">
-        <v>8991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="17" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="B14" s="18">
         <v>2026</v>
@@ -16053,7 +16107,7 @@
         <v>18</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E14" s="18">
         <v>1</v>
@@ -16062,10 +16116,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="18">
         <v>0</v>
@@ -16091,31 +16145,31 @@
         <v>111</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E15" s="18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F15" s="18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G15" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="18">
-        <v>0</v>
+        <v>8991</v>
       </c>
       <c r="K15" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="18">
-        <v>0</v>
+        <v>8991</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -16129,31 +16183,31 @@
         <v>18</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E16" s="18">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F16" s="18">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G16" s="18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" s="18">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="18">
-        <v>6827</v>
+        <v>0</v>
       </c>
       <c r="K16" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="18">
-        <v>6827</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -16167,31 +16221,31 @@
         <v>111</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E17" s="18">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F17" s="18">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G17" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="18">
-        <v>8658</v>
+        <v>0</v>
       </c>
       <c r="K17" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="18">
-        <v>8658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -16205,36 +16259,36 @@
         <v>18</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E18" s="18">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F18" s="18">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G18" s="18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H18" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="18">
-        <v>0</v>
+        <v>13049</v>
       </c>
       <c r="K18" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="18">
-        <v>0</v>
+        <v>13049</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B19" s="18">
         <v>2026</v>
@@ -16243,36 +16297,36 @@
         <v>111</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E19" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19" s="18">
         <v>1</v>
       </c>
       <c r="J19" s="18">
-        <v>2286</v>
+        <v>8658</v>
       </c>
       <c r="K19" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="18">
-        <v>0</v>
+        <v>8658</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B20" s="18">
         <v>2026</v>
@@ -16281,25 +16335,25 @@
         <v>18</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E20" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="18">
-        <v>5410</v>
+        <v>0</v>
       </c>
       <c r="K20" s="18">
         <v>0</v>
@@ -16316,13 +16370,13 @@
         <v>2026</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="18">
         <v>0</v>
@@ -16331,13 +16385,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="18">
-        <v>0</v>
+        <v>2286</v>
       </c>
       <c r="K21" s="18">
         <v>0</v>
@@ -16354,28 +16408,28 @@
         <v>2026</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E22" s="18">
         <v>1</v>
       </c>
       <c r="F22" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="18">
         <v>0</v>
       </c>
       <c r="H22" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="18">
-        <v>0</v>
+        <v>5410</v>
       </c>
       <c r="K22" s="18">
         <v>0</v>
@@ -16386,28 +16440,28 @@
     </row>
     <row r="23" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="18">
         <v>2026</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="E23" s="18">
         <v>1</v>
       </c>
       <c r="F23" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="18">
         <v>0</v>
       </c>
       <c r="H23" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="18">
         <v>0</v>
@@ -16424,7 +16478,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="B24" s="18">
         <v>2026</v>
@@ -16433,25 +16487,25 @@
         <v>111</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>160.31</v>
+        <v>0</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -16462,13 +16516,13 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B25" s="18">
         <v>2026</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D25" t="s">
         <v>13</v>
@@ -16477,7 +16531,7 @@
         <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -16500,7 +16554,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B26" s="18">
         <v>2026</v>
@@ -16515,19 +16569,19 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>160.31</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -16538,7 +16592,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B27" s="18">
         <v>2026</v>
@@ -16547,16 +16601,16 @@
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -16576,7 +16630,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" s="18">
         <v>2026</v>
@@ -16588,16 +16642,16 @@
         <v>13</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -16614,28 +16668,28 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B29" s="18">
         <v>2026</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -16658,16 +16712,16 @@
         <v>2026</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -16696,22 +16750,22 @@
         <v>2026</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -16734,10 +16788,10 @@
         <v>2026</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -16746,10 +16800,10 @@
         <v>1</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -16766,66 +16820,66 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B33" s="18">
         <v>2026</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33">
-        <v>5234</v>
+        <v>0</v>
       </c>
       <c r="K33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>5234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B34" s="18">
         <v>2026</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -16851,31 +16905,31 @@
         <v>111</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>5234</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>5234</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
@@ -16889,7 +16943,7 @@
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -16904,16 +16958,16 @@
         <v>1</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36">
-        <v>7855.68</v>
+        <v>0</v>
       </c>
       <c r="K36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36">
-        <v>7855.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
@@ -16927,25 +16981,25 @@
         <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>5234</v>
+        <v>0</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -16965,7 +17019,7 @@
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -16980,21 +17034,21 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>7855.68</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>7855.68</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B39" s="18">
         <v>2026</v>
@@ -17003,36 +17057,36 @@
         <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E39">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>36031</v>
+        <v>5234</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L39">
-        <v>36031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B40" s="18">
         <v>2026</v>
@@ -17041,31 +17095,31 @@
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E40">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F40">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40">
-        <v>20397</v>
+        <v>3152.16</v>
       </c>
       <c r="K40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L40">
-        <v>20397</v>
+        <v>3152.16</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
@@ -17079,31 +17133,31 @@
         <v>111</v>
       </c>
       <c r="D41" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>36031</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>36031</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -17117,31 +17171,31 @@
         <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>20397</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>20397</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -17155,7 +17209,7 @@
         <v>111</v>
       </c>
       <c r="D43" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -17193,7 +17247,7 @@
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -17231,19 +17285,19 @@
         <v>111</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -17269,7 +17323,7 @@
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E46">
         <v>2</v>
@@ -17307,19 +17361,19 @@
         <v>111</v>
       </c>
       <c r="D47" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E47">
         <v>3</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -17345,19 +17399,19 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -17374,7 +17428,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B49" s="18">
         <v>2026</v>
@@ -17383,19 +17437,19 @@
         <v>111</v>
       </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E49">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -17412,7 +17466,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B50" s="18">
         <v>2026</v>
@@ -17421,31 +17475,31 @@
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E50">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J50">
-        <v>15374</v>
+        <v>0</v>
       </c>
       <c r="K50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50">
-        <v>15374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
@@ -17456,22 +17510,22 @@
         <v>2026</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -17488,7 +17542,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B52" s="18">
         <v>2026</v>
@@ -17497,57 +17551,57 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>15374</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>15374</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B53" s="18">
         <v>2026</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -17564,7 +17618,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B54" s="18">
         <v>2026</v>
@@ -17573,31 +17627,31 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E54">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54">
-        <v>17865</v>
+        <v>0</v>
       </c>
       <c r="K54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54">
-        <v>17865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -17611,19 +17665,19 @@
         <v>111</v>
       </c>
       <c r="D55" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -17646,34 +17700,34 @@
         <v>2026</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>17865</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>17865</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -17687,16 +17741,16 @@
         <v>111</v>
       </c>
       <c r="D57" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -17725,7 +17779,7 @@
         <v>111</v>
       </c>
       <c r="D58" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -17734,10 +17788,10 @@
         <v>1</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -17760,16 +17814,16 @@
         <v>2026</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D59" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -17801,7 +17855,7 @@
         <v>111</v>
       </c>
       <c r="D60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -17810,48 +17864,48 @@
         <v>1</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60">
-        <v>7816</v>
+        <v>0</v>
       </c>
       <c r="K60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60">
-        <v>7816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B61" s="18">
         <v>2026</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -17868,40 +17922,40 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B62" s="18">
         <v>2026</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D62" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I62">
         <v>1</v>
       </c>
       <c r="J62">
-        <v>299</v>
+        <v>7816</v>
       </c>
       <c r="K62">
         <v>1</v>
       </c>
       <c r="L62">
-        <v>299</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
@@ -17912,10 +17966,10 @@
         <v>2026</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D63" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E63">
         <v>2</v>
@@ -17924,22 +17978,22 @@
         <v>2</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63">
-        <v>7818.1200000000008</v>
+        <v>0</v>
       </c>
       <c r="K63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63">
-        <v>7818.1200000000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
@@ -17950,34 +18004,34 @@
         <v>2026</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
@@ -17991,36 +18045,36 @@
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E65">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B66" s="18">
         <v>2026</v>
@@ -18029,25 +18083,25 @@
         <v>111</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66">
         <v>0</v>
       </c>
       <c r="I66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66">
-        <v>7072</v>
+        <v>0</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -18058,28 +18112,28 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B67" s="18">
         <v>2026</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="E67">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F67">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -18102,28 +18156,28 @@
         <v>2026</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D68" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>7072</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -18134,7 +18188,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B69" s="18">
         <v>2026</v>
@@ -18143,19 +18197,19 @@
         <v>111</v>
       </c>
       <c r="D69" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F69">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -18172,7 +18226,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B70" s="18">
         <v>2026</v>
@@ -18181,16 +18235,16 @@
         <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -18219,7 +18273,7 @@
         <v>111</v>
       </c>
       <c r="D71" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -18248,13 +18302,13 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B72" s="18">
         <v>2026</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
@@ -18269,7 +18323,7 @@
         <v>1</v>
       </c>
       <c r="H72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -18286,25 +18340,25 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B73" s="18">
         <v>2026</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D73" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -18333,40 +18387,108 @@
         <v>111</v>
       </c>
       <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+      <c r="F74">
+        <v>1</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>103</v>
+      </c>
+      <c r="B75" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>103</v>
+      </c>
+      <c r="B76" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D76" t="s">
         <v>39</v>
       </c>
-      <c r="E74">
-        <v>1</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
-      <c r="H74">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B75" s="18"/>
-      <c r="C75" s="19"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B76" s="18"/>
-      <c r="C76" s="19"/>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B77" s="18"/>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A66798D-E716-4BCE-9095-9289D772F083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D41539-8955-48C7-808A-A5AA4A7495D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1013,49 +1013,49 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="C6" s="5">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D6" s="5">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="E6" s="5">
-        <v>34231.550000000003</v>
+        <v>35823.019999999997</v>
       </c>
       <c r="F6" s="5">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G6" s="5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H6" s="5">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="I6" s="5">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J6" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K6" s="5">
-        <v>267.43398437500002</v>
+        <v>261.48189781021898</v>
       </c>
       <c r="L6" s="5">
-        <v>855.78875000000005</v>
+        <v>778.76130434782601</v>
       </c>
       <c r="M6" s="5">
-        <v>189.31193591876399</v>
+        <v>180.18006298743001</v>
       </c>
       <c r="N6" s="6">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="O6" s="6">
-        <v>67122.909999999902</v>
+        <v>69626.44</v>
       </c>
       <c r="P6" s="6">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="Q6" s="6">
         <v>69</v>
@@ -1064,13 +1064,13 @@
         <v>19</v>
       </c>
       <c r="S6" s="6">
-        <v>200.966796407185</v>
+        <v>201.23248554913201</v>
       </c>
       <c r="T6" s="6">
-        <v>972.79579710144901</v>
+        <v>1009.07884057971</v>
       </c>
       <c r="U6" s="6">
-        <v>110.990971636956</v>
+        <v>104.38683925244401</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1105,49 +1105,49 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C7" s="5">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D7" s="5">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E7" s="5">
-        <v>5957.33</v>
+        <v>6222.22</v>
       </c>
       <c r="F7" s="5">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G7" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="5">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I7" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7" s="5">
-        <v>93.083281249999999</v>
+        <v>91.503235294117601</v>
       </c>
       <c r="L7" s="5">
-        <v>458.25615384615298</v>
+        <v>444.444285714285</v>
       </c>
       <c r="M7" s="5">
-        <v>896.16774628902499</v>
+        <v>875.18249113660397</v>
       </c>
       <c r="N7" s="6">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="O7" s="6">
-        <v>16311.04</v>
+        <v>16908.099999999999</v>
       </c>
       <c r="P7" s="6">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="Q7" s="6">
         <v>19</v>
@@ -1156,13 +1156,13 @@
         <v>11</v>
       </c>
       <c r="S7" s="6">
-        <v>100.067730061349</v>
+        <v>100.643452380952</v>
       </c>
       <c r="T7" s="6">
-        <v>858.47578947368402</v>
+        <v>889.9</v>
       </c>
       <c r="U7" s="6">
-        <v>427.47556256375998</v>
+        <v>412.89470727047899</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1189,7 +1189,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1206,7 +1206,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="5">
-        <v>2023.85</v>
+        <v>2146.91</v>
       </c>
       <c r="F8" s="5">
         <v>4</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>505.96249999999998</v>
+        <v>536.72749999999996</v>
       </c>
       <c r="L8" s="5">
-        <v>2023.85</v>
+        <v>2146.91</v>
       </c>
       <c r="M8" s="5">
         <v>-100</v>
@@ -1236,7 +1236,7 @@
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>2336.71</v>
+        <v>2373.48</v>
       </c>
       <c r="P8" s="6">
         <v>5</v>
@@ -1248,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>467.34199999999998</v>
+        <v>474.69600000000003</v>
       </c>
       <c r="T8" s="6">
-        <v>1168.355</v>
+        <v>1186.74</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1281,7 +1281,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1289,49 +1289,49 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="5">
         <v>22</v>
       </c>
       <c r="E9" s="5">
-        <v>6871.47</v>
+        <v>7136.79</v>
       </c>
       <c r="F9" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="5">
         <v>13</v>
       </c>
       <c r="I9" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" s="5">
         <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>490.819285714285</v>
+        <v>475.786</v>
       </c>
       <c r="L9" s="5">
-        <v>1374.2940000000001</v>
+        <v>1189.4649999999999</v>
       </c>
       <c r="M9" s="5">
-        <v>128.068812059137</v>
+        <v>119.590039779788</v>
       </c>
       <c r="N9" s="6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O9" s="6">
-        <v>7029.13</v>
+        <v>7343.53</v>
       </c>
       <c r="P9" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q9" s="6">
         <v>7</v>
@@ -1340,13 +1340,13 @@
         <v>2</v>
       </c>
       <c r="S9" s="6">
-        <v>369.95421052631502</v>
+        <v>367.17649999999998</v>
       </c>
       <c r="T9" s="6">
-        <v>1004.1614285714199</v>
+        <v>1049.0757142857101</v>
       </c>
       <c r="U9" s="6">
-        <v>67.545627979564998</v>
+        <v>60.372463924025602</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1367,7 +1367,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1390,7 +1390,7 @@
         <v>4</v>
       </c>
       <c r="O10" s="6">
-        <v>2291.2399999999998</v>
+        <v>2358.0500000000002</v>
       </c>
       <c r="P10" s="6">
         <v>9</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="S10" s="6">
-        <v>254.58222222222199</v>
+        <v>262.00555555555502</v>
       </c>
       <c r="T10" s="6">
-        <v>458.24799999999902</v>
+        <v>471.61</v>
       </c>
       <c r="U10" s="6">
         <v>-100</v>
@@ -1423,7 +1423,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1440,7 +1440,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="5">
-        <v>3606.08</v>
+        <v>3764.8</v>
       </c>
       <c r="F11" s="5">
         <v>6</v>
@@ -1458,10 +1458,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>601.01333333333298</v>
+        <v>627.46666666666601</v>
       </c>
       <c r="L11" s="5">
-        <v>901.52</v>
+        <v>941.2</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
@@ -1470,7 +1470,7 @@
         <v>3</v>
       </c>
       <c r="O11" s="6">
-        <v>1393.6</v>
+        <v>1459.33</v>
       </c>
       <c r="P11" s="6">
         <v>5</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>278.719999999999</v>
+        <v>291.86599999999999</v>
       </c>
       <c r="T11" s="6">
-        <v>1393.6</v>
+        <v>1459.33</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1515,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1538,7 +1538,7 @@
         <v>2</v>
       </c>
       <c r="O12" s="6">
-        <v>349.61</v>
+        <v>362.04</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1559,7 +1559,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1567,49 +1567,49 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C13" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E13" s="5">
-        <v>7504.9</v>
+        <v>7824.12</v>
       </c>
       <c r="F13" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G13" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" s="5">
         <v>12</v>
       </c>
       <c r="I13" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" s="5">
         <v>3</v>
       </c>
       <c r="K13" s="5">
-        <v>441.46470588235201</v>
+        <v>434.67333333333301</v>
       </c>
       <c r="L13" s="5">
-        <v>1250.81666666666</v>
+        <v>1117.7314285714201</v>
       </c>
       <c r="M13" s="5">
-        <v>178.04660954842799</v>
+        <v>166.70245343885301</v>
       </c>
       <c r="N13" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O13" s="6">
-        <v>4001.61</v>
+        <v>4256.5</v>
       </c>
       <c r="P13" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q13" s="6">
         <v>9</v>
@@ -1618,13 +1618,13 @@
         <v>2</v>
       </c>
       <c r="S13" s="6">
-        <v>210.61105263157799</v>
+        <v>202.69047619047601</v>
       </c>
       <c r="T13" s="6">
-        <v>444.62333333333299</v>
+        <v>472.944444444444</v>
       </c>
       <c r="U13" s="6">
-        <v>299.68912512713598</v>
+        <v>275.75472806296199</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1651,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1674,7 +1674,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>709.73</v>
+        <v>715.01</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>354.86500000000001</v>
+        <v>357.505</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1711,7 +1711,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1755,7 +1755,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1778,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="O16" s="6">
-        <v>1106.19</v>
+        <v>1149.8900000000001</v>
       </c>
       <c r="P16" s="6">
         <v>1</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>1106.19</v>
+        <v>1149.8900000000001</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="6">
@@ -1815,7 +1815,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>1345.21</v>
+        <v>1406.05</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1850,10 +1850,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1345.21</v>
+        <v>1406.05</v>
       </c>
       <c r="L17" s="5">
-        <v>1345.21</v>
+        <v>1406.05</v>
       </c>
       <c r="M17" s="5">
         <v>-100</v>
@@ -1862,7 +1862,7 @@
         <v>2</v>
       </c>
       <c r="O17" s="6">
-        <v>919.93</v>
+        <v>925.57</v>
       </c>
       <c r="P17" s="6">
         <v>3</v>
@@ -1874,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>306.64333333333298</v>
+        <v>308.52333333333303</v>
       </c>
       <c r="T17" s="6">
-        <v>459.96499999999997</v>
+        <v>462.78500000000003</v>
       </c>
       <c r="U17" s="6">
         <v>-100</v>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1930,10 +1930,10 @@
         <v>17</v>
       </c>
       <c r="O18" s="6">
-        <v>3384.39</v>
+        <v>3458.43</v>
       </c>
       <c r="P18" s="6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q18" s="6">
         <v>3</v>
@@ -1942,10 +1942,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>260.33769230769201</v>
+        <v>247.030714285714</v>
       </c>
       <c r="T18" s="6">
-        <v>1128.1299999999901</v>
+        <v>1152.81</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1969,7 +1969,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1986,7 +1986,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="5">
-        <v>3003.67</v>
+        <v>3130.87</v>
       </c>
       <c r="F19" s="5">
         <v>5</v>
@@ -2004,19 +2004,19 @@
         <v>1</v>
       </c>
       <c r="K19" s="5">
-        <v>600.73400000000004</v>
+        <v>626.17399999999998</v>
       </c>
       <c r="L19" s="5">
-        <v>1001.2233333333299</v>
+        <v>1043.62333333333</v>
       </c>
       <c r="M19" s="5">
-        <v>4.94361897278994</v>
+        <v>0.68000268296032595</v>
       </c>
       <c r="N19" s="6">
         <v>26</v>
       </c>
       <c r="O19" s="6">
-        <v>3907.52</v>
+        <v>4076.81</v>
       </c>
       <c r="P19" s="6">
         <v>15</v>
@@ -2028,13 +2028,13 @@
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>260.50133333333298</v>
+        <v>271.78733333333298</v>
       </c>
       <c r="T19" s="6">
-        <v>781.50400000000002</v>
+        <v>815.36199999999997</v>
       </c>
       <c r="U19" s="6">
-        <v>81.702460895913504</v>
+        <v>74.157245493412702</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2061,7 +2061,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2084,7 +2084,7 @@
         <v>17</v>
       </c>
       <c r="O20" s="6">
-        <v>3896.05</v>
+        <v>4020.96</v>
       </c>
       <c r="P20" s="6">
         <v>18</v>
@@ -2096,10 +2096,10 @@
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>216.447222222222</v>
+        <v>223.386666666666</v>
       </c>
       <c r="T20" s="6">
-        <v>487.00625000000002</v>
+        <v>502.62</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2123,7 +2123,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2143,13 +2143,13 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O21" s="6">
-        <v>9970.2199999999993</v>
+        <v>10272.89</v>
       </c>
       <c r="P21" s="6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q21" s="6">
         <v>5</v>
@@ -2158,13 +2158,13 @@
         <v>2</v>
       </c>
       <c r="S21" s="6">
-        <v>293.24176470588202</v>
+        <v>285.35805555555498</v>
       </c>
       <c r="T21" s="6">
-        <v>1994.0439999999901</v>
+        <v>2054.578</v>
       </c>
       <c r="U21" s="6">
-        <v>57.093424217319097</v>
+        <v>52.464983076816701</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2185,7 +2185,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2193,37 +2193,37 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C22" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="5">
+        <v>24</v>
+      </c>
+      <c r="E22" s="5">
+        <v>4191.26</v>
+      </c>
+      <c r="F22" s="5">
+        <v>20</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
         <v>19</v>
       </c>
-      <c r="E22" s="5">
-        <v>3919.04</v>
-      </c>
-      <c r="F22" s="5">
-        <v>17</v>
-      </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
-        <v>16</v>
-      </c>
       <c r="I22" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J22" s="5">
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>230.53176470588201</v>
+        <v>209.56299999999999</v>
       </c>
       <c r="L22" s="5">
-        <v>559.86285714285702</v>
+        <v>419.12599999999998</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2232,7 +2232,7 @@
         <v>6</v>
       </c>
       <c r="O22" s="6">
-        <v>3273.44</v>
+        <v>3440.36</v>
       </c>
       <c r="P22" s="6">
         <v>8</v>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>409.18</v>
+        <v>430.04500000000002</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2275,7 +2275,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2298,10 +2298,10 @@
         <v>30</v>
       </c>
       <c r="O23" s="6">
-        <v>3975.32</v>
+        <v>4131.46</v>
       </c>
       <c r="P23" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="6">
         <v>2</v>
@@ -2310,13 +2310,13 @@
         <v>1</v>
       </c>
       <c r="S23" s="6">
-        <v>265.02133333333302</v>
+        <v>258.21625</v>
       </c>
       <c r="T23" s="6">
-        <v>1987.66</v>
+        <v>2065.73</v>
       </c>
       <c r="U23" s="6">
-        <v>27.107000191179502</v>
+        <v>22.3032535713767</v>
       </c>
       <c r="V23" s="7">
         <v>37</v>
@@ -2341,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2364,7 +2364,7 @@
         <v>7</v>
       </c>
       <c r="O24" s="6">
-        <v>2264.44</v>
+        <v>2371.29</v>
       </c>
       <c r="P24" s="6">
         <v>5</v>
@@ -2376,10 +2376,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>452.88799999999998</v>
+        <v>474.25799999999998</v>
       </c>
       <c r="T24" s="6">
-        <v>2264.44</v>
+        <v>2371.29</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2403,7 +2403,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3041,10 +3041,10 @@
         <v>45253.33</v>
       </c>
       <c r="L5" s="18">
-        <v>11.18</v>
+        <v>10.97</v>
       </c>
       <c r="M5" s="18">
-        <v>20.04</v>
+        <v>20.72</v>
       </c>
       <c r="N5" s="18">
         <v>47.06</v>
@@ -3067,13 +3067,13 @@
         <v>18</v>
       </c>
       <c r="D6" s="18">
+        <v>18</v>
+      </c>
+      <c r="E6" s="18">
         <v>17</v>
       </c>
-      <c r="E6" s="18">
-        <v>16</v>
-      </c>
       <c r="F6" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="18">
         <v>6</v>
@@ -3091,19 +3091,19 @@
         <v>7816</v>
       </c>
       <c r="L6" s="18">
-        <v>5.59</v>
+        <v>5.81</v>
       </c>
       <c r="M6" s="18">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="N6" s="18">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="O6" s="18">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="P6" s="18">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3141,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="18">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M7" s="18">
         <v>0</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="18">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M8" s="18">
         <v>0</v>
@@ -3227,31 +3227,31 @@
         <v>6</v>
       </c>
       <c r="H9" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" s="18">
-        <v>17649</v>
+        <v>8991</v>
       </c>
       <c r="J9" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="18">
-        <v>17649</v>
+        <v>8991</v>
       </c>
       <c r="L9" s="18">
-        <v>4.6100000000000003</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="M9" s="18">
-        <v>7.82</v>
+        <v>4.12</v>
       </c>
       <c r="N9" s="18">
         <v>42.86</v>
       </c>
       <c r="O9" s="18">
-        <v>33.33</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="P9" s="18">
-        <v>14.29</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3265,13 +3265,13 @@
         <v>18</v>
       </c>
       <c r="D10" s="18">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E10" s="18">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F10" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="18">
         <v>3</v>
@@ -3289,19 +3289,19 @@
         <v>13049</v>
       </c>
       <c r="L10" s="18">
-        <v>5.59</v>
+        <v>6.13</v>
       </c>
       <c r="M10" s="18">
-        <v>5.78</v>
+        <v>5.97</v>
       </c>
       <c r="N10" s="18">
-        <v>35.29</v>
+        <v>36.840000000000003</v>
       </c>
       <c r="O10" s="18">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="P10" s="18">
-        <v>11.76</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3339,10 +3339,10 @@
         <v>0</v>
       </c>
       <c r="L11" s="18">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="M11" s="18">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N11" s="18">
         <v>0</v>
@@ -3363,7 +3363,7 @@
         <v>18</v>
       </c>
       <c r="D12" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="18">
         <v>0</v>
@@ -3372,13 +3372,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="18">
-        <v>5410</v>
+        <v>6743</v>
       </c>
       <c r="J12" s="18">
         <v>0</v>
@@ -3387,17 +3387,17 @@
         <v>0</v>
       </c>
       <c r="L12" s="18">
-        <v>0.66</v>
+        <v>0.97</v>
       </c>
       <c r="M12" s="18">
-        <v>2.4</v>
+        <v>3.09</v>
       </c>
       <c r="N12" s="18">
         <v>0</v>
       </c>
       <c r="O12" s="18"/>
       <c r="P12" s="18">
-        <v>50</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="18">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M13" s="18">
         <v>0</v>
@@ -3483,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="18">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M14" s="18">
         <v>7.0000000000000007E-2</v>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="18">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M15" s="18">
         <v>0</v>
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="18">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M16" s="18">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="18">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M17" s="18">
         <v>0</v>
@@ -3679,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="18">
-        <v>2.2999999999999998</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="M18" s="18">
         <v>0</v>
@@ -3729,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="10">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="M19" s="10">
         <v>0</v>
@@ -3755,13 +3755,13 @@
         <v>111</v>
       </c>
       <c r="D20" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="10">
         <v>4</v>
@@ -3779,19 +3779,19 @@
         <v>5234</v>
       </c>
       <c r="L20" s="10">
-        <v>3.29</v>
+        <v>2.9</v>
       </c>
       <c r="M20" s="10">
-        <v>4.6399999999999997</v>
+        <v>4.79</v>
       </c>
       <c r="N20" s="10">
-        <v>60</v>
+        <v>55.56</v>
       </c>
       <c r="O20" s="10">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="P20" s="10">
-        <v>20</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -3829,10 +3829,10 @@
         <v>11007.84</v>
       </c>
       <c r="L21" s="10">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="M21" s="10">
-        <v>4.88</v>
+        <v>5.04</v>
       </c>
       <c r="N21" s="10">
         <v>44.44</v>
@@ -3879,10 +3879,10 @@
         <v>36031</v>
       </c>
       <c r="L22" s="10">
-        <v>23.03</v>
+        <v>22.58</v>
       </c>
       <c r="M22" s="10">
-        <v>15.96</v>
+        <v>16.489999999999998</v>
       </c>
       <c r="N22" s="10">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
+        <v>43</v>
+      </c>
+      <c r="E23" s="10">
         <v>42</v>
-      </c>
-      <c r="E23" s="10">
-        <v>41</v>
       </c>
       <c r="F23" s="10">
         <v>0</v>
@@ -3927,17 +3927,17 @@
         <v>20397</v>
       </c>
       <c r="L23" s="10">
-        <v>13.82</v>
+        <v>13.87</v>
       </c>
       <c r="M23" s="10">
-        <v>9.0299999999999994</v>
+        <v>9.34</v>
       </c>
       <c r="N23" s="10">
         <v>0</v>
       </c>
       <c r="O23" s="10"/>
       <c r="P23" s="10">
-        <v>7.14</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -4007,7 +4007,7 @@
         <v>9</v>
       </c>
       <c r="F25" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="10">
         <v>2</v>
@@ -4025,16 +4025,16 @@
         <v>15374</v>
       </c>
       <c r="L25" s="10">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="M25" s="10">
-        <v>6.81</v>
+        <v>7.04</v>
       </c>
       <c r="N25" s="10">
-        <v>22.22</v>
+        <v>33.33</v>
       </c>
       <c r="O25" s="10">
-        <v>100</v>
+        <v>66.67</v>
       </c>
       <c r="P25" s="10">
         <v>22.22</v>
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M26" s="10">
         <v>0</v>
@@ -4123,10 +4123,10 @@
         <v>7816</v>
       </c>
       <c r="L27" s="10">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="M27" s="10">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="N27" s="10">
         <v>30</v>
@@ -4173,10 +4173,10 @@
         <v>17865</v>
       </c>
       <c r="L28" s="10">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="M28" s="10">
-        <v>7.91</v>
+        <v>8.18</v>
       </c>
       <c r="N28" s="10">
         <v>50</v>
@@ -4223,7 +4223,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
@@ -4249,16 +4249,16 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E30" s="10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F30" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="10">
         <v>2</v>
@@ -4273,19 +4273,19 @@
         <v>8117.12</v>
       </c>
       <c r="L30" s="10">
-        <v>4.6100000000000003</v>
+        <v>5.16</v>
       </c>
       <c r="M30" s="10">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="N30" s="10">
-        <v>64.290000000000006</v>
+        <v>62.5</v>
       </c>
       <c r="O30" s="10">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="P30" s="10">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -4323,10 +4323,10 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="M31" s="10">
-        <v>3.13</v>
+        <v>3.24</v>
       </c>
       <c r="N31" s="10">
         <v>11.11</v>
@@ -4358,7 +4358,7 @@
         <v>3</v>
       </c>
       <c r="G32" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="10">
         <v>0</v>
@@ -4373,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="10">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="M32" s="10">
         <v>0</v>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="10">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="M34" s="10">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="10">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="M35" s="10">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -4771,7 +4771,7 @@
         <v>129</v>
       </c>
       <c r="G8" s="5">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H8" s="5">
         <v>34</v>
@@ -5162,13 +5162,13 @@
         <v>23</v>
       </c>
       <c r="I19" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J19" s="5">
-        <v>86665.64</v>
+        <v>91957.64</v>
       </c>
       <c r="K19" s="5">
-        <v>11.02</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -5217,28 +5217,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>2453</v>
+        <v>2539</v>
       </c>
       <c r="E21" s="10">
-        <v>5957.33</v>
+        <v>6222.22</v>
       </c>
       <c r="F21" s="10">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G21" s="10">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H21" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I21" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J21" s="10">
-        <v>59345</v>
+        <v>60678</v>
       </c>
       <c r="K21" s="10">
-        <v>8.9600000000000009</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5812,10 +5812,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="E38" s="10">
-        <v>2023.85</v>
+        <v>2146.91</v>
       </c>
       <c r="F38" s="10">
         <v>9</v>
@@ -6407,19 +6407,19 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>887</v>
+        <v>921</v>
       </c>
       <c r="E55" s="10">
-        <v>6871.47</v>
+        <v>7136.79</v>
       </c>
       <c r="F55" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G55" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H55" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I55" s="10">
         <v>2</v>
@@ -6428,7 +6428,7 @@
         <v>15671.68</v>
       </c>
       <c r="K55" s="10">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6581,7 +6581,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H60" s="10">
         <v>4</v>
@@ -7402,10 +7402,10 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="E84" s="10">
-        <v>3606.08</v>
+        <v>3764.8</v>
       </c>
       <c r="F84" s="10">
         <v>11</v>
@@ -7551,7 +7551,7 @@
         <v>1</v>
       </c>
       <c r="G88" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" s="10">
         <v>0</v>
@@ -8292,19 +8292,19 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>735</v>
+        <v>772</v>
       </c>
       <c r="E110" s="10">
-        <v>7504.9</v>
+        <v>7824.12</v>
       </c>
       <c r="F110" s="10">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G110" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H110" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I110" s="10">
         <v>3</v>
@@ -8313,7 +8313,7 @@
         <v>20867.12</v>
       </c>
       <c r="K110" s="10">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9807,10 +9807,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E155" s="10">
-        <v>1345.21</v>
+        <v>1406.05</v>
       </c>
       <c r="F155" s="10">
         <v>2</v>
@@ -9851,7 +9851,7 @@
         <v>30</v>
       </c>
       <c r="G156" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H156" s="10">
         <v>2</v>
@@ -10893,10 +10893,10 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="E186" s="10">
-        <v>3003.67</v>
+        <v>3130.87</v>
       </c>
       <c r="F186" s="10">
         <v>15</v>
@@ -10914,7 +10914,7 @@
         <v>3152.16</v>
       </c>
       <c r="K186" s="10">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
@@ -12448,13 +12448,13 @@
         <v>2</v>
       </c>
       <c r="I230" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J230" s="10">
-        <v>8658</v>
+        <v>0</v>
       </c>
       <c r="K230" s="10">
-        <v>0.62</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.3">
@@ -12468,19 +12468,19 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>500</v>
+        <v>528</v>
       </c>
       <c r="E231" s="10">
-        <v>3919.04</v>
+        <v>4191.26</v>
       </c>
       <c r="F231" s="10">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G231" s="10">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H231" s="10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I231" s="10">
         <v>0</v>
@@ -15958,13 +15958,13 @@
         <v>107</v>
       </c>
       <c r="E10" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="18">
         <v>3</v>
@@ -16262,13 +16262,13 @@
         <v>29</v>
       </c>
       <c r="E18" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" s="18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="18">
         <v>3</v>
@@ -16312,16 +16312,16 @@
         <v>1</v>
       </c>
       <c r="I19" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="18">
-        <v>8658</v>
+        <v>0</v>
       </c>
       <c r="K19" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="18">
-        <v>8658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -16338,10 +16338,10 @@
         <v>39</v>
       </c>
       <c r="E20" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="18">
         <v>2</v>
@@ -16414,7 +16414,7 @@
         <v>13</v>
       </c>
       <c r="E22" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="18">
         <v>0</v>
@@ -16423,13 +16423,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="18">
-        <v>5410</v>
+        <v>6743</v>
       </c>
       <c r="K22" s="18">
         <v>0</v>
@@ -16908,13 +16908,13 @@
         <v>13</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -17174,10 +17174,10 @@
         <v>13</v>
       </c>
       <c r="E42">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F42">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -17326,10 +17326,10 @@
         <v>107</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -17560,7 +17560,7 @@
         <v>8</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H52">
         <v>2</v>
@@ -18010,16 +18010,16 @@
         <v>13</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G64">
         <v>2</v>
       </c>
       <c r="H64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64">
         <v>1</v>
@@ -18124,13 +18124,13 @@
         <v>39</v>
       </c>
       <c r="E67">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F67">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H67">
         <v>2</v>
@@ -18247,7 +18247,7 @@
         <v>3</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70">
         <v>0</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D41539-8955-48C7-808A-A5AA4A7495D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45CB4DA2-848E-4DD9-B49F-7F68E65574F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -511,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -564,6 +564,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1013,64 +1016,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="C6" s="5">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D6" s="5">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E6" s="5">
-        <v>35823.019999999997</v>
+        <v>37445.93</v>
       </c>
       <c r="F6" s="5">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G6" s="5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H6" s="5">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I6" s="5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J6" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K6" s="5">
-        <v>261.48189781021898</v>
+        <v>258.24779310344798</v>
       </c>
       <c r="L6" s="5">
-        <v>778.76130434782601</v>
+        <v>780.12354166666603</v>
       </c>
       <c r="M6" s="5">
-        <v>180.18006298743001</v>
+        <v>182.16941066759401</v>
       </c>
       <c r="N6" s="6">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="O6" s="6">
-        <v>69626.44</v>
+        <v>72656.889999999898</v>
       </c>
       <c r="P6" s="6">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="Q6" s="6">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="R6" s="6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="S6" s="6">
-        <v>201.23248554913201</v>
+        <v>199.60684065934001</v>
       </c>
       <c r="T6" s="6">
-        <v>1009.07884057971</v>
+        <v>995.29986301369797</v>
       </c>
       <c r="U6" s="6">
-        <v>104.38683925244401</v>
+        <v>138.65370510628799</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1085,7 +1088,7 @@
         <v>77</v>
       </c>
       <c r="Z6" s="7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AA6" s="8">
         <v>45500</v>
@@ -1097,7 +1100,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1105,64 +1108,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="C7" s="5">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D7" s="5">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E7" s="5">
-        <v>6222.22</v>
+        <v>6514.17</v>
       </c>
       <c r="F7" s="5">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G7" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H7" s="5">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I7" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" s="5">
         <v>10</v>
       </c>
       <c r="K7" s="5">
-        <v>91.503235294117601</v>
+        <v>88.029324324324307</v>
       </c>
       <c r="L7" s="5">
-        <v>444.444285714285</v>
+        <v>434.27800000000002</v>
       </c>
       <c r="M7" s="5">
-        <v>875.18249113660397</v>
+        <v>831.47707229009904</v>
       </c>
       <c r="N7" s="6">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="O7" s="6">
-        <v>16908.099999999999</v>
+        <v>17824.419999999998</v>
       </c>
       <c r="P7" s="6">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="Q7" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R7" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S7" s="6">
-        <v>100.643452380952</v>
+        <v>100.702937853107</v>
       </c>
       <c r="T7" s="6">
-        <v>889.9</v>
+        <v>848.781904761904</v>
       </c>
       <c r="U7" s="6">
-        <v>412.89470727047899</v>
+        <v>463.43392940695901</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1177,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="Z7" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA7" s="8">
         <v>10000</v>
@@ -1189,7 +1192,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1206,37 +1209,37 @@
         <v>3</v>
       </c>
       <c r="E8" s="5">
-        <v>2146.91</v>
+        <v>2279.7199999999998</v>
       </c>
       <c r="F8" s="5">
+        <v>5</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
         <v>4</v>
       </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5">
-        <v>3</v>
-      </c>
       <c r="I8" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="5">
-        <v>536.72749999999996</v>
+        <v>455.94400000000002</v>
       </c>
       <c r="L8" s="5">
-        <v>2146.91</v>
+        <v>1139.8599999999999</v>
       </c>
       <c r="M8" s="5">
-        <v>-100</v>
+        <v>132.13377081395899</v>
       </c>
       <c r="N8" s="6">
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>2373.48</v>
+        <v>2414.48</v>
       </c>
       <c r="P8" s="6">
         <v>5</v>
@@ -1248,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>474.69600000000003</v>
+        <v>482.89600000000002</v>
       </c>
       <c r="T8" s="6">
-        <v>1186.74</v>
+        <v>1207.24</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1281,7 +1284,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1289,25 +1292,25 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E9" s="5">
-        <v>7136.79</v>
+        <v>7460.19</v>
       </c>
       <c r="F9" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
       </c>
       <c r="H9" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="5">
         <v>6</v>
@@ -1316,22 +1319,22 @@
         <v>2</v>
       </c>
       <c r="K9" s="5">
-        <v>475.786</v>
+        <v>466.26187499999997</v>
       </c>
       <c r="L9" s="5">
-        <v>1189.4649999999999</v>
+        <v>1243.365</v>
       </c>
       <c r="M9" s="5">
-        <v>119.590039779788</v>
+        <v>110.070789081779</v>
       </c>
       <c r="N9" s="6">
         <v>28</v>
       </c>
       <c r="O9" s="6">
-        <v>7343.53</v>
+        <v>7640.18</v>
       </c>
       <c r="P9" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q9" s="6">
         <v>7</v>
@@ -1340,13 +1343,13 @@
         <v>2</v>
       </c>
       <c r="S9" s="6">
-        <v>367.17649999999998</v>
+        <v>363.818095238095</v>
       </c>
       <c r="T9" s="6">
-        <v>1049.0757142857101</v>
+        <v>1091.4542857142801</v>
       </c>
       <c r="U9" s="6">
-        <v>60.372463924025602</v>
+        <v>54.1455829574695</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1367,7 +1370,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1390,7 +1393,7 @@
         <v>4</v>
       </c>
       <c r="O10" s="6">
-        <v>2358.0500000000002</v>
+        <v>2409.84</v>
       </c>
       <c r="P10" s="6">
         <v>9</v>
@@ -1399,16 +1402,16 @@
         <v>5</v>
       </c>
       <c r="R10" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="6">
-        <v>262.00555555555502</v>
+        <v>267.76</v>
       </c>
       <c r="T10" s="6">
-        <v>471.61</v>
+        <v>481.96800000000002</v>
       </c>
       <c r="U10" s="6">
-        <v>-100</v>
+        <v>190.18524051389301</v>
       </c>
       <c r="V10" s="7">
         <v>5</v>
@@ -1423,7 +1426,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1431,16 +1434,16 @@
         <v>106</v>
       </c>
       <c r="B11" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5">
         <v>9</v>
       </c>
       <c r="E11" s="5">
-        <v>3764.8</v>
+        <v>3927.6</v>
       </c>
       <c r="F11" s="5">
         <v>6</v>
@@ -1458,19 +1461,19 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>627.46666666666601</v>
+        <v>654.6</v>
       </c>
       <c r="L11" s="5">
-        <v>941.2</v>
+        <v>981.9</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
       </c>
       <c r="N11" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" s="6">
-        <v>1459.33</v>
+        <v>1527.86</v>
       </c>
       <c r="P11" s="6">
         <v>5</v>
@@ -1482,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>291.86599999999999</v>
+        <v>305.572</v>
       </c>
       <c r="T11" s="6">
-        <v>1459.33</v>
+        <v>1527.86</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1515,7 +1518,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1538,7 +1541,7 @@
         <v>2</v>
       </c>
       <c r="O12" s="6">
-        <v>362.04</v>
+        <v>382.3</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1559,7 +1562,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1576,7 +1579,7 @@
         <v>24</v>
       </c>
       <c r="E13" s="5">
-        <v>7824.12</v>
+        <v>8155.05</v>
       </c>
       <c r="F13" s="5">
         <v>18</v>
@@ -1594,37 +1597,37 @@
         <v>3</v>
       </c>
       <c r="K13" s="5">
-        <v>434.67333333333301</v>
+        <v>453.058333333333</v>
       </c>
       <c r="L13" s="5">
-        <v>1117.7314285714201</v>
+        <v>1165.00714285714</v>
       </c>
       <c r="M13" s="5">
-        <v>166.70245343885301</v>
+        <v>155.87973096424901</v>
       </c>
       <c r="N13" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O13" s="6">
-        <v>4256.5</v>
+        <v>4341.9799999999996</v>
       </c>
       <c r="P13" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q13" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R13" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S13" s="6">
-        <v>202.69047619047601</v>
+        <v>197.362727272727</v>
       </c>
       <c r="T13" s="6">
-        <v>472.944444444444</v>
+        <v>434.19799999999998</v>
       </c>
       <c r="U13" s="6">
-        <v>275.75472806296199</v>
+        <v>507.64904490577999</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1639,7 +1642,7 @@
         <v>12</v>
       </c>
       <c r="Z13" s="7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA13" s="8">
         <v>8000</v>
@@ -1651,7 +1654,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1674,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>715.01</v>
+        <v>732.74</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1686,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>357.505</v>
+        <v>366.37</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1711,7 +1714,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1755,7 +1758,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1778,7 +1781,7 @@
         <v>5</v>
       </c>
       <c r="O16" s="6">
-        <v>1149.8900000000001</v>
+        <v>1198.54</v>
       </c>
       <c r="P16" s="6">
         <v>1</v>
@@ -1790,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>1149.8900000000001</v>
+        <v>1198.54</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="6">
@@ -1815,7 +1818,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1832,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="5">
-        <v>1406.05</v>
+        <v>1458</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1850,10 +1853,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1406.05</v>
+        <v>1458</v>
       </c>
       <c r="L17" s="5">
-        <v>1406.05</v>
+        <v>1458</v>
       </c>
       <c r="M17" s="5">
         <v>-100</v>
@@ -1862,7 +1865,7 @@
         <v>2</v>
       </c>
       <c r="O17" s="6">
-        <v>925.57</v>
+        <v>934.59</v>
       </c>
       <c r="P17" s="6">
         <v>3</v>
@@ -1874,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>308.52333333333303</v>
+        <v>311.52999999999997</v>
       </c>
       <c r="T17" s="6">
-        <v>462.78500000000003</v>
+        <v>467.29500000000002</v>
       </c>
       <c r="U17" s="6">
         <v>-100</v>
@@ -1907,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1927,13 +1930,13 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O18" s="6">
-        <v>3458.43</v>
+        <v>3651.26</v>
       </c>
       <c r="P18" s="6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q18" s="6">
         <v>3</v>
@@ -1942,10 +1945,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>247.030714285714</v>
+        <v>243.417333333333</v>
       </c>
       <c r="T18" s="6">
-        <v>1152.81</v>
+        <v>1217.08666666666</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1969,7 +1972,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1986,7 +1989,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="5">
-        <v>3130.87</v>
+        <v>3257.1</v>
       </c>
       <c r="F19" s="5">
         <v>5</v>
@@ -2004,22 +2007,22 @@
         <v>1</v>
       </c>
       <c r="K19" s="5">
-        <v>626.17399999999998</v>
+        <v>651.41999999999996</v>
       </c>
       <c r="L19" s="5">
-        <v>1043.62333333333</v>
+        <v>1085.7</v>
       </c>
       <c r="M19" s="5">
-        <v>0.68000268296032595</v>
+        <v>-3.2218844984802399</v>
       </c>
       <c r="N19" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O19" s="6">
-        <v>4076.81</v>
+        <v>4220.88</v>
       </c>
       <c r="P19" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="6">
         <v>5</v>
@@ -2028,13 +2031,13 @@
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>271.78733333333298</v>
+        <v>263.80500000000001</v>
       </c>
       <c r="T19" s="6">
-        <v>815.36199999999997</v>
+        <v>844.17600000000004</v>
       </c>
       <c r="U19" s="6">
-        <v>74.157245493412702</v>
+        <v>68.212789750004703</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2061,7 +2064,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2081,25 +2084,25 @@
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O20" s="6">
-        <v>4020.96</v>
+        <v>4210.1099999999997</v>
       </c>
       <c r="P20" s="6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q20" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R20" s="6">
         <v>0</v>
       </c>
       <c r="S20" s="6">
-        <v>223.386666666666</v>
+        <v>221.584736842105</v>
       </c>
       <c r="T20" s="6">
-        <v>502.62</v>
+        <v>467.789999999999</v>
       </c>
       <c r="U20" s="6">
         <v>-100</v>
@@ -2123,7 +2126,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2143,13 +2146,13 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O21" s="6">
-        <v>10272.89</v>
+        <v>10747.25</v>
       </c>
       <c r="P21" s="6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q21" s="6">
         <v>5</v>
@@ -2158,13 +2161,13 @@
         <v>2</v>
       </c>
       <c r="S21" s="6">
-        <v>285.35805555555498</v>
+        <v>290.46621621621603</v>
       </c>
       <c r="T21" s="6">
-        <v>2054.578</v>
+        <v>2149.4499999999998</v>
       </c>
       <c r="U21" s="6">
-        <v>52.464983076816701</v>
+        <v>45.735513736072001</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2185,7 +2188,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2202,7 +2205,7 @@
         <v>24</v>
       </c>
       <c r="E22" s="5">
-        <v>4191.26</v>
+        <v>4394.1000000000004</v>
       </c>
       <c r="F22" s="5">
         <v>20</v>
@@ -2220,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>209.56299999999999</v>
+        <v>219.70500000000001</v>
       </c>
       <c r="L22" s="5">
-        <v>419.12599999999998</v>
+        <v>439.41</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2232,10 +2235,10 @@
         <v>6</v>
       </c>
       <c r="O22" s="6">
-        <v>3440.36</v>
+        <v>3630.26</v>
       </c>
       <c r="P22" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -2244,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>430.04500000000002</v>
+        <v>363.02600000000001</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2275,7 +2278,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2295,13 +2298,13 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="O23" s="6">
-        <v>4131.46</v>
+        <v>4310.54</v>
       </c>
       <c r="P23" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q23" s="6">
         <v>2</v>
@@ -2310,13 +2313,13 @@
         <v>1</v>
       </c>
       <c r="S23" s="6">
-        <v>258.21625</v>
+        <v>253.56117647058801</v>
       </c>
       <c r="T23" s="6">
-        <v>2065.73</v>
+        <v>2155.27</v>
       </c>
       <c r="U23" s="6">
-        <v>22.3032535713767</v>
+        <v>17.222204178594701</v>
       </c>
       <c r="V23" s="7">
         <v>37</v>
@@ -2341,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2364,7 +2367,7 @@
         <v>7</v>
       </c>
       <c r="O24" s="6">
-        <v>2371.29</v>
+        <v>2476.92</v>
       </c>
       <c r="P24" s="6">
         <v>5</v>
@@ -2376,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>474.25799999999998</v>
+        <v>495.38400000000001</v>
       </c>
       <c r="T24" s="6">
-        <v>2371.29</v>
+        <v>2476.92</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2403,7 +2406,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2941,18 +2944,19 @@
   <dimension ref="A1:P36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="3" width="8" customWidth="1"/>
-    <col min="4" max="16" width="13" customWidth="1"/>
+    <col min="1" max="1" width="22" style="10" customWidth="1"/>
+    <col min="2" max="3" width="8" style="10" customWidth="1"/>
+    <col min="4" max="16" width="13" style="10" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="22" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="21" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3041,10 +3045,10 @@
         <v>45253.33</v>
       </c>
       <c r="L5" s="18">
-        <v>10.97</v>
+        <v>10.62</v>
       </c>
       <c r="M5" s="18">
-        <v>20.72</v>
+        <v>19.690000000000001</v>
       </c>
       <c r="N5" s="18">
         <v>47.06</v>
@@ -3067,43 +3071,43 @@
         <v>18</v>
       </c>
       <c r="D6" s="18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E6" s="18">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" s="18">
-        <v>7816</v>
+        <v>13108</v>
       </c>
       <c r="J6" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="18">
-        <v>7816</v>
+        <v>13108</v>
       </c>
       <c r="L6" s="18">
-        <v>5.81</v>
+        <v>6.25</v>
       </c>
       <c r="M6" s="18">
-        <v>3.58</v>
+        <v>5.7</v>
       </c>
       <c r="N6" s="18">
         <v>50</v>
       </c>
       <c r="O6" s="18">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="P6" s="18">
-        <v>5.56</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3141,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="18">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="M7" s="18">
         <v>0</v>
@@ -3189,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="18">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="M8" s="18">
         <v>0</v>
@@ -3227,31 +3231,31 @@
         <v>6</v>
       </c>
       <c r="H9" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="18">
-        <v>8991</v>
+        <v>15101</v>
       </c>
       <c r="J9" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" s="18">
-        <v>8991</v>
+        <v>15101</v>
       </c>
       <c r="L9" s="18">
-        <v>4.5199999999999996</v>
+        <v>4.38</v>
       </c>
       <c r="M9" s="18">
-        <v>4.12</v>
+        <v>6.57</v>
       </c>
       <c r="N9" s="18">
         <v>42.86</v>
       </c>
       <c r="O9" s="18">
-        <v>16.670000000000002</v>
+        <v>33.33</v>
       </c>
       <c r="P9" s="18">
-        <v>7.14</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3274,7 +3278,7 @@
         <v>7</v>
       </c>
       <c r="G10" s="18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" s="18">
         <v>2</v>
@@ -3289,10 +3293,10 @@
         <v>13049</v>
       </c>
       <c r="L10" s="18">
-        <v>6.13</v>
+        <v>5.94</v>
       </c>
       <c r="M10" s="18">
-        <v>5.97</v>
+        <v>5.68</v>
       </c>
       <c r="N10" s="18">
         <v>36.840000000000003</v>
@@ -3339,10 +3343,10 @@
         <v>0</v>
       </c>
       <c r="L11" s="18">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="M11" s="18">
-        <v>1.05</v>
+        <v>0.99</v>
       </c>
       <c r="N11" s="18">
         <v>0</v>
@@ -3387,10 +3391,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="18">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="M12" s="18">
-        <v>3.09</v>
+        <v>2.93</v>
       </c>
       <c r="N12" s="18">
         <v>0</v>
@@ -3435,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="18">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="M13" s="18">
         <v>0</v>
@@ -3483,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="18">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="M14" s="18">
         <v>7.0000000000000007E-2</v>
@@ -3533,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="18">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="M15" s="18">
         <v>0</v>
@@ -3581,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="18">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="M16" s="18">
         <v>0</v>
@@ -3629,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="18">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="M17" s="18">
         <v>0</v>
@@ -3679,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="18">
-        <v>2.2599999999999998</v>
+        <v>2.19</v>
       </c>
       <c r="M18" s="18">
         <v>0</v>
@@ -3729,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="10">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="M19" s="10">
         <v>0</v>
@@ -3755,13 +3759,13 @@
         <v>111</v>
       </c>
       <c r="D20" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="10">
         <v>4</v>
@@ -3779,19 +3783,19 @@
         <v>5234</v>
       </c>
       <c r="L20" s="10">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="M20" s="10">
-        <v>4.79</v>
+        <v>4.55</v>
       </c>
       <c r="N20" s="10">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="O20" s="10">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="P20" s="10">
-        <v>22.22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -3805,10 +3809,10 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E21" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" s="10">
         <v>4</v>
@@ -3829,19 +3833,19 @@
         <v>11007.84</v>
       </c>
       <c r="L21" s="10">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="M21" s="10">
-        <v>5.04</v>
+        <v>4.79</v>
       </c>
       <c r="N21" s="10">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="O21" s="10">
         <v>50</v>
       </c>
       <c r="P21" s="10">
-        <v>22.22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -3864,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H22" s="10">
         <v>4</v>
@@ -3879,15 +3883,14 @@
         <v>36031</v>
       </c>
       <c r="L22" s="10">
-        <v>22.58</v>
+        <v>21.88</v>
       </c>
       <c r="M22" s="10">
-        <v>16.489999999999998</v>
+        <v>15.68</v>
       </c>
       <c r="N22" s="10">
         <v>0</v>
       </c>
-      <c r="O22" s="10"/>
       <c r="P22" s="10">
         <v>5.71</v>
       </c>
@@ -3903,16 +3906,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E23" s="10">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F23" s="10">
         <v>0</v>
       </c>
       <c r="G23" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H23" s="10">
         <v>3</v>
@@ -3927,17 +3930,16 @@
         <v>20397</v>
       </c>
       <c r="L23" s="10">
-        <v>13.87</v>
+        <v>14.37</v>
       </c>
       <c r="M23" s="10">
-        <v>9.34</v>
+        <v>8.8699999999999992</v>
       </c>
       <c r="N23" s="10">
         <v>0</v>
       </c>
-      <c r="O23" s="10"/>
       <c r="P23" s="10">
-        <v>6.98</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -3975,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -4001,16 +4003,16 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E25" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F25" s="10">
+        <v>4</v>
+      </c>
+      <c r="G25" s="10">
         <v>3</v>
-      </c>
-      <c r="G25" s="10">
-        <v>2</v>
       </c>
       <c r="H25" s="10">
         <v>2</v>
@@ -4025,19 +4027,19 @@
         <v>15374</v>
       </c>
       <c r="L25" s="10">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="M25" s="10">
-        <v>7.04</v>
+        <v>6.69</v>
       </c>
       <c r="N25" s="10">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="O25" s="10">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="P25" s="10">
-        <v>22.22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
@@ -4075,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="M26" s="10">
         <v>0</v>
@@ -4083,7 +4085,6 @@
       <c r="N26" s="10">
         <v>0</v>
       </c>
-      <c r="O26" s="10"/>
       <c r="P26" s="10">
         <v>0</v>
       </c>
@@ -4123,10 +4124,10 @@
         <v>7816</v>
       </c>
       <c r="L27" s="10">
-        <v>3.23</v>
+        <v>3.12</v>
       </c>
       <c r="M27" s="10">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="N27" s="10">
         <v>30</v>
@@ -4173,10 +4174,10 @@
         <v>17865</v>
       </c>
       <c r="L28" s="10">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="M28" s="10">
-        <v>8.18</v>
+        <v>7.77</v>
       </c>
       <c r="N28" s="10">
         <v>50</v>
@@ -4223,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
@@ -4249,16 +4250,16 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E30" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F30" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H30" s="10">
         <v>2</v>
@@ -4273,19 +4274,19 @@
         <v>8117.12</v>
       </c>
       <c r="L30" s="10">
-        <v>5.16</v>
+        <v>5.31</v>
       </c>
       <c r="M30" s="10">
-        <v>3.72</v>
+        <v>3.53</v>
       </c>
       <c r="N30" s="10">
-        <v>62.5</v>
+        <v>64.709999999999994</v>
       </c>
       <c r="O30" s="10">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="P30" s="10">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -4323,10 +4324,10 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="M31" s="10">
-        <v>3.24</v>
+        <v>3.08</v>
       </c>
       <c r="N31" s="10">
         <v>11.11</v>
@@ -4373,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="10">
-        <v>0.97</v>
+        <v>0.94</v>
       </c>
       <c r="M32" s="10">
         <v>0</v>
@@ -4423,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
@@ -4431,7 +4432,6 @@
       <c r="N33" s="10">
         <v>0</v>
       </c>
-      <c r="O33" s="10"/>
       <c r="P33" s="10">
         <v>0</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="10">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="M34" s="10">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="10">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="M35" s="10">
         <v>0</v>
@@ -4537,52 +4537,52 @@
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+      <c r="A36" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="10">
         <v>2026</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D36">
-        <v>2</v>
-      </c>
-      <c r="E36">
-        <v>2</v>
-      </c>
-      <c r="F36">
-        <v>2</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36">
-        <v>0</v>
-      </c>
-      <c r="L36">
-        <v>0.65</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>100</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
+      <c r="D36" s="10">
+        <v>3</v>
+      </c>
+      <c r="E36" s="10">
+        <v>2</v>
+      </c>
+      <c r="F36" s="10">
+        <v>2</v>
+      </c>
+      <c r="G36" s="10">
+        <v>0</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0</v>
+      </c>
+      <c r="I36" s="10">
+        <v>0</v>
+      </c>
+      <c r="J36" s="10">
+        <v>0</v>
+      </c>
+      <c r="K36" s="10">
+        <v>0</v>
+      </c>
+      <c r="L36" s="10">
+        <v>0.94</v>
+      </c>
+      <c r="M36" s="10">
+        <v>0</v>
+      </c>
+      <c r="N36" s="10">
+        <v>66.67</v>
+      </c>
+      <c r="O36" s="10">
+        <v>0</v>
+      </c>
+      <c r="P36" s="10">
         <v>0</v>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
         <v>164</v>
       </c>
       <c r="G19" s="5">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" s="5">
         <v>23</v>
@@ -5197,13 +5197,13 @@
         <v>18</v>
       </c>
       <c r="I20" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="10">
-        <v>59614</v>
+        <v>65724</v>
       </c>
       <c r="K20" s="10">
-        <v>7</v>
+        <v>7.82</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -5217,19 +5217,19 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>2539</v>
+        <v>2661</v>
       </c>
       <c r="E21" s="10">
-        <v>6222.22</v>
+        <v>6514.17</v>
       </c>
       <c r="F21" s="10">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G21" s="10">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H21" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I21" s="10">
         <v>10</v>
@@ -5238,7 +5238,7 @@
         <v>60678</v>
       </c>
       <c r="K21" s="10">
-        <v>8.75</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5812,28 +5812,28 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="E38" s="10">
-        <v>2146.91</v>
+        <v>2279.7199999999998</v>
       </c>
       <c r="F38" s="10">
         <v>9</v>
       </c>
       <c r="G38" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H38" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="10">
-        <v>0</v>
+        <v>5292</v>
       </c>
       <c r="K38" s="10">
-        <v>-1</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -6241,7 +6241,7 @@
         <v>35</v>
       </c>
       <c r="G50" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H50" s="10">
         <v>12</v>
@@ -6407,16 +6407,16 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>921</v>
+        <v>964</v>
       </c>
       <c r="E55" s="10">
-        <v>7136.79</v>
+        <v>7460.19</v>
       </c>
       <c r="F55" s="10">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G55" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H55" s="10">
         <v>6</v>
@@ -6428,7 +6428,7 @@
         <v>15671.68</v>
       </c>
       <c r="K55" s="10">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6581,7 +6581,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H60" s="10">
         <v>4</v>
@@ -7402,13 +7402,13 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>504</v>
+        <v>526</v>
       </c>
       <c r="E84" s="10">
-        <v>3764.8</v>
+        <v>3927.6</v>
       </c>
       <c r="F84" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G84" s="10">
         <v>6</v>
@@ -7881,10 +7881,10 @@
         <v>17</v>
       </c>
       <c r="G98" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H98" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I98" s="10">
         <v>6</v>
@@ -8292,10 +8292,10 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>772</v>
+        <v>806</v>
       </c>
       <c r="E110" s="10">
-        <v>7824.12</v>
+        <v>8155.05</v>
       </c>
       <c r="F110" s="10">
         <v>35</v>
@@ -8313,7 +8313,7 @@
         <v>20867.12</v>
       </c>
       <c r="K110" s="10">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9011,7 +9011,7 @@
         <v>6</v>
       </c>
       <c r="G132" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H132" s="10">
         <v>2</v>
@@ -9807,10 +9807,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E155" s="10">
-        <v>1406.05</v>
+        <v>1458</v>
       </c>
       <c r="F155" s="10">
         <v>2</v>
@@ -10893,10 +10893,10 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="E186" s="10">
-        <v>3130.87</v>
+        <v>3257.1</v>
       </c>
       <c r="F186" s="10">
         <v>15</v>
@@ -10914,7 +10914,7 @@
         <v>3152.16</v>
       </c>
       <c r="K186" s="10">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
@@ -12468,19 +12468,19 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="E231" s="10">
-        <v>4191.26</v>
+        <v>4394.1000000000004</v>
       </c>
       <c r="F231" s="10">
         <v>28</v>
       </c>
       <c r="G231" s="10">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H231" s="10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I231" s="10">
         <v>0</v>
@@ -15882,28 +15882,28 @@
         <v>26</v>
       </c>
       <c r="E8" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="18">
-        <v>0</v>
+        <v>5292</v>
       </c>
       <c r="K8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="18">
-        <v>0</v>
+        <v>5292</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -15958,10 +15958,10 @@
         <v>107</v>
       </c>
       <c r="E10" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="18">
         <v>5</v>
@@ -16160,16 +16160,16 @@
         <v>2</v>
       </c>
       <c r="I15" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="18">
-        <v>8991</v>
+        <v>15101</v>
       </c>
       <c r="K15" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="18">
-        <v>8991</v>
+        <v>15101</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -16271,7 +16271,7 @@
         <v>5</v>
       </c>
       <c r="H18" s="18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="18">
         <v>2</v>
@@ -16347,7 +16347,7 @@
         <v>2</v>
       </c>
       <c r="H20" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="18">
         <v>0</v>
@@ -16908,13 +16908,13 @@
         <v>13</v>
       </c>
       <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35">
         <v>3</v>
       </c>
-      <c r="F35">
-        <v>2</v>
-      </c>
       <c r="G35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -16946,10 +16946,10 @@
         <v>13</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -17145,7 +17145,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I41">
         <v>4</v>
@@ -17174,16 +17174,16 @@
         <v>13</v>
       </c>
       <c r="E42">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F42">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I42">
         <v>3</v>
@@ -17554,16 +17554,16 @@
         <v>13</v>
       </c>
       <c r="E52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G52">
+        <v>4</v>
+      </c>
+      <c r="H52">
         <v>3</v>
-      </c>
-      <c r="H52">
-        <v>2</v>
       </c>
       <c r="I52">
         <v>2</v>
@@ -18057,7 +18057,7 @@
         <v>2</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I65">
         <v>1</v>
@@ -18124,16 +18124,16 @@
         <v>39</v>
       </c>
       <c r="E67">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F67">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G67">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -18428,7 +18428,7 @@
         <v>13</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F75">
         <v>2</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45CB4DA2-848E-4DD9-B49F-7F68E65574F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0A4605-3EA6-4D86-813D-F26FF138214A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tab1_KPI" sheetId="1" r:id="rId1"/>
@@ -1016,64 +1016,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="C6" s="5">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D6" s="5">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E6" s="5">
-        <v>37445.93</v>
+        <v>38945.39</v>
       </c>
       <c r="F6" s="5">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G6" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="5">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="I6" s="5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J6" s="5">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K6" s="5">
-        <v>258.24779310344798</v>
+        <v>252.89214285714201</v>
       </c>
       <c r="L6" s="5">
-        <v>780.12354166666603</v>
+        <v>778.90779999999995</v>
       </c>
       <c r="M6" s="5">
-        <v>182.16941066759401</v>
+        <v>207.625831966248</v>
       </c>
       <c r="N6" s="6">
-        <v>360</v>
+        <v>397</v>
       </c>
       <c r="O6" s="6">
-        <v>72656.889999999898</v>
+        <v>78553.06</v>
       </c>
       <c r="P6" s="6">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="Q6" s="6">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R6" s="6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S6" s="6">
-        <v>199.60684065934001</v>
+        <v>204.56526041666601</v>
       </c>
       <c r="T6" s="6">
-        <v>995.29986301369797</v>
+        <v>1020.1696103896101</v>
       </c>
       <c r="U6" s="6">
-        <v>138.65370510628799</v>
+        <v>136.22949888903099</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1088,7 +1088,7 @@
         <v>77</v>
       </c>
       <c r="Z6" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA6" s="8">
         <v>45500</v>
@@ -1100,7 +1100,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1108,64 +1108,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="C7" s="5">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D7" s="5">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E7" s="5">
-        <v>6514.17</v>
+        <v>6778.23</v>
       </c>
       <c r="F7" s="5">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G7" s="5">
+        <v>13</v>
+      </c>
+      <c r="H7" s="5">
+        <v>67</v>
+      </c>
+      <c r="I7" s="5">
+        <v>17</v>
+      </c>
+      <c r="J7" s="5">
         <v>12</v>
       </c>
-      <c r="H7" s="5">
-        <v>62</v>
-      </c>
-      <c r="I7" s="5">
-        <v>15</v>
-      </c>
-      <c r="J7" s="5">
-        <v>10</v>
-      </c>
       <c r="K7" s="5">
-        <v>88.029324324324307</v>
+        <v>84.727874999999997</v>
       </c>
       <c r="L7" s="5">
-        <v>434.27800000000002</v>
+        <v>398.719411764705</v>
       </c>
       <c r="M7" s="5">
-        <v>831.47707229009904</v>
+        <v>899.83328981164698</v>
       </c>
       <c r="N7" s="6">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="O7" s="6">
-        <v>17824.419999999998</v>
+        <v>19337.04</v>
       </c>
       <c r="P7" s="6">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="Q7" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R7" s="6">
         <v>13</v>
       </c>
       <c r="S7" s="6">
-        <v>100.702937853107</v>
+        <v>102.85659574468001</v>
       </c>
       <c r="T7" s="6">
-        <v>848.781904761904</v>
+        <v>878.95636363636299</v>
       </c>
       <c r="U7" s="6">
-        <v>463.43392940695901</v>
+        <v>419.359891689731</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1192,7 +1192,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1209,17 +1209,17 @@
         <v>3</v>
       </c>
       <c r="E8" s="5">
-        <v>2279.7199999999998</v>
+        <v>2358.38</v>
       </c>
       <c r="F8" s="5">
+        <v>6</v>
+      </c>
+      <c r="G8" s="5">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
         <v>5</v>
       </c>
-      <c r="G8" s="5">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5">
-        <v>4</v>
-      </c>
       <c r="I8" s="5">
         <v>2</v>
       </c>
@@ -1227,22 +1227,22 @@
         <v>1</v>
       </c>
       <c r="K8" s="5">
-        <v>455.94400000000002</v>
+        <v>393.06333333333299</v>
       </c>
       <c r="L8" s="5">
-        <v>1139.8599999999999</v>
+        <v>1179.19</v>
       </c>
       <c r="M8" s="5">
-        <v>132.13377081395899</v>
+        <v>124.391319465056</v>
       </c>
       <c r="N8" s="6">
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>2414.48</v>
+        <v>2538.56</v>
       </c>
       <c r="P8" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="6">
         <v>2</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>482.89600000000002</v>
+        <v>423.09333333333302</v>
       </c>
       <c r="T8" s="6">
-        <v>1207.24</v>
+        <v>1269.28</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1284,7 +1284,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1301,7 +1301,7 @@
         <v>23</v>
       </c>
       <c r="E9" s="5">
-        <v>7460.19</v>
+        <v>7705.92</v>
       </c>
       <c r="F9" s="5">
         <v>16</v>
@@ -1316,22 +1316,22 @@
         <v>6</v>
       </c>
       <c r="J9" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" s="5">
-        <v>466.26187499999997</v>
+        <v>481.62</v>
       </c>
       <c r="L9" s="5">
-        <v>1243.365</v>
+        <v>1284.32</v>
       </c>
       <c r="M9" s="5">
-        <v>110.070789081779</v>
+        <v>194.88756696150401</v>
       </c>
       <c r="N9" s="6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O9" s="6">
-        <v>7640.18</v>
+        <v>8141.28</v>
       </c>
       <c r="P9" s="6">
         <v>21</v>
@@ -1340,16 +1340,16 @@
         <v>7</v>
       </c>
       <c r="R9" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S9" s="6">
-        <v>363.818095238095</v>
+        <v>387.68</v>
       </c>
       <c r="T9" s="6">
-        <v>1091.4542857142801</v>
+        <v>1163.04</v>
       </c>
       <c r="U9" s="6">
-        <v>54.1455829574695</v>
+        <v>102.97913841558</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1370,7 +1370,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1390,13 +1390,13 @@
       <c r="L10" s="5"/>
       <c r="M10" s="5"/>
       <c r="N10" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O10" s="6">
-        <v>2409.84</v>
+        <v>2644.14</v>
       </c>
       <c r="P10" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q10" s="6">
         <v>5</v>
@@ -1405,13 +1405,13 @@
         <v>1</v>
       </c>
       <c r="S10" s="6">
-        <v>267.76</v>
+        <v>264.41399999999999</v>
       </c>
       <c r="T10" s="6">
-        <v>481.96800000000002</v>
+        <v>528.82799999999997</v>
       </c>
       <c r="U10" s="6">
-        <v>190.18524051389301</v>
+        <v>164.47162404411199</v>
       </c>
       <c r="V10" s="7">
         <v>5</v>
@@ -1426,7 +1426,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1443,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="5">
-        <v>3927.6</v>
+        <v>4100.59</v>
       </c>
       <c r="F11" s="5">
         <v>6</v>
@@ -1461,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>654.6</v>
+        <v>683.43166666666605</v>
       </c>
       <c r="L11" s="5">
-        <v>981.9</v>
+        <v>1025.1475</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
@@ -1473,7 +1473,7 @@
         <v>4</v>
       </c>
       <c r="O11" s="6">
-        <v>1527.86</v>
+        <v>1665.55</v>
       </c>
       <c r="P11" s="6">
         <v>5</v>
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>305.572</v>
+        <v>333.11</v>
       </c>
       <c r="T11" s="6">
-        <v>1527.86</v>
+        <v>1665.55</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1518,7 +1518,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1541,7 +1541,7 @@
         <v>2</v>
       </c>
       <c r="O12" s="6">
-        <v>382.3</v>
+        <v>430.18</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1562,7 +1562,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1570,25 +1570,25 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C13" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="5">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E13" s="5">
-        <v>8155.05</v>
+        <v>8454.8700000000008</v>
       </c>
       <c r="F13" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" s="5">
         <v>6</v>
       </c>
       <c r="H13" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I13" s="5">
         <v>7</v>
@@ -1597,37 +1597,37 @@
         <v>3</v>
       </c>
       <c r="K13" s="5">
-        <v>453.058333333333</v>
+        <v>444.99315789473599</v>
       </c>
       <c r="L13" s="5">
-        <v>1165.00714285714</v>
+        <v>1207.83857142857</v>
       </c>
       <c r="M13" s="5">
-        <v>155.87973096424901</v>
+        <v>146.805923686585</v>
       </c>
       <c r="N13" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O13" s="6">
-        <v>4341.9799999999996</v>
+        <v>4577.29</v>
       </c>
       <c r="P13" s="6">
         <v>22</v>
       </c>
       <c r="Q13" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R13" s="6">
         <v>4</v>
       </c>
       <c r="S13" s="6">
-        <v>197.362727272727</v>
+        <v>208.058636363636</v>
       </c>
       <c r="T13" s="6">
-        <v>434.19799999999998</v>
+        <v>416.117272727272</v>
       </c>
       <c r="U13" s="6">
-        <v>507.64904490577999</v>
+        <v>476.41093310670698</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1654,7 +1654,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1677,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="6">
-        <v>732.74</v>
+        <v>779.28</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>366.37</v>
+        <v>389.64</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1714,7 +1714,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1758,7 +1758,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1781,7 +1781,7 @@
         <v>5</v>
       </c>
       <c r="O16" s="6">
-        <v>1198.54</v>
+        <v>1335.98</v>
       </c>
       <c r="P16" s="6">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>1198.54</v>
+        <v>1335.98</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="6">
@@ -1818,7 +1818,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1826,16 +1826,16 @@
         <v>34</v>
       </c>
       <c r="B17" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" s="5">
         <v>2</v>
       </c>
       <c r="D17" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5">
-        <v>1458</v>
+        <v>1591.23</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1853,10 +1853,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1458</v>
+        <v>1591.23</v>
       </c>
       <c r="L17" s="5">
-        <v>1458</v>
+        <v>1591.23</v>
       </c>
       <c r="M17" s="5">
         <v>-100</v>
@@ -1865,7 +1865,7 @@
         <v>2</v>
       </c>
       <c r="O17" s="6">
-        <v>934.59</v>
+        <v>979.62</v>
       </c>
       <c r="P17" s="6">
         <v>3</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>311.52999999999997</v>
+        <v>326.54000000000002</v>
       </c>
       <c r="T17" s="6">
-        <v>467.29500000000002</v>
+        <v>489.81</v>
       </c>
       <c r="U17" s="6">
         <v>-100</v>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1930,13 +1930,13 @@
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
       <c r="N18" s="6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O18" s="6">
-        <v>3651.26</v>
+        <v>4028.41</v>
       </c>
       <c r="P18" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q18" s="6">
         <v>3</v>
@@ -1945,10 +1945,10 @@
         <v>0</v>
       </c>
       <c r="S18" s="6">
-        <v>243.417333333333</v>
+        <v>236.96529411764701</v>
       </c>
       <c r="T18" s="6">
-        <v>1217.08666666666</v>
+        <v>1342.8033333333301</v>
       </c>
       <c r="U18" s="6">
         <v>-100</v>
@@ -1972,7 +1972,7 @@
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1989,7 +1989,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="5">
-        <v>3257.1</v>
+        <v>3386.92</v>
       </c>
       <c r="F19" s="5">
         <v>5</v>
@@ -2007,37 +2007,37 @@
         <v>1</v>
       </c>
       <c r="K19" s="5">
-        <v>651.41999999999996</v>
+        <v>677.38400000000001</v>
       </c>
       <c r="L19" s="5">
-        <v>1085.7</v>
+        <v>1128.9733333333299</v>
       </c>
       <c r="M19" s="5">
-        <v>-3.2218844984802399</v>
+        <v>-6.9313712753770398</v>
       </c>
       <c r="N19" s="6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O19" s="6">
-        <v>4220.88</v>
+        <v>4532.6499999999996</v>
       </c>
       <c r="P19" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q19" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R19" s="6">
         <v>1</v>
       </c>
       <c r="S19" s="6">
-        <v>263.80500000000001</v>
+        <v>251.81388888888799</v>
       </c>
       <c r="T19" s="6">
-        <v>844.17600000000004</v>
+        <v>755.44166666666604</v>
       </c>
       <c r="U19" s="6">
-        <v>68.212789750004703</v>
+        <v>56.642582153927599</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2064,7 +2064,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2087,7 +2087,7 @@
         <v>18</v>
       </c>
       <c r="O20" s="6">
-        <v>4210.1099999999997</v>
+        <v>4627.3100000000004</v>
       </c>
       <c r="P20" s="6">
         <v>19</v>
@@ -2096,16 +2096,16 @@
         <v>9</v>
       </c>
       <c r="R20" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="6">
-        <v>221.584736842105</v>
+        <v>243.54263157894701</v>
       </c>
       <c r="T20" s="6">
-        <v>467.789999999999</v>
+        <v>514.14555555555501</v>
       </c>
       <c r="U20" s="6">
-        <v>-100</v>
+        <v>60.331596543131901</v>
       </c>
       <c r="V20" s="7">
         <v>18</v>
@@ -2120,13 +2120,13 @@
         <v>10</v>
       </c>
       <c r="Z20" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20" s="8"/>
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2146,10 +2146,10 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="O21" s="6">
-        <v>10747.25</v>
+        <v>11774.2</v>
       </c>
       <c r="P21" s="6">
         <v>37</v>
@@ -2161,13 +2161,13 @@
         <v>2</v>
       </c>
       <c r="S21" s="6">
-        <v>290.46621621621603</v>
+        <v>318.22162162162101</v>
       </c>
       <c r="T21" s="6">
-        <v>2149.4499999999998</v>
+        <v>2354.84</v>
       </c>
       <c r="U21" s="6">
-        <v>45.735513736072001</v>
+        <v>33.024409301693503</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2188,7 +2188,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2196,25 +2196,25 @@
         <v>39</v>
       </c>
       <c r="B22" s="5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C22" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22" s="5">
-        <v>4394.1000000000004</v>
+        <v>4569.25</v>
       </c>
       <c r="F22" s="5">
+        <v>21</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5">
         <v>20</v>
-      </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
-        <v>19</v>
       </c>
       <c r="I22" s="5">
         <v>10</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="K22" s="5">
-        <v>219.70500000000001</v>
+        <v>217.583333333333</v>
       </c>
       <c r="L22" s="5">
-        <v>439.41</v>
+        <v>456.92500000000001</v>
       </c>
       <c r="M22" s="5">
         <v>-100</v>
@@ -2235,10 +2235,10 @@
         <v>6</v>
       </c>
       <c r="O22" s="6">
-        <v>3630.26</v>
+        <v>3743.07</v>
       </c>
       <c r="P22" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q22" s="6">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="6">
-        <v>363.02600000000001</v>
+        <v>340.27909090908997</v>
       </c>
       <c r="T22" s="6"/>
       <c r="U22" s="6">
@@ -2278,7 +2278,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2298,28 +2298,28 @@
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
       <c r="N23" s="6">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O23" s="6">
-        <v>4310.54</v>
+        <v>4672.7700000000004</v>
       </c>
       <c r="P23" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q23" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R23" s="6">
         <v>1</v>
       </c>
       <c r="S23" s="6">
-        <v>253.56117647058801</v>
+        <v>245.93526315789401</v>
       </c>
       <c r="T23" s="6">
-        <v>2155.27</v>
+        <v>1557.59</v>
       </c>
       <c r="U23" s="6">
-        <v>17.222204178594701</v>
+        <v>8.1352174406187192</v>
       </c>
       <c r="V23" s="7">
         <v>37</v>
@@ -2344,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2364,10 +2364,10 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O24" s="6">
-        <v>2476.92</v>
+        <v>2742.99</v>
       </c>
       <c r="P24" s="6">
         <v>5</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>495.38400000000001</v>
+        <v>548.59799999999996</v>
       </c>
       <c r="T24" s="6">
-        <v>2476.92</v>
+        <v>2742.99</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2406,7 +2406,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46169</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3045,10 +3045,10 @@
         <v>45253.33</v>
       </c>
       <c r="L5" s="18">
-        <v>10.62</v>
+        <v>10.37</v>
       </c>
       <c r="M5" s="18">
-        <v>19.690000000000001</v>
+        <v>18.55</v>
       </c>
       <c r="N5" s="18">
         <v>47.06</v>
@@ -3071,43 +3071,43 @@
         <v>18</v>
       </c>
       <c r="D6" s="18">
+        <v>21</v>
+      </c>
+      <c r="E6" s="18">
         <v>20</v>
-      </c>
-      <c r="E6" s="18">
-        <v>19</v>
       </c>
       <c r="F6" s="18">
         <v>10</v>
       </c>
       <c r="G6" s="18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" s="18">
-        <v>13108</v>
+        <v>20160.12</v>
       </c>
       <c r="J6" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="18">
-        <v>13108</v>
+        <v>20160.12</v>
       </c>
       <c r="L6" s="18">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="M6" s="18">
-        <v>5.7</v>
+        <v>8.26</v>
       </c>
       <c r="N6" s="18">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="O6" s="18">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P6" s="18">
-        <v>10</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3145,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="18">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M7" s="18">
         <v>0</v>
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="18">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M8" s="18">
         <v>0</v>
@@ -3243,10 +3243,10 @@
         <v>15101</v>
       </c>
       <c r="L9" s="18">
-        <v>4.38</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="M9" s="18">
-        <v>6.57</v>
+        <v>6.19</v>
       </c>
       <c r="N9" s="18">
         <v>42.86</v>
@@ -3269,10 +3269,10 @@
         <v>18</v>
       </c>
       <c r="D10" s="18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" s="18">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F10" s="18">
         <v>7</v>
@@ -3293,19 +3293,19 @@
         <v>13049</v>
       </c>
       <c r="L10" s="18">
-        <v>5.94</v>
+        <v>6.1</v>
       </c>
       <c r="M10" s="18">
-        <v>5.68</v>
+        <v>5.35</v>
       </c>
       <c r="N10" s="18">
-        <v>36.840000000000003</v>
+        <v>35</v>
       </c>
       <c r="O10" s="18">
         <v>28.57</v>
       </c>
       <c r="P10" s="18">
-        <v>10.53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3343,10 +3343,10 @@
         <v>0</v>
       </c>
       <c r="L11" s="18">
+        <v>0.91</v>
+      </c>
+      <c r="M11" s="18">
         <v>0.94</v>
-      </c>
-      <c r="M11" s="18">
-        <v>0.99</v>
       </c>
       <c r="N11" s="18">
         <v>0</v>
@@ -3391,10 +3391,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="18">
-        <v>0.94</v>
+        <v>0.91</v>
       </c>
       <c r="M12" s="18">
-        <v>2.93</v>
+        <v>2.76</v>
       </c>
       <c r="N12" s="18">
         <v>0</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="18">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M13" s="18">
         <v>0</v>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="18">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M14" s="18">
         <v>7.0000000000000007E-2</v>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="18">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M15" s="18">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="18">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M16" s="18">
         <v>0</v>
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="18">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M17" s="18">
         <v>0</v>
@@ -3683,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="18">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="M18" s="18">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="10">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="M19" s="10">
         <v>0</v>
@@ -3759,13 +3759,13 @@
         <v>111</v>
       </c>
       <c r="D20" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" s="10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="10">
         <v>4</v>
@@ -3783,19 +3783,19 @@
         <v>5234</v>
       </c>
       <c r="L20" s="10">
-        <v>3.12</v>
+        <v>2.74</v>
       </c>
       <c r="M20" s="10">
-        <v>4.55</v>
+        <v>4.29</v>
       </c>
       <c r="N20" s="10">
-        <v>60</v>
+        <v>55.56</v>
       </c>
       <c r="O20" s="10">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="P20" s="10">
-        <v>20</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -3833,10 +3833,10 @@
         <v>11007.84</v>
       </c>
       <c r="L21" s="10">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="M21" s="10">
-        <v>4.79</v>
+        <v>4.51</v>
       </c>
       <c r="N21" s="10">
         <v>40</v>
@@ -3868,7 +3868,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H22" s="10">
         <v>4</v>
@@ -3883,10 +3883,10 @@
         <v>36031</v>
       </c>
       <c r="L22" s="10">
-        <v>21.88</v>
+        <v>21.34</v>
       </c>
       <c r="M22" s="10">
-        <v>15.68</v>
+        <v>14.77</v>
       </c>
       <c r="N22" s="10">
         <v>0</v>
@@ -3906,40 +3906,40 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E23" s="10">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F23" s="10">
         <v>0</v>
       </c>
       <c r="G23" s="10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H23" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I23" s="10">
-        <v>20397</v>
+        <v>27490</v>
       </c>
       <c r="J23" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" s="10">
-        <v>20397</v>
+        <v>21100</v>
       </c>
       <c r="L23" s="10">
-        <v>14.37</v>
+        <v>14.94</v>
       </c>
       <c r="M23" s="10">
-        <v>8.8699999999999992</v>
+        <v>11.27</v>
       </c>
       <c r="N23" s="10">
         <v>0</v>
       </c>
       <c r="P23" s="10">
-        <v>6.52</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -3977,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -4003,16 +4003,16 @@
         <v>18</v>
       </c>
       <c r="D25" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E25" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F25" s="10">
+        <v>6</v>
+      </c>
+      <c r="G25" s="10">
         <v>4</v>
-      </c>
-      <c r="G25" s="10">
-        <v>3</v>
       </c>
       <c r="H25" s="10">
         <v>2</v>
@@ -4027,19 +4027,19 @@
         <v>15374</v>
       </c>
       <c r="L25" s="10">
-        <v>3.12</v>
+        <v>3.66</v>
       </c>
       <c r="M25" s="10">
-        <v>6.69</v>
+        <v>6.3</v>
       </c>
       <c r="N25" s="10">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O25" s="10">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="P25" s="10">
-        <v>20</v>
+        <v>16.670000000000002</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M26" s="10">
         <v>0</v>
@@ -4124,10 +4124,10 @@
         <v>7816</v>
       </c>
       <c r="L27" s="10">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="M27" s="10">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N27" s="10">
         <v>30</v>
@@ -4150,10 +4150,10 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
+        <v>7</v>
+      </c>
+      <c r="E28" s="10">
         <v>6</v>
-      </c>
-      <c r="E28" s="10">
-        <v>5</v>
       </c>
       <c r="F28" s="10">
         <v>3</v>
@@ -4174,19 +4174,19 @@
         <v>17865</v>
       </c>
       <c r="L28" s="10">
-        <v>1.88</v>
+        <v>2.13</v>
       </c>
       <c r="M28" s="10">
-        <v>7.77</v>
+        <v>7.32</v>
       </c>
       <c r="N28" s="10">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="O28" s="10">
         <v>66.67</v>
       </c>
       <c r="P28" s="10">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
@@ -4224,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>0.94</v>
+        <v>0.91</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E30" s="10">
         <v>17</v>
@@ -4259,7 +4259,7 @@
         <v>11</v>
       </c>
       <c r="G30" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H30" s="10">
         <v>2</v>
@@ -4274,19 +4274,19 @@
         <v>8117.12</v>
       </c>
       <c r="L30" s="10">
-        <v>5.31</v>
+        <v>5.49</v>
       </c>
       <c r="M30" s="10">
-        <v>3.53</v>
+        <v>3.33</v>
       </c>
       <c r="N30" s="10">
-        <v>64.709999999999994</v>
+        <v>61.11</v>
       </c>
       <c r="O30" s="10">
         <v>18.18</v>
       </c>
       <c r="P30" s="10">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -4324,10 +4324,10 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="M31" s="10">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="N31" s="10">
         <v>11.11</v>
@@ -4374,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="10">
-        <v>0.94</v>
+        <v>0.91</v>
       </c>
       <c r="M32" s="10">
         <v>0</v>
@@ -4424,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
@@ -4471,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="10">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M34" s="10">
         <v>0</v>
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="10">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="M35" s="10">
         <v>0</v>
@@ -4556,7 +4556,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="10">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="10">
-        <v>0.94</v>
+        <v>0.91</v>
       </c>
       <c r="M36" s="10">
         <v>0</v>
@@ -5165,10 +5165,10 @@
         <v>12</v>
       </c>
       <c r="J19" s="5">
-        <v>91957.64</v>
+        <v>92332.64</v>
       </c>
       <c r="K19" s="5">
-        <v>11.76</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -5217,28 +5217,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>2661</v>
+        <v>2750</v>
       </c>
       <c r="E21" s="10">
-        <v>6514.17</v>
+        <v>6778.23</v>
       </c>
       <c r="F21" s="10">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G21" s="10">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H21" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I21" s="10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J21" s="10">
-        <v>60678</v>
+        <v>67771</v>
       </c>
       <c r="K21" s="10">
-        <v>8.31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5812,16 +5812,16 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E38" s="10">
-        <v>2279.7199999999998</v>
+        <v>2358.38</v>
       </c>
       <c r="F38" s="10">
         <v>9</v>
       </c>
       <c r="G38" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H38" s="10">
         <v>2</v>
@@ -5833,7 +5833,7 @@
         <v>5292</v>
       </c>
       <c r="K38" s="10">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -6407,10 +6407,10 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>964</v>
+        <v>992</v>
       </c>
       <c r="E55" s="10">
-        <v>7460.19</v>
+        <v>7705.92</v>
       </c>
       <c r="F55" s="10">
         <v>33</v>
@@ -6422,13 +6422,13 @@
         <v>6</v>
       </c>
       <c r="I55" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J55" s="10">
-        <v>15671.68</v>
+        <v>22723.8</v>
       </c>
       <c r="K55" s="10">
-        <v>1.1000000000000001</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6581,7 +6581,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H60" s="10">
         <v>4</v>
@@ -7402,10 +7402,10 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>526</v>
+        <v>558</v>
       </c>
       <c r="E84" s="10">
-        <v>3927.6</v>
+        <v>4100.59</v>
       </c>
       <c r="F84" s="10">
         <v>12</v>
@@ -7881,10 +7881,10 @@
         <v>17</v>
       </c>
       <c r="G98" s="10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H98" s="10">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I98" s="10">
         <v>6</v>
@@ -8292,19 +8292,19 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>806</v>
+        <v>842</v>
       </c>
       <c r="E110" s="10">
-        <v>8155.05</v>
+        <v>8454.8700000000008</v>
       </c>
       <c r="F110" s="10">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G110" s="10">
         <v>18</v>
       </c>
       <c r="H110" s="10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I110" s="10">
         <v>3</v>
@@ -8313,7 +8313,7 @@
         <v>20867.12</v>
       </c>
       <c r="K110" s="10">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9011,7 +9011,7 @@
         <v>6</v>
       </c>
       <c r="G132" s="10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H132" s="10">
         <v>2</v>
@@ -9807,13 +9807,13 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E155" s="10">
-        <v>1458</v>
+        <v>1591.23</v>
       </c>
       <c r="F155" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G155" s="10">
         <v>1</v>
@@ -10893,10 +10893,10 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="E186" s="10">
-        <v>3257.1</v>
+        <v>3386.92</v>
       </c>
       <c r="F186" s="10">
         <v>15</v>
@@ -10914,7 +10914,7 @@
         <v>3152.16</v>
       </c>
       <c r="K186" s="10">
-        <v>-0.03</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
@@ -12468,16 +12468,16 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>552</v>
+        <v>572</v>
       </c>
       <c r="E231" s="10">
-        <v>4394.1000000000004</v>
+        <v>4569.25</v>
       </c>
       <c r="F231" s="10">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G231" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H231" s="10">
         <v>10</v>
@@ -15882,16 +15882,16 @@
         <v>26</v>
       </c>
       <c r="E8" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="18">
         <v>2</v>
       </c>
       <c r="H8" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="18">
         <v>1</v>
@@ -15970,16 +15970,16 @@
         <v>3</v>
       </c>
       <c r="I10" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="18">
-        <v>7816</v>
+        <v>14868.12</v>
       </c>
       <c r="K10" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="18">
-        <v>7816</v>
+        <v>14868.12</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -16262,10 +16262,10 @@
         <v>29</v>
       </c>
       <c r="E18" s="18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18" s="18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" s="18">
         <v>5</v>
@@ -16908,13 +16908,13 @@
         <v>13</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -17145,7 +17145,7 @@
         <v>0</v>
       </c>
       <c r="H41">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I41">
         <v>4</v>
@@ -17174,28 +17174,28 @@
         <v>13</v>
       </c>
       <c r="E42">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F42">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J42">
-        <v>20397</v>
+        <v>27490</v>
       </c>
       <c r="K42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42">
-        <v>20397</v>
+        <v>21100</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -17554,16 +17554,16 @@
         <v>13</v>
       </c>
       <c r="E52">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F52">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G52">
+        <v>6</v>
+      </c>
+      <c r="H52">
         <v>4</v>
-      </c>
-      <c r="H52">
-        <v>3</v>
       </c>
       <c r="I52">
         <v>2</v>
@@ -17706,10 +17706,10 @@
         <v>13</v>
       </c>
       <c r="E56">
+        <v>6</v>
+      </c>
+      <c r="F56">
         <v>5</v>
-      </c>
-      <c r="F56">
-        <v>4</v>
       </c>
       <c r="G56">
         <v>3</v>
@@ -18051,7 +18051,7 @@
         <v>2</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65">
         <v>2</v>
@@ -18124,16 +18124,16 @@
         <v>39</v>
       </c>
       <c r="E67">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F67">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G67">
         <v>7</v>
       </c>
       <c r="H67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -18437,7 +18437,7 @@
         <v>2</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75">
         <v>0</v>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0A4605-3EA6-4D86-813D-F26FF138214A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE4F70D-3094-484B-8059-C3F8CD201F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="29016" windowHeight="15696" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="113">
   <si>
     <t>Tab 3 — Campaign Performance</t>
   </si>
@@ -1016,64 +1016,64 @@
         <v>74</v>
       </c>
       <c r="B6" s="5">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C6" s="5">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D6" s="5">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="E6" s="5">
-        <v>38945.39</v>
+        <v>43526.91</v>
       </c>
       <c r="F6" s="5">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="G6" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H6" s="5">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="I6" s="5">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J6" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K6" s="5">
-        <v>252.89214285714201</v>
+        <v>263.79945454545401</v>
       </c>
       <c r="L6" s="5">
-        <v>778.90779999999995</v>
+        <v>821.26245283018795</v>
       </c>
       <c r="M6" s="5">
-        <v>207.625831966248</v>
+        <v>217.84953262246199</v>
       </c>
       <c r="N6" s="6">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="O6" s="6">
-        <v>78553.06</v>
+        <v>83434</v>
       </c>
       <c r="P6" s="6">
-        <v>384</v>
+        <v>424</v>
       </c>
       <c r="Q6" s="6">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="R6" s="6">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="S6" s="6">
-        <v>204.56526041666601</v>
+        <v>196.77830188679201</v>
       </c>
       <c r="T6" s="6">
-        <v>1020.1696103896101</v>
+        <v>937.46067415730295</v>
       </c>
       <c r="U6" s="6">
-        <v>136.22949888903099</v>
+        <v>160.13941558597199</v>
       </c>
       <c r="V6" s="7">
         <v>420</v>
@@ -1088,7 +1088,7 @@
         <v>77</v>
       </c>
       <c r="Z6" s="7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AA6" s="8">
         <v>45500</v>
@@ -1100,7 +1100,7 @@
         <v>39</v>
       </c>
       <c r="AD6" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1108,64 +1108,64 @@
         <v>13</v>
       </c>
       <c r="B7" s="5">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C7" s="5">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7" s="5">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="E7" s="5">
-        <v>6778.23</v>
+        <v>7216.49</v>
       </c>
       <c r="F7" s="5">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G7" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="5">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I7" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J7" s="5">
         <v>12</v>
       </c>
       <c r="K7" s="5">
-        <v>84.727874999999997</v>
+        <v>82.9481609195402</v>
       </c>
       <c r="L7" s="5">
-        <v>398.719411764705</v>
+        <v>379.81526315789398</v>
       </c>
       <c r="M7" s="5">
-        <v>899.83328981164698</v>
+        <v>948.18270377981503</v>
       </c>
       <c r="N7" s="6">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="O7" s="6">
-        <v>19337.04</v>
+        <v>20468.29</v>
       </c>
       <c r="P7" s="6">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="Q7" s="6">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="R7" s="6">
         <v>13</v>
       </c>
       <c r="S7" s="6">
-        <v>102.85659574468001</v>
+        <v>98.880628019323595</v>
       </c>
       <c r="T7" s="6">
-        <v>878.95636363636299</v>
+        <v>705.80310344827501</v>
       </c>
       <c r="U7" s="6">
-        <v>419.359891689731</v>
+        <v>390.65569229280999</v>
       </c>
       <c r="V7" s="7">
         <v>170</v>
@@ -1192,7 +1192,7 @@
         <v>14</v>
       </c>
       <c r="AD7" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1209,7 +1209,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="5">
-        <v>2358.38</v>
+        <v>2740.91</v>
       </c>
       <c r="F8" s="5">
         <v>6</v>
@@ -1227,19 +1227,19 @@
         <v>1</v>
       </c>
       <c r="K8" s="5">
-        <v>393.06333333333299</v>
+        <v>456.81833333333299</v>
       </c>
       <c r="L8" s="5">
-        <v>1179.19</v>
+        <v>1370.4549999999999</v>
       </c>
       <c r="M8" s="5">
-        <v>124.391319465056</v>
+        <v>93.074562827674001</v>
       </c>
       <c r="N8" s="6">
         <v>3</v>
       </c>
       <c r="O8" s="6">
-        <v>2538.56</v>
+        <v>2661.46</v>
       </c>
       <c r="P8" s="6">
         <v>6</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="S8" s="6">
-        <v>423.09333333333302</v>
+        <v>443.57666666666597</v>
       </c>
       <c r="T8" s="6">
-        <v>1269.28</v>
+        <v>1330.73</v>
       </c>
       <c r="U8" s="6">
         <v>-100</v>
@@ -1284,7 +1284,7 @@
         <v>3</v>
       </c>
       <c r="AD8" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1292,16 +1292,16 @@
         <v>107</v>
       </c>
       <c r="B9" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="5">
         <v>10</v>
       </c>
       <c r="D9" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" s="5">
-        <v>7705.92</v>
+        <v>8741.84</v>
       </c>
       <c r="F9" s="5">
         <v>16</v>
@@ -1319,19 +1319,19 @@
         <v>3</v>
       </c>
       <c r="K9" s="5">
-        <v>481.62</v>
+        <v>546.36500000000001</v>
       </c>
       <c r="L9" s="5">
-        <v>1284.32</v>
+        <v>1456.9733333333299</v>
       </c>
       <c r="M9" s="5">
-        <v>194.88756696150401</v>
+        <v>159.94298683114701</v>
       </c>
       <c r="N9" s="6">
         <v>31</v>
       </c>
       <c r="O9" s="6">
-        <v>8141.28</v>
+        <v>8512.2800000000007</v>
       </c>
       <c r="P9" s="6">
         <v>21</v>
@@ -1343,13 +1343,13 @@
         <v>3</v>
       </c>
       <c r="S9" s="6">
-        <v>387.68</v>
+        <v>405.34666666666601</v>
       </c>
       <c r="T9" s="6">
-        <v>1163.04</v>
+        <v>1216.04</v>
       </c>
       <c r="U9" s="6">
-        <v>102.97913841558</v>
+        <v>94.132476845216502</v>
       </c>
       <c r="V9" s="7">
         <v>31</v>
@@ -1370,7 +1370,7 @@
         <v>14</v>
       </c>
       <c r="AD9" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1393,25 +1393,25 @@
         <v>5</v>
       </c>
       <c r="O10" s="6">
-        <v>2644.14</v>
+        <v>2892.95</v>
       </c>
       <c r="P10" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q10" s="6">
         <v>5</v>
       </c>
       <c r="R10" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S10" s="6">
-        <v>264.41399999999999</v>
+        <v>241.079166666666</v>
       </c>
       <c r="T10" s="6">
-        <v>528.82799999999997</v>
+        <v>578.58999999999901</v>
       </c>
       <c r="U10" s="6">
-        <v>164.47162404411199</v>
+        <v>579.30659015883396</v>
       </c>
       <c r="V10" s="7">
         <v>5</v>
@@ -1426,7 +1426,7 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1434,16 +1434,16 @@
         <v>106</v>
       </c>
       <c r="B11" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5">
         <v>9</v>
       </c>
       <c r="E11" s="5">
-        <v>4100.59</v>
+        <v>4664.99</v>
       </c>
       <c r="F11" s="5">
         <v>6</v>
@@ -1461,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>683.43166666666605</v>
+        <v>777.49833333333299</v>
       </c>
       <c r="L11" s="5">
-        <v>1025.1475</v>
+        <v>1166.2474999999999</v>
       </c>
       <c r="M11" s="5">
         <v>-100</v>
@@ -1473,7 +1473,7 @@
         <v>4</v>
       </c>
       <c r="O11" s="6">
-        <v>1665.55</v>
+        <v>1769.98</v>
       </c>
       <c r="P11" s="6">
         <v>5</v>
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="S11" s="6">
-        <v>333.11</v>
+        <v>353.99599999999998</v>
       </c>
       <c r="T11" s="6">
-        <v>1665.55</v>
+        <v>1769.98</v>
       </c>
       <c r="U11" s="6">
         <v>-100</v>
@@ -1518,7 +1518,7 @@
         <v>1</v>
       </c>
       <c r="AD11" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1541,7 +1541,7 @@
         <v>2</v>
       </c>
       <c r="O12" s="6">
-        <v>430.18</v>
+        <v>478.71</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1562,7 +1562,7 @@
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
       <c r="AD12" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1570,64 +1570,64 @@
         <v>29</v>
       </c>
       <c r="B13" s="5">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C13" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="5">
-        <v>8454.8700000000008</v>
+        <v>9171.67</v>
       </c>
       <c r="F13" s="5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G13" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="5">
         <v>7</v>
       </c>
       <c r="J13" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="5">
-        <v>444.99315789473599</v>
+        <v>436.74619047619001</v>
       </c>
       <c r="L13" s="5">
-        <v>1207.83857142857</v>
+        <v>1310.2385714285699</v>
       </c>
       <c r="M13" s="5">
-        <v>146.805923686585</v>
+        <v>163.26852143611799</v>
       </c>
       <c r="N13" s="6">
         <v>17</v>
       </c>
       <c r="O13" s="6">
-        <v>4577.29</v>
+        <v>4709.1899999999996</v>
       </c>
       <c r="P13" s="6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q13" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R13" s="6">
         <v>4</v>
       </c>
       <c r="S13" s="6">
-        <v>208.058636363636</v>
+        <v>204.74739130434699</v>
       </c>
       <c r="T13" s="6">
-        <v>416.117272727272</v>
+        <v>392.43249999999898</v>
       </c>
       <c r="U13" s="6">
-        <v>476.41093310670698</v>
+        <v>460.26620289264099</v>
       </c>
       <c r="V13" s="7">
         <v>17</v>
@@ -1654,7 +1654,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1674,10 +1674,10 @@
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
       <c r="N14" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O14" s="6">
-        <v>779.28</v>
+        <v>807.79</v>
       </c>
       <c r="P14" s="6">
         <v>2</v>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>389.64</v>
+        <v>403.89499999999998</v>
       </c>
       <c r="T14" s="6"/>
       <c r="U14" s="6">
@@ -1714,7 +1714,7 @@
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
       <c r="AD14" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1758,7 +1758,7 @@
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
       <c r="AD15" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1778,13 +1778,13 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O16" s="6">
-        <v>1335.98</v>
+        <v>1438.64</v>
       </c>
       <c r="P16" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="6">
         <v>0</v>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="6">
-        <v>1335.98</v>
+        <v>479.546666666666</v>
       </c>
       <c r="T16" s="6"/>
       <c r="U16" s="6">
@@ -1818,7 +1818,7 @@
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
       <c r="AD16" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1835,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="5">
-        <v>1591.23</v>
+        <v>1694.86</v>
       </c>
       <c r="F17" s="5">
         <v>1</v>
@@ -1853,10 +1853,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="5">
-        <v>1591.23</v>
+        <v>1694.86</v>
       </c>
       <c r="L17" s="5">
-        <v>1591.23</v>
+        <v>1694.86</v>
       </c>
       <c r="M17" s="5">
         <v>-100</v>
@@ -1865,10 +1865,10 @@
         <v>2</v>
       </c>
       <c r="O17" s="6">
-        <v>979.62</v>
+        <v>1036.2</v>
       </c>
       <c r="P17" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="6">
         <v>2</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="S17" s="6">
-        <v>326.54000000000002</v>
+        <v>259.05</v>
       </c>
       <c r="T17" s="6">
-        <v>489.81</v>
+        <v>518.1</v>
       </c>
       <c r="U17" s="6">
         <v>-100</v>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1933,25 +1933,25 @@
         <v>22</v>
       </c>
       <c r="O18" s="6">
-        <v>4028.41</v>
+        <v>4412.01</v>
       </c>
       <c r="P18" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q18" s="6">
         <v>3</v>
       </c>
       <c r="R18" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="6">
-        <v>236.96529411764701</v>
+        <v>232.21105263157801</v>
       </c>
       <c r="T18" s="6">
-        <v>1342.8033333333301</v>
+        <v>1470.67</v>
       </c>
       <c r="U18" s="6">
-        <v>-100</v>
+        <v>9.3619461424611501</v>
       </c>
       <c r="V18" s="7">
         <v>22</v>
@@ -1966,13 +1966,13 @@
         <v>3</v>
       </c>
       <c r="Z18" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18" s="8"/>
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
       <c r="AD18" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1980,25 +1980,25 @@
         <v>36</v>
       </c>
       <c r="B19" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C19" s="5">
         <v>6</v>
       </c>
       <c r="D19" s="5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E19" s="5">
-        <v>3386.92</v>
+        <v>3740.45</v>
       </c>
       <c r="F19" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G19" s="5">
         <v>1</v>
       </c>
       <c r="H19" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I19" s="5">
         <v>3</v>
@@ -2007,37 +2007,37 @@
         <v>1</v>
       </c>
       <c r="K19" s="5">
-        <v>677.38400000000001</v>
+        <v>534.35</v>
       </c>
       <c r="L19" s="5">
-        <v>1128.9733333333299</v>
+        <v>1246.81666666666</v>
       </c>
       <c r="M19" s="5">
-        <v>-6.9313712753770398</v>
+        <v>-15.7277867636247</v>
       </c>
       <c r="N19" s="6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O19" s="6">
-        <v>4532.6499999999996</v>
+        <v>4789.4399999999996</v>
       </c>
       <c r="P19" s="6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q19" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R19" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S19" s="6">
-        <v>251.81388888888799</v>
+        <v>239.47199999999901</v>
       </c>
       <c r="T19" s="6">
-        <v>755.44166666666604</v>
+        <v>684.20571428571395</v>
       </c>
       <c r="U19" s="6">
-        <v>56.642582153927599</v>
+        <v>191.333015968464</v>
       </c>
       <c r="V19" s="7">
         <v>29</v>
@@ -2052,7 +2052,7 @@
         <v>7</v>
       </c>
       <c r="Z19" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA19" s="8">
         <v>3500</v>
@@ -2064,7 +2064,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2087,25 +2087,25 @@
         <v>18</v>
       </c>
       <c r="O20" s="6">
-        <v>4627.3100000000004</v>
+        <v>4995.3100000000004</v>
       </c>
       <c r="P20" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q20" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R20" s="6">
         <v>1</v>
       </c>
       <c r="S20" s="6">
-        <v>243.54263157894701</v>
+        <v>237.87190476190401</v>
       </c>
       <c r="T20" s="6">
-        <v>514.14555555555501</v>
+        <v>499.53100000000001</v>
       </c>
       <c r="U20" s="6">
-        <v>60.331596543131901</v>
+        <v>48.520111864929198</v>
       </c>
       <c r="V20" s="7">
         <v>18</v>
@@ -2126,7 +2126,7 @@
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
       <c r="AD20" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2146,13 +2146,13 @@
       <c r="L21" s="5"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O21" s="6">
-        <v>11774.2</v>
+        <v>12747.77</v>
       </c>
       <c r="P21" s="6">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q21" s="6">
         <v>5</v>
@@ -2161,13 +2161,13 @@
         <v>2</v>
       </c>
       <c r="S21" s="6">
-        <v>318.22162162162101</v>
+        <v>296.45976744185998</v>
       </c>
       <c r="T21" s="6">
-        <v>2354.84</v>
+        <v>2549.5540000000001</v>
       </c>
       <c r="U21" s="6">
-        <v>33.024409301693503</v>
+        <v>22.865097189547601</v>
       </c>
       <c r="V21" s="7">
         <v>51</v>
@@ -2188,7 +2188,7 @@
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
       <c r="AD21" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2205,7 +2205,7 @@
         <v>25</v>
       </c>
       <c r="E22" s="5">
-        <v>4569.25</v>
+        <v>5555.7</v>
       </c>
       <c r="F22" s="5">
         <v>21</v>
@@ -2217,41 +2217,43 @@
         <v>20</v>
       </c>
       <c r="I22" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="5">
-        <v>217.583333333333</v>
+        <v>264.55714285714203</v>
       </c>
       <c r="L22" s="5">
-        <v>456.92500000000001</v>
+        <v>505.06363636363602</v>
       </c>
       <c r="M22" s="5">
-        <v>-100</v>
+        <v>33.088539697967803</v>
       </c>
       <c r="N22" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O22" s="6">
-        <v>3743.07</v>
+        <v>3793.72</v>
       </c>
       <c r="P22" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q22" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="6">
-        <v>340.27909090908997</v>
-      </c>
-      <c r="T22" s="6"/>
+        <v>291.82461538461502</v>
+      </c>
+      <c r="T22" s="6">
+        <v>3793.72</v>
+      </c>
       <c r="U22" s="6">
-        <v>-100</v>
+        <v>88.258490347205296</v>
       </c>
       <c r="V22" s="7">
         <v>8</v>
@@ -2266,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="Z22" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="8">
         <v>5000</v>
@@ -2278,7 +2280,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2301,25 +2303,25 @@
         <v>37</v>
       </c>
       <c r="O23" s="6">
-        <v>4672.7700000000004</v>
+        <v>5009.66</v>
       </c>
       <c r="P23" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q23" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R23" s="6">
         <v>1</v>
       </c>
       <c r="S23" s="6">
-        <v>245.93526315789401</v>
+        <v>250.483</v>
       </c>
       <c r="T23" s="6">
-        <v>1557.59</v>
+        <v>1252.415</v>
       </c>
       <c r="U23" s="6">
-        <v>8.1352174406187192</v>
+        <v>0.86333204249390105</v>
       </c>
       <c r="V23" s="7">
         <v>37</v>
@@ -2344,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="AD23" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2364,10 +2366,10 @@
       <c r="L24" s="5"/>
       <c r="M24" s="5"/>
       <c r="N24" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O24" s="6">
-        <v>2742.99</v>
+        <v>2907.86</v>
       </c>
       <c r="P24" s="6">
         <v>5</v>
@@ -2379,10 +2381,10 @@
         <v>0</v>
       </c>
       <c r="S24" s="6">
-        <v>548.59799999999996</v>
+        <v>581.572</v>
       </c>
       <c r="T24" s="6">
-        <v>2742.99</v>
+        <v>2907.86</v>
       </c>
       <c r="U24" s="6">
         <v>-100</v>
@@ -2406,7 +2408,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
       <c r="AD24" s="13">
-        <v>46170</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3045,10 +3047,10 @@
         <v>45253.33</v>
       </c>
       <c r="L5" s="18">
-        <v>10.37</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="M5" s="18">
-        <v>18.55</v>
+        <v>17.21</v>
       </c>
       <c r="N5" s="18">
         <v>47.06</v>
@@ -3071,10 +3073,10 @@
         <v>18</v>
       </c>
       <c r="D6" s="18">
+        <v>22</v>
+      </c>
+      <c r="E6" s="18">
         <v>21</v>
-      </c>
-      <c r="E6" s="18">
-        <v>20</v>
       </c>
       <c r="F6" s="18">
         <v>10</v>
@@ -3095,19 +3097,19 @@
         <v>20160.12</v>
       </c>
       <c r="L6" s="18">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="M6" s="18">
-        <v>8.26</v>
+        <v>7.67</v>
       </c>
       <c r="N6" s="18">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="O6" s="18">
         <v>30</v>
       </c>
       <c r="P6" s="18">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3145,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="18">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M7" s="18">
         <v>0</v>
@@ -3193,7 +3195,7 @@
         <v>0</v>
       </c>
       <c r="L8" s="18">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M8" s="18">
         <v>0</v>
@@ -3234,19 +3236,19 @@
         <v>2</v>
       </c>
       <c r="I9" s="18">
-        <v>15101</v>
+        <v>15476</v>
       </c>
       <c r="J9" s="18">
         <v>2</v>
       </c>
       <c r="K9" s="18">
-        <v>15101</v>
+        <v>15476</v>
       </c>
       <c r="L9" s="18">
-        <v>4.2699999999999996</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="M9" s="18">
-        <v>6.19</v>
+        <v>5.89</v>
       </c>
       <c r="N9" s="18">
         <v>42.86</v>
@@ -3269,10 +3271,10 @@
         <v>18</v>
       </c>
       <c r="D10" s="18">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" s="18">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" s="18">
         <v>7</v>
@@ -3293,19 +3295,19 @@
         <v>13049</v>
       </c>
       <c r="L10" s="18">
-        <v>6.1</v>
+        <v>5.57</v>
       </c>
       <c r="M10" s="18">
-        <v>5.35</v>
+        <v>4.96</v>
       </c>
       <c r="N10" s="18">
-        <v>35</v>
+        <v>36.840000000000003</v>
       </c>
       <c r="O10" s="18">
         <v>28.57</v>
       </c>
       <c r="P10" s="18">
-        <v>10</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3343,10 +3345,10 @@
         <v>0</v>
       </c>
       <c r="L11" s="18">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="M11" s="18">
-        <v>0.94</v>
+        <v>0.87</v>
       </c>
       <c r="N11" s="18">
         <v>0</v>
@@ -3367,22 +3369,22 @@
         <v>18</v>
       </c>
       <c r="D12" s="18">
+        <v>4</v>
+      </c>
+      <c r="E12" s="18">
+        <v>0</v>
+      </c>
+      <c r="F12" s="18">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
+        <v>4</v>
+      </c>
+      <c r="H12" s="18">
         <v>3</v>
       </c>
-      <c r="E12" s="18">
-        <v>0</v>
-      </c>
-      <c r="F12" s="18">
-        <v>0</v>
-      </c>
-      <c r="G12" s="18">
-        <v>3</v>
-      </c>
-      <c r="H12" s="18">
-        <v>2</v>
-      </c>
       <c r="I12" s="18">
-        <v>6743</v>
+        <v>17893</v>
       </c>
       <c r="J12" s="18">
         <v>0</v>
@@ -3391,17 +3393,17 @@
         <v>0</v>
       </c>
       <c r="L12" s="18">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="M12" s="18">
-        <v>2.76</v>
+        <v>6.81</v>
       </c>
       <c r="N12" s="18">
         <v>0</v>
       </c>
       <c r="O12" s="18"/>
       <c r="P12" s="18">
-        <v>66.67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3439,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="L13" s="18">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M13" s="18">
         <v>0</v>
@@ -3487,10 +3489,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="18">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M14" s="18">
-        <v>7.0000000000000007E-2</v>
+        <v>0.06</v>
       </c>
       <c r="N14" s="18">
         <v>100</v>
@@ -3537,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="18">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M15" s="18">
         <v>0</v>
@@ -3585,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="18">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M16" s="18">
         <v>0</v>
@@ -3633,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="18">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M17" s="18">
         <v>0</v>
@@ -3683,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="18">
-        <v>2.13</v>
+        <v>2.0499999999999998</v>
       </c>
       <c r="M18" s="18">
         <v>0</v>
@@ -3709,13 +3711,13 @@
         <v>18</v>
       </c>
       <c r="D19" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="10">
         <v>1</v>
@@ -3733,13 +3735,13 @@
         <v>0</v>
       </c>
       <c r="L19" s="10">
-        <v>0.61</v>
+        <v>0.88</v>
       </c>
       <c r="M19" s="10">
         <v>0</v>
       </c>
       <c r="N19" s="10">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="O19" s="10">
         <v>0</v>
@@ -3759,13 +3761,13 @@
         <v>111</v>
       </c>
       <c r="D20" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="10">
         <v>4</v>
@@ -3783,19 +3785,19 @@
         <v>5234</v>
       </c>
       <c r="L20" s="10">
-        <v>2.74</v>
+        <v>2.93</v>
       </c>
       <c r="M20" s="10">
-        <v>4.29</v>
+        <v>3.98</v>
       </c>
       <c r="N20" s="10">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="O20" s="10">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="P20" s="10">
-        <v>22.22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
@@ -3809,7 +3811,7 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" s="10">
         <v>10</v>
@@ -3833,19 +3835,19 @@
         <v>11007.84</v>
       </c>
       <c r="L21" s="10">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="M21" s="10">
-        <v>4.51</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="N21" s="10">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="O21" s="10">
         <v>50</v>
       </c>
       <c r="P21" s="10">
-        <v>20</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
@@ -3883,10 +3885,10 @@
         <v>36031</v>
       </c>
       <c r="L22" s="10">
-        <v>21.34</v>
+        <v>20.53</v>
       </c>
       <c r="M22" s="10">
-        <v>14.77</v>
+        <v>13.7</v>
       </c>
       <c r="N22" s="10">
         <v>0</v>
@@ -3906,10 +3908,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="10">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E23" s="10">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F23" s="10">
         <v>0</v>
@@ -3930,16 +3932,16 @@
         <v>21100</v>
       </c>
       <c r="L23" s="10">
-        <v>14.94</v>
+        <v>15.25</v>
       </c>
       <c r="M23" s="10">
-        <v>11.27</v>
+        <v>10.46</v>
       </c>
       <c r="N23" s="10">
         <v>0</v>
       </c>
       <c r="P23" s="10">
-        <v>10.199999999999999</v>
+        <v>9.6199999999999992</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
@@ -3977,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="10">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="M24" s="10">
         <v>0</v>
@@ -4012,7 +4014,7 @@
         <v>6</v>
       </c>
       <c r="G25" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="10">
         <v>2</v>
@@ -4027,10 +4029,10 @@
         <v>15374</v>
       </c>
       <c r="L25" s="10">
-        <v>3.66</v>
+        <v>3.52</v>
       </c>
       <c r="M25" s="10">
-        <v>6.3</v>
+        <v>5.85</v>
       </c>
       <c r="N25" s="10">
         <v>50</v>
@@ -4077,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="10">
-        <v>0.3</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M26" s="10">
         <v>0</v>
@@ -4124,10 +4126,10 @@
         <v>7816</v>
       </c>
       <c r="L27" s="10">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="M27" s="10">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="N27" s="10">
         <v>30</v>
@@ -4150,10 +4152,10 @@
         <v>18</v>
       </c>
       <c r="D28" s="10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E28" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F28" s="10">
         <v>3</v>
@@ -4174,19 +4176,19 @@
         <v>17865</v>
       </c>
       <c r="L28" s="10">
-        <v>2.13</v>
+        <v>2.93</v>
       </c>
       <c r="M28" s="10">
-        <v>7.32</v>
+        <v>6.8</v>
       </c>
       <c r="N28" s="10">
-        <v>42.86</v>
+        <v>30</v>
       </c>
       <c r="O28" s="10">
         <v>66.67</v>
       </c>
       <c r="P28" s="10">
-        <v>28.57</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
@@ -4224,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="10">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="M29" s="10">
         <v>0</v>
@@ -4250,43 +4252,43 @@
         <v>18</v>
       </c>
       <c r="D30" s="10">
+        <v>19</v>
+      </c>
+      <c r="E30" s="10">
         <v>18</v>
       </c>
-      <c r="E30" s="10">
-        <v>17</v>
-      </c>
       <c r="F30" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" s="10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H30" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="10">
-        <v>8117.12</v>
+        <v>15511.12</v>
       </c>
       <c r="J30" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="10">
-        <v>8117.12</v>
+        <v>15511.12</v>
       </c>
       <c r="L30" s="10">
-        <v>5.49</v>
+        <v>5.57</v>
       </c>
       <c r="M30" s="10">
-        <v>3.33</v>
+        <v>5.9</v>
       </c>
       <c r="N30" s="10">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="O30" s="10">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="P30" s="10">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
@@ -4324,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="L31" s="10">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="M31" s="10">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="N31" s="10">
         <v>11.11</v>
@@ -4374,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="10">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="M32" s="10">
         <v>0</v>
@@ -4424,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="L33" s="10">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="M33" s="10">
         <v>0</v>
@@ -4447,13 +4449,13 @@
         <v>18</v>
       </c>
       <c r="D34" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="10">
         <v>1</v>
       </c>
       <c r="F34" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="10">
         <v>0</v>
@@ -4471,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="L34" s="10">
-        <v>0.3</v>
+        <v>0.59</v>
       </c>
       <c r="M34" s="10">
         <v>0</v>
@@ -4521,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="10">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="M35" s="10">
         <v>0</v>
@@ -4547,11 +4549,11 @@
         <v>18</v>
       </c>
       <c r="D36" s="10">
+        <v>4</v>
+      </c>
+      <c r="E36" s="10">
         <v>3</v>
       </c>
-      <c r="E36" s="10">
-        <v>2</v>
-      </c>
       <c r="F36" s="10">
         <v>2</v>
       </c>
@@ -4571,13 +4573,13 @@
         <v>0</v>
       </c>
       <c r="L36" s="10">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="M36" s="10">
         <v>0</v>
       </c>
       <c r="N36" s="10">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="O36" s="10">
         <v>0</v>
@@ -5156,7 +5158,7 @@
         <v>164</v>
       </c>
       <c r="G19" s="5">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H19" s="5">
         <v>23</v>
@@ -5191,19 +5193,19 @@
         <v>167</v>
       </c>
       <c r="G20" s="10">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H20" s="10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I20" s="10">
         <v>9</v>
       </c>
       <c r="J20" s="10">
-        <v>65724</v>
+        <v>66099</v>
       </c>
       <c r="K20" s="10">
-        <v>7.82</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -5217,28 +5219,28 @@
         <v>18</v>
       </c>
       <c r="D21" s="10">
-        <v>2750</v>
+        <v>2963</v>
       </c>
       <c r="E21" s="10">
-        <v>6778.23</v>
+        <v>7216.49</v>
       </c>
       <c r="F21" s="10">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G21" s="10">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H21" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I21" s="10">
         <v>12</v>
       </c>
       <c r="J21" s="10">
-        <v>67771</v>
+        <v>75642</v>
       </c>
       <c r="K21" s="10">
-        <v>9</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -5812,10 +5814,10 @@
         <v>18</v>
       </c>
       <c r="D38" s="10">
-        <v>269</v>
+        <v>312</v>
       </c>
       <c r="E38" s="10">
-        <v>2358.38</v>
+        <v>2740.91</v>
       </c>
       <c r="F38" s="10">
         <v>9</v>
@@ -5833,7 +5835,7 @@
         <v>5292</v>
       </c>
       <c r="K38" s="10">
-        <v>1.24</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -6241,7 +6243,7 @@
         <v>35</v>
       </c>
       <c r="G50" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H50" s="10">
         <v>12</v>
@@ -6407,16 +6409,16 @@
         <v>18</v>
       </c>
       <c r="D55" s="10">
-        <v>992</v>
+        <v>1099</v>
       </c>
       <c r="E55" s="10">
-        <v>7705.92</v>
+        <v>8741.84</v>
       </c>
       <c r="F55" s="10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G55" s="10">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H55" s="10">
         <v>6</v>
@@ -6428,7 +6430,7 @@
         <v>22723.8</v>
       </c>
       <c r="K55" s="10">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
@@ -6581,7 +6583,7 @@
         <v>8</v>
       </c>
       <c r="G60" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H60" s="10">
         <v>4</v>
@@ -7402,13 +7404,13 @@
         <v>18</v>
       </c>
       <c r="D84" s="10">
-        <v>558</v>
+        <v>627</v>
       </c>
       <c r="E84" s="10">
-        <v>4100.59</v>
+        <v>4664.99</v>
       </c>
       <c r="F84" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G84" s="10">
         <v>6</v>
@@ -7881,10 +7883,10 @@
         <v>17</v>
       </c>
       <c r="G98" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H98" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I98" s="10">
         <v>6</v>
@@ -8292,28 +8294,28 @@
         <v>18</v>
       </c>
       <c r="D110" s="10">
-        <v>842</v>
+        <v>918</v>
       </c>
       <c r="E110" s="10">
-        <v>8454.8700000000008</v>
+        <v>9171.67</v>
       </c>
       <c r="F110" s="10">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G110" s="10">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H110" s="10">
         <v>7</v>
       </c>
       <c r="I110" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J110" s="10">
-        <v>20867.12</v>
+        <v>24146.12</v>
       </c>
       <c r="K110" s="10">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -9011,7 +9013,7 @@
         <v>6</v>
       </c>
       <c r="G132" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H132" s="10">
         <v>2</v>
@@ -9807,10 +9809,10 @@
         <v>18</v>
       </c>
       <c r="D155" s="10">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="E155" s="10">
-        <v>1591.23</v>
+        <v>1694.86</v>
       </c>
       <c r="F155" s="10">
         <v>3</v>
@@ -10893,16 +10895,16 @@
         <v>18</v>
       </c>
       <c r="D186" s="10">
-        <v>485</v>
+        <v>541</v>
       </c>
       <c r="E186" s="10">
-        <v>3386.92</v>
+        <v>3740.45</v>
       </c>
       <c r="F186" s="10">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G186" s="10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H186" s="10">
         <v>3</v>
@@ -10914,7 +10916,7 @@
         <v>3152.16</v>
       </c>
       <c r="K186" s="10">
-        <v>-7.0000000000000007E-2</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="187" spans="1:15" x14ac:dyDescent="0.3">
@@ -12468,10 +12470,10 @@
         <v>18</v>
       </c>
       <c r="D231" s="10">
-        <v>572</v>
+        <v>640</v>
       </c>
       <c r="E231" s="10">
-        <v>4569.25</v>
+        <v>5555.7</v>
       </c>
       <c r="F231" s="10">
         <v>30</v>
@@ -12480,16 +12482,16 @@
         <v>20</v>
       </c>
       <c r="H231" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I231" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J231" s="10">
-        <v>0</v>
+        <v>7394</v>
       </c>
       <c r="K231" s="10">
-        <v>-1</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.3">
@@ -15958,10 +15960,10 @@
         <v>107</v>
       </c>
       <c r="E10" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" s="18">
         <v>5</v>
@@ -16163,13 +16165,13 @@
         <v>2</v>
       </c>
       <c r="J15" s="18">
-        <v>15101</v>
+        <v>15476</v>
       </c>
       <c r="K15" s="18">
         <v>2</v>
       </c>
       <c r="L15" s="18">
-        <v>15101</v>
+        <v>15476</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -16262,10 +16264,10 @@
         <v>29</v>
       </c>
       <c r="E18" s="18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" s="18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" s="18">
         <v>5</v>
@@ -16429,7 +16431,7 @@
         <v>2</v>
       </c>
       <c r="J22" s="18">
-        <v>6743</v>
+        <v>14614</v>
       </c>
       <c r="K22" s="18">
         <v>0</v>
@@ -16484,28 +16486,28 @@
         <v>2026</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>3279</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -16516,7 +16518,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B25" s="18">
         <v>2026</v>
@@ -16525,7 +16527,7 @@
         <v>111</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -16554,7 +16556,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B26" s="18">
         <v>2026</v>
@@ -16569,19 +16571,19 @@
         <v>1</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <v>160.31</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -16598,7 +16600,7 @@
         <v>2026</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -16610,16 +16612,16 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>160.31</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -16630,13 +16632,13 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B28" s="18">
         <v>2026</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
@@ -16645,7 +16647,7 @@
         <v>1</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -16674,10 +16676,10 @@
         <v>2026</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -16686,7 +16688,7 @@
         <v>1</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -16706,28 +16708,28 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B30" s="18">
         <v>2026</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -16753,7 +16755,7 @@
         <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E31">
         <v>3</v>
@@ -16762,7 +16764,7 @@
         <v>3</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -16791,7 +16793,7 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -16803,7 +16805,7 @@
         <v>1</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -16826,22 +16828,22 @@
         <v>2026</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -16864,10 +16866,10 @@
         <v>2026</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -16876,10 +16878,10 @@
         <v>1</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -16896,66 +16898,66 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B35" s="18">
         <v>2026</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35">
-        <v>5234</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35">
-        <v>5234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B36" s="18">
         <v>2026</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -16981,31 +16983,31 @@
         <v>111</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>5234</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>5234</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
@@ -17019,7 +17021,7 @@
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E38">
         <v>3</v>
@@ -17034,16 +17036,16 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>7855.68</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38">
-        <v>7855.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
@@ -17057,25 +17059,25 @@
         <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>5234</v>
+        <v>0</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -17095,36 +17097,36 @@
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40">
         <v>1</v>
       </c>
       <c r="J40">
-        <v>3152.16</v>
+        <v>7855.68</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>3152.16</v>
+        <v>7855.68</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B41" s="18">
         <v>2026</v>
@@ -17133,36 +17135,36 @@
         <v>111</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E41">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J41">
-        <v>36031</v>
+        <v>5234</v>
       </c>
       <c r="K41">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L41">
-        <v>36031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B42" s="18">
         <v>2026</v>
@@ -17171,31 +17173,31 @@
         <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E42">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="F42">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J42">
-        <v>27490</v>
+        <v>3152.16</v>
       </c>
       <c r="K42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L42">
-        <v>21100</v>
+        <v>3152.16</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
@@ -17209,31 +17211,31 @@
         <v>111</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="F43">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>36031</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>36031</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
@@ -17247,31 +17249,31 @@
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="F44">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J44">
-        <v>0</v>
+        <v>27490</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>21100</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
@@ -17285,7 +17287,7 @@
         <v>111</v>
       </c>
       <c r="D45" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E45">
         <v>1</v>
@@ -17323,7 +17325,7 @@
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="E46">
         <v>1</v>
@@ -17361,19 +17363,19 @@
         <v>111</v>
       </c>
       <c r="D47" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -17399,13 +17401,13 @@
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -17437,19 +17439,19 @@
         <v>111</v>
       </c>
       <c r="D49" t="s">
-        <v>29</v>
+        <v>106</v>
       </c>
       <c r="E49">
         <v>3</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -17475,19 +17477,19 @@
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>39</v>
+        <v>106</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -17504,7 +17506,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B51" s="18">
         <v>2026</v>
@@ -17513,19 +17515,19 @@
         <v>111</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E51">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F51">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -17542,7 +17544,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="18">
         <v>2026</v>
@@ -17551,31 +17553,31 @@
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E52">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>15374</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52">
-        <v>15374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
@@ -17586,22 +17588,22 @@
         <v>2026</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D53" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F53">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -17618,7 +17620,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B54" s="18">
         <v>2026</v>
@@ -17627,57 +17629,57 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>15374</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>15374</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B55" s="18">
         <v>2026</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -17694,7 +17696,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="B56" s="18">
         <v>2026</v>
@@ -17703,31 +17705,31 @@
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E56">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H56">
         <v>0</v>
       </c>
       <c r="I56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>17865</v>
+        <v>0</v>
       </c>
       <c r="K56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56">
-        <v>17865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -17741,19 +17743,19 @@
         <v>111</v>
       </c>
       <c r="D57" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -17776,34 +17778,34 @@
         <v>2026</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>17865</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>17865</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
@@ -17817,16 +17819,16 @@
         <v>111</v>
       </c>
       <c r="D59" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -17855,7 +17857,7 @@
         <v>111</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -17864,10 +17866,10 @@
         <v>1</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -17890,16 +17892,16 @@
         <v>2026</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D61" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -17928,10 +17930,10 @@
         <v>2026</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -17940,48 +17942,48 @@
         <v>1</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
       <c r="I62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62">
-        <v>7816</v>
+        <v>0</v>
       </c>
       <c r="K62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62">
-        <v>7816</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B63" s="18">
         <v>2026</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -17998,45 +18000,45 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B64" s="18">
         <v>2026</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D64" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B65" s="18">
         <v>2026</v>
@@ -18045,36 +18047,36 @@
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65">
-        <v>7818.1200000000008</v>
+        <v>0</v>
       </c>
       <c r="K65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65">
-        <v>7818.1200000000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B66" s="18">
         <v>2026</v>
@@ -18083,7 +18085,7 @@
         <v>111</v>
       </c>
       <c r="D66" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E66">
         <v>1</v>
@@ -18098,16 +18100,16 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>7816</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>7816</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
@@ -18118,22 +18120,22 @@
         <v>2026</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D67" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="E67">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F67">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G67">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -18150,104 +18152,104 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B68" s="18">
         <v>2026</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D68" t="s">
         <v>13</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I68">
         <v>1</v>
       </c>
       <c r="J68">
-        <v>7072</v>
+        <v>299</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B69" s="18">
         <v>2026</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>29</v>
       </c>
       <c r="E69">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F69">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>7818.1200000000008</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B70" s="18">
         <v>2026</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D70" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -18264,72 +18266,72 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B71" s="18">
         <v>2026</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D71" t="s">
+        <v>39</v>
+      </c>
+      <c r="E71">
         <v>13</v>
       </c>
-      <c r="E71">
-        <v>1</v>
-      </c>
       <c r="F71">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>7394</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>7394</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B72" s="18">
         <v>2026</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
       </c>
       <c r="E72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72">
         <v>0</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>7072</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -18340,7 +18342,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B73" s="18">
         <v>2026</v>
@@ -18349,19 +18351,19 @@
         <v>111</v>
       </c>
       <c r="D73" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -18378,25 +18380,25 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B74" s="18">
         <v>2026</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -18416,28 +18418,28 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B75" s="18">
         <v>2026</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>18</v>
+        <v>111</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -18454,57 +18456,193 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B76" s="18">
         <v>2026</v>
       </c>
       <c r="C76" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
+      </c>
+      <c r="F76">
+        <v>1</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>102</v>
+      </c>
+      <c r="B77" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C77" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D77" t="s">
+        <v>40</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>1</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>103</v>
+      </c>
+      <c r="B78" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="F78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78">
+        <v>1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>103</v>
+      </c>
+      <c r="B79" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79">
+        <v>4</v>
+      </c>
+      <c r="F79">
+        <v>3</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>103</v>
+      </c>
+      <c r="B80" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D80" t="s">
         <v>39</v>
       </c>
-      <c r="E76">
-        <v>1</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76">
-        <v>0</v>
-      </c>
-      <c r="H76">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <v>0</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B77" s="18"/>
-      <c r="C77" s="19"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B78" s="18"/>
-      <c r="C78" s="19"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B79" s="18"/>
-      <c r="C79" s="19"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B80" s="18"/>
-      <c r="C80" s="19"/>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80">
+        <v>1</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B81" s="18"/>

--- a/dashboard_data.xlsx
+++ b/dashboard_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PanpanZhu\Documents\Claude dashboard\google\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C923CD-7311-48DF-8D48-EE614F08EC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F162C6-027D-4B77-90A4-2FE598553041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28692" yWindow="-108" windowWidth="19416" windowHeight="11496" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7401,9 +7401,15 @@
       <c r="C20" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
+      <c r="D20" s="10">
+        <v>3159</v>
+      </c>
+      <c r="E20" s="10">
+        <v>7449.1</v>
+      </c>
+      <c r="F20" s="10">
+        <v>167</v>
+      </c>
       <c r="G20" s="10">
         <v>98</v>
       </c>
@@ -7416,7 +7422,9 @@
       <c r="J20" s="10">
         <v>66099</v>
       </c>
-      <c r="K20" s="10"/>
+      <c r="K20" s="10">
+        <v>7.87</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
@@ -8023,9 +8031,15 @@
       <c r="C38" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
+      <c r="D38" s="10">
+        <v>457</v>
+      </c>
+      <c r="E38" s="10">
+        <v>2190.62</v>
+      </c>
+      <c r="F38" s="10">
+        <v>13</v>
+      </c>
       <c r="G38" s="10">
         <v>8</v>
       </c>
@@ -8038,7 +8052,9 @@
       <c r="J38" s="10">
         <v>0</v>
       </c>
-      <c r="K38" s="10"/>
+      <c r="K38" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
@@ -8645,9 +8661,15 @@
       <c r="C56" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
+      <c r="D56" s="10">
+        <v>1750</v>
+      </c>
+      <c r="E56" s="10">
+        <v>8784.25</v>
+      </c>
+      <c r="F56" s="10">
+        <v>58</v>
+      </c>
       <c r="G56" s="10">
         <v>27</v>
       </c>
@@ -8660,7 +8682,9 @@
       <c r="J56" s="10">
         <v>45253.33</v>
       </c>
-      <c r="K56" s="10"/>
+      <c r="K56" s="10">
+        <v>4.1500000000000004</v>
+      </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
@@ -8882,7 +8906,7 @@
         <v>8</v>
       </c>
       <c r="G63" s="10">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H63" s="10">
         <v>4</v>
@@ -9692,9 +9716,15 @@
       <c r="C87" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
+      <c r="D87" s="10">
+        <v>731</v>
+      </c>
+      <c r="E87" s="10">
+        <v>4773.3500000000004</v>
+      </c>
+      <c r="F87" s="10">
+        <v>13</v>
+      </c>
       <c r="G87" s="10">
         <v>11</v>
       </c>
@@ -9707,7 +9737,9 @@
       <c r="J87" s="10">
         <v>0</v>
       </c>
-      <c r="K87" s="10"/>
+      <c r="K87" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
@@ -10249,10 +10281,10 @@
         <v>17</v>
       </c>
       <c r="G104" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H104" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I104" s="10">
         <v>6</v>
@@ -10624,9 +10656,15 @@
       <c r="C115" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D115" s="10"/>
-      <c r="E115" s="10"/>
-      <c r="F115" s="10"/>
+      <c r="D115" s="10">
+        <v>914</v>
+      </c>
+      <c r="E115" s="10">
+        <v>9347.0499999999993</v>
+      </c>
+      <c r="F115" s="10">
+        <v>35</v>
+      </c>
       <c r="G115" s="10">
         <v>13</v>
       </c>
@@ -10639,7 +10677,9 @@
       <c r="J115" s="10">
         <v>0</v>
       </c>
-      <c r="K115" s="10"/>
+      <c r="K115" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="10" t="s">
@@ -11446,7 +11486,7 @@
         <v>6</v>
       </c>
       <c r="G141" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H141" s="10">
         <v>2</v>
@@ -12231,9 +12271,15 @@
       <c r="C164" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D164" s="10"/>
-      <c r="E164" s="10"/>
-      <c r="F164" s="10"/>
+      <c r="D164" s="10">
+        <v>320</v>
+      </c>
+      <c r="E164" s="10">
+        <v>1653.17</v>
+      </c>
+      <c r="F164" s="10">
+        <v>5</v>
+      </c>
       <c r="G164" s="10">
         <v>3</v>
       </c>
@@ -12246,7 +12292,9 @@
       <c r="J164" s="10">
         <v>0</v>
       </c>
-      <c r="K164" s="10"/>
+      <c r="K164" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="10" t="s">
@@ -13359,9 +13407,15 @@
       <c r="C197" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D197" s="10"/>
-      <c r="E197" s="10"/>
-      <c r="F197" s="10"/>
+      <c r="D197" s="10">
+        <v>931</v>
+      </c>
+      <c r="E197" s="10">
+        <v>3744.73</v>
+      </c>
+      <c r="F197" s="10">
+        <v>13</v>
+      </c>
       <c r="G197" s="10">
         <v>5</v>
       </c>
@@ -13374,7 +13428,9 @@
       <c r="J197" s="10">
         <v>0</v>
       </c>
-      <c r="K197" s="10"/>
+      <c r="K197" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="10" t="s">
@@ -15011,9 +15067,15 @@
       <c r="C245" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D245" s="10"/>
-      <c r="E245" s="10"/>
-      <c r="F245" s="10"/>
+      <c r="D245" s="10">
+        <v>744</v>
+      </c>
+      <c r="E245" s="10">
+        <v>5338.34</v>
+      </c>
+      <c r="F245" s="10">
+        <v>5</v>
+      </c>
       <c r="G245" s="10">
         <v>4</v>
       </c>
@@ -15026,7 +15088,9 @@
       <c r="J245" s="10">
         <v>0</v>
       </c>
-      <c r="K245" s="10"/>
+      <c r="K245" s="10">
+        <v>-1</v>
+      </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" s="10" t="s">
@@ -15623,9 +15687,15 @@
       <c r="C263" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D263" s="10"/>
-      <c r="E263" s="10"/>
-      <c r="F263" s="10"/>
+      <c r="D263" s="10">
+        <v>703</v>
+      </c>
+      <c r="E263" s="10">
+        <v>3598.49</v>
+      </c>
+      <c r="F263" s="10">
+        <v>14</v>
+      </c>
       <c r="G263" s="10">
         <v>4</v>
       </c>
@@ -15638,7 +15708,9 @@
       <c r="J263" s="10">
         <v>7816</v>
       </c>
-      <c r="K263" s="10"/>
+      <c r="K263" s="10">
+        <v>1.17</v>
+      </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" s="10" t="s">
